--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09F2664-C256-0044-A7F1-7A6BFBD41EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D898AE88-426D-9640-A522-388FD017DA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5780" yWindow="2640" windowWidth="43820" windowHeight="24440" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -9061,7 +9061,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMI112"/>
+  <dimension ref="A1:AMH112"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -9076,10 +9076,9 @@
     <col min="14" max="14" width="15.6640625" style="1" customWidth="1"/>
     <col min="15" max="15" width="19.1640625" style="1" customWidth="1"/>
     <col min="16" max="16" width="22" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1023" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1022" s="3" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -9128,15 +9127,15 @@
       <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
+      <c r="AMB1" s="5"/>
       <c r="AMC1" s="5"/>
       <c r="AMD1" s="5"/>
       <c r="AME1" s="5"/>
-      <c r="AMF1" s="5"/>
+      <c r="AMF1"/>
       <c r="AMG1"/>
       <c r="AMH1"/>
-      <c r="AMI1"/>
-    </row>
-    <row r="2" spans="1:1023" x14ac:dyDescent="0.15">
+    </row>
+    <row r="2" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>16</v>
       </c>
@@ -9186,7 +9185,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>22</v>
       </c>
@@ -9236,7 +9235,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A4" s="6" t="s">
         <v>26</v>
       </c>
@@ -9286,7 +9285,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
@@ -9336,7 +9335,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -9386,7 +9385,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>37</v>
       </c>
@@ -9436,7 +9435,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -9486,7 +9485,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>43</v>
       </c>
@@ -9536,7 +9535,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A10" s="6" t="s">
         <v>45</v>
       </c>
@@ -9586,7 +9585,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A11" s="6" t="s">
         <v>48</v>
       </c>
@@ -9636,7 +9635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
         <v>50</v>
       </c>
@@ -9686,7 +9685,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -9736,7 +9735,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -9786,7 +9785,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>58</v>
       </c>
@@ -9836,7 +9835,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="16" spans="1:1023" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>60</v>
       </c>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CDE8CBB-CA71-0C45-BA5D-E6BF2C10E43E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E01F07-4EAB-DE44-9565-92AEB2B0E996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10135" uniqueCount="2875">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10250" uniqueCount="2923">
   <si>
     <t>tag</t>
   </si>
@@ -8667,6 +8667,150 @@
   </si>
   <si>
     <t>Epoxomicin is a naturally occurring selective proteasome inhibitor.</t>
+  </si>
+  <si>
+    <t>ProtFa</t>
+  </si>
+  <si>
+    <t>CECAD Proteomics Facility</t>
+  </si>
+  <si>
+    <t>CECAD Proteomics facility</t>
+  </si>
+  <si>
+    <t>frezza</t>
+  </si>
+  <si>
+    <t>Department Frezza</t>
+  </si>
+  <si>
+    <t>Metabolomics in Aging</t>
+  </si>
+  <si>
+    <t>krueger</t>
+  </si>
+  <si>
+    <t>Department Krueger</t>
+  </si>
+  <si>
+    <t>Institute for Genetics</t>
+  </si>
+  <si>
+    <t>rugarli</t>
+  </si>
+  <si>
+    <t>Department Rugali</t>
+  </si>
+  <si>
+    <t>trifunovic</t>
+  </si>
+  <si>
+    <t>Department Trifunovic</t>
+  </si>
+  <si>
+    <t>Institute for Mitochondrial Diseases and Aging</t>
+  </si>
+  <si>
+    <t>niessen</t>
+  </si>
+  <si>
+    <t>Department Niessen</t>
+  </si>
+  <si>
+    <t>gloeckner</t>
+  </si>
+  <si>
+    <t>Department Gloeckner</t>
+  </si>
+  <si>
+    <t>Center for Biochemistry</t>
+  </si>
+  <si>
+    <t>bazzi</t>
+  </si>
+  <si>
+    <t>Department Bazzi</t>
+  </si>
+  <si>
+    <t>Polyclinic of Dermatology and Venereology</t>
+  </si>
+  <si>
+    <t>hallek</t>
+  </si>
+  <si>
+    <t>Department Hallek</t>
+  </si>
+  <si>
+    <t>Clinic of Internal Medicine I</t>
+  </si>
+  <si>
+    <t>benzing</t>
+  </si>
+  <si>
+    <t>Department Benzing</t>
+  </si>
+  <si>
+    <t>Clinic of Internal Medicine II, UKK</t>
+  </si>
+  <si>
+    <t>hennies</t>
+  </si>
+  <si>
+    <t>Department Hennies</t>
+  </si>
+  <si>
+    <t>Cologne Center for Genomics, UoC</t>
+  </si>
+  <si>
+    <t>vonkarstedt</t>
+  </si>
+  <si>
+    <t>Department vonKarstedt</t>
+  </si>
+  <si>
+    <t>Dept. of Translational Genomics</t>
+  </si>
+  <si>
+    <t>laessig</t>
+  </si>
+  <si>
+    <t>Department Laessig</t>
+  </si>
+  <si>
+    <t>Institute for Biological Physics,UoC</t>
+  </si>
+  <si>
+    <t>hoppe</t>
+  </si>
+  <si>
+    <t>Department Hoppe</t>
+  </si>
+  <si>
+    <t>Institute for Genetics, UoC</t>
+  </si>
+  <si>
+    <t>garcia</t>
+  </si>
+  <si>
+    <t>Department Garcia</t>
+  </si>
+  <si>
+    <t>khaskar</t>
+  </si>
+  <si>
+    <t>Department Kashkar</t>
+  </si>
+  <si>
+    <t>Institute for Medical Microbiology  Immunology and Hygiene, UKK</t>
+  </si>
+  <si>
+    <t>krieg</t>
+  </si>
+  <si>
+    <t>Department Krieg</t>
+  </si>
+  <si>
+    <t>Translational Matrix Biology, UKK</t>
   </si>
 </sst>
 </file>
@@ -8830,7 +8974,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <font>
         <color rgb="FFCC0000"/>
@@ -8855,13 +8999,6 @@
       <font>
         <color rgb="FFCC0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC5E0B4"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -14981,18 +15118,13 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:F112 K1:P112 I2:J112">
-    <cfRule type="containsText" dxfId="7" priority="4" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J113:P113">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TRUE">
+  <conditionalFormatting sqref="J113:P114">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J113)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J114:P114">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",J114)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15002,7 +15134,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ889"/>
+  <dimension ref="A1:AMJ912"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -33506,7 +33638,7 @@
         <v>248</v>
       </c>
       <c r="C881" s="8" t="str">
-        <f t="shared" ref="C881:C889" si="19">B881&amp;":"&amp;A881</f>
+        <f t="shared" ref="C881:C912" si="19">B881&amp;":"&amp;A881</f>
         <v>att_user_institute:mpiage</v>
       </c>
       <c r="D881" s="9" t="s">
@@ -33584,103 +33716,586 @@
     </row>
     <row r="885" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A885" s="8" t="s">
-        <v>2824</v>
-      </c>
-      <c r="B885" s="22" t="s">
-        <v>2820</v>
+        <v>2493</v>
+      </c>
+      <c r="B885" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="C885" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>att_diet:wd</v>
+        <v>att_user_institute:biochem</v>
       </c>
       <c r="D885" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E885" s="8" t="s">
-        <v>2823</v>
+        <v>2494</v>
       </c>
       <c r="F885" s="8" t="s">
-        <v>2822</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A886" s="8" t="s">
-        <v>2825</v>
-      </c>
-      <c r="B886" s="22" t="s">
-        <v>2820</v>
+        <v>2496</v>
+      </c>
+      <c r="B886" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="C886" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>att_diet:sd</v>
+        <v>att_user_institute:cecad</v>
       </c>
       <c r="D886" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E886" s="8" t="s">
-        <v>2826</v>
+        <v>2497</v>
+      </c>
+      <c r="F886" s="8" t="s">
+        <v>2498</v>
       </c>
     </row>
     <row r="887" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A887" s="8" t="s">
-        <v>2827</v>
-      </c>
-      <c r="B887" s="22" t="s">
-        <v>2820</v>
+        <v>2499</v>
+      </c>
+      <c r="B887" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="C887" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>att_diet:veg</v>
+        <v>att_user_institute:mpiage</v>
       </c>
       <c r="D887" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E887" s="8" t="s">
-        <v>2828</v>
+        <v>2500</v>
       </c>
       <c r="F887" s="8" t="s">
-        <v>2829</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A888" s="8" t="s">
-        <v>2832</v>
-      </c>
-      <c r="B888" s="22" t="s">
-        <v>2820</v>
+        <v>2502</v>
+      </c>
+      <c r="B888" s="8" t="s">
+        <v>248</v>
       </c>
       <c r="C888" s="8" t="str">
         <f t="shared" si="19"/>
-        <v>att_diet:hg</v>
+        <v>att_user_institute:mpimetab</v>
       </c>
       <c r="D888" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E888" s="8" t="s">
-        <v>2830</v>
+        <v>2503</v>
       </c>
       <c r="F888" s="8" t="s">
-        <v>2831</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="889" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A889" s="8" t="s">
-        <v>2835</v>
+        <v>2505</v>
       </c>
       <c r="B889" s="8" t="s">
-        <v>2820</v>
+        <v>252</v>
       </c>
       <c r="C889" s="8" t="str">
         <f t="shared" si="19"/>
+        <v>att_user_research_group:mitoprotea</v>
+      </c>
+      <c r="D889" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E889" s="8" t="s">
+        <v>2506</v>
+      </c>
+      <c r="F889" s="8" t="s">
+        <v>2507</v>
+      </c>
+    </row>
+    <row r="890" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A890" s="8" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B890" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C890" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:molageing</v>
+      </c>
+      <c r="D890" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E890" s="8" t="s">
+        <v>2509</v>
+      </c>
+      <c r="F890" s="8" t="s">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="891" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A891" s="8" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B891" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C891" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:ProtFa</v>
+      </c>
+      <c r="D891" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E891" s="8" t="s">
+        <v>2876</v>
+      </c>
+      <c r="F891" s="8" t="s">
+        <v>2877</v>
+      </c>
+    </row>
+    <row r="892" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A892" s="8" t="s">
+        <v>2878</v>
+      </c>
+      <c r="B892" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C892" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:frezza</v>
+      </c>
+      <c r="D892" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E892" s="8" t="s">
+        <v>2879</v>
+      </c>
+      <c r="F892" s="8" t="s">
+        <v>2880</v>
+      </c>
+    </row>
+    <row r="893" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A893" s="8" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B893" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C893" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:krueger</v>
+      </c>
+      <c r="D893" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E893" s="8" t="s">
+        <v>2882</v>
+      </c>
+      <c r="F893" s="8" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="894" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A894" s="8" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B894" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C894" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:rugarli</v>
+      </c>
+      <c r="D894" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E894" s="8" t="s">
+        <v>2885</v>
+      </c>
+      <c r="F894" s="8" t="s">
+        <v>2883</v>
+      </c>
+    </row>
+    <row r="895" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A895" s="8" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B895" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C895" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:trifunovic</v>
+      </c>
+      <c r="D895" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E895" s="8" t="s">
+        <v>2887</v>
+      </c>
+      <c r="F895" s="8" t="s">
+        <v>2888</v>
+      </c>
+    </row>
+    <row r="896" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A896" s="8" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B896" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C896" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:niessen</v>
+      </c>
+      <c r="D896" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E896" s="8" t="s">
+        <v>2890</v>
+      </c>
+      <c r="F896" s="8" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A897" s="8" t="s">
+        <v>2891</v>
+      </c>
+      <c r="B897" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C897" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:gloeckner</v>
+      </c>
+      <c r="D897" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E897" s="8" t="s">
+        <v>2892</v>
+      </c>
+      <c r="F897" s="8" t="s">
+        <v>2893</v>
+      </c>
+    </row>
+    <row r="898" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A898" s="8" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B898" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C898" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:bazzi</v>
+      </c>
+      <c r="D898" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E898" s="8" t="s">
+        <v>2895</v>
+      </c>
+      <c r="F898" s="8" t="s">
+        <v>2896</v>
+      </c>
+    </row>
+    <row r="899" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A899" s="8" t="s">
+        <v>2897</v>
+      </c>
+      <c r="B899" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C899" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:hallek</v>
+      </c>
+      <c r="D899" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E899" s="8" t="s">
+        <v>2898</v>
+      </c>
+      <c r="F899" s="8" t="s">
+        <v>2899</v>
+      </c>
+    </row>
+    <row r="900" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A900" s="8" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B900" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C900" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:benzing</v>
+      </c>
+      <c r="D900" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E900" s="8" t="s">
+        <v>2901</v>
+      </c>
+      <c r="F900" s="8" t="s">
+        <v>2902</v>
+      </c>
+    </row>
+    <row r="901" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A901" s="8" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B901" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C901" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:hennies</v>
+      </c>
+      <c r="D901" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E901" s="8" t="s">
+        <v>2904</v>
+      </c>
+      <c r="F901" s="8" t="s">
+        <v>2905</v>
+      </c>
+    </row>
+    <row r="902" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A902" s="8" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B902" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C902" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:vonkarstedt</v>
+      </c>
+      <c r="D902" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E902" s="8" t="s">
+        <v>2907</v>
+      </c>
+      <c r="F902" s="8" t="s">
+        <v>2908</v>
+      </c>
+    </row>
+    <row r="903" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A903" s="8" t="s">
+        <v>2909</v>
+      </c>
+      <c r="B903" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C903" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:laessig</v>
+      </c>
+      <c r="D903" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E903" s="8" t="s">
+        <v>2910</v>
+      </c>
+      <c r="F903" s="8" t="s">
+        <v>2911</v>
+      </c>
+    </row>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A904" s="8" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B904" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C904" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:hoppe</v>
+      </c>
+      <c r="D904" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E904" s="8" t="s">
+        <v>2913</v>
+      </c>
+      <c r="F904" s="8" t="s">
+        <v>2914</v>
+      </c>
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A905" s="8" t="s">
+        <v>2915</v>
+      </c>
+      <c r="B905" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C905" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:garcia</v>
+      </c>
+      <c r="D905" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E905" s="8" t="s">
+        <v>2916</v>
+      </c>
+      <c r="F905" s="8" t="s">
+        <v>2914</v>
+      </c>
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A906" s="8" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B906" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C906" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:khaskar</v>
+      </c>
+      <c r="D906" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E906" s="8" t="s">
+        <v>2918</v>
+      </c>
+      <c r="F906" s="8" t="s">
+        <v>2919</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A907" s="8" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B907" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C907" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_user_research_group:krieg</v>
+      </c>
+      <c r="D907" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E907" s="8" t="s">
+        <v>2921</v>
+      </c>
+      <c r="F907" s="8" t="s">
+        <v>2922</v>
+      </c>
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A908" s="8" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B908" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C908" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_diet:wd</v>
+      </c>
+      <c r="D908" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E908" s="8" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F908" s="8" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A909" s="8" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B909" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C909" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_diet:sd</v>
+      </c>
+      <c r="D909" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E909" s="8" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="910" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A910" s="8" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B910" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C910" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_diet:veg</v>
+      </c>
+      <c r="D910" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E910" s="8" t="s">
+        <v>2828</v>
+      </c>
+      <c r="F910" s="8" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="911" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A911" s="8" t="s">
+        <v>2832</v>
+      </c>
+      <c r="B911" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C911" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_diet:hg</v>
+      </c>
+      <c r="D911" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E911" s="8" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F911" s="8" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="912" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A912" s="8" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B912" s="8" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C912" s="8" t="str">
+        <f t="shared" si="19"/>
         <v>att_diet:hfd</v>
       </c>
-      <c r="D889" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E889" s="8" t="s">
+      <c r="D912" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E912" s="8" t="s">
         <v>2833</v>
       </c>
-      <c r="F889" s="8" t="s">
+      <c r="F912" s="8" t="s">
         <v>2834</v>
       </c>
     </row>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E01F07-4EAB-DE44-9565-92AEB2B0E996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F4EC38-AFB6-C146-863D-859E20916875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2460" yWindow="540" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10250" uniqueCount="2923">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10262" uniqueCount="2926">
   <si>
     <t>tag</t>
   </si>
@@ -8811,6 +8811,15 @@
   </si>
   <si>
     <t>Translational Matrix Biology, UKK</t>
+  </si>
+  <si>
+    <t>att_protein_treatment</t>
+  </si>
+  <si>
+    <t>protein</t>
+  </si>
+  <si>
+    <t>Protein/Hormone Treatment</t>
   </si>
 </sst>
 </file>
@@ -8974,7 +8983,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
     <dxf>
       <font>
         <color rgb="FFCC0000"/>
@@ -8999,6 +9008,13 @@
       <font>
         <color rgb="FFCC0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC5E0B4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -9392,7 +9408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH114"/>
+  <dimension ref="A1:AMH115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -15116,15 +15132,70 @@
         <v>19</v>
       </c>
     </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A115" t="s">
+        <v>2923</v>
+      </c>
+      <c r="B115" t="s">
+        <v>17</v>
+      </c>
+      <c r="C115" t="s">
+        <v>2925</v>
+      </c>
+      <c r="D115">
+        <v>600</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G115" t="s">
+        <v>2924</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P115" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E1:F112 K1:P112 I2:J112">
-    <cfRule type="containsText" dxfId="6" priority="4" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J113:P114">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",J113)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M115:P115">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",J113)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",M115)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9F4EC38-AFB6-C146-863D-859E20916875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C73029A-C218-104A-A9F4-7268D847F023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2460" yWindow="540" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10262" uniqueCount="2926">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10267" uniqueCount="2930">
   <si>
     <t>tag</t>
   </si>
@@ -8603,9 +8603,6 @@
     <t>pulldown</t>
   </si>
   <si>
-    <t>Pulldown / Immunoprecipitation</t>
-  </si>
-  <si>
     <t>chemical</t>
   </si>
   <si>
@@ -8819,7 +8816,22 @@
     <t>protein</t>
   </si>
   <si>
-    <t>Protein/Hormone Treatment</t>
+    <t>Pulldown Bait</t>
+  </si>
+  <si>
+    <t>Protein and Hormone Treatment</t>
+  </si>
+  <si>
+    <t>control</t>
+  </si>
+  <si>
+    <t>Control Target Proteins</t>
+  </si>
+  <si>
+    <t>Control targets proteins such as GFP, LacZ</t>
+  </si>
+  <si>
+    <t>controls</t>
   </si>
 </sst>
 </file>
@@ -9811,7 +9823,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>21</v>
@@ -9861,7 +9873,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>21</v>
@@ -11340,7 +11352,7 @@
         <v>105</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2857</v>
+        <v>2856</v>
       </c>
       <c r="D39">
         <v>500</v>
@@ -13193,7 +13205,7 @@
         <v>184</v>
       </c>
       <c r="D76">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>19</v>
@@ -13243,7 +13255,7 @@
         <v>188</v>
       </c>
       <c r="D77">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>19</v>
@@ -13276,7 +13288,7 @@
         <v>19</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P77" s="1" t="s">
         <v>21</v>
@@ -13293,7 +13305,7 @@
         <v>189</v>
       </c>
       <c r="D78">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>19</v>
@@ -13343,7 +13355,7 @@
         <v>191</v>
       </c>
       <c r="D79">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>19</v>
@@ -13390,10 +13402,10 @@
         <v>183</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>2864</v>
+        <v>2863</v>
       </c>
       <c r="D80">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>19</v>
@@ -14740,7 +14752,7 @@
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>2862</v>
+        <v>2861</v>
       </c>
       <c r="D107">
         <v>800</v>
@@ -15090,7 +15102,7 @@
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>2853</v>
+        <v>2924</v>
       </c>
       <c r="D114">
         <v>500</v>
@@ -15134,7 +15146,7 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
@@ -15152,7 +15164,7 @@
         <v>19</v>
       </c>
       <c r="G115" t="s">
-        <v>2924</v>
+        <v>2923</v>
       </c>
       <c r="H115">
         <v>0</v>
@@ -15205,7 +15217,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ912"/>
+  <dimension ref="A1:AMJ913"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -19373,10 +19385,10 @@
         <v>17</v>
       </c>
       <c r="E198" s="8" t="s">
+        <v>2859</v>
+      </c>
+      <c r="F198" s="8" t="s">
         <v>2860</v>
-      </c>
-      <c r="F198" s="8" t="s">
-        <v>2861</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.15">
@@ -19717,7 +19729,7 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A215" s="8" t="s">
-        <v>2873</v>
+        <v>2872</v>
       </c>
       <c r="B215" s="8" t="s">
         <v>69</v>
@@ -19727,13 +19739,13 @@
         <v>att_compound:epoximicin</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>2872</v>
+        <v>2871</v>
       </c>
       <c r="E215" s="8" t="s">
-        <v>2871</v>
+        <v>2870</v>
       </c>
       <c r="F215" s="8" t="s">
-        <v>2874</v>
+        <v>2873</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.15">
@@ -19801,7 +19813,7 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A219" s="8" t="s">
-        <v>2868</v>
+        <v>2867</v>
       </c>
       <c r="B219" s="8" t="s">
         <v>69</v>
@@ -19811,13 +19823,13 @@
         <v>att_compound:h2o2</v>
       </c>
       <c r="D219" s="8" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E219" s="8" t="s">
         <v>2868</v>
       </c>
-      <c r="E219" s="8" t="s">
+      <c r="F219" s="8" t="s">
         <v>2869</v>
-      </c>
-      <c r="F219" s="8" t="s">
-        <v>2870</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.15">
@@ -23972,7 +23984,7 @@
         <v>17</v>
       </c>
       <c r="E417" s="8" t="s">
-        <v>2863</v>
+        <v>2862</v>
       </c>
       <c r="F417" s="8" t="s">
         <v>2815</v>
@@ -24539,10 +24551,10 @@
         <v>1363</v>
       </c>
       <c r="E444" s="8" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
       <c r="F444" s="8" t="s">
-        <v>2858</v>
+        <v>2857</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.15">
@@ -24560,10 +24572,10 @@
         <v>1363</v>
       </c>
       <c r="E445" s="8" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
       <c r="F445" s="8" t="s">
-        <v>2859</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.15">
@@ -24673,7 +24685,7 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A451" s="8" t="s">
-        <v>2854</v>
+        <v>2853</v>
       </c>
       <c r="B451" s="8" t="s">
         <v>91</v>
@@ -24686,15 +24698,15 @@
         <v>17</v>
       </c>
       <c r="E451" s="8" t="s">
+        <v>2854</v>
+      </c>
+      <c r="F451" s="8" t="s">
         <v>2855</v>
-      </c>
-      <c r="F451" s="8" t="s">
-        <v>2856</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A452" s="8" t="s">
-        <v>2866</v>
+        <v>2865</v>
       </c>
       <c r="B452" s="8" t="s">
         <v>91</v>
@@ -24707,10 +24719,10 @@
         <v>17</v>
       </c>
       <c r="E452" s="8" t="s">
-        <v>2867</v>
+        <v>2866</v>
       </c>
       <c r="F452" s="8" t="s">
-        <v>2865</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.15">
@@ -30916,7 +30928,7 @@
         <v>196</v>
       </c>
       <c r="C748" s="8" t="str">
-        <f t="shared" ref="C748:C816" si="16">B748&amp;":"&amp;A748</f>
+        <f t="shared" ref="C748:C817" si="16">B748&amp;":"&amp;A748</f>
         <v>att_organism:UP000001940</v>
       </c>
       <c r="D748" s="8" t="s">
@@ -30994,3379 +31006,3400 @@
     </row>
     <row r="752" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A752" s="8" t="s">
-        <v>2219</v>
+        <v>2929</v>
       </c>
       <c r="B752" s="8" t="s">
-        <v>2220</v>
+        <v>196</v>
       </c>
       <c r="C752" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:cardiovascular</v>
-      </c>
-      <c r="D752" s="9" t="s">
-        <v>17</v>
+        <v>att_organism:controls</v>
+      </c>
+      <c r="D752" s="8" t="s">
+        <v>2926</v>
       </c>
       <c r="E752" s="8" t="s">
-        <v>2221</v>
+        <v>2927</v>
       </c>
       <c r="F752" s="8" t="s">
-        <v>2222</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="753" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A753" s="8" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="B753" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C753" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:digestive</v>
+        <v>att_organsystem:cardiovascular</v>
       </c>
       <c r="D753" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E753" s="8" t="s">
-        <v>2224</v>
+        <v>2221</v>
       </c>
       <c r="F753" s="8" t="s">
-        <v>2225</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="754" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A754" s="8" t="s">
-        <v>2226</v>
+        <v>2223</v>
       </c>
       <c r="B754" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C754" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:endocrine</v>
+        <v>att_organsystem:digestive</v>
       </c>
       <c r="D754" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E754" s="8" t="s">
-        <v>2227</v>
+        <v>2224</v>
       </c>
       <c r="F754" s="8" t="s">
-        <v>2228</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="755" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A755" s="8" t="s">
-        <v>2229</v>
+        <v>2226</v>
       </c>
       <c r="B755" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C755" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:excretory</v>
+        <v>att_organsystem:endocrine</v>
       </c>
       <c r="D755" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E755" s="8" t="s">
-        <v>2230</v>
+        <v>2227</v>
       </c>
       <c r="F755" s="8" t="s">
-        <v>2231</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="756" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A756" s="8" t="s">
-        <v>2232</v>
+        <v>2229</v>
       </c>
       <c r="B756" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C756" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:integumentary</v>
+        <v>att_organsystem:excretory</v>
       </c>
       <c r="D756" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E756" s="8" t="s">
-        <v>2233</v>
+        <v>2230</v>
       </c>
       <c r="F756" s="8" t="s">
-        <v>2234</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="757" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A757" s="8" t="s">
-        <v>2235</v>
+        <v>2232</v>
       </c>
       <c r="B757" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C757" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:lymphatic</v>
+        <v>att_organsystem:integumentary</v>
       </c>
       <c r="D757" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E757" s="8" t="s">
-        <v>2236</v>
+        <v>2233</v>
       </c>
       <c r="F757" s="8" t="s">
-        <v>2237</v>
+        <v>2234</v>
       </c>
     </row>
     <row r="758" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A758" s="8" t="s">
-        <v>2238</v>
+        <v>2235</v>
       </c>
       <c r="B758" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C758" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:muscular</v>
+        <v>att_organsystem:lymphatic</v>
       </c>
       <c r="D758" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E758" s="8" t="s">
-        <v>2239</v>
+        <v>2236</v>
       </c>
       <c r="F758" s="8" t="s">
-        <v>2240</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="759" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A759" s="8" t="s">
-        <v>2241</v>
+        <v>2238</v>
       </c>
       <c r="B759" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C759" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:nervous_system</v>
+        <v>att_organsystem:muscular</v>
       </c>
       <c r="D759" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E759" s="8" t="s">
-        <v>2242</v>
+        <v>2239</v>
       </c>
       <c r="F759" s="8" t="s">
-        <v>2243</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="760" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A760" s="8" t="s">
-        <v>2244</v>
+        <v>2241</v>
       </c>
       <c r="B760" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C760" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:reproductive</v>
+        <v>att_organsystem:nervous_system</v>
       </c>
       <c r="D760" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E760" s="8" t="s">
-        <v>2245</v>
+        <v>2242</v>
       </c>
       <c r="F760" s="8" t="s">
-        <v>2246</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="761" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A761" s="8" t="s">
-        <v>2247</v>
+        <v>2244</v>
       </c>
       <c r="B761" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C761" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:respiratory</v>
+        <v>att_organsystem:reproductive</v>
       </c>
       <c r="D761" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E761" s="8" t="s">
-        <v>2248</v>
+        <v>2245</v>
       </c>
       <c r="F761" s="8" t="s">
-        <v>2249</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="762" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A762" s="8" t="s">
-        <v>2250</v>
+        <v>2247</v>
       </c>
       <c r="B762" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C762" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:skeletal</v>
+        <v>att_organsystem:respiratory</v>
       </c>
       <c r="D762" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E762" s="8" t="s">
-        <v>2251</v>
+        <v>2248</v>
       </c>
       <c r="F762" s="8" t="s">
-        <v>2252</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="763" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A763" s="8" t="s">
-        <v>2253</v>
+        <v>2250</v>
       </c>
       <c r="B763" s="8" t="s">
         <v>2220</v>
       </c>
       <c r="C763" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_organsystem:urinary</v>
+        <v>att_organsystem:skeletal</v>
       </c>
       <c r="D763" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E763" s="8" t="s">
-        <v>2254</v>
+        <v>2251</v>
       </c>
       <c r="F763" s="8" t="s">
-        <v>2255</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="764" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A764" s="8" t="s">
-        <v>2256</v>
+        <v>2253</v>
       </c>
       <c r="B764" s="8" t="s">
-        <v>198</v>
+        <v>2220</v>
       </c>
       <c r="C764" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_phystraining:intervalcardio</v>
+        <v>att_organsystem:urinary</v>
       </c>
       <c r="D764" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E764" s="8" t="s">
-        <v>2257</v>
+        <v>2254</v>
       </c>
       <c r="F764" s="8" t="s">
-        <v>2258</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="765" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A765" s="8" t="s">
-        <v>2259</v>
+        <v>2256</v>
       </c>
       <c r="B765" s="8" t="s">
         <v>198</v>
       </c>
       <c r="C765" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_phystraining:steadycardio</v>
+        <v>att_phystraining:intervalcardio</v>
       </c>
       <c r="D765" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E765" s="8" t="s">
-        <v>2836</v>
+        <v>2257</v>
       </c>
       <c r="F765" s="8" t="s">
-        <v>2260</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="766" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A766" s="8" t="s">
-        <v>2261</v>
+        <v>2259</v>
       </c>
       <c r="B766" s="8" t="s">
         <v>198</v>
       </c>
       <c r="C766" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_phystraining:strength</v>
+        <v>att_phystraining:steadycardio</v>
       </c>
       <c r="D766" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E766" s="8" t="s">
-        <v>2262</v>
+        <v>2836</v>
       </c>
       <c r="F766" s="8" t="s">
-        <v>2263</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="767" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A767" s="8" t="s">
-        <v>2837</v>
+        <v>2261</v>
       </c>
       <c r="B767" s="8" t="s">
         <v>198</v>
       </c>
       <c r="C767" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_phystraining:hiit</v>
+        <v>att_phystraining:strength</v>
       </c>
       <c r="D767" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E767" s="8" t="s">
-        <v>2838</v>
+        <v>2262</v>
       </c>
       <c r="F767" s="8" t="s">
-        <v>2839</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="768" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A768" s="8" t="s">
-        <v>2264</v>
+        <v>2837</v>
       </c>
       <c r="B768" s="8" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C768" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:argc</v>
+        <v>att_phystraining:hiit</v>
       </c>
       <c r="D768" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E768" s="8" t="s">
-        <v>2265</v>
+        <v>2838</v>
       </c>
       <c r="F768" s="8" t="s">
-        <v>2266</v>
+        <v>2839</v>
       </c>
     </row>
     <row r="769" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A769" s="8" t="s">
-        <v>2267</v>
+        <v>2264</v>
       </c>
       <c r="B769" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C769" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:aspn</v>
+        <v>att_protease:argc</v>
       </c>
       <c r="D769" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E769" s="8" t="s">
-        <v>2268</v>
+        <v>2265</v>
       </c>
       <c r="F769" s="8" t="s">
-        <v>2269</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="770" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A770" s="8" t="s">
-        <v>2270</v>
+        <v>2267</v>
       </c>
       <c r="B770" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C770" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:chymotrypsin</v>
+        <v>att_protease:aspn</v>
       </c>
       <c r="D770" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E770" s="8" t="s">
-        <v>2271</v>
+        <v>2268</v>
       </c>
       <c r="F770" s="8" t="s">
-        <v>2272</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="771" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A771" s="8" t="s">
-        <v>2273</v>
+        <v>2270</v>
       </c>
       <c r="B771" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C771" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:elastase</v>
+        <v>att_protease:chymotrypsin</v>
       </c>
       <c r="D771" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E771" s="8" t="s">
-        <v>2274</v>
+        <v>2271</v>
       </c>
       <c r="F771" s="8" t="s">
-        <v>2275</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="772" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A772" s="8" t="s">
-        <v>2276</v>
+        <v>2273</v>
       </c>
       <c r="B772" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C772" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:gluc</v>
+        <v>att_protease:elastase</v>
       </c>
       <c r="D772" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E772" s="8" t="s">
-        <v>2277</v>
+        <v>2274</v>
       </c>
       <c r="F772" s="8" t="s">
-        <v>2278</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="773" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A773" s="8" t="s">
-        <v>2279</v>
+        <v>2276</v>
       </c>
       <c r="B773" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C773" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:lysc</v>
+        <v>att_protease:gluc</v>
       </c>
       <c r="D773" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E773" s="8" t="s">
-        <v>2280</v>
+        <v>2277</v>
       </c>
       <c r="F773" s="8" t="s">
-        <v>2281</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="774" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A774" s="8" t="s">
-        <v>2282</v>
+        <v>2279</v>
       </c>
       <c r="B774" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C774" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:raspn</v>
+        <v>att_protease:lysc</v>
       </c>
       <c r="D774" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E774" s="8" t="s">
-        <v>2283</v>
+        <v>2280</v>
       </c>
       <c r="F774" s="8" t="s">
-        <v>2284</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="775" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A775" s="8" t="s">
-        <v>2285</v>
+        <v>2282</v>
       </c>
       <c r="B775" s="8" t="s">
         <v>203</v>
       </c>
       <c r="C775" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protease:trypsin</v>
+        <v>att_protease:raspn</v>
       </c>
       <c r="D775" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E775" s="8" t="s">
-        <v>2286</v>
+        <v>2283</v>
       </c>
       <c r="F775" s="8" t="s">
-        <v>2287</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="776" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A776" s="8" t="s">
-        <v>2840</v>
+        <v>2285</v>
       </c>
       <c r="B776" s="8" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C776" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:apex</v>
+        <v>att_protease:trypsin</v>
       </c>
       <c r="D776" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E776" s="8" t="s">
-        <v>2841</v>
+        <v>2286</v>
       </c>
       <c r="F776" s="8" t="s">
-        <v>2842</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="777" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A777" s="8" t="s">
-        <v>2843</v>
+        <v>2840</v>
       </c>
       <c r="B777" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C777" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:bioid</v>
+        <v>att_protein_mutation:apex</v>
       </c>
       <c r="D777" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E777" s="8" t="s">
-        <v>2844</v>
+        <v>2841</v>
       </c>
       <c r="F777" s="8" t="s">
-        <v>2845</v>
+        <v>2842</v>
       </c>
     </row>
     <row r="778" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A778" s="8" t="s">
-        <v>2846</v>
+        <v>2843</v>
       </c>
       <c r="B778" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C778" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:turboid</v>
+        <v>att_protein_mutation:bioid</v>
       </c>
       <c r="D778" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E778" s="8" t="s">
-        <v>2847</v>
+        <v>2844</v>
       </c>
       <c r="F778" s="8" t="s">
-        <v>2848</v>
+        <v>2845</v>
       </c>
     </row>
     <row r="779" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A779" s="8" t="s">
-        <v>1275</v>
+        <v>2846</v>
       </c>
       <c r="B779" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C779" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:deletion</v>
+        <v>att_protein_mutation:turboid</v>
       </c>
       <c r="D779" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E779" s="8" t="s">
-        <v>2288</v>
+        <v>2847</v>
       </c>
       <c r="F779" s="8" t="s">
-        <v>2289</v>
+        <v>2848</v>
       </c>
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A780" s="8" t="s">
-        <v>2290</v>
+        <v>1275</v>
       </c>
       <c r="B780" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C780" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:flag</v>
+        <v>att_protein_mutation:deletion</v>
       </c>
       <c r="D780" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E780" s="8" t="s">
-        <v>2291</v>
+        <v>2288</v>
       </c>
       <c r="F780" s="8" t="s">
-        <v>2292</v>
+        <v>2289</v>
       </c>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A781" s="8" t="s">
-        <v>2293</v>
+        <v>2290</v>
       </c>
       <c r="B781" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C781" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:frameshift</v>
+        <v>att_protein_mutation:flag</v>
       </c>
       <c r="D781" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E781" s="8" t="s">
-        <v>2294</v>
+        <v>2291</v>
       </c>
       <c r="F781" s="8" t="s">
-        <v>2295</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="782" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A782" s="8" t="s">
-        <v>2296</v>
+        <v>2293</v>
       </c>
       <c r="B782" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C782" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:gfp</v>
+        <v>att_protein_mutation:frameshift</v>
       </c>
       <c r="D782" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E782" s="8" t="s">
-        <v>2297</v>
+        <v>2294</v>
       </c>
       <c r="F782" s="8" t="s">
-        <v>2298</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="783" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A783" s="8" t="s">
-        <v>2299</v>
+        <v>2296</v>
       </c>
       <c r="B783" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C783" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:ha</v>
+        <v>att_protein_mutation:gfp</v>
       </c>
       <c r="D783" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E783" s="8" t="s">
-        <v>2300</v>
+        <v>2297</v>
       </c>
       <c r="F783" s="8" t="s">
-        <v>2301</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="784" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A784" s="8" t="s">
-        <v>2302</v>
+        <v>2299</v>
       </c>
       <c r="B784" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C784" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:his</v>
+        <v>att_protein_mutation:ha</v>
       </c>
       <c r="D784" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E784" s="8" t="s">
-        <v>2303</v>
+        <v>2300</v>
       </c>
       <c r="F784" s="8" t="s">
-        <v>2304</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="785" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A785" s="8" t="s">
-        <v>2305</v>
+        <v>2302</v>
       </c>
       <c r="B785" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C785" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:insertion</v>
+        <v>att_protein_mutation:his</v>
       </c>
       <c r="D785" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E785" s="8" t="s">
-        <v>2306</v>
+        <v>2303</v>
       </c>
       <c r="F785" s="8" t="s">
-        <v>2307</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="786" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A786" s="8" t="s">
-        <v>2308</v>
+        <v>2305</v>
       </c>
       <c r="B786" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C786" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:myc</v>
+        <v>att_protein_mutation:insertion</v>
       </c>
       <c r="D786" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E786" s="8" t="s">
-        <v>2309</v>
+        <v>2306</v>
       </c>
       <c r="F786" s="8" t="s">
-        <v>2310</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="787" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A787" s="8" t="s">
-        <v>2311</v>
+        <v>2308</v>
       </c>
       <c r="B787" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C787" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:pep86</v>
+        <v>att_protein_mutation:myc</v>
       </c>
       <c r="D787" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E787" s="8" t="s">
-        <v>2812</v>
+        <v>2309</v>
       </c>
       <c r="F787" s="8" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="788" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A788" s="8" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="B788" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C788" s="8" t="str">
         <f t="shared" si="16"/>
-        <v>att_protein_mutation:substitution</v>
+        <v>att_protein_mutation:pep86</v>
       </c>
       <c r="D788" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E788" s="8" t="s">
-        <v>2314</v>
+        <v>2812</v>
       </c>
       <c r="F788" s="8" t="s">
-        <v>2315</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="789" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A789" s="8" t="s">
-        <v>2316</v>
+        <v>2313</v>
       </c>
       <c r="B789" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C789" s="8" t="str">
-        <f t="shared" ref="C789" si="17">B789&amp;":"&amp;A789</f>
-        <v>att_protein_mutation:truncation</v>
+        <f t="shared" si="16"/>
+        <v>att_protein_mutation:substitution</v>
       </c>
       <c r="D789" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E789" s="8" t="s">
-        <v>2317</v>
+        <v>2314</v>
       </c>
       <c r="F789" s="8" t="s">
-        <v>2318</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="790" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A790" s="8" t="s">
-        <v>342</v>
+        <v>2316</v>
       </c>
       <c r="B790" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C790" s="8" t="str">
+        <f t="shared" ref="C790" si="17">B790&amp;":"&amp;A790</f>
+        <v>att_protein_mutation:truncation</v>
+      </c>
+      <c r="D790" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E790" s="8" t="s">
+        <v>2317</v>
+      </c>
+      <c r="F790" s="8" t="s">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="791" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A791" s="8" t="s">
+        <v>342</v>
+      </c>
+      <c r="B791" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C791" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_protein_mutation:none</v>
       </c>
-      <c r="D790" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E790" s="8" t="s">
+      <c r="D791" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E791" s="8" t="s">
         <v>1874</v>
       </c>
-      <c r="F790" s="8" t="s">
+      <c r="F791" s="8" t="s">
         <v>2813</v>
       </c>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A791" s="8" t="s">
+    <row r="792" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A792" s="8" t="s">
         <v>2319</v>
       </c>
-      <c r="B791" s="8" t="s">
+      <c r="B792" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C791" s="8" t="str">
+      <c r="C792" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_protein_position:aa</v>
       </c>
-      <c r="D791" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E791" s="8" t="s">
+      <c r="D792" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E792" s="8" t="s">
         <v>2320</v>
       </c>
-      <c r="F791" s="8" t="s">
+      <c r="F792" s="8" t="s">
         <v>2321</v>
       </c>
     </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A792" s="8" t="s">
+    <row r="793" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A793" s="8" t="s">
         <v>2322</v>
       </c>
-      <c r="B792" s="8" t="s">
+      <c r="B793" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C792" s="8" t="str">
+      <c r="C793" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_protein_position:cterm</v>
       </c>
-      <c r="D792" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E792" s="8" t="s">
+      <c r="D793" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E793" s="8" t="s">
         <v>2323</v>
       </c>
-      <c r="F792" s="8" t="s">
+      <c r="F793" s="8" t="s">
         <v>2324</v>
       </c>
     </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A793" s="8" t="s">
+    <row r="794" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A794" s="8" t="s">
         <v>2325</v>
       </c>
-      <c r="B793" s="8" t="s">
+      <c r="B794" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C793" s="8" t="str">
+      <c r="C794" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_protein_position:nterm</v>
       </c>
-      <c r="D793" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E793" s="8" t="s">
+      <c r="D794" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E794" s="8" t="s">
         <v>2326</v>
       </c>
-      <c r="F793" s="8" t="s">
+      <c r="F794" s="8" t="s">
         <v>2327</v>
       </c>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A794" s="8" t="s">
+    <row r="795" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A795" s="8" t="s">
         <v>2328</v>
       </c>
-      <c r="B794" s="8" t="s">
+      <c r="B795" s="8" t="s">
         <v>208</v>
       </c>
-      <c r="C794" s="8" t="str">
+      <c r="C795" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_protein_position:region</v>
       </c>
-      <c r="D794" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E794" s="8" t="s">
+      <c r="D795" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E795" s="8" t="s">
         <v>2329</v>
       </c>
-      <c r="F794" s="8" t="s">
+      <c r="F795" s="8" t="s">
         <v>2330</v>
       </c>
     </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A795" s="8" t="s">
+    <row r="796" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A796" s="8" t="s">
         <v>2331</v>
       </c>
-      <c r="B795" s="8" t="s">
+      <c r="B796" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C795" s="8" t="str">
+      <c r="C796" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_quant_algorithm:directlfq</v>
       </c>
-      <c r="D795" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E795" s="8" t="s">
+      <c r="D796" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E796" s="8" t="s">
         <v>2332</v>
       </c>
-      <c r="F795" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A796" s="8" t="s">
+      <c r="F796" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="797" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A797" s="8" t="s">
         <v>2333</v>
       </c>
-      <c r="B796" s="8" t="s">
+      <c r="B797" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C796" s="8" t="str">
+      <c r="C797" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_quant_algorithm:maxlfq</v>
       </c>
-      <c r="D796" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E796" s="8" t="s">
+      <c r="D797" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E797" s="8" t="s">
         <v>2334</v>
       </c>
-      <c r="F796" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="797" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A797" s="8" t="s">
+      <c r="F797" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A798" s="8" t="s">
         <v>2335</v>
       </c>
-      <c r="B797" s="8" t="s">
+      <c r="B798" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C797" s="8" t="str">
+      <c r="C798" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_quant_algorithm:speccount</v>
       </c>
-      <c r="D797" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E797" s="8" t="s">
+      <c r="D798" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E798" s="8" t="s">
         <v>2336</v>
       </c>
-      <c r="F797" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A798" s="8" t="s">
+      <c r="F798" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="799" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A799" s="8" t="s">
         <v>2337</v>
       </c>
-      <c r="B798" s="8" t="s">
+      <c r="B799" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C798" s="8" t="str">
+      <c r="C799" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_quantification:isobaric</v>
       </c>
-      <c r="D798" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E798" s="8" t="s">
+      <c r="D799" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E799" s="8" t="s">
         <v>2337</v>
       </c>
-      <c r="F798" s="8" t="s">
+      <c r="F799" s="8" t="s">
         <v>2338</v>
       </c>
     </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A799" s="8" t="s">
+    <row r="800" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A800" s="8" t="s">
         <v>2339</v>
       </c>
-      <c r="B799" s="8" t="s">
+      <c r="B800" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C799" s="8" t="str">
+      <c r="C800" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_quantification:istopic</v>
       </c>
-      <c r="D799" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E799" s="8" t="s">
+      <c r="D800" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E800" s="8" t="s">
         <v>2339</v>
       </c>
-      <c r="F799" s="8" t="s">
+      <c r="F800" s="8" t="s">
         <v>2340</v>
       </c>
     </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A800" s="8" t="s">
+    <row r="801" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A801" s="8" t="s">
         <v>2341</v>
       </c>
-      <c r="B800" s="8" t="s">
+      <c r="B801" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C800" s="8" t="str">
+      <c r="C801" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_quantification:label_free</v>
       </c>
-      <c r="D800" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E800" s="8" t="s">
+      <c r="D801" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E801" s="8" t="s">
         <v>2342</v>
       </c>
-      <c r="F800" s="8" t="s">
+      <c r="F801" s="8" t="s">
         <v>2343</v>
       </c>
     </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A801" s="8" t="s">
+    <row r="802" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A802" s="8" t="s">
         <v>2344</v>
       </c>
-      <c r="B801" s="8" t="s">
+      <c r="B802" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="C801" s="8" t="str">
+      <c r="C802" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_quantification:silac</v>
       </c>
-      <c r="D801" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E801" s="8" t="s">
+      <c r="D802" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E802" s="8" t="s">
         <v>2344</v>
       </c>
-      <c r="F801" s="8" t="s">
+      <c r="F802" s="8" t="s">
         <v>2345</v>
       </c>
     </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A802" s="8" t="s">
+    <row r="803" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A803" s="8" t="s">
         <v>2346</v>
       </c>
-      <c r="B802" s="8" t="s">
+      <c r="B803" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C802" s="8" t="str">
+      <c r="C803" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_reduction:dtt</v>
       </c>
-      <c r="D802" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E802" s="8" t="s">
+      <c r="D803" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E803" s="8" t="s">
         <v>2347</v>
       </c>
-      <c r="F802" s="8" t="s">
+      <c r="F803" s="8" t="s">
         <v>2348</v>
       </c>
     </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A803" s="8" t="s">
+    <row r="804" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A804" s="8" t="s">
         <v>342</v>
       </c>
-      <c r="B803" s="8" t="s">
+      <c r="B804" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C803" s="8" t="str">
+      <c r="C804" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_reduction:none</v>
       </c>
-      <c r="D803" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E803" s="8" t="s">
+      <c r="D804" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E804" s="8" t="s">
         <v>343</v>
       </c>
-      <c r="F803" s="8" t="s">
+      <c r="F804" s="8" t="s">
         <v>2349</v>
       </c>
     </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A804" s="8" t="s">
+    <row r="805" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A805" s="8" t="s">
         <v>2350</v>
       </c>
-      <c r="B804" s="8" t="s">
+      <c r="B805" s="8" t="s">
         <v>214</v>
       </c>
-      <c r="C804" s="8" t="str">
+      <c r="C805" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_reduction:tcep</v>
       </c>
-      <c r="D804" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E804" s="8" t="s">
+      <c r="D805" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E805" s="8" t="s">
         <v>2351</v>
       </c>
-      <c r="F804" s="8" t="s">
+      <c r="F805" s="8" t="s">
         <v>2352</v>
       </c>
     </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A805" s="8" t="s">
+    <row r="806" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A806" s="8" t="s">
         <v>1417</v>
       </c>
-      <c r="B805" s="8" t="s">
+      <c r="B806" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C805" s="8" t="str">
+      <c r="C806" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:apoptosis</v>
       </c>
-      <c r="D805" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E805" s="8" t="s">
+      <c r="D806" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E806" s="8" t="s">
         <v>1418</v>
       </c>
-      <c r="F805" s="8" t="s">
+      <c r="F806" s="8" t="s">
         <v>2354</v>
       </c>
     </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A806" s="8" t="s">
+    <row r="807" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A807" s="8" t="s">
         <v>2355</v>
       </c>
-      <c r="B806" s="8" t="s">
+      <c r="B807" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C806" s="8" t="str">
+      <c r="C807" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:autocrine</v>
       </c>
-      <c r="D806" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E806" s="8" t="s">
+      <c r="D807" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E807" s="8" t="s">
         <v>2356</v>
       </c>
-      <c r="F806" s="8" t="s">
+      <c r="F807" s="8" t="s">
         <v>2357</v>
       </c>
     </row>
-    <row r="807" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A807" s="8" t="s">
+    <row r="808" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A808" s="8" t="s">
         <v>2358</v>
       </c>
-      <c r="B807" s="8" t="s">
+      <c r="B808" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C807" s="8" t="str">
+      <c r="C808" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:complement</v>
       </c>
-      <c r="D807" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E807" s="8" t="s">
+      <c r="D808" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E808" s="8" t="s">
         <v>2359</v>
       </c>
-      <c r="F807" s="8" t="s">
+      <c r="F808" s="8" t="s">
         <v>2360</v>
       </c>
     </row>
-    <row r="808" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A808" s="8" t="s">
+    <row r="809" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A809" s="8" t="s">
         <v>2361</v>
       </c>
-      <c r="B808" s="8" t="s">
+      <c r="B809" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C808" s="8" t="str">
+      <c r="C809" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:cytokines</v>
       </c>
-      <c r="D808" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E808" s="8" t="s">
+      <c r="D809" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E809" s="8" t="s">
         <v>2362</v>
       </c>
-      <c r="F808" s="8" t="s">
+      <c r="F809" s="8" t="s">
         <v>2363</v>
       </c>
     </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A809" s="8" t="s">
+    <row r="810" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A810" s="8" t="s">
         <v>2364</v>
       </c>
-      <c r="B809" s="8" t="s">
+      <c r="B810" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C809" s="8" t="str">
+      <c r="C810" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:inflammation</v>
       </c>
-      <c r="D809" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E809" s="8" t="s">
+      <c r="D810" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E810" s="8" t="s">
         <v>2365</v>
       </c>
-      <c r="F809" s="8" t="s">
+      <c r="F810" s="8" t="s">
         <v>2366</v>
       </c>
     </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A810" s="8" t="s">
+    <row r="811" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A811" s="8" t="s">
         <v>2367</v>
       </c>
-      <c r="B810" s="8" t="s">
+      <c r="B811" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C810" s="8" t="str">
+      <c r="C811" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:insulin</v>
       </c>
-      <c r="D810" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E810" s="8" t="s">
+      <c r="D811" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E811" s="8" t="s">
         <v>2368</v>
       </c>
-      <c r="F810" s="8" t="s">
+      <c r="F811" s="8" t="s">
         <v>2369</v>
       </c>
     </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A811" s="8" t="s">
+    <row r="812" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A812" s="8" t="s">
         <v>2370</v>
       </c>
-      <c r="B811" s="8" t="s">
+      <c r="B812" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C811" s="8" t="str">
+      <c r="C812" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:juxtacrine</v>
       </c>
-      <c r="D811" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E811" s="8" t="s">
+      <c r="D812" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E812" s="8" t="s">
         <v>2371</v>
       </c>
-      <c r="F811" s="8" t="s">
+      <c r="F812" s="8" t="s">
         <v>2372</v>
       </c>
     </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A812" s="8" t="s">
+    <row r="813" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A813" s="8" t="s">
         <v>2373</v>
       </c>
-      <c r="B812" s="8" t="s">
+      <c r="B813" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C812" s="8" t="str">
+      <c r="C813" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:necrosis</v>
       </c>
-      <c r="D812" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E812" s="8" t="s">
+      <c r="D813" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E813" s="8" t="s">
         <v>2374</v>
       </c>
-      <c r="F812" s="8" t="s">
+      <c r="F813" s="8" t="s">
         <v>2375</v>
       </c>
     </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A813" s="8" t="s">
+    <row r="814" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A814" s="8" t="s">
         <v>2376</v>
       </c>
-      <c r="B813" s="8" t="s">
+      <c r="B814" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C813" s="8" t="str">
+      <c r="C814" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:paracrine</v>
       </c>
-      <c r="D813" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E813" s="8" t="s">
+      <c r="D814" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E814" s="8" t="s">
         <v>2377</v>
       </c>
-      <c r="F813" s="8" t="s">
+      <c r="F814" s="8" t="s">
         <v>2378</v>
       </c>
     </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A814" s="8" t="s">
+    <row r="815" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A815" s="8" t="s">
         <v>1765</v>
       </c>
-      <c r="B814" s="8" t="s">
+      <c r="B815" s="8" t="s">
         <v>2353</v>
       </c>
-      <c r="C814" s="8" t="str">
+      <c r="C815" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_signalling:signaling</v>
       </c>
-      <c r="D814" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E814" s="8" t="s">
+      <c r="D815" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E815" s="8" t="s">
         <v>1766</v>
       </c>
-      <c r="F814" s="8" t="s">
+      <c r="F815" s="8" t="s">
         <v>2379</v>
       </c>
     </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A815" s="8" t="s">
+    <row r="816" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A816" s="8" t="s">
         <v>2380</v>
       </c>
-      <c r="B815" s="8" t="s">
+      <c r="B816" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C815" s="8" t="str">
+      <c r="C816" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_software:diann</v>
       </c>
-      <c r="D815" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E815" s="8" t="s">
+      <c r="D816" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E816" s="8" t="s">
         <v>2381</v>
       </c>
-      <c r="F815" s="8" t="s">
+      <c r="F816" s="8" t="s">
         <v>2382</v>
       </c>
     </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A816" s="8" t="s">
+    <row r="817" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A817" s="8" t="s">
         <v>2383</v>
       </c>
-      <c r="B816" s="8" t="s">
+      <c r="B817" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C816" s="8" t="str">
+      <c r="C817" s="8" t="str">
         <f t="shared" si="16"/>
         <v>att_software:maxquant</v>
       </c>
-      <c r="D816" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E816" s="8" t="s">
+      <c r="D817" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E817" s="8" t="s">
         <v>2384</v>
       </c>
-      <c r="F816" s="8" t="s">
+      <c r="F817" s="8" t="s">
         <v>2385</v>
-      </c>
-    </row>
-    <row r="817" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A817" s="8" t="s">
-        <v>2386</v>
-      </c>
-      <c r="B817" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C817" s="8" t="str">
-        <f t="shared" ref="C817:C880" si="18">B817&amp;":"&amp;A817</f>
-        <v>att_software:metamorpheus</v>
-      </c>
-      <c r="D817" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E817" s="8" t="s">
-        <v>2387</v>
-      </c>
-      <c r="F817" s="8" t="s">
-        <v>2388</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A818" s="8" t="s">
-        <v>2389</v>
+        <v>2386</v>
       </c>
       <c r="B818" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C818" s="8" t="str">
+        <f t="shared" ref="C818:C881" si="18">B818&amp;":"&amp;A818</f>
+        <v>att_software:metamorpheus</v>
+      </c>
+      <c r="D818" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E818" s="8" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F818" s="8" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="819" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A819" s="8" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B819" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C819" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_software:minora</v>
       </c>
-      <c r="D818" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E818" s="8" t="s">
+      <c r="D819" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E819" s="8" t="s">
         <v>2390</v>
       </c>
-      <c r="F818" s="8" t="s">
+      <c r="F819" s="8" t="s">
         <v>2391</v>
       </c>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A819" s="8" t="s">
+    <row r="820" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A820" s="8" t="s">
         <v>2392</v>
       </c>
-      <c r="B819" s="8" t="s">
+      <c r="B820" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C819" s="8" t="str">
+      <c r="C820" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_software:msfragger</v>
       </c>
-      <c r="D819" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E819" s="8" t="s">
+      <c r="D820" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E820" s="8" t="s">
         <v>2393</v>
       </c>
-      <c r="F819" s="8" t="s">
+      <c r="F820" s="8" t="s">
         <v>2394</v>
       </c>
     </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A820" s="8" t="s">
+    <row r="821" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A821" s="8" t="s">
         <v>2395</v>
       </c>
-      <c r="B820" s="8" t="s">
+      <c r="B821" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C820" s="8" t="str">
+      <c r="C821" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_software:msgf</v>
       </c>
-      <c r="D820" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E820" s="8" t="s">
+      <c r="D821" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E821" s="8" t="s">
         <v>2396</v>
       </c>
-      <c r="F820" s="8" t="s">
+      <c r="F821" s="8" t="s">
         <v>2397</v>
       </c>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A821" s="8" t="s">
+    <row r="822" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A822" s="8" t="s">
         <v>2398</v>
       </c>
-      <c r="B821" s="8" t="s">
+      <c r="B822" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C821" s="8" t="str">
+      <c r="C822" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_software:spectronaut</v>
       </c>
-      <c r="D821" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E821" s="8" t="s">
+      <c r="D822" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E822" s="8" t="s">
         <v>2399</v>
       </c>
-      <c r="F821" s="8" t="s">
+      <c r="F822" s="8" t="s">
         <v>2400</v>
       </c>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A822" s="8" t="s">
+    <row r="823" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A823" s="8" t="s">
         <v>2401</v>
       </c>
-      <c r="B822" s="8" t="s">
+      <c r="B823" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C822" s="8" t="str">
+      <c r="C823" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:adipose</v>
       </c>
-      <c r="D822" s="8" t="s">
+      <c r="D823" s="8" t="s">
         <v>2401</v>
       </c>
-      <c r="E822" s="8" t="s">
+      <c r="E823" s="8" t="s">
         <v>2402</v>
       </c>
-      <c r="F822" s="8" t="s">
+      <c r="F823" s="8" t="s">
         <v>2403</v>
       </c>
     </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A823" s="8" t="s">
+    <row r="824" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A824" s="8" t="s">
         <v>2404</v>
       </c>
-      <c r="B823" s="8" t="s">
+      <c r="B824" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C823" s="8" t="str">
+      <c r="C824" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:areolar</v>
       </c>
-      <c r="D823" s="8" t="s">
+      <c r="D824" s="8" t="s">
         <v>2404</v>
       </c>
-      <c r="E823" s="8" t="s">
+      <c r="E824" s="8" t="s">
         <v>2405</v>
       </c>
-      <c r="F823" s="8" t="s">
+      <c r="F824" s="8" t="s">
         <v>2406</v>
       </c>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A824" s="8" t="s">
+    <row r="825" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A825" s="8" t="s">
         <v>2407</v>
       </c>
-      <c r="B824" s="8" t="s">
+      <c r="B825" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C824" s="8" t="str">
+      <c r="C825" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:blood</v>
       </c>
-      <c r="D824" s="8" t="s">
+      <c r="D825" s="8" t="s">
         <v>2407</v>
       </c>
-      <c r="E824" s="8" t="s">
+      <c r="E825" s="8" t="s">
         <v>2408</v>
       </c>
-      <c r="F824" s="8" t="s">
+      <c r="F825" s="8" t="s">
         <v>2408</v>
       </c>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A825" s="8" t="s">
+    <row r="826" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A826" s="8" t="s">
         <v>2409</v>
       </c>
-      <c r="B825" s="8" t="s">
+      <c r="B826" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C825" s="8" t="str">
+      <c r="C826" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:connective</v>
       </c>
-      <c r="D825" s="8" t="s">
+      <c r="D826" s="8" t="s">
         <v>2409</v>
       </c>
-      <c r="E825" s="8" t="s">
+      <c r="E826" s="8" t="s">
         <v>2410</v>
       </c>
-      <c r="F825" s="8" t="s">
+      <c r="F826" s="8" t="s">
         <v>2411</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A826" s="8" t="s">
+    <row r="827" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A827" s="8" t="s">
         <v>2412</v>
       </c>
-      <c r="B826" s="8" t="s">
+      <c r="B827" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C826" s="8" t="str">
+      <c r="C827" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:dermis</v>
       </c>
-      <c r="D826" s="8" t="s">
+      <c r="D827" s="8" t="s">
         <v>2412</v>
       </c>
-      <c r="E826" s="8" t="s">
+      <c r="E827" s="8" t="s">
         <v>2413</v>
       </c>
-      <c r="F826" s="8" t="s">
+      <c r="F827" s="8" t="s">
         <v>2413</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A827" s="8" t="s">
+    <row r="828" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A828" s="8" t="s">
         <v>2414</v>
       </c>
-      <c r="B827" s="8" t="s">
+      <c r="B828" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C827" s="8" t="str">
+      <c r="C828" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:epidermis</v>
       </c>
-      <c r="D827" s="8" t="s">
+      <c r="D828" s="8" t="s">
         <v>2414</v>
       </c>
-      <c r="E827" s="8" t="s">
+      <c r="E828" s="8" t="s">
         <v>2415</v>
       </c>
-      <c r="F827" s="8" t="s">
+      <c r="F828" s="8" t="s">
         <v>2415</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A828" s="8" t="s">
+    <row r="829" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A829" s="8" t="s">
         <v>2416</v>
       </c>
-      <c r="B828" s="8" t="s">
+      <c r="B829" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C828" s="8" t="str">
+      <c r="C829" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:epithelial</v>
       </c>
-      <c r="D828" s="8" t="s">
+      <c r="D829" s="8" t="s">
         <v>2416</v>
       </c>
-      <c r="E828" s="8" t="s">
+      <c r="E829" s="8" t="s">
         <v>2417</v>
       </c>
-      <c r="F828" s="8" t="s">
+      <c r="F829" s="8" t="s">
         <v>2418</v>
       </c>
     </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A829" s="8" t="s">
+    <row r="830" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A830" s="8" t="s">
         <v>2419</v>
       </c>
-      <c r="B829" s="8" t="s">
+      <c r="B830" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C829" s="8" t="str">
+      <c r="C830" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:hypodermis</v>
       </c>
-      <c r="D829" s="8" t="s">
+      <c r="D830" s="8" t="s">
         <v>2419</v>
       </c>
-      <c r="E829" s="8" t="s">
+      <c r="E830" s="8" t="s">
         <v>2420</v>
       </c>
-      <c r="F829" s="8" t="s">
+      <c r="F830" s="8" t="s">
         <v>2420</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A830" s="8" t="s">
+    <row r="831" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A831" s="8" t="s">
         <v>2421</v>
       </c>
-      <c r="B830" s="8" t="s">
+      <c r="B831" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C830" s="8" t="str">
+      <c r="C831" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:muscle</v>
       </c>
-      <c r="D830" s="8" t="s">
+      <c r="D831" s="8" t="s">
         <v>2421</v>
       </c>
-      <c r="E830" s="8" t="s">
+      <c r="E831" s="8" t="s">
         <v>2819</v>
       </c>
-      <c r="F830" s="8" t="s">
+      <c r="F831" s="8" t="s">
         <v>2422</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A831" s="8" t="s">
+    <row r="832" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A832" s="8" t="s">
         <v>2423</v>
       </c>
-      <c r="B831" s="8" t="s">
+      <c r="B832" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C831" s="8" t="str">
+      <c r="C832" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:nervous</v>
       </c>
-      <c r="D831" s="8" t="s">
+      <c r="D832" s="8" t="s">
         <v>2423</v>
       </c>
-      <c r="E831" s="8" t="s">
+      <c r="E832" s="8" t="s">
         <v>2242</v>
       </c>
-      <c r="F831" s="8" t="s">
+      <c r="F832" s="8" t="s">
         <v>2424</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A832" s="8" t="s">
+    <row r="833" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A833" s="8" t="s">
         <v>2425</v>
       </c>
-      <c r="B832" s="8" t="s">
+      <c r="B833" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C832" s="8" t="str">
+      <c r="C833" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:reticular</v>
       </c>
-      <c r="D832" s="8" t="s">
+      <c r="D833" s="8" t="s">
         <v>2425</v>
       </c>
-      <c r="E832" s="8" t="s">
+      <c r="E833" s="8" t="s">
         <v>2426</v>
       </c>
-      <c r="F832" s="8" t="s">
+      <c r="F833" s="8" t="s">
         <v>2427</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A833" s="8" t="s">
+    <row r="834" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A834" s="8" t="s">
         <v>2428</v>
       </c>
-      <c r="B833" s="8" t="s">
+      <c r="B834" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C833" s="8" t="str">
+      <c r="C834" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:stromal</v>
       </c>
-      <c r="D833" s="8" t="s">
+      <c r="D834" s="8" t="s">
         <v>2428</v>
       </c>
-      <c r="E833" s="8" t="s">
+      <c r="E834" s="8" t="s">
         <v>2429</v>
       </c>
-      <c r="F833" s="8" t="s">
+      <c r="F834" s="8" t="s">
         <v>2430</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A834" s="8" t="s">
+    <row r="835" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A835" s="8" t="s">
         <v>2431</v>
       </c>
-      <c r="B834" s="8" t="s">
+      <c r="B835" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C834" s="8" t="str">
+      <c r="C835" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_126</v>
       </c>
-      <c r="D834" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E834" s="8">
+      <c r="D835" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E835" s="8">
         <v>126</v>
       </c>
-      <c r="F834" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A835" s="8" t="s">
+      <c r="F835" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="836" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A836" s="8" t="s">
         <v>2432</v>
       </c>
-      <c r="B835" s="8" t="s">
+      <c r="B836" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C835" s="8" t="str">
+      <c r="C836" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_127C</v>
       </c>
-      <c r="D835" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E835" s="8" t="s">
+      <c r="D836" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E836" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F835" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A836" s="8" t="s">
+      <c r="F836" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="837" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A837" s="8" t="s">
         <v>2434</v>
       </c>
-      <c r="B836" s="8" t="s">
+      <c r="B837" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C836" s="8" t="str">
+      <c r="C837" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_127N</v>
       </c>
-      <c r="D836" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E836" s="8" t="s">
+      <c r="D837" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E837" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F836" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A837" s="8" t="s">
+      <c r="F837" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="838" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A838" s="8" t="s">
         <v>2436</v>
       </c>
-      <c r="B837" s="8" t="s">
+      <c r="B838" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C837" s="8" t="str">
+      <c r="C838" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_128C</v>
       </c>
-      <c r="D837" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E837" s="8" t="s">
+      <c r="D838" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E838" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F837" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A838" s="8" t="s">
+      <c r="F838" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="839" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A839" s="8" t="s">
         <v>2438</v>
       </c>
-      <c r="B838" s="8" t="s">
+      <c r="B839" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C838" s="8" t="str">
+      <c r="C839" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_128N</v>
       </c>
-      <c r="D838" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E838" s="8" t="s">
+      <c r="D839" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E839" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F838" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A839" s="8" t="s">
+      <c r="F839" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="840" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A840" s="8" t="s">
         <v>2440</v>
       </c>
-      <c r="B839" s="8" t="s">
+      <c r="B840" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C839" s="8" t="str">
+      <c r="C840" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_129C</v>
       </c>
-      <c r="D839" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E839" s="8" t="s">
+      <c r="D840" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E840" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F839" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A840" s="8" t="s">
+      <c r="F840" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="841" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A841" s="8" t="s">
         <v>2442</v>
       </c>
-      <c r="B840" s="8" t="s">
+      <c r="B841" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C840" s="8" t="str">
+      <c r="C841" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_129N</v>
       </c>
-      <c r="D840" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E840" s="8" t="s">
+      <c r="D841" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E841" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F840" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A841" s="8" t="s">
+      <c r="F841" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="842" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A842" s="8" t="s">
         <v>2444</v>
       </c>
-      <c r="B841" s="8" t="s">
+      <c r="B842" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C841" s="8" t="str">
+      <c r="C842" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_130C</v>
       </c>
-      <c r="D841" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E841" s="8" t="s">
+      <c r="D842" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E842" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F841" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A842" s="8" t="s">
+      <c r="F842" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A843" s="8" t="s">
         <v>2446</v>
       </c>
-      <c r="B842" s="8" t="s">
+      <c r="B843" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C842" s="8" t="str">
+      <c r="C843" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_130N</v>
       </c>
-      <c r="D842" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E842" s="8" t="s">
+      <c r="D843" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E843" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F842" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A843" s="8" t="s">
+      <c r="F843" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A844" s="8" t="s">
         <v>2448</v>
       </c>
-      <c r="B843" s="8" t="s">
+      <c r="B844" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C843" s="8" t="str">
+      <c r="C844" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_131</v>
       </c>
-      <c r="D843" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E843" s="8">
+      <c r="D844" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E844" s="8">
         <v>131</v>
       </c>
-      <c r="F843" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A844" s="8" t="s">
+      <c r="F844" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A845" s="8" t="s">
         <v>2449</v>
       </c>
-      <c r="B844" s="8" t="s">
+      <c r="B845" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C844" s="8" t="str">
+      <c r="C845" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_126</v>
       </c>
-      <c r="D844" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E844" s="8">
+      <c r="D845" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E845" s="8">
         <v>126</v>
       </c>
-      <c r="F844" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A845" s="8" t="s">
+      <c r="F845" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A846" s="8" t="s">
         <v>2450</v>
       </c>
-      <c r="B845" s="8" t="s">
+      <c r="B846" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C845" s="8" t="str">
+      <c r="C846" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_127C</v>
       </c>
-      <c r="D845" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E845" s="8" t="s">
+      <c r="D846" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E846" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F845" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A846" s="8" t="s">
+      <c r="F846" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A847" s="8" t="s">
         <v>2451</v>
       </c>
-      <c r="B846" s="8" t="s">
+      <c r="B847" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C846" s="8" t="str">
+      <c r="C847" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_127N</v>
       </c>
-      <c r="D846" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E846" s="8" t="s">
+      <c r="D847" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E847" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F846" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A847" s="8" t="s">
+      <c r="F847" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="848" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A848" s="8" t="s">
         <v>2452</v>
       </c>
-      <c r="B847" s="8" t="s">
+      <c r="B848" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C847" s="8" t="str">
+      <c r="C848" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_128C</v>
       </c>
-      <c r="D847" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E847" s="8" t="s">
+      <c r="D848" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E848" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F847" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A848" s="8" t="s">
+      <c r="F848" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A849" s="8" t="s">
         <v>2453</v>
       </c>
-      <c r="B848" s="8" t="s">
+      <c r="B849" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C848" s="8" t="str">
+      <c r="C849" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_128N</v>
       </c>
-      <c r="D848" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E848" s="8" t="s">
+      <c r="D849" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E849" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F848" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A849" s="8" t="s">
+      <c r="F849" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A850" s="8" t="s">
         <v>2454</v>
       </c>
-      <c r="B849" s="8" t="s">
+      <c r="B850" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C849" s="8" t="str">
+      <c r="C850" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_129C</v>
       </c>
-      <c r="D849" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E849" s="8" t="s">
+      <c r="D850" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E850" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F849" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A850" s="8" t="s">
+      <c r="F850" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A851" s="8" t="s">
         <v>2455</v>
       </c>
-      <c r="B850" s="8" t="s">
+      <c r="B851" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C850" s="8" t="str">
+      <c r="C851" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_129N</v>
       </c>
-      <c r="D850" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E850" s="8" t="s">
+      <c r="D851" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E851" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F850" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A851" s="8" t="s">
+      <c r="F851" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A852" s="8" t="s">
         <v>2456</v>
       </c>
-      <c r="B851" s="8" t="s">
+      <c r="B852" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C851" s="8" t="str">
+      <c r="C852" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_130C</v>
       </c>
-      <c r="D851" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E851" s="8" t="s">
+      <c r="D852" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E852" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F851" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A852" s="8" t="s">
+      <c r="F852" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A853" s="8" t="s">
         <v>2457</v>
       </c>
-      <c r="B852" s="8" t="s">
+      <c r="B853" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C852" s="8" t="str">
+      <c r="C853" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_130N</v>
       </c>
-      <c r="D852" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E852" s="8" t="s">
+      <c r="D853" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E853" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F852" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A853" s="8" t="s">
+      <c r="F853" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A854" s="8" t="s">
         <v>2458</v>
       </c>
-      <c r="B853" s="8" t="s">
+      <c r="B854" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C853" s="8" t="str">
+      <c r="C854" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_131C</v>
       </c>
-      <c r="D853" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E853" s="8" t="s">
+      <c r="D854" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E854" s="8" t="s">
         <v>2459</v>
       </c>
-      <c r="F853" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A854" s="8" t="s">
+      <c r="F854" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A855" s="8" t="s">
         <v>2460</v>
       </c>
-      <c r="B854" s="8" t="s">
+      <c r="B855" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C854" s="8" t="str">
+      <c r="C855" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_131N</v>
       </c>
-      <c r="D854" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E854" s="8" t="s">
+      <c r="D855" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E855" s="8" t="s">
         <v>2461</v>
       </c>
-      <c r="F854" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A855" s="8" t="s">
+      <c r="F855" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A856" s="8" t="s">
         <v>2462</v>
       </c>
-      <c r="B855" s="8" t="s">
+      <c r="B856" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C855" s="8" t="str">
+      <c r="C856" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_126</v>
       </c>
-      <c r="D855" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E855" s="8">
+      <c r="D856" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E856" s="8">
         <v>126</v>
       </c>
-      <c r="F855" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A856" s="8" t="s">
+      <c r="F856" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A857" s="8" t="s">
         <v>2463</v>
       </c>
-      <c r="B856" s="8" t="s">
+      <c r="B857" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C856" s="8" t="str">
+      <c r="C857" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_127C</v>
       </c>
-      <c r="D856" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E856" s="8" t="s">
+      <c r="D857" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E857" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F856" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A857" s="8" t="s">
+      <c r="F857" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A858" s="8" t="s">
         <v>2464</v>
       </c>
-      <c r="B857" s="8" t="s">
+      <c r="B858" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C857" s="8" t="str">
+      <c r="C858" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_127N</v>
       </c>
-      <c r="D857" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E857" s="8" t="s">
+      <c r="D858" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E858" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F857" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A858" s="8" t="s">
+      <c r="F858" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A859" s="8" t="s">
         <v>2465</v>
       </c>
-      <c r="B858" s="8" t="s">
+      <c r="B859" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C858" s="8" t="str">
+      <c r="C859" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_128C</v>
       </c>
-      <c r="D858" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E858" s="8" t="s">
+      <c r="D859" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E859" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F858" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A859" s="8" t="s">
+      <c r="F859" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A860" s="8" t="s">
         <v>2466</v>
       </c>
-      <c r="B859" s="8" t="s">
+      <c r="B860" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C859" s="8" t="str">
+      <c r="C860" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_128N</v>
       </c>
-      <c r="D859" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E859" s="8" t="s">
+      <c r="D860" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E860" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F859" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A860" s="8" t="s">
+      <c r="F860" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A861" s="8" t="s">
         <v>2467</v>
       </c>
-      <c r="B860" s="8" t="s">
+      <c r="B861" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C860" s="8" t="str">
+      <c r="C861" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_129C</v>
       </c>
-      <c r="D860" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E860" s="8" t="s">
+      <c r="D861" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E861" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F860" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A861" s="8" t="s">
+      <c r="F861" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A862" s="8" t="s">
         <v>2468</v>
       </c>
-      <c r="B861" s="8" t="s">
+      <c r="B862" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C861" s="8" t="str">
+      <c r="C862" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_129N</v>
       </c>
-      <c r="D861" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E861" s="8" t="s">
+      <c r="D862" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E862" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F861" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A862" s="8" t="s">
+      <c r="F862" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A863" s="8" t="s">
         <v>2469</v>
       </c>
-      <c r="B862" s="8" t="s">
+      <c r="B863" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C862" s="8" t="str">
+      <c r="C863" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_130C</v>
       </c>
-      <c r="D862" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E862" s="8" t="s">
+      <c r="D863" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E863" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F862" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A863" s="8" t="s">
+      <c r="F863" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A864" s="8" t="s">
         <v>2470</v>
       </c>
-      <c r="B863" s="8" t="s">
+      <c r="B864" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C863" s="8" t="str">
+      <c r="C864" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_130N</v>
       </c>
-      <c r="D863" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E863" s="8" t="s">
+      <c r="D864" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E864" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F863" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A864" s="8" t="s">
+      <c r="F864" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A865" s="8" t="s">
         <v>2471</v>
       </c>
-      <c r="B864" s="8" t="s">
+      <c r="B865" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C864" s="8" t="str">
+      <c r="C865" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_131C</v>
       </c>
-      <c r="D864" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E864" s="8" t="s">
+      <c r="D865" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E865" s="8" t="s">
         <v>2459</v>
       </c>
-      <c r="F864" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A865" s="8" t="s">
+      <c r="F865" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A866" s="8" t="s">
         <v>2472</v>
       </c>
-      <c r="B865" s="8" t="s">
+      <c r="B866" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C865" s="8" t="str">
+      <c r="C866" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_131N</v>
       </c>
-      <c r="D865" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E865" s="8" t="s">
+      <c r="D866" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E866" s="8" t="s">
         <v>2461</v>
       </c>
-      <c r="F865" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A866" s="8" t="s">
+      <c r="F866" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A867" s="8" t="s">
         <v>2473</v>
       </c>
-      <c r="B866" s="8" t="s">
+      <c r="B867" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C866" s="8" t="str">
+      <c r="C867" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_132C</v>
       </c>
-      <c r="D866" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E866" s="8" t="s">
+      <c r="D867" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E867" s="8" t="s">
         <v>2474</v>
       </c>
-      <c r="F866" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A867" s="8" t="s">
+      <c r="F867" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A868" s="8" t="s">
         <v>2475</v>
       </c>
-      <c r="B867" s="8" t="s">
+      <c r="B868" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C867" s="8" t="str">
+      <c r="C868" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_132N</v>
       </c>
-      <c r="D867" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E867" s="8" t="s">
+      <c r="D868" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E868" s="8" t="s">
         <v>2476</v>
       </c>
-      <c r="F867" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A868" s="8" t="s">
+      <c r="F868" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A869" s="8" t="s">
         <v>2477</v>
       </c>
-      <c r="B868" s="8" t="s">
+      <c r="B869" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C868" s="8" t="str">
+      <c r="C869" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_133C</v>
       </c>
-      <c r="D868" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E868" s="8" t="s">
+      <c r="D869" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E869" s="8" t="s">
         <v>2478</v>
       </c>
-      <c r="F868" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A869" s="8" t="s">
+      <c r="F869" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A870" s="8" t="s">
         <v>2479</v>
       </c>
-      <c r="B869" s="8" t="s">
+      <c r="B870" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C869" s="8" t="str">
+      <c r="C870" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_133N</v>
       </c>
-      <c r="D869" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E869" s="8" t="s">
+      <c r="D870" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E870" s="8" t="s">
         <v>2480</v>
       </c>
-      <c r="F869" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A870" s="8" t="s">
+      <c r="F870" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A871" s="8" t="s">
         <v>2481</v>
       </c>
-      <c r="B870" s="8" t="s">
+      <c r="B871" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C870" s="8" t="str">
+      <c r="C871" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_134C</v>
       </c>
-      <c r="D870" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E870" s="8" t="s">
+      <c r="D871" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E871" s="8" t="s">
         <v>2482</v>
       </c>
-      <c r="F870" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A871" s="8" t="s">
+      <c r="F871" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A872" s="8" t="s">
         <v>2483</v>
       </c>
-      <c r="B871" s="8" t="s">
+      <c r="B872" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C871" s="8" t="str">
+      <c r="C872" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_134N</v>
       </c>
-      <c r="D871" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E871" s="8" t="s">
+      <c r="D872" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E872" s="8" t="s">
         <v>2484</v>
       </c>
-      <c r="F871" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A872" s="8" t="s">
+      <c r="F872" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A873" s="8" t="s">
         <v>2485</v>
       </c>
-      <c r="B872" s="8" t="s">
+      <c r="B873" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C872" s="8" t="str">
+      <c r="C873" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_135N</v>
       </c>
-      <c r="D872" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E872" s="8" t="s">
+      <c r="D873" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E873" s="8" t="s">
         <v>2486</v>
       </c>
-      <c r="F872" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A873" s="8" t="s">
+      <c r="F873" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A874" s="8" t="s">
         <v>2487</v>
       </c>
-      <c r="B873" s="8" t="s">
+      <c r="B874" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C873" s="8" t="str">
+      <c r="C874" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_126</v>
       </c>
-      <c r="D873" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E873" s="8">
+      <c r="D874" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E874" s="8">
         <v>126</v>
       </c>
-      <c r="F873" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A874" s="8" t="s">
+      <c r="F874" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A875" s="8" t="s">
         <v>2488</v>
       </c>
-      <c r="B874" s="8" t="s">
+      <c r="B875" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C874" s="8" t="str">
+      <c r="C875" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_127</v>
       </c>
-      <c r="D874" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E874" s="8">
+      <c r="D875" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E875" s="8">
         <v>127</v>
       </c>
-      <c r="F874" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A875" s="8" t="s">
+      <c r="F875" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A876" s="8" t="s">
         <v>2489</v>
       </c>
-      <c r="B875" s="8" t="s">
+      <c r="B876" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C875" s="8" t="str">
+      <c r="C876" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_128</v>
       </c>
-      <c r="D875" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E875" s="8">
+      <c r="D876" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E876" s="8">
         <v>128</v>
       </c>
-      <c r="F875" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A876" s="8" t="s">
+      <c r="F876" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A877" s="8" t="s">
         <v>2490</v>
       </c>
-      <c r="B876" s="8" t="s">
+      <c r="B877" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C876" s="8" t="str">
+      <c r="C877" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_129</v>
       </c>
-      <c r="D876" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E876" s="8">
+      <c r="D877" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E877" s="8">
         <v>129</v>
       </c>
-      <c r="F876" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A877" s="8" t="s">
+      <c r="F877" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A878" s="8" t="s">
         <v>2491</v>
       </c>
-      <c r="B877" s="8" t="s">
+      <c r="B878" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C877" s="8" t="str">
+      <c r="C878" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_130</v>
       </c>
-      <c r="D877" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E877" s="8">
+      <c r="D878" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E878" s="8">
         <v>130</v>
       </c>
-      <c r="F877" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A878" s="8" t="s">
+      <c r="F878" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A879" s="8" t="s">
         <v>2492</v>
       </c>
-      <c r="B878" s="8" t="s">
+      <c r="B879" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C878" s="8" t="str">
+      <c r="C879" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_131</v>
       </c>
-      <c r="D878" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E878" s="8">
+      <c r="D879" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E879" s="8">
         <v>131</v>
       </c>
-      <c r="F878" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A879" s="8" t="s">
+      <c r="F879" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A880" s="8" t="s">
         <v>2493</v>
       </c>
-      <c r="B879" s="8" t="s">
+      <c r="B880" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C879" s="8" t="str">
+      <c r="C880" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_user_institute:biochem</v>
       </c>
-      <c r="D879" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E879" s="8" t="s">
+      <c r="D880" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E880" s="8" t="s">
         <v>2494</v>
       </c>
-      <c r="F879" s="8" t="s">
+      <c r="F880" s="8" t="s">
         <v>2495</v>
       </c>
     </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A880" s="8" t="s">
+    <row r="881" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A881" s="8" t="s">
         <v>2496</v>
       </c>
-      <c r="B880" s="8" t="s">
+      <c r="B881" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C880" s="8" t="str">
+      <c r="C881" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_user_institute:cecad</v>
       </c>
-      <c r="D880" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E880" s="8" t="s">
+      <c r="D881" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E881" s="8" t="s">
         <v>2497</v>
       </c>
-      <c r="F880" s="8" t="s">
+      <c r="F881" s="8" t="s">
         <v>2498</v>
-      </c>
-    </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A881" s="8" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B881" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="C881" s="8" t="str">
-        <f t="shared" ref="C881:C912" si="19">B881&amp;":"&amp;A881</f>
-        <v>att_user_institute:mpiage</v>
-      </c>
-      <c r="D881" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E881" s="8" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F881" s="8" t="s">
-        <v>2501</v>
       </c>
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A882" s="8" t="s">
-        <v>2502</v>
+        <v>2499</v>
       </c>
       <c r="B882" s="8" t="s">
         <v>248</v>
       </c>
       <c r="C882" s="8" t="str">
+        <f t="shared" ref="C882:C913" si="19">B882&amp;":"&amp;A882</f>
+        <v>att_user_institute:mpiage</v>
+      </c>
+      <c r="D882" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E882" s="8" t="s">
+        <v>2500</v>
+      </c>
+      <c r="F882" s="8" t="s">
+        <v>2501</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A883" s="8" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B883" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="C883" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_institute:mpimetab</v>
       </c>
-      <c r="D882" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E882" s="8" t="s">
+      <c r="D883" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E883" s="8" t="s">
         <v>2503</v>
       </c>
-      <c r="F882" s="8" t="s">
+      <c r="F883" s="8" t="s">
         <v>2504</v>
       </c>
     </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A883" s="8" t="s">
+    <row r="884" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A884" s="8" t="s">
         <v>2505</v>
       </c>
-      <c r="B883" s="8" t="s">
+      <c r="B884" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C883" s="8" t="str">
+      <c r="C884" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:mitoprotea</v>
       </c>
-      <c r="D883" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E883" s="8" t="s">
+      <c r="D884" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E884" s="8" t="s">
         <v>2506</v>
       </c>
-      <c r="F883" s="8" t="s">
+      <c r="F884" s="8" t="s">
         <v>2507</v>
       </c>
     </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A884" s="8" t="s">
+    <row r="885" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A885" s="8" t="s">
         <v>2508</v>
       </c>
-      <c r="B884" s="8" t="s">
+      <c r="B885" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C884" s="8" t="str">
+      <c r="C885" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:molageing</v>
       </c>
-      <c r="D884" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E884" s="8" t="s">
+      <c r="D885" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E885" s="8" t="s">
         <v>2509</v>
       </c>
-      <c r="F884" s="8" t="s">
+      <c r="F885" s="8" t="s">
         <v>2510</v>
       </c>
     </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A885" s="8" t="s">
+    <row r="886" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A886" s="8" t="s">
         <v>2493</v>
       </c>
-      <c r="B885" s="8" t="s">
+      <c r="B886" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C885" s="8" t="str">
+      <c r="C886" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_institute:biochem</v>
       </c>
-      <c r="D885" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E885" s="8" t="s">
+      <c r="D886" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E886" s="8" t="s">
         <v>2494</v>
       </c>
-      <c r="F885" s="8" t="s">
+      <c r="F886" s="8" t="s">
         <v>2495</v>
       </c>
     </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A886" s="8" t="s">
+    <row r="887" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A887" s="8" t="s">
         <v>2496</v>
       </c>
-      <c r="B886" s="8" t="s">
+      <c r="B887" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C886" s="8" t="str">
+      <c r="C887" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_institute:cecad</v>
       </c>
-      <c r="D886" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E886" s="8" t="s">
+      <c r="D887" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E887" s="8" t="s">
         <v>2497</v>
       </c>
-      <c r="F886" s="8" t="s">
+      <c r="F887" s="8" t="s">
         <v>2498</v>
       </c>
     </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A887" s="8" t="s">
+    <row r="888" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A888" s="8" t="s">
         <v>2499</v>
       </c>
-      <c r="B887" s="8" t="s">
+      <c r="B888" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C887" s="8" t="str">
+      <c r="C888" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_institute:mpiage</v>
       </c>
-      <c r="D887" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E887" s="8" t="s">
+      <c r="D888" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E888" s="8" t="s">
         <v>2500</v>
       </c>
-      <c r="F887" s="8" t="s">
+      <c r="F888" s="8" t="s">
         <v>2501</v>
       </c>
     </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A888" s="8" t="s">
+    <row r="889" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A889" s="8" t="s">
         <v>2502</v>
       </c>
-      <c r="B888" s="8" t="s">
+      <c r="B889" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C888" s="8" t="str">
+      <c r="C889" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_institute:mpimetab</v>
       </c>
-      <c r="D888" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E888" s="8" t="s">
+      <c r="D889" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E889" s="8" t="s">
         <v>2503</v>
       </c>
-      <c r="F888" s="8" t="s">
+      <c r="F889" s="8" t="s">
         <v>2504</v>
       </c>
     </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A889" s="8" t="s">
+    <row r="890" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A890" s="8" t="s">
         <v>2505</v>
       </c>
-      <c r="B889" s="8" t="s">
+      <c r="B890" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C889" s="8" t="str">
+      <c r="C890" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:mitoprotea</v>
       </c>
-      <c r="D889" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E889" s="8" t="s">
+      <c r="D890" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E890" s="8" t="s">
         <v>2506</v>
       </c>
-      <c r="F889" s="8" t="s">
+      <c r="F890" s="8" t="s">
         <v>2507</v>
       </c>
     </row>
-    <row r="890" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A890" s="8" t="s">
+    <row r="891" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A891" s="8" t="s">
         <v>2508</v>
       </c>
-      <c r="B890" s="8" t="s">
+      <c r="B891" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C890" s="8" t="str">
+      <c r="C891" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:molageing</v>
       </c>
-      <c r="D890" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E890" s="8" t="s">
+      <c r="D891" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E891" s="8" t="s">
         <v>2509</v>
       </c>
-      <c r="F890" s="8" t="s">
+      <c r="F891" s="8" t="s">
         <v>2510</v>
       </c>
     </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A891" s="8" t="s">
-        <v>2875</v>
-      </c>
-      <c r="B891" s="8" t="s">
+    <row r="892" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A892" s="8" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B892" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C891" s="8" t="str">
+      <c r="C892" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:ProtFa</v>
       </c>
-      <c r="D891" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E891" s="8" t="s">
+      <c r="D892" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E892" s="8" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F892" s="8" t="s">
         <v>2876</v>
       </c>
-      <c r="F891" s="8" t="s">
+    </row>
+    <row r="893" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A893" s="8" t="s">
         <v>2877</v>
       </c>
-    </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A892" s="8" t="s">
-        <v>2878</v>
-      </c>
-      <c r="B892" s="8" t="s">
+      <c r="B893" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C892" s="8" t="str">
+      <c r="C893" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:frezza</v>
       </c>
-      <c r="D892" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E892" s="8" t="s">
+      <c r="D893" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E893" s="8" t="s">
+        <v>2878</v>
+      </c>
+      <c r="F893" s="8" t="s">
         <v>2879</v>
       </c>
-      <c r="F892" s="8" t="s">
+    </row>
+    <row r="894" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A894" s="8" t="s">
         <v>2880</v>
       </c>
-    </row>
-    <row r="893" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A893" s="8" t="s">
-        <v>2881</v>
-      </c>
-      <c r="B893" s="8" t="s">
+      <c r="B894" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C893" s="8" t="str">
+      <c r="C894" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:krueger</v>
       </c>
-      <c r="D893" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E893" s="8" t="s">
+      <c r="D894" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E894" s="8" t="s">
+        <v>2881</v>
+      </c>
+      <c r="F894" s="8" t="s">
         <v>2882</v>
       </c>
-      <c r="F893" s="8" t="s">
+    </row>
+    <row r="895" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A895" s="8" t="s">
         <v>2883</v>
       </c>
-    </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A894" s="8" t="s">
-        <v>2884</v>
-      </c>
-      <c r="B894" s="8" t="s">
+      <c r="B895" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C894" s="8" t="str">
+      <c r="C895" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:rugarli</v>
       </c>
-      <c r="D894" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E894" s="8" t="s">
+      <c r="D895" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E895" s="8" t="s">
+        <v>2884</v>
+      </c>
+      <c r="F895" s="8" t="s">
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="896" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A896" s="8" t="s">
         <v>2885</v>
       </c>
-      <c r="F894" s="8" t="s">
-        <v>2883</v>
-      </c>
-    </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A895" s="8" t="s">
-        <v>2886</v>
-      </c>
-      <c r="B895" s="8" t="s">
+      <c r="B896" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C895" s="8" t="str">
+      <c r="C896" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:trifunovic</v>
       </c>
-      <c r="D895" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E895" s="8" t="s">
+      <c r="D896" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E896" s="8" t="s">
+        <v>2886</v>
+      </c>
+      <c r="F896" s="8" t="s">
         <v>2887</v>
       </c>
-      <c r="F895" s="8" t="s">
+    </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A897" s="8" t="s">
         <v>2888</v>
       </c>
-    </row>
-    <row r="896" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A896" s="8" t="s">
-        <v>2889</v>
-      </c>
-      <c r="B896" s="8" t="s">
+      <c r="B897" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C896" s="8" t="str">
+      <c r="C897" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:niessen</v>
       </c>
-      <c r="D896" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E896" s="8" t="s">
+      <c r="D897" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E897" s="8" t="s">
+        <v>2889</v>
+      </c>
+      <c r="F897" s="8" t="s">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="898" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A898" s="8" t="s">
         <v>2890</v>
       </c>
-      <c r="F896" s="8" t="s">
-        <v>2497</v>
-      </c>
-    </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A897" s="8" t="s">
-        <v>2891</v>
-      </c>
-      <c r="B897" s="8" t="s">
+      <c r="B898" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C897" s="8" t="str">
+      <c r="C898" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:gloeckner</v>
       </c>
-      <c r="D897" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E897" s="8" t="s">
+      <c r="D898" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E898" s="8" t="s">
+        <v>2891</v>
+      </c>
+      <c r="F898" s="8" t="s">
         <v>2892</v>
       </c>
-      <c r="F897" s="8" t="s">
+    </row>
+    <row r="899" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A899" s="8" t="s">
         <v>2893</v>
       </c>
-    </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A898" s="8" t="s">
-        <v>2894</v>
-      </c>
-      <c r="B898" s="8" t="s">
+      <c r="B899" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C898" s="8" t="str">
+      <c r="C899" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:bazzi</v>
       </c>
-      <c r="D898" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E898" s="8" t="s">
+      <c r="D899" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E899" s="8" t="s">
+        <v>2894</v>
+      </c>
+      <c r="F899" s="8" t="s">
         <v>2895</v>
       </c>
-      <c r="F898" s="8" t="s">
+    </row>
+    <row r="900" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A900" s="8" t="s">
         <v>2896</v>
       </c>
-    </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A899" s="8" t="s">
-        <v>2897</v>
-      </c>
-      <c r="B899" s="8" t="s">
+      <c r="B900" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C899" s="8" t="str">
+      <c r="C900" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:hallek</v>
       </c>
-      <c r="D899" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E899" s="8" t="s">
+      <c r="D900" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E900" s="8" t="s">
+        <v>2897</v>
+      </c>
+      <c r="F900" s="8" t="s">
         <v>2898</v>
       </c>
-      <c r="F899" s="8" t="s">
+    </row>
+    <row r="901" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A901" s="8" t="s">
         <v>2899</v>
       </c>
-    </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A900" s="8" t="s">
-        <v>2900</v>
-      </c>
-      <c r="B900" s="8" t="s">
+      <c r="B901" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C900" s="8" t="str">
+      <c r="C901" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:benzing</v>
       </c>
-      <c r="D900" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E900" s="8" t="s">
+      <c r="D901" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E901" s="8" t="s">
+        <v>2900</v>
+      </c>
+      <c r="F901" s="8" t="s">
         <v>2901</v>
       </c>
-      <c r="F900" s="8" t="s">
+    </row>
+    <row r="902" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A902" s="8" t="s">
         <v>2902</v>
       </c>
-    </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A901" s="8" t="s">
-        <v>2903</v>
-      </c>
-      <c r="B901" s="8" t="s">
+      <c r="B902" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C901" s="8" t="str">
+      <c r="C902" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:hennies</v>
       </c>
-      <c r="D901" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E901" s="8" t="s">
+      <c r="D902" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E902" s="8" t="s">
+        <v>2903</v>
+      </c>
+      <c r="F902" s="8" t="s">
         <v>2904</v>
       </c>
-      <c r="F901" s="8" t="s">
+    </row>
+    <row r="903" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A903" s="8" t="s">
         <v>2905</v>
       </c>
-    </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A902" s="8" t="s">
-        <v>2906</v>
-      </c>
-      <c r="B902" s="8" t="s">
+      <c r="B903" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C902" s="8" t="str">
+      <c r="C903" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:vonkarstedt</v>
       </c>
-      <c r="D902" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E902" s="8" t="s">
+      <c r="D903" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E903" s="8" t="s">
+        <v>2906</v>
+      </c>
+      <c r="F903" s="8" t="s">
         <v>2907</v>
       </c>
-      <c r="F902" s="8" t="s">
+    </row>
+    <row r="904" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A904" s="8" t="s">
         <v>2908</v>
       </c>
-    </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A903" s="8" t="s">
-        <v>2909</v>
-      </c>
-      <c r="B903" s="8" t="s">
+      <c r="B904" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C903" s="8" t="str">
+      <c r="C904" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:laessig</v>
       </c>
-      <c r="D903" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E903" s="8" t="s">
+      <c r="D904" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E904" s="8" t="s">
+        <v>2909</v>
+      </c>
+      <c r="F904" s="8" t="s">
         <v>2910</v>
       </c>
-      <c r="F903" s="8" t="s">
+    </row>
+    <row r="905" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A905" s="8" t="s">
         <v>2911</v>
       </c>
-    </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A904" s="8" t="s">
-        <v>2912</v>
-      </c>
-      <c r="B904" s="8" t="s">
+      <c r="B905" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C904" s="8" t="str">
+      <c r="C905" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:hoppe</v>
       </c>
-      <c r="D904" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E904" s="8" t="s">
+      <c r="D905" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E905" s="8" t="s">
+        <v>2912</v>
+      </c>
+      <c r="F905" s="8" t="s">
         <v>2913</v>
       </c>
-      <c r="F904" s="8" t="s">
+    </row>
+    <row r="906" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A906" s="8" t="s">
         <v>2914</v>
       </c>
-    </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A905" s="8" t="s">
-        <v>2915</v>
-      </c>
-      <c r="B905" s="8" t="s">
+      <c r="B906" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C905" s="8" t="str">
+      <c r="C906" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:garcia</v>
       </c>
-      <c r="D905" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E905" s="8" t="s">
+      <c r="D906" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E906" s="8" t="s">
+        <v>2915</v>
+      </c>
+      <c r="F906" s="8" t="s">
+        <v>2913</v>
+      </c>
+    </row>
+    <row r="907" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A907" s="8" t="s">
         <v>2916</v>
       </c>
-      <c r="F905" s="8" t="s">
-        <v>2914</v>
-      </c>
-    </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A906" s="8" t="s">
-        <v>2917</v>
-      </c>
-      <c r="B906" s="8" t="s">
+      <c r="B907" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C906" s="8" t="str">
+      <c r="C907" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:khaskar</v>
       </c>
-      <c r="D906" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E906" s="8" t="s">
+      <c r="D907" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E907" s="8" t="s">
+        <v>2917</v>
+      </c>
+      <c r="F907" s="8" t="s">
         <v>2918</v>
       </c>
-      <c r="F906" s="8" t="s">
+    </row>
+    <row r="908" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A908" s="8" t="s">
         <v>2919</v>
       </c>
-    </row>
-    <row r="907" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A907" s="8" t="s">
-        <v>2920</v>
-      </c>
-      <c r="B907" s="8" t="s">
+      <c r="B908" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C907" s="8" t="str">
+      <c r="C908" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_user_research_group:krieg</v>
       </c>
-      <c r="D907" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E907" s="8" t="s">
+      <c r="D908" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E908" s="8" t="s">
+        <v>2920</v>
+      </c>
+      <c r="F908" s="8" t="s">
         <v>2921</v>
       </c>
-      <c r="F907" s="8" t="s">
-        <v>2922</v>
-      </c>
-    </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A908" s="8" t="s">
+    </row>
+    <row r="909" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A909" s="8" t="s">
         <v>2824</v>
       </c>
-      <c r="B908" s="22" t="s">
+      <c r="B909" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C908" s="8" t="str">
+      <c r="C909" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_diet:wd</v>
       </c>
-      <c r="D908" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E908" s="8" t="s">
+      <c r="D909" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E909" s="8" t="s">
         <v>2823</v>
       </c>
-      <c r="F908" s="8" t="s">
+      <c r="F909" s="8" t="s">
         <v>2822</v>
       </c>
     </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A909" s="8" t="s">
+    <row r="910" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A910" s="8" t="s">
         <v>2825</v>
       </c>
-      <c r="B909" s="22" t="s">
+      <c r="B910" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C909" s="8" t="str">
+      <c r="C910" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_diet:sd</v>
       </c>
-      <c r="D909" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E909" s="8" t="s">
+      <c r="D910" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E910" s="8" t="s">
         <v>2826</v>
       </c>
     </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A910" s="8" t="s">
+    <row r="911" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A911" s="8" t="s">
         <v>2827</v>
       </c>
-      <c r="B910" s="22" t="s">
+      <c r="B911" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C910" s="8" t="str">
+      <c r="C911" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_diet:veg</v>
       </c>
-      <c r="D910" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E910" s="8" t="s">
+      <c r="D911" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E911" s="8" t="s">
         <v>2828</v>
       </c>
-      <c r="F910" s="8" t="s">
+      <c r="F911" s="8" t="s">
         <v>2829</v>
       </c>
     </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A911" s="8" t="s">
+    <row r="912" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A912" s="8" t="s">
         <v>2832</v>
       </c>
-      <c r="B911" s="22" t="s">
+      <c r="B912" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C911" s="8" t="str">
+      <c r="C912" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_diet:hg</v>
       </c>
-      <c r="D911" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E911" s="8" t="s">
+      <c r="D912" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E912" s="8" t="s">
         <v>2830</v>
       </c>
-      <c r="F911" s="8" t="s">
+      <c r="F912" s="8" t="s">
         <v>2831</v>
       </c>
     </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A912" s="8" t="s">
+    <row r="913" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A913" s="8" t="s">
         <v>2835</v>
       </c>
-      <c r="B912" s="8" t="s">
+      <c r="B913" s="8" t="s">
         <v>2820</v>
       </c>
-      <c r="C912" s="8" t="str">
+      <c r="C913" s="8" t="str">
         <f t="shared" si="19"/>
         <v>att_diet:hfd</v>
       </c>
-      <c r="D912" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E912" s="8" t="s">
+      <c r="D913" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E913" s="8" t="s">
         <v>2833</v>
       </c>
-      <c r="F912" s="8" t="s">
+      <c r="F913" s="8" t="s">
         <v>2834</v>
       </c>
     </row>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C73029A-C218-104A-A9F4-7268D847F023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B58F20-8815-B046-B5D7-65042C04D653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10820" yWindow="1040" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">attribute_values_ar!$A$1:$O$365</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10267" uniqueCount="2930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10304" uniqueCount="2953">
   <si>
     <t>tag</t>
   </si>
@@ -8832,6 +8832,75 @@
   </si>
   <si>
     <t>controls</t>
+  </si>
+  <si>
+    <t>att_subcellular_compartment</t>
+  </si>
+  <si>
+    <t>Subceullar Compartment</t>
+  </si>
+  <si>
+    <t>wc</t>
+  </si>
+  <si>
+    <t>Whole cell</t>
+  </si>
+  <si>
+    <t>Complete cell</t>
+  </si>
+  <si>
+    <t>mitochondria</t>
+  </si>
+  <si>
+    <t>membrane</t>
+  </si>
+  <si>
+    <t>Membrane Fraction</t>
+  </si>
+  <si>
+    <t>Membrane fraction (Mitochondria, ER)</t>
+  </si>
+  <si>
+    <t>golgi</t>
+  </si>
+  <si>
+    <t>Golgi</t>
+  </si>
+  <si>
+    <t>Golgi fraction</t>
+  </si>
+  <si>
+    <t>plasmamembrane</t>
+  </si>
+  <si>
+    <t>Plasmamembrane fraction</t>
+  </si>
+  <si>
+    <t>nucleus</t>
+  </si>
+  <si>
+    <t>Nucleus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nucleus </t>
+  </si>
+  <si>
+    <t>cytosol</t>
+  </si>
+  <si>
+    <t>Cytosol</t>
+  </si>
+  <si>
+    <t>Cytosolic fraction</t>
+  </si>
+  <si>
+    <t>Plasma membrane</t>
+  </si>
+  <si>
+    <t>Pure mitochondria enriched fraction</t>
+  </si>
+  <si>
+    <t>Mitochondria</t>
   </si>
 </sst>
 </file>
@@ -9420,7 +9489,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH115"/>
+  <dimension ref="A1:AMH116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -9905,7 +9974,7 @@
         <v>46</v>
       </c>
       <c r="D10">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>19</v>
@@ -9955,7 +10024,7 @@
         <v>49</v>
       </c>
       <c r="D11">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>19</v>
@@ -10955,7 +11024,7 @@
         <v>92</v>
       </c>
       <c r="D31">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>19</v>
@@ -11305,7 +11374,7 @@
         <v>106</v>
       </c>
       <c r="D38">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>19</v>
@@ -11355,7 +11424,7 @@
         <v>2856</v>
       </c>
       <c r="D39">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>19</v>
@@ -12355,7 +12424,7 @@
         <v>151</v>
       </c>
       <c r="D59">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>19</v>
@@ -13688,7 +13757,7 @@
         <v>19</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P85" s="1" t="s">
         <v>19</v>
@@ -15155,7 +15224,7 @@
         <v>2925</v>
       </c>
       <c r="D115">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>21</v>
@@ -15192,6 +15261,56 @@
       </c>
       <c r="P115" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A116" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D116">
+        <v>650</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G116" t="s">
+        <v>47</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P116" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -15217,7 +15336,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ913"/>
+  <dimension ref="A1:AMJ918"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -32398,7 +32517,7 @@
         <v>31</v>
       </c>
       <c r="C818" s="8" t="str">
-        <f t="shared" ref="C818:C881" si="18">B818&amp;":"&amp;A818</f>
+        <f t="shared" ref="C818:C888" si="18">B818&amp;":"&amp;A818</f>
         <v>att_software:metamorpheus</v>
       </c>
       <c r="D818" s="9" t="s">
@@ -32497,1909 +32616,2014 @@
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A823" s="8" t="s">
-        <v>2401</v>
+        <v>2932</v>
       </c>
       <c r="B823" s="8" t="s">
-        <v>238</v>
+        <v>2930</v>
       </c>
       <c r="C823" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_tissue:adipose</v>
-      </c>
-      <c r="D823" s="8" t="s">
-        <v>2401</v>
+        <v>att_subcellular_compartment:wc</v>
+      </c>
+      <c r="D823" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="E823" s="8" t="s">
-        <v>2402</v>
+        <v>2933</v>
       </c>
       <c r="F823" s="8" t="s">
-        <v>2403</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A824" s="8" t="s">
-        <v>2404</v>
+        <v>2936</v>
       </c>
       <c r="B824" s="8" t="s">
-        <v>238</v>
+        <v>2930</v>
       </c>
       <c r="C824" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_tissue:areolar</v>
-      </c>
-      <c r="D824" s="8" t="s">
-        <v>2404</v>
+        <v>att_subcellular_compartment:membrane</v>
+      </c>
+      <c r="D824" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="E824" s="8" t="s">
-        <v>2405</v>
+        <v>2937</v>
       </c>
       <c r="F824" s="8" t="s">
-        <v>2406</v>
+        <v>2938</v>
       </c>
     </row>
     <row r="825" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A825" s="8" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B825" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C825" s="8" t="str">
+        <f t="shared" ref="C825" si="19">B825&amp;":"&amp;A825</f>
+        <v>att_subcellular_compartment:mitochondria</v>
+      </c>
+      <c r="D825" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E825" s="8" t="s">
+        <v>2952</v>
+      </c>
+      <c r="F825" s="8" t="s">
+        <v>2951</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A826" s="8" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B826" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C826" s="8" t="str">
+        <f t="shared" si="18"/>
+        <v>att_subcellular_compartment:golgi</v>
+      </c>
+      <c r="D826" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E826" s="8" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F826" s="8" t="s">
+        <v>2941</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A827" s="8" t="s">
+        <v>2942</v>
+      </c>
+      <c r="B827" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C827" s="8" t="str">
+        <f t="shared" ref="C827:C829" si="20">B827&amp;":"&amp;A827</f>
+        <v>att_subcellular_compartment:plasmamembrane</v>
+      </c>
+      <c r="D827" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E827" s="8" t="s">
+        <v>2950</v>
+      </c>
+      <c r="F827" s="8" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A828" s="8" t="s">
+        <v>2944</v>
+      </c>
+      <c r="B828" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C828" s="8" t="str">
+        <f t="shared" si="20"/>
+        <v>att_subcellular_compartment:nucleus</v>
+      </c>
+      <c r="D828" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E828" s="8" t="s">
+        <v>2945</v>
+      </c>
+      <c r="F828" s="8" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="829" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A829" s="8" t="s">
+        <v>2947</v>
+      </c>
+      <c r="B829" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C829" s="8" t="str">
+        <f t="shared" si="20"/>
+        <v>att_subcellular_compartment:cytosol</v>
+      </c>
+      <c r="D829" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E829" s="8" t="s">
+        <v>2948</v>
+      </c>
+      <c r="F829" s="8" t="s">
+        <v>2949</v>
+      </c>
+    </row>
+    <row r="830" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A830" s="8" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B830" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C830" s="8" t="str">
+        <f t="shared" si="18"/>
+        <v>att_tissue:adipose</v>
+      </c>
+      <c r="D830" s="8" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E830" s="8" t="s">
+        <v>2402</v>
+      </c>
+      <c r="F830" s="8" t="s">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="831" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A831" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B831" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="C831" s="8" t="str">
+        <f t="shared" si="18"/>
+        <v>att_tissue:areolar</v>
+      </c>
+      <c r="D831" s="8" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E831" s="8" t="s">
+        <v>2405</v>
+      </c>
+      <c r="F831" s="8" t="s">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="832" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A832" s="8" t="s">
         <v>2407</v>
       </c>
-      <c r="B825" s="8" t="s">
+      <c r="B832" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C825" s="8" t="str">
+      <c r="C832" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:blood</v>
       </c>
-      <c r="D825" s="8" t="s">
+      <c r="D832" s="8" t="s">
         <v>2407</v>
       </c>
-      <c r="E825" s="8" t="s">
+      <c r="E832" s="8" t="s">
         <v>2408</v>
       </c>
-      <c r="F825" s="8" t="s">
+      <c r="F832" s="8" t="s">
         <v>2408</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A826" s="8" t="s">
+    <row r="833" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A833" s="8" t="s">
         <v>2409</v>
       </c>
-      <c r="B826" s="8" t="s">
+      <c r="B833" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C826" s="8" t="str">
+      <c r="C833" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:connective</v>
       </c>
-      <c r="D826" s="8" t="s">
+      <c r="D833" s="8" t="s">
         <v>2409</v>
       </c>
-      <c r="E826" s="8" t="s">
+      <c r="E833" s="8" t="s">
         <v>2410</v>
       </c>
-      <c r="F826" s="8" t="s">
+      <c r="F833" s="8" t="s">
         <v>2411</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A827" s="8" t="s">
+    <row r="834" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A834" s="8" t="s">
         <v>2412</v>
       </c>
-      <c r="B827" s="8" t="s">
+      <c r="B834" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C827" s="8" t="str">
+      <c r="C834" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:dermis</v>
       </c>
-      <c r="D827" s="8" t="s">
+      <c r="D834" s="8" t="s">
         <v>2412</v>
       </c>
-      <c r="E827" s="8" t="s">
+      <c r="E834" s="8" t="s">
         <v>2413</v>
       </c>
-      <c r="F827" s="8" t="s">
+      <c r="F834" s="8" t="s">
         <v>2413</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A828" s="8" t="s">
+    <row r="835" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A835" s="8" t="s">
         <v>2414</v>
       </c>
-      <c r="B828" s="8" t="s">
+      <c r="B835" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C828" s="8" t="str">
+      <c r="C835" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:epidermis</v>
       </c>
-      <c r="D828" s="8" t="s">
+      <c r="D835" s="8" t="s">
         <v>2414</v>
       </c>
-      <c r="E828" s="8" t="s">
+      <c r="E835" s="8" t="s">
         <v>2415</v>
       </c>
-      <c r="F828" s="8" t="s">
+      <c r="F835" s="8" t="s">
         <v>2415</v>
       </c>
     </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A829" s="8" t="s">
+    <row r="836" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A836" s="8" t="s">
         <v>2416</v>
       </c>
-      <c r="B829" s="8" t="s">
+      <c r="B836" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C829" s="8" t="str">
+      <c r="C836" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:epithelial</v>
       </c>
-      <c r="D829" s="8" t="s">
+      <c r="D836" s="8" t="s">
         <v>2416</v>
       </c>
-      <c r="E829" s="8" t="s">
+      <c r="E836" s="8" t="s">
         <v>2417</v>
       </c>
-      <c r="F829" s="8" t="s">
+      <c r="F836" s="8" t="s">
         <v>2418</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A830" s="8" t="s">
+    <row r="837" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A837" s="8" t="s">
         <v>2419</v>
       </c>
-      <c r="B830" s="8" t="s">
+      <c r="B837" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C830" s="8" t="str">
+      <c r="C837" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:hypodermis</v>
       </c>
-      <c r="D830" s="8" t="s">
+      <c r="D837" s="8" t="s">
         <v>2419</v>
       </c>
-      <c r="E830" s="8" t="s">
+      <c r="E837" s="8" t="s">
         <v>2420</v>
       </c>
-      <c r="F830" s="8" t="s">
+      <c r="F837" s="8" t="s">
         <v>2420</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A831" s="8" t="s">
+    <row r="838" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A838" s="8" t="s">
         <v>2421</v>
       </c>
-      <c r="B831" s="8" t="s">
+      <c r="B838" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C831" s="8" t="str">
+      <c r="C838" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:muscle</v>
       </c>
-      <c r="D831" s="8" t="s">
+      <c r="D838" s="8" t="s">
         <v>2421</v>
       </c>
-      <c r="E831" s="8" t="s">
+      <c r="E838" s="8" t="s">
         <v>2819</v>
       </c>
-      <c r="F831" s="8" t="s">
+      <c r="F838" s="8" t="s">
         <v>2422</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A832" s="8" t="s">
+    <row r="839" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A839" s="8" t="s">
         <v>2423</v>
       </c>
-      <c r="B832" s="8" t="s">
+      <c r="B839" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C832" s="8" t="str">
+      <c r="C839" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:nervous</v>
       </c>
-      <c r="D832" s="8" t="s">
+      <c r="D839" s="8" t="s">
         <v>2423</v>
       </c>
-      <c r="E832" s="8" t="s">
+      <c r="E839" s="8" t="s">
         <v>2242</v>
       </c>
-      <c r="F832" s="8" t="s">
+      <c r="F839" s="8" t="s">
         <v>2424</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A833" s="8" t="s">
+    <row r="840" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A840" s="8" t="s">
         <v>2425</v>
       </c>
-      <c r="B833" s="8" t="s">
+      <c r="B840" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C833" s="8" t="str">
+      <c r="C840" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:reticular</v>
       </c>
-      <c r="D833" s="8" t="s">
+      <c r="D840" s="8" t="s">
         <v>2425</v>
       </c>
-      <c r="E833" s="8" t="s">
+      <c r="E840" s="8" t="s">
         <v>2426</v>
       </c>
-      <c r="F833" s="8" t="s">
+      <c r="F840" s="8" t="s">
         <v>2427</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A834" s="8" t="s">
+    <row r="841" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A841" s="8" t="s">
         <v>2428</v>
       </c>
-      <c r="B834" s="8" t="s">
+      <c r="B841" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C834" s="8" t="str">
+      <c r="C841" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tissue:stromal</v>
       </c>
-      <c r="D834" s="8" t="s">
+      <c r="D841" s="8" t="s">
         <v>2428</v>
       </c>
-      <c r="E834" s="8" t="s">
+      <c r="E841" s="8" t="s">
         <v>2429</v>
       </c>
-      <c r="F834" s="8" t="s">
+      <c r="F841" s="8" t="s">
         <v>2430</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A835" s="8" t="s">
+    <row r="842" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A842" s="8" t="s">
         <v>2431</v>
       </c>
-      <c r="B835" s="8" t="s">
+      <c r="B842" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C835" s="8" t="str">
+      <c r="C842" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_126</v>
       </c>
-      <c r="D835" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E835" s="8">
+      <c r="D842" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E842" s="8">
         <v>126</v>
       </c>
-      <c r="F835" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A836" s="8" t="s">
+      <c r="F842" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="843" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A843" s="8" t="s">
         <v>2432</v>
       </c>
-      <c r="B836" s="8" t="s">
+      <c r="B843" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C836" s="8" t="str">
+      <c r="C843" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_127C</v>
       </c>
-      <c r="D836" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E836" s="8" t="s">
+      <c r="D843" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E843" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F836" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A837" s="8" t="s">
+      <c r="F843" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="844" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A844" s="8" t="s">
         <v>2434</v>
       </c>
-      <c r="B837" s="8" t="s">
+      <c r="B844" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C837" s="8" t="str">
+      <c r="C844" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_127N</v>
       </c>
-      <c r="D837" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E837" s="8" t="s">
+      <c r="D844" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E844" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F837" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A838" s="8" t="s">
+      <c r="F844" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="845" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A845" s="8" t="s">
         <v>2436</v>
       </c>
-      <c r="B838" s="8" t="s">
+      <c r="B845" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C838" s="8" t="str">
+      <c r="C845" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_128C</v>
       </c>
-      <c r="D838" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E838" s="8" t="s">
+      <c r="D845" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E845" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F838" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A839" s="8" t="s">
+      <c r="F845" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="846" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A846" s="8" t="s">
         <v>2438</v>
       </c>
-      <c r="B839" s="8" t="s">
+      <c r="B846" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C839" s="8" t="str">
+      <c r="C846" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_128N</v>
       </c>
-      <c r="D839" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E839" s="8" t="s">
+      <c r="D846" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E846" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F839" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A840" s="8" t="s">
+      <c r="F846" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="847" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A847" s="8" t="s">
         <v>2440</v>
       </c>
-      <c r="B840" s="8" t="s">
+      <c r="B847" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C840" s="8" t="str">
+      <c r="C847" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_129C</v>
       </c>
-      <c r="D840" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E840" s="8" t="s">
+      <c r="D847" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E847" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F840" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A841" s="8" t="s">
+      <c r="F847" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="848" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A848" s="8" t="s">
         <v>2442</v>
       </c>
-      <c r="B841" s="8" t="s">
+      <c r="B848" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C841" s="8" t="str">
+      <c r="C848" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_129N</v>
       </c>
-      <c r="D841" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E841" s="8" t="s">
+      <c r="D848" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E848" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F841" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A842" s="8" t="s">
+      <c r="F848" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="849" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A849" s="8" t="s">
         <v>2444</v>
       </c>
-      <c r="B842" s="8" t="s">
+      <c r="B849" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C842" s="8" t="str">
+      <c r="C849" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_130C</v>
       </c>
-      <c r="D842" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E842" s="8" t="s">
+      <c r="D849" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E849" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F842" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A843" s="8" t="s">
+      <c r="F849" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="850" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A850" s="8" t="s">
         <v>2446</v>
       </c>
-      <c r="B843" s="8" t="s">
+      <c r="B850" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C843" s="8" t="str">
+      <c r="C850" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_130N</v>
       </c>
-      <c r="D843" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E843" s="8" t="s">
+      <c r="D850" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E850" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F843" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A844" s="8" t="s">
+      <c r="F850" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="851" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A851" s="8" t="s">
         <v>2448</v>
       </c>
-      <c r="B844" s="8" t="s">
+      <c r="B851" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C844" s="8" t="str">
+      <c r="C851" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt10_131</v>
       </c>
-      <c r="D844" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E844" s="8">
+      <c r="D851" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E851" s="8">
         <v>131</v>
       </c>
-      <c r="F844" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A845" s="8" t="s">
+      <c r="F851" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="852" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A852" s="8" t="s">
         <v>2449</v>
       </c>
-      <c r="B845" s="8" t="s">
+      <c r="B852" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C845" s="8" t="str">
+      <c r="C852" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_126</v>
       </c>
-      <c r="D845" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E845" s="8">
+      <c r="D852" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E852" s="8">
         <v>126</v>
       </c>
-      <c r="F845" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A846" s="8" t="s">
+      <c r="F852" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A853" s="8" t="s">
         <v>2450</v>
       </c>
-      <c r="B846" s="8" t="s">
+      <c r="B853" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C846" s="8" t="str">
+      <c r="C853" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_127C</v>
       </c>
-      <c r="D846" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E846" s="8" t="s">
+      <c r="D853" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E853" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F846" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A847" s="8" t="s">
+      <c r="F853" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A854" s="8" t="s">
         <v>2451</v>
       </c>
-      <c r="B847" s="8" t="s">
+      <c r="B854" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C847" s="8" t="str">
+      <c r="C854" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_127N</v>
       </c>
-      <c r="D847" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E847" s="8" t="s">
+      <c r="D854" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E854" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F847" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A848" s="8" t="s">
+      <c r="F854" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A855" s="8" t="s">
         <v>2452</v>
       </c>
-      <c r="B848" s="8" t="s">
+      <c r="B855" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C848" s="8" t="str">
+      <c r="C855" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_128C</v>
       </c>
-      <c r="D848" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E848" s="8" t="s">
+      <c r="D855" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E855" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F848" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A849" s="8" t="s">
+      <c r="F855" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A856" s="8" t="s">
         <v>2453</v>
       </c>
-      <c r="B849" s="8" t="s">
+      <c r="B856" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C849" s="8" t="str">
+      <c r="C856" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_128N</v>
       </c>
-      <c r="D849" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E849" s="8" t="s">
+      <c r="D856" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E856" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F849" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A850" s="8" t="s">
+      <c r="F856" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A857" s="8" t="s">
         <v>2454</v>
       </c>
-      <c r="B850" s="8" t="s">
+      <c r="B857" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C850" s="8" t="str">
+      <c r="C857" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_129C</v>
       </c>
-      <c r="D850" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E850" s="8" t="s">
+      <c r="D857" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E857" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F850" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A851" s="8" t="s">
+      <c r="F857" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A858" s="8" t="s">
         <v>2455</v>
       </c>
-      <c r="B851" s="8" t="s">
+      <c r="B858" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C851" s="8" t="str">
+      <c r="C858" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_129N</v>
       </c>
-      <c r="D851" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E851" s="8" t="s">
+      <c r="D858" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E858" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F851" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A852" s="8" t="s">
+      <c r="F858" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A859" s="8" t="s">
         <v>2456</v>
       </c>
-      <c r="B852" s="8" t="s">
+      <c r="B859" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C852" s="8" t="str">
+      <c r="C859" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_130C</v>
       </c>
-      <c r="D852" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E852" s="8" t="s">
+      <c r="D859" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E859" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F852" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A853" s="8" t="s">
+      <c r="F859" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A860" s="8" t="s">
         <v>2457</v>
       </c>
-      <c r="B853" s="8" t="s">
+      <c r="B860" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C853" s="8" t="str">
+      <c r="C860" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_130N</v>
       </c>
-      <c r="D853" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E853" s="8" t="s">
+      <c r="D860" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E860" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F853" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A854" s="8" t="s">
+      <c r="F860" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A861" s="8" t="s">
         <v>2458</v>
       </c>
-      <c r="B854" s="8" t="s">
+      <c r="B861" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C854" s="8" t="str">
+      <c r="C861" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_131C</v>
       </c>
-      <c r="D854" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E854" s="8" t="s">
+      <c r="D861" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E861" s="8" t="s">
         <v>2459</v>
       </c>
-      <c r="F854" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A855" s="8" t="s">
+      <c r="F861" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A862" s="8" t="s">
         <v>2460</v>
       </c>
-      <c r="B855" s="8" t="s">
+      <c r="B862" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C855" s="8" t="str">
+      <c r="C862" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt11_131N</v>
       </c>
-      <c r="D855" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E855" s="8" t="s">
+      <c r="D862" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E862" s="8" t="s">
         <v>2461</v>
       </c>
-      <c r="F855" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A856" s="8" t="s">
+      <c r="F862" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A863" s="8" t="s">
         <v>2462</v>
       </c>
-      <c r="B856" s="8" t="s">
+      <c r="B863" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C856" s="8" t="str">
+      <c r="C863" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_126</v>
       </c>
-      <c r="D856" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E856" s="8">
+      <c r="D863" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E863" s="8">
         <v>126</v>
       </c>
-      <c r="F856" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A857" s="8" t="s">
+      <c r="F863" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A864" s="8" t="s">
         <v>2463</v>
       </c>
-      <c r="B857" s="8" t="s">
+      <c r="B864" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C857" s="8" t="str">
+      <c r="C864" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_127C</v>
       </c>
-      <c r="D857" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E857" s="8" t="s">
+      <c r="D864" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E864" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F857" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A858" s="8" t="s">
+      <c r="F864" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A865" s="8" t="s">
         <v>2464</v>
       </c>
-      <c r="B858" s="8" t="s">
+      <c r="B865" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C858" s="8" t="str">
+      <c r="C865" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_127N</v>
       </c>
-      <c r="D858" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E858" s="8" t="s">
+      <c r="D865" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E865" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F858" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A859" s="8" t="s">
+      <c r="F865" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A866" s="8" t="s">
         <v>2465</v>
       </c>
-      <c r="B859" s="8" t="s">
+      <c r="B866" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C859" s="8" t="str">
+      <c r="C866" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_128C</v>
       </c>
-      <c r="D859" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E859" s="8" t="s">
+      <c r="D866" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E866" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F859" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A860" s="8" t="s">
+      <c r="F866" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A867" s="8" t="s">
         <v>2466</v>
       </c>
-      <c r="B860" s="8" t="s">
+      <c r="B867" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C860" s="8" t="str">
+      <c r="C867" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_128N</v>
       </c>
-      <c r="D860" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E860" s="8" t="s">
+      <c r="D867" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E867" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F860" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A861" s="8" t="s">
+      <c r="F867" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A868" s="8" t="s">
         <v>2467</v>
       </c>
-      <c r="B861" s="8" t="s">
+      <c r="B868" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C861" s="8" t="str">
+      <c r="C868" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_129C</v>
       </c>
-      <c r="D861" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E861" s="8" t="s">
+      <c r="D868" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E868" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F861" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A862" s="8" t="s">
+      <c r="F868" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A869" s="8" t="s">
         <v>2468</v>
       </c>
-      <c r="B862" s="8" t="s">
+      <c r="B869" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C862" s="8" t="str">
+      <c r="C869" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_129N</v>
       </c>
-      <c r="D862" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E862" s="8" t="s">
+      <c r="D869" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E869" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F862" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A863" s="8" t="s">
+      <c r="F869" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A870" s="8" t="s">
         <v>2469</v>
       </c>
-      <c r="B863" s="8" t="s">
+      <c r="B870" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C863" s="8" t="str">
+      <c r="C870" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_130C</v>
       </c>
-      <c r="D863" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E863" s="8" t="s">
+      <c r="D870" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E870" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F863" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A864" s="8" t="s">
+      <c r="F870" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A871" s="8" t="s">
         <v>2470</v>
       </c>
-      <c r="B864" s="8" t="s">
+      <c r="B871" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C864" s="8" t="str">
+      <c r="C871" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_130N</v>
       </c>
-      <c r="D864" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E864" s="8" t="s">
+      <c r="D871" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E871" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F864" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A865" s="8" t="s">
+      <c r="F871" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A872" s="8" t="s">
         <v>2471</v>
       </c>
-      <c r="B865" s="8" t="s">
+      <c r="B872" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C865" s="8" t="str">
+      <c r="C872" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_131C</v>
       </c>
-      <c r="D865" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E865" s="8" t="s">
+      <c r="D872" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E872" s="8" t="s">
         <v>2459</v>
       </c>
-      <c r="F865" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A866" s="8" t="s">
+      <c r="F872" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A873" s="8" t="s">
         <v>2472</v>
       </c>
-      <c r="B866" s="8" t="s">
+      <c r="B873" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C866" s="8" t="str">
+      <c r="C873" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_131N</v>
       </c>
-      <c r="D866" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E866" s="8" t="s">
+      <c r="D873" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E873" s="8" t="s">
         <v>2461</v>
       </c>
-      <c r="F866" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A867" s="8" t="s">
+      <c r="F873" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A874" s="8" t="s">
         <v>2473</v>
       </c>
-      <c r="B867" s="8" t="s">
+      <c r="B874" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C867" s="8" t="str">
+      <c r="C874" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_132C</v>
       </c>
-      <c r="D867" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E867" s="8" t="s">
+      <c r="D874" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E874" s="8" t="s">
         <v>2474</v>
       </c>
-      <c r="F867" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A868" s="8" t="s">
+      <c r="F874" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A875" s="8" t="s">
         <v>2475</v>
       </c>
-      <c r="B868" s="8" t="s">
+      <c r="B875" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C868" s="8" t="str">
+      <c r="C875" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_132N</v>
       </c>
-      <c r="D868" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E868" s="8" t="s">
+      <c r="D875" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E875" s="8" t="s">
         <v>2476</v>
       </c>
-      <c r="F868" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A869" s="8" t="s">
+      <c r="F875" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A876" s="8" t="s">
         <v>2477</v>
       </c>
-      <c r="B869" s="8" t="s">
+      <c r="B876" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C869" s="8" t="str">
+      <c r="C876" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_133C</v>
       </c>
-      <c r="D869" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E869" s="8" t="s">
+      <c r="D876" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E876" s="8" t="s">
         <v>2478</v>
       </c>
-      <c r="F869" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A870" s="8" t="s">
+      <c r="F876" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A877" s="8" t="s">
         <v>2479</v>
       </c>
-      <c r="B870" s="8" t="s">
+      <c r="B877" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C870" s="8" t="str">
+      <c r="C877" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_133N</v>
       </c>
-      <c r="D870" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E870" s="8" t="s">
+      <c r="D877" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E877" s="8" t="s">
         <v>2480</v>
       </c>
-      <c r="F870" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A871" s="8" t="s">
+      <c r="F877" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A878" s="8" t="s">
         <v>2481</v>
       </c>
-      <c r="B871" s="8" t="s">
+      <c r="B878" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C871" s="8" t="str">
+      <c r="C878" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_134C</v>
       </c>
-      <c r="D871" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E871" s="8" t="s">
+      <c r="D878" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E878" s="8" t="s">
         <v>2482</v>
       </c>
-      <c r="F871" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A872" s="8" t="s">
+      <c r="F878" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A879" s="8" t="s">
         <v>2483</v>
       </c>
-      <c r="B872" s="8" t="s">
+      <c r="B879" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C872" s="8" t="str">
+      <c r="C879" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_134N</v>
       </c>
-      <c r="D872" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E872" s="8" t="s">
+      <c r="D879" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E879" s="8" t="s">
         <v>2484</v>
       </c>
-      <c r="F872" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A873" s="8" t="s">
+      <c r="F879" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A880" s="8" t="s">
         <v>2485</v>
       </c>
-      <c r="B873" s="8" t="s">
+      <c r="B880" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C873" s="8" t="str">
+      <c r="C880" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt18_135N</v>
       </c>
-      <c r="D873" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E873" s="8" t="s">
+      <c r="D880" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E880" s="8" t="s">
         <v>2486</v>
       </c>
-      <c r="F873" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A874" s="8" t="s">
+      <c r="F880" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="881" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A881" s="8" t="s">
         <v>2487</v>
       </c>
-      <c r="B874" s="8" t="s">
+      <c r="B881" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C874" s="8" t="str">
+      <c r="C881" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_126</v>
       </c>
-      <c r="D874" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E874" s="8">
+      <c r="D881" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E881" s="8">
         <v>126</v>
       </c>
-      <c r="F874" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A875" s="8" t="s">
+      <c r="F881" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="882" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A882" s="8" t="s">
         <v>2488</v>
       </c>
-      <c r="B875" s="8" t="s">
+      <c r="B882" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C875" s="8" t="str">
+      <c r="C882" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_127</v>
       </c>
-      <c r="D875" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E875" s="8">
+      <c r="D882" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E882" s="8">
         <v>127</v>
       </c>
-      <c r="F875" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A876" s="8" t="s">
+      <c r="F882" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A883" s="8" t="s">
         <v>2489</v>
       </c>
-      <c r="B876" s="8" t="s">
+      <c r="B883" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C876" s="8" t="str">
+      <c r="C883" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_128</v>
       </c>
-      <c r="D876" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E876" s="8">
+      <c r="D883" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E883" s="8">
         <v>128</v>
       </c>
-      <c r="F876" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A877" s="8" t="s">
+      <c r="F883" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A884" s="8" t="s">
         <v>2490</v>
       </c>
-      <c r="B877" s="8" t="s">
+      <c r="B884" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C877" s="8" t="str">
+      <c r="C884" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_129</v>
       </c>
-      <c r="D877" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E877" s="8">
+      <c r="D884" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E884" s="8">
         <v>129</v>
       </c>
-      <c r="F877" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A878" s="8" t="s">
+      <c r="F884" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A885" s="8" t="s">
         <v>2491</v>
       </c>
-      <c r="B878" s="8" t="s">
+      <c r="B885" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C878" s="8" t="str">
+      <c r="C885" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_130</v>
       </c>
-      <c r="D878" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E878" s="8">
+      <c r="D885" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E885" s="8">
         <v>130</v>
       </c>
-      <c r="F878" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A879" s="8" t="s">
+      <c r="F885" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A886" s="8" t="s">
         <v>2492</v>
       </c>
-      <c r="B879" s="8" t="s">
+      <c r="B886" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C879" s="8" t="str">
+      <c r="C886" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_tmt_channel:tmt6_131</v>
       </c>
-      <c r="D879" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E879" s="8">
+      <c r="D886" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E886" s="8">
         <v>131</v>
       </c>
-      <c r="F879" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A880" s="8" t="s">
+      <c r="F886" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A887" s="8" t="s">
         <v>2493</v>
       </c>
-      <c r="B880" s="8" t="s">
+      <c r="B887" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C880" s="8" t="str">
+      <c r="C887" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_user_institute:biochem</v>
       </c>
-      <c r="D880" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E880" s="8" t="s">
+      <c r="D887" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E887" s="8" t="s">
         <v>2494</v>
       </c>
-      <c r="F880" s="8" t="s">
+      <c r="F887" s="8" t="s">
         <v>2495</v>
       </c>
     </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A881" s="8" t="s">
+    <row r="888" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A888" s="8" t="s">
         <v>2496</v>
       </c>
-      <c r="B881" s="8" t="s">
+      <c r="B888" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C881" s="8" t="str">
+      <c r="C888" s="8" t="str">
         <f t="shared" si="18"/>
         <v>att_user_institute:cecad</v>
       </c>
-      <c r="D881" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E881" s="8" t="s">
+      <c r="D888" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E888" s="8" t="s">
         <v>2497</v>
       </c>
-      <c r="F881" s="8" t="s">
+      <c r="F888" s="8" t="s">
         <v>2498</v>
-      </c>
-    </row>
-    <row r="882" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A882" s="8" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B882" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="C882" s="8" t="str">
-        <f t="shared" ref="C882:C913" si="19">B882&amp;":"&amp;A882</f>
-        <v>att_user_institute:mpiage</v>
-      </c>
-      <c r="D882" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E882" s="8" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F882" s="8" t="s">
-        <v>2501</v>
-      </c>
-    </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A883" s="8" t="s">
-        <v>2502</v>
-      </c>
-      <c r="B883" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="C883" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_institute:mpimetab</v>
-      </c>
-      <c r="D883" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E883" s="8" t="s">
-        <v>2503</v>
-      </c>
-      <c r="F883" s="8" t="s">
-        <v>2504</v>
-      </c>
-    </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A884" s="8" t="s">
-        <v>2505</v>
-      </c>
-      <c r="B884" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C884" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:mitoprotea</v>
-      </c>
-      <c r="D884" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E884" s="8" t="s">
-        <v>2506</v>
-      </c>
-      <c r="F884" s="8" t="s">
-        <v>2507</v>
-      </c>
-    </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A885" s="8" t="s">
-        <v>2508</v>
-      </c>
-      <c r="B885" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="C885" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:molageing</v>
-      </c>
-      <c r="D885" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E885" s="8" t="s">
-        <v>2509</v>
-      </c>
-      <c r="F885" s="8" t="s">
-        <v>2510</v>
-      </c>
-    </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A886" s="8" t="s">
-        <v>2493</v>
-      </c>
-      <c r="B886" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="C886" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_institute:biochem</v>
-      </c>
-      <c r="D886" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E886" s="8" t="s">
-        <v>2494</v>
-      </c>
-      <c r="F886" s="8" t="s">
-        <v>2495</v>
-      </c>
-    </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A887" s="8" t="s">
-        <v>2496</v>
-      </c>
-      <c r="B887" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="C887" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_institute:cecad</v>
-      </c>
-      <c r="D887" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E887" s="8" t="s">
-        <v>2497</v>
-      </c>
-      <c r="F887" s="8" t="s">
-        <v>2498</v>
-      </c>
-    </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A888" s="8" t="s">
-        <v>2499</v>
-      </c>
-      <c r="B888" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="C888" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_institute:mpiage</v>
-      </c>
-      <c r="D888" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E888" s="8" t="s">
-        <v>2500</v>
-      </c>
-      <c r="F888" s="8" t="s">
-        <v>2501</v>
       </c>
     </row>
     <row r="889" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A889" s="8" t="s">
-        <v>2502</v>
+        <v>2499</v>
       </c>
       <c r="B889" s="8" t="s">
         <v>248</v>
       </c>
       <c r="C889" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_institute:mpimetab</v>
-      </c>
-      <c r="D889" s="8" t="s">
+        <f t="shared" ref="C889:C918" si="21">B889&amp;":"&amp;A889</f>
+        <v>att_user_institute:mpiage</v>
+      </c>
+      <c r="D889" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E889" s="8" t="s">
-        <v>2503</v>
+        <v>2500</v>
       </c>
       <c r="F889" s="8" t="s">
-        <v>2504</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A890" s="8" t="s">
-        <v>2505</v>
+        <v>2502</v>
       </c>
       <c r="B890" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C890" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:mitoprotea</v>
-      </c>
-      <c r="D890" s="8" t="s">
+        <f t="shared" si="21"/>
+        <v>att_user_institute:mpimetab</v>
+      </c>
+      <c r="D890" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E890" s="8" t="s">
-        <v>2506</v>
+        <v>2503</v>
       </c>
       <c r="F890" s="8" t="s">
-        <v>2507</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="891" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A891" s="8" t="s">
-        <v>2508</v>
+        <v>2493</v>
       </c>
       <c r="B891" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C891" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:molageing</v>
+        <f t="shared" si="21"/>
+        <v>att_user_institute:biochem</v>
       </c>
       <c r="D891" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E891" s="8" t="s">
-        <v>2509</v>
+        <v>2494</v>
       </c>
       <c r="F891" s="8" t="s">
-        <v>2510</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="892" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A892" s="8" t="s">
-        <v>2874</v>
+        <v>2496</v>
       </c>
       <c r="B892" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C892" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:ProtFa</v>
+        <f t="shared" si="21"/>
+        <v>att_user_institute:cecad</v>
       </c>
       <c r="D892" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E892" s="8" t="s">
-        <v>2875</v>
+        <v>2497</v>
       </c>
       <c r="F892" s="8" t="s">
-        <v>2876</v>
+        <v>2498</v>
       </c>
     </row>
     <row r="893" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A893" s="8" t="s">
-        <v>2877</v>
+        <v>2499</v>
       </c>
       <c r="B893" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C893" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:frezza</v>
+        <f t="shared" si="21"/>
+        <v>att_user_institute:mpiage</v>
       </c>
       <c r="D893" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E893" s="8" t="s">
-        <v>2878</v>
+        <v>2500</v>
       </c>
       <c r="F893" s="8" t="s">
-        <v>2879</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A894" s="8" t="s">
-        <v>2880</v>
+        <v>2502</v>
       </c>
       <c r="B894" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C894" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:krueger</v>
+        <f t="shared" si="21"/>
+        <v>att_user_institute:mpimetab</v>
       </c>
       <c r="D894" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E894" s="8" t="s">
-        <v>2881</v>
+        <v>2503</v>
       </c>
       <c r="F894" s="8" t="s">
-        <v>2882</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="895" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A895" s="8" t="s">
-        <v>2883</v>
+        <v>2505</v>
       </c>
       <c r="B895" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C895" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:rugarli</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:mitoprotea</v>
       </c>
       <c r="D895" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E895" s="8" t="s">
-        <v>2884</v>
+        <v>2506</v>
       </c>
       <c r="F895" s="8" t="s">
-        <v>2882</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A896" s="8" t="s">
-        <v>2885</v>
+        <v>2508</v>
       </c>
       <c r="B896" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C896" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:trifunovic</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:molageing</v>
       </c>
       <c r="D896" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E896" s="8" t="s">
-        <v>2886</v>
+        <v>2509</v>
       </c>
       <c r="F896" s="8" t="s">
-        <v>2887</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="897" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A897" s="8" t="s">
-        <v>2888</v>
+        <v>2874</v>
       </c>
       <c r="B897" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C897" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:niessen</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:ProtFa</v>
       </c>
       <c r="D897" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E897" s="8" t="s">
-        <v>2889</v>
+        <v>2875</v>
       </c>
       <c r="F897" s="8" t="s">
-        <v>2497</v>
+        <v>2876</v>
       </c>
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A898" s="8" t="s">
-        <v>2890</v>
+        <v>2877</v>
       </c>
       <c r="B898" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C898" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:gloeckner</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:frezza</v>
       </c>
       <c r="D898" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E898" s="8" t="s">
-        <v>2891</v>
+        <v>2878</v>
       </c>
       <c r="F898" s="8" t="s">
-        <v>2892</v>
+        <v>2879</v>
       </c>
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A899" s="8" t="s">
-        <v>2893</v>
+        <v>2880</v>
       </c>
       <c r="B899" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C899" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:bazzi</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:krueger</v>
       </c>
       <c r="D899" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E899" s="8" t="s">
-        <v>2894</v>
+        <v>2881</v>
       </c>
       <c r="F899" s="8" t="s">
-        <v>2895</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="900" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A900" s="8" t="s">
-        <v>2896</v>
+        <v>2883</v>
       </c>
       <c r="B900" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C900" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:hallek</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:rugarli</v>
       </c>
       <c r="D900" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E900" s="8" t="s">
-        <v>2897</v>
+        <v>2884</v>
       </c>
       <c r="F900" s="8" t="s">
-        <v>2898</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="901" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A901" s="8" t="s">
-        <v>2899</v>
+        <v>2885</v>
       </c>
       <c r="B901" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C901" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:benzing</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:trifunovic</v>
       </c>
       <c r="D901" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E901" s="8" t="s">
-        <v>2900</v>
+        <v>2886</v>
       </c>
       <c r="F901" s="8" t="s">
-        <v>2901</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="902" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A902" s="8" t="s">
-        <v>2902</v>
+        <v>2888</v>
       </c>
       <c r="B902" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C902" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:hennies</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:niessen</v>
       </c>
       <c r="D902" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E902" s="8" t="s">
-        <v>2903</v>
+        <v>2889</v>
       </c>
       <c r="F902" s="8" t="s">
-        <v>2904</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A903" s="8" t="s">
-        <v>2905</v>
+        <v>2890</v>
       </c>
       <c r="B903" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C903" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:vonkarstedt</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:gloeckner</v>
       </c>
       <c r="D903" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E903" s="8" t="s">
-        <v>2906</v>
+        <v>2891</v>
       </c>
       <c r="F903" s="8" t="s">
-        <v>2907</v>
+        <v>2892</v>
       </c>
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A904" s="8" t="s">
-        <v>2908</v>
+        <v>2893</v>
       </c>
       <c r="B904" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C904" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:laessig</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:bazzi</v>
       </c>
       <c r="D904" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E904" s="8" t="s">
-        <v>2909</v>
+        <v>2894</v>
       </c>
       <c r="F904" s="8" t="s">
-        <v>2910</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A905" s="8" t="s">
-        <v>2911</v>
+        <v>2896</v>
       </c>
       <c r="B905" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C905" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:hoppe</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:hallek</v>
       </c>
       <c r="D905" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E905" s="8" t="s">
-        <v>2912</v>
+        <v>2897</v>
       </c>
       <c r="F905" s="8" t="s">
-        <v>2913</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="906" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A906" s="8" t="s">
-        <v>2914</v>
+        <v>2899</v>
       </c>
       <c r="B906" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C906" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:garcia</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:benzing</v>
       </c>
       <c r="D906" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E906" s="8" t="s">
-        <v>2915</v>
+        <v>2900</v>
       </c>
       <c r="F906" s="8" t="s">
-        <v>2913</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="907" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A907" s="8" t="s">
-        <v>2916</v>
+        <v>2902</v>
       </c>
       <c r="B907" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C907" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:khaskar</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:hennies</v>
       </c>
       <c r="D907" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E907" s="8" t="s">
-        <v>2917</v>
+        <v>2903</v>
       </c>
       <c r="F907" s="8" t="s">
-        <v>2918</v>
+        <v>2904</v>
       </c>
     </row>
     <row r="908" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A908" s="8" t="s">
-        <v>2919</v>
+        <v>2905</v>
       </c>
       <c r="B908" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C908" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_user_research_group:krieg</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:vonkarstedt</v>
       </c>
       <c r="D908" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E908" s="8" t="s">
-        <v>2920</v>
+        <v>2906</v>
       </c>
       <c r="F908" s="8" t="s">
-        <v>2921</v>
+        <v>2907</v>
       </c>
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A909" s="8" t="s">
-        <v>2824</v>
-      </c>
-      <c r="B909" s="22" t="s">
-        <v>2820</v>
+        <v>2908</v>
+      </c>
+      <c r="B909" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="C909" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_diet:wd</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:laessig</v>
       </c>
       <c r="D909" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E909" s="8" t="s">
-        <v>2823</v>
+        <v>2909</v>
       </c>
       <c r="F909" s="8" t="s">
-        <v>2822</v>
+        <v>2910</v>
       </c>
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A910" s="8" t="s">
-        <v>2825</v>
-      </c>
-      <c r="B910" s="22" t="s">
-        <v>2820</v>
+        <v>2911</v>
+      </c>
+      <c r="B910" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="C910" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_diet:sd</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:hoppe</v>
       </c>
       <c r="D910" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E910" s="8" t="s">
-        <v>2826</v>
+        <v>2912</v>
+      </c>
+      <c r="F910" s="8" t="s">
+        <v>2913</v>
       </c>
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A911" s="8" t="s">
-        <v>2827</v>
-      </c>
-      <c r="B911" s="22" t="s">
-        <v>2820</v>
+        <v>2914</v>
+      </c>
+      <c r="B911" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="C911" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_diet:veg</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:garcia</v>
       </c>
       <c r="D911" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E911" s="8" t="s">
-        <v>2828</v>
+        <v>2915</v>
       </c>
       <c r="F911" s="8" t="s">
-        <v>2829</v>
+        <v>2913</v>
       </c>
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A912" s="8" t="s">
-        <v>2832</v>
-      </c>
-      <c r="B912" s="22" t="s">
-        <v>2820</v>
+        <v>2916</v>
+      </c>
+      <c r="B912" s="8" t="s">
+        <v>252</v>
       </c>
       <c r="C912" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_diet:hg</v>
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:khaskar</v>
       </c>
       <c r="D912" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E912" s="8" t="s">
-        <v>2830</v>
+        <v>2917</v>
       </c>
       <c r="F912" s="8" t="s">
-        <v>2831</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A913" s="8" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B913" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="C913" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v>att_user_research_group:krieg</v>
+      </c>
+      <c r="D913" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E913" s="8" t="s">
+        <v>2920</v>
+      </c>
+      <c r="F913" s="8" t="s">
+        <v>2921</v>
+      </c>
+    </row>
+    <row r="914" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A914" s="8" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B914" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C914" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v>att_diet:wd</v>
+      </c>
+      <c r="D914" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E914" s="8" t="s">
+        <v>2823</v>
+      </c>
+      <c r="F914" s="8" t="s">
+        <v>2822</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A915" s="8" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B915" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C915" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v>att_diet:sd</v>
+      </c>
+      <c r="D915" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E915" s="8" t="s">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A916" s="8" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B916" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C916" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v>att_diet:veg</v>
+      </c>
+      <c r="D916" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E916" s="8" t="s">
+        <v>2828</v>
+      </c>
+      <c r="F916" s="8" t="s">
+        <v>2829</v>
+      </c>
+    </row>
+    <row r="917" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A917" s="8" t="s">
+        <v>2832</v>
+      </c>
+      <c r="B917" s="22" t="s">
+        <v>2820</v>
+      </c>
+      <c r="C917" s="8" t="str">
+        <f t="shared" si="21"/>
+        <v>att_diet:hg</v>
+      </c>
+      <c r="D917" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E917" s="8" t="s">
+        <v>2830</v>
+      </c>
+      <c r="F917" s="8" t="s">
+        <v>2831</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A918" s="8" t="s">
         <v>2835</v>
       </c>
-      <c r="B913" s="8" t="s">
+      <c r="B918" s="8" t="s">
         <v>2820</v>
       </c>
-      <c r="C913" s="8" t="str">
-        <f t="shared" si="19"/>
+      <c r="C918" s="8" t="str">
+        <f t="shared" si="21"/>
         <v>att_diet:hfd</v>
       </c>
-      <c r="D913" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E913" s="8" t="s">
+      <c r="D918" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E918" s="8" t="s">
         <v>2833</v>
       </c>
-      <c r="F913" s="8" t="s">
+      <c r="F918" s="8" t="s">
         <v>2834</v>
       </c>
     </row>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B58F20-8815-B046-B5D7-65042C04D653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DD3072-8B6B-9149-8BC0-8DDB089452B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10820" yWindow="1040" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10820" yWindow="1040" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -12124,7 +12124,7 @@
         <v>2849</v>
       </c>
       <c r="D53">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>21</v>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F2B467-76C7-5645-83A9-BBDC764BEB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43A955C-6D16-1E44-9C40-7076749B4541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="700" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10322" uniqueCount="2965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10322" uniqueCount="2966">
   <si>
     <t>tag</t>
   </si>
@@ -8937,6 +8937,9 @@
   </si>
   <si>
     <t>Membrane fraction (Mitochondria, ER) with Proteinase K digestion.</t>
+  </si>
+  <si>
+    <t>mitochondriapk</t>
   </si>
 </sst>
 </file>
@@ -9102,6 +9105,27 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC5E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC5E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC5E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <font>
         <color rgb="FFCC0000"/>
       </font>
@@ -9125,27 +9149,6 @@
       <font>
         <color rgb="FFCC0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC5E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC5E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC5E0B4"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -15351,17 +15354,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E1:F112 K1:P112 I2:J112">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="2" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J113:P114">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J113)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M115:P115">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",M115)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -32774,14 +32777,14 @@
     </row>
     <row r="829" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A829" s="8" t="s">
-        <v>2935</v>
+        <v>2965</v>
       </c>
       <c r="B829" s="8" t="s">
         <v>2930</v>
       </c>
       <c r="C829" s="8" t="str">
         <f t="shared" ref="C829" si="22">B829&amp;":"&amp;A829</f>
-        <v>att_subcellular_compartment:mitochondria</v>
+        <v>att_subcellular_compartment:mitochondriapk</v>
       </c>
       <c r="D829" s="9" t="s">
         <v>17</v>
@@ -34745,17 +34748,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F331:F339 E240 F9:F329">
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F369">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F158">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="4" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -57036,12 +57039,12 @@
   </sheetData>
   <autoFilter ref="A1:O365" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <conditionalFormatting sqref="C323:C335 I320 I175:I177 C365 C2:C321">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C439">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61EDE2A0-C2D6-6D49-97FE-C2162E7C7C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E2B93-9EF5-D14B-B7E1-E788B50AC516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="500" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15620" yWindow="500" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10361" uniqueCount="2977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10368" uniqueCount="2979">
   <si>
     <t>tag</t>
   </si>
@@ -8973,6 +8973,12 @@
   </si>
   <si>
     <t>Mouse ID</t>
+  </si>
+  <si>
+    <t>att_cloneid</t>
+  </si>
+  <si>
+    <t>Clone Identifier</t>
   </si>
 </sst>
 </file>
@@ -9076,7 +9082,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9131,6 +9137,9 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9561,7 +9570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH118"/>
+  <dimension ref="A1:AMH119"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -10137,13 +10146,13 @@
     </row>
     <row r="12" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>51</v>
+        <v>2977</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>2978</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -10155,10 +10164,10 @@
         <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I12" s="7" t="b">
         <v>0</v>
@@ -10166,34 +10175,34 @@
       <c r="J12" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="K12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" s="1" t="s">
+      <c r="K12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="23" t="b">
+        <v>0</v>
+      </c>
+      <c r="O12" s="23" t="b">
+        <v>1</v>
+      </c>
+      <c r="P12" s="11" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:1022" x14ac:dyDescent="0.15">
-      <c r="A13" t="s">
-        <v>52</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>54</v>
+      <c r="A13" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>51</v>
       </c>
       <c r="D13">
         <v>500</v>
@@ -10205,7 +10214,7 @@
         <v>21</v>
       </c>
       <c r="G13" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="H13">
         <v>2</v>
@@ -10217,7 +10226,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>19</v>
@@ -10226,7 +10235,7 @@
         <v>19</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>21</v>
@@ -10237,13 +10246,13 @@
     </row>
     <row r="14" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B14" t="s">
         <v>53</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D14">
         <v>500</v>
@@ -10287,13 +10296,13 @@
     </row>
     <row r="15" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15">
         <v>500</v>
@@ -10337,13 +10346,13 @@
     </row>
     <row r="16" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" t="s">
         <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D16">
         <v>500</v>
@@ -10376,7 +10385,7 @@
         <v>19</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>21</v>
@@ -10387,13 +10396,13 @@
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
         <v>53</v>
       </c>
       <c r="C17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D17">
         <v>500</v>
@@ -10426,7 +10435,7 @@
         <v>19</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>21</v>
@@ -10437,13 +10446,13 @@
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
         <v>53</v>
       </c>
       <c r="C18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D18">
         <v>500</v>
@@ -10487,13 +10496,13 @@
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B19" t="s">
         <v>53</v>
       </c>
       <c r="C19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="D19">
         <v>500</v>
@@ -10537,13 +10546,13 @@
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" t="s">
         <v>53</v>
       </c>
-      <c r="B20" t="s">
-        <v>17</v>
-      </c>
       <c r="C20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D20">
         <v>500</v>
@@ -10552,7 +10561,7 @@
         <v>19</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
         <v>55</v>
@@ -10567,7 +10576,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>19</v>
@@ -10586,17 +10595,17 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A21" s="6" t="s">
-        <v>69</v>
+      <c r="A21" t="s">
+        <v>53</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
       </c>
       <c r="C21" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D21">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>19</v>
@@ -10605,10 +10614,10 @@
         <v>19</v>
       </c>
       <c r="G21" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I21" s="7" t="b">
         <v>0</v>
@@ -10626,27 +10635,27 @@
         <v>19</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A22" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
         <v>17</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D22">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>19</v>
@@ -10687,13 +10696,13 @@
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A23" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
       </c>
       <c r="C23" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D23">
         <v>500</v>
@@ -10737,13 +10746,13 @@
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B24" t="s">
         <v>17</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D24">
         <v>500</v>
@@ -10787,13 +10796,13 @@
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
         <v>17</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D25">
         <v>500</v>
@@ -10836,17 +10845,17 @@
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A26" t="s">
-        <v>79</v>
+      <c r="A26" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D26">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>19</v>
@@ -10855,7 +10864,7 @@
         <v>19</v>
       </c>
       <c r="G26" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -10887,13 +10896,13 @@
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D27">
         <v>200</v>
@@ -10936,14 +10945,14 @@
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A28" s="6" t="s">
-        <v>84</v>
+      <c r="A28" t="s">
+        <v>82</v>
       </c>
       <c r="B28" t="s">
         <v>17</v>
       </c>
       <c r="C28" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D28">
         <v>200</v>
@@ -10986,14 +10995,14 @@
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A29" t="s">
-        <v>86</v>
+      <c r="A29" s="6" t="s">
+        <v>84</v>
       </c>
       <c r="B29" t="s">
         <v>17</v>
       </c>
       <c r="C29" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D29">
         <v>200</v>
@@ -11036,29 +11045,29 @@
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A30" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>89</v>
+      <c r="A30" t="s">
+        <v>86</v>
+      </c>
+      <c r="B30" t="s">
+        <v>17</v>
+      </c>
+      <c r="C30" t="s">
+        <v>87</v>
       </c>
       <c r="D30">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E30" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>81</v>
       </c>
       <c r="H30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I30" s="7" t="b">
         <v>0</v>
@@ -11082,33 +11091,33 @@
         <v>21</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A31" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D31">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E31" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G31" t="s">
-        <v>93</v>
+        <v>25</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" s="7" t="b">
         <v>0</v>
@@ -11132,33 +11141,33 @@
         <v>21</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A32" s="6" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D32">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G32" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="H32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I32" s="7" t="b">
         <v>0</v>
@@ -11182,18 +11191,18 @@
         <v>21</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A33" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>95</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D33">
         <v>500</v>
@@ -11237,13 +11246,13 @@
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A34" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B34" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>22</v>
-      </c>
       <c r="C34" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D34">
         <v>500</v>
@@ -11287,13 +11296,13 @@
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A35" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B35" t="s">
-        <v>17</v>
-      </c>
-      <c r="C35" t="s">
-        <v>100</v>
+        <v>95</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>99</v>
       </c>
       <c r="D35">
         <v>500</v>
@@ -11302,19 +11311,19 @@
         <v>19</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G35" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J35" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>21</v>
@@ -11332,18 +11341,18 @@
         <v>21</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A36" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="B36" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>102</v>
+      <c r="B36" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" t="s">
+        <v>100</v>
       </c>
       <c r="D36">
         <v>500</v>
@@ -11352,7 +11361,7 @@
         <v>19</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G36" t="s">
         <v>29</v>
@@ -11364,7 +11373,7 @@
         <v>0</v>
       </c>
       <c r="J36" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>21</v>
@@ -11387,13 +11396,13 @@
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A37" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D37">
         <v>500</v>
@@ -11437,22 +11446,22 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A38" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D38">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E38" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G38" t="s">
         <v>29</v>
@@ -11487,16 +11496,16 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A39" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>105</v>
+        <v>27</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>2856</v>
+        <v>106</v>
       </c>
       <c r="D39">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>19</v>
@@ -11536,17 +11545,17 @@
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A40" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" t="s">
-        <v>17</v>
-      </c>
-      <c r="C40" t="s">
-        <v>109</v>
+      <c r="A40" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>2856</v>
       </c>
       <c r="D40">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>19</v>
@@ -11555,10 +11564,10 @@
         <v>19</v>
       </c>
       <c r="G40" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I40" s="7" t="b">
         <v>0</v>
@@ -11586,14 +11595,14 @@
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A41" s="6" t="s">
-        <v>110</v>
+      <c r="A41" t="s">
+        <v>108</v>
       </c>
       <c r="B41" t="s">
         <v>17</v>
       </c>
       <c r="C41" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D41">
         <v>500</v>
@@ -11605,7 +11614,7 @@
         <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="H41">
         <v>0</v>
@@ -11636,14 +11645,14 @@
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A42" t="s">
-        <v>112</v>
+      <c r="A42" s="6" t="s">
+        <v>110</v>
       </c>
       <c r="B42" t="s">
         <v>17</v>
       </c>
       <c r="C42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D42">
         <v>500</v>
@@ -11655,16 +11664,16 @@
         <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="H42">
         <v>0</v>
       </c>
       <c r="I42" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J42" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" s="1" t="s">
         <v>21</v>
@@ -11687,13 +11696,13 @@
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B43" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
+      </c>
+      <c r="B43" t="s">
+        <v>17</v>
+      </c>
+      <c r="C43" t="s">
+        <v>113</v>
       </c>
       <c r="D43">
         <v>500</v>
@@ -11702,19 +11711,19 @@
         <v>19</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>25</v>
+        <v>114</v>
       </c>
       <c r="H43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I43" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K43" s="1" t="s">
         <v>21</v>
@@ -11732,18 +11741,18 @@
         <v>21</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D44">
         <v>500</v>
@@ -11787,13 +11796,13 @@
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D45">
         <v>500</v>
@@ -11837,13 +11846,13 @@
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>116</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D46">
         <v>500</v>
@@ -11886,14 +11895,14 @@
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A47" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="B47" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" t="s">
-        <v>125</v>
+      <c r="A47" t="s">
+        <v>122</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>123</v>
       </c>
       <c r="D47">
         <v>500</v>
@@ -11902,13 +11911,13 @@
         <v>19</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G47" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" s="7" t="b">
         <v>0</v>
@@ -11932,18 +11941,18 @@
         <v>21</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A48" t="s">
-        <v>126</v>
+      <c r="A48" s="6" t="s">
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C48" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D48">
         <v>500</v>
@@ -11955,7 +11964,7 @@
         <v>19</v>
       </c>
       <c r="G48" t="s">
-        <v>128</v>
+        <v>33</v>
       </c>
       <c r="H48">
         <v>0</v>
@@ -11987,13 +11996,13 @@
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
-        <v>130</v>
+        <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D49">
         <v>500</v>
@@ -12005,7 +12014,7 @@
         <v>19</v>
       </c>
       <c r="G49" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H49">
         <v>0</v>
@@ -12023,13 +12032,13 @@
         <v>19</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N49" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P49" s="1" t="s">
         <v>19</v>
@@ -12037,13 +12046,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C50" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D50">
         <v>500</v>
@@ -12087,13 +12096,13 @@
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B51" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C51" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D51">
         <v>500</v>
@@ -12137,16 +12146,16 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
-        <v>2966</v>
+        <v>130</v>
       </c>
       <c r="B52" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="C52" t="s">
-        <v>2967</v>
+        <v>136</v>
       </c>
       <c r="D52">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>19</v>
@@ -12155,7 +12164,7 @@
         <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="H52">
         <v>0</v>
@@ -12173,42 +12182,42 @@
         <v>19</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A53" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B53" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>138</v>
+      <c r="A53" t="s">
+        <v>2966</v>
+      </c>
+      <c r="B53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53" t="s">
+        <v>2967</v>
       </c>
       <c r="D53">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I53" s="7" t="b">
         <v>0</v>
@@ -12236,29 +12245,29 @@
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A54" t="s">
-        <v>139</v>
+      <c r="A54" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>2849</v>
+        <v>138</v>
       </c>
       <c r="D54">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G54" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="H54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I54" s="7" t="b">
         <v>0</v>
@@ -12282,24 +12291,24 @@
         <v>21</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A55" s="6" t="s">
+      <c r="A55" t="s">
+        <v>139</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B55" t="s">
-        <v>17</v>
-      </c>
-      <c r="C55" t="s">
-        <v>2850</v>
+      <c r="C55" s="6" t="s">
+        <v>2849</v>
       </c>
       <c r="D55">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>19</v>
@@ -12336,14 +12345,14 @@
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A56" t="s">
-        <v>143</v>
+      <c r="A56" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="B56" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="C56" t="s">
-        <v>145</v>
+        <v>2850</v>
       </c>
       <c r="D56">
         <v>500</v>
@@ -12352,13 +12361,13 @@
         <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G56" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="H56">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I56" s="7" t="b">
         <v>0</v>
@@ -12367,7 +12376,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L56" s="1" t="s">
         <v>19</v>
@@ -12376,24 +12385,24 @@
         <v>19</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O56" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B57" t="s">
         <v>144</v>
       </c>
       <c r="C57" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D57">
         <v>500</v>
@@ -12402,7 +12411,7 @@
         <v>19</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G57" t="s">
         <v>55</v>
@@ -12437,13 +12446,13 @@
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B58" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="C58" t="s">
-        <v>2806</v>
+        <v>147</v>
       </c>
       <c r="D58">
         <v>500</v>
@@ -12464,10 +12473,10 @@
         <v>0</v>
       </c>
       <c r="J58" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>19</v>
@@ -12487,13 +12496,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="C59" t="s">
-        <v>2807</v>
+        <v>2806</v>
       </c>
       <c r="D59">
         <v>500</v>
@@ -12536,17 +12545,17 @@
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A60" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B60" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>151</v>
+      <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s">
+        <v>148</v>
+      </c>
+      <c r="C60" t="s">
+        <v>2807</v>
       </c>
       <c r="D60">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>19</v>
@@ -12555,16 +12564,16 @@
         <v>19</v>
       </c>
       <c r="G60" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J60" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K60" s="1" t="s">
         <v>21</v>
@@ -12576,27 +12585,27 @@
         <v>19</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O60" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A61" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C61" t="s">
-        <v>153</v>
+        <v>27</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="D61">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>19</v>
@@ -12605,7 +12614,7 @@
         <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -12637,13 +12646,13 @@
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A62" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B62" t="s">
-        <v>17</v>
-      </c>
       <c r="C62" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D62">
         <v>500</v>
@@ -12687,13 +12696,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A63" s="6" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D63">
         <v>500</v>
@@ -12705,10 +12714,10 @@
         <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="7" t="b">
         <v>0</v>
@@ -12736,14 +12745,14 @@
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A64" t="s">
-        <v>157</v>
+      <c r="A64" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D64">
         <v>500</v>
@@ -12755,7 +12764,7 @@
         <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="H64">
         <v>0</v>
@@ -12787,13 +12796,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D65">
         <v>500</v>
@@ -12805,7 +12814,7 @@
         <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -12836,14 +12845,14 @@
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A66" s="6" t="s">
-        <v>2972</v>
+      <c r="A66" t="s">
+        <v>160</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>2976</v>
+        <v>161</v>
       </c>
       <c r="D66">
         <v>500</v>
@@ -12852,7 +12861,7 @@
         <v>19</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G66" t="s">
         <v>42</v>
@@ -12867,7 +12876,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L66" s="1" t="s">
         <v>19</v>
@@ -12882,18 +12891,18 @@
         <v>21</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A67" t="s">
-        <v>23</v>
+      <c r="A67" s="6" t="s">
+        <v>2972</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>162</v>
+        <v>2976</v>
       </c>
       <c r="D67">
         <v>500</v>
@@ -12902,22 +12911,22 @@
         <v>19</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G67" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I67" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J67" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>19</v>
@@ -12926,7 +12935,7 @@
         <v>19</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O67" s="1" t="s">
         <v>21</v>
@@ -12936,14 +12945,14 @@
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A68" s="6" t="s">
-        <v>116</v>
+      <c r="A68" t="s">
+        <v>23</v>
       </c>
       <c r="B68" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D68">
         <v>500</v>
@@ -12964,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="J68" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" s="1" t="s">
         <v>21</v>
@@ -12976,7 +12985,7 @@
         <v>19</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>21</v>
@@ -12986,14 +12995,14 @@
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A69" t="s">
-        <v>38</v>
+      <c r="A69" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="B69" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="C69" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D69">
         <v>500</v>
@@ -13014,7 +13023,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>21</v>
@@ -13026,7 +13035,7 @@
         <v>19</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>21</v>
@@ -13037,13 +13046,13 @@
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" t="s">
         <v>164</v>
       </c>
-      <c r="B70" t="s">
-        <v>23</v>
-      </c>
       <c r="C70" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D70">
         <v>500</v>
@@ -13086,14 +13095,14 @@
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A71" s="6" t="s">
-        <v>167</v>
+      <c r="A71" t="s">
+        <v>164</v>
       </c>
       <c r="B71" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D71">
         <v>500</v>
@@ -13102,7 +13111,7 @@
         <v>19</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G71" t="s">
         <v>25</v>
@@ -13114,7 +13123,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>21</v>
@@ -13126,7 +13135,7 @@
         <v>19</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O71" s="1" t="s">
         <v>21</v>
@@ -13137,13 +13146,13 @@
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A72" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B72" t="s">
         <v>168</v>
       </c>
       <c r="C72" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D72">
         <v>500</v>
@@ -13186,14 +13195,14 @@
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A73" t="s">
+      <c r="A73" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" t="s">
         <v>168</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>172</v>
+      <c r="C73" t="s">
+        <v>171</v>
       </c>
       <c r="D73">
         <v>500</v>
@@ -13236,14 +13245,14 @@
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A74" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B74" t="s">
-        <v>174</v>
-      </c>
-      <c r="C74" t="s">
-        <v>175</v>
+      <c r="A74" t="s">
+        <v>168</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="D74">
         <v>500</v>
@@ -13287,13 +13296,13 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A75" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B75" t="s">
         <v>174</v>
       </c>
       <c r="C75" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D75">
         <v>500</v>
@@ -13336,14 +13345,14 @@
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A76" t="s">
+      <c r="A76" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B76" t="s">
         <v>174</v>
       </c>
-      <c r="B76" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>178</v>
+      <c r="C76" t="s">
+        <v>177</v>
       </c>
       <c r="D76">
         <v>500</v>
@@ -13387,13 +13396,13 @@
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
-        <v>179</v>
-      </c>
-      <c r="B77" t="s">
-        <v>180</v>
-      </c>
-      <c r="C77" t="s">
-        <v>2805</v>
+        <v>174</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="D77">
         <v>500</v>
@@ -13402,13 +13411,13 @@
         <v>19</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G77" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H77">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I77" s="7" t="b">
         <v>0</v>
@@ -13432,33 +13441,33 @@
         <v>21</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A78" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>184</v>
+      <c r="A78" t="s">
+        <v>179</v>
+      </c>
+      <c r="B78" t="s">
+        <v>180</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2805</v>
       </c>
       <c r="D78">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G78" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="H78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I78" s="7" t="b">
         <v>0</v>
@@ -13487,13 +13496,13 @@
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A79" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D79">
         <v>400</v>
@@ -13517,7 +13526,7 @@
         <v>0</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L79" s="1" t="s">
         <v>19</v>
@@ -13529,21 +13538,21 @@
         <v>19</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P79" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B80" t="s">
-        <v>17</v>
-      </c>
-      <c r="C80" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="D80">
         <v>400</v>
@@ -13552,7 +13561,7 @@
         <v>19</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G80" t="s">
         <v>185</v>
@@ -13567,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>19</v>
@@ -13579,21 +13588,21 @@
         <v>19</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B81" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>191</v>
+      <c r="B81" t="s">
+        <v>17</v>
+      </c>
+      <c r="C81" t="s">
+        <v>189</v>
       </c>
       <c r="D81">
         <v>400</v>
@@ -13602,7 +13611,7 @@
         <v>19</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G81" t="s">
         <v>185</v>
@@ -13637,13 +13646,13 @@
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A82" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>183</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>2863</v>
+        <v>191</v>
       </c>
       <c r="D82">
         <v>400</v>
@@ -13686,35 +13695,35 @@
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A83" t="s">
-        <v>193</v>
-      </c>
-      <c r="B83" t="s">
-        <v>17</v>
-      </c>
-      <c r="C83" t="s">
-        <v>194</v>
+      <c r="A83" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>2863</v>
       </c>
       <c r="D83">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G83" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="H83">
+        <v>1</v>
+      </c>
+      <c r="I83" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="I83" s="7" t="b">
-        <v>1</v>
-      </c>
       <c r="J83" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" s="1" t="s">
         <v>21</v>
@@ -13737,13 +13746,13 @@
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B84" t="s">
         <v>17</v>
       </c>
       <c r="C84" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D84">
         <v>500</v>
@@ -13755,16 +13764,16 @@
         <v>19</v>
       </c>
       <c r="G84" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="H84">
         <v>0</v>
       </c>
       <c r="I84" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J84" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K84" s="1" t="s">
         <v>21</v>
@@ -13786,14 +13795,14 @@
       </c>
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A85" s="6" t="s">
-        <v>196</v>
+      <c r="A85" t="s">
+        <v>180</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D85">
         <v>500</v>
@@ -13811,7 +13820,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85" s="7" t="b">
         <v>0</v>
@@ -13836,14 +13845,14 @@
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A86" t="s">
-        <v>198</v>
+      <c r="A86" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D86">
         <v>500</v>
@@ -13861,7 +13870,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J86" s="7" t="b">
         <v>0</v>
@@ -13887,34 +13896,34 @@
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D87">
         <v>500</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G87" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="H87">
         <v>0</v>
       </c>
       <c r="I87" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J87" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K87" s="1" t="s">
         <v>21</v>
@@ -13936,32 +13945,32 @@
       </c>
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A88" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B88" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>204</v>
+      <c r="A88" t="s">
+        <v>200</v>
+      </c>
+      <c r="B88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C88" t="s">
+        <v>201</v>
       </c>
       <c r="D88">
         <v>500</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G88" t="s">
-        <v>29</v>
+        <v>202</v>
       </c>
       <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88" s="7" t="b">
         <v>1</v>
-      </c>
-      <c r="I88" s="7" t="b">
-        <v>0</v>
       </c>
       <c r="J88" s="7" t="b">
         <v>1</v>
@@ -13986,35 +13995,35 @@
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A89" t="s">
-        <v>134</v>
-      </c>
-      <c r="B89" t="s">
-        <v>17</v>
+      <c r="A89" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D89">
         <v>500</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G89" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="H89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I89" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J89" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K89" s="1" t="s">
         <v>21</v>
@@ -14023,13 +14032,13 @@
         <v>19</v>
       </c>
       <c r="M89" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P89" s="1" t="s">
         <v>19</v>
@@ -14037,19 +14046,19 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
-        <v>206</v>
+        <v>134</v>
       </c>
       <c r="B90" t="s">
-        <v>129</v>
-      </c>
-      <c r="C90" t="s">
-        <v>207</v>
+        <v>17</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>205</v>
       </c>
       <c r="D90">
         <v>500</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>19</v>
@@ -14087,13 +14096,13 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B91" t="s">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="C91" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D91">
         <v>500</v>
@@ -14136,14 +14145,14 @@
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A92" s="6" t="s">
-        <v>210</v>
+      <c r="A92" t="s">
+        <v>208</v>
       </c>
       <c r="B92" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C92" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D92">
         <v>500</v>
@@ -14155,16 +14164,16 @@
         <v>19</v>
       </c>
       <c r="G92" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="H92">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I92" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J92" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K92" s="1" t="s">
         <v>21</v>
@@ -14173,13 +14182,13 @@
         <v>19</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P92" s="1" t="s">
         <v>19</v>
@@ -14187,13 +14196,13 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A93" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B93" t="s">
         <v>211</v>
       </c>
-      <c r="B93" t="s">
-        <v>17</v>
-      </c>
       <c r="C93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D93">
         <v>500</v>
@@ -14237,13 +14246,13 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A94" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>213</v>
       </c>
       <c r="D94">
         <v>500</v>
@@ -14255,16 +14264,16 @@
         <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I94" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J94" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K94" s="1" t="s">
         <v>21</v>
@@ -14286,14 +14295,14 @@
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A95" t="s">
-        <v>216</v>
-      </c>
-      <c r="B95" t="s">
-        <v>23</v>
-      </c>
-      <c r="C95" t="s">
-        <v>217</v>
+      <c r="A95" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="D95">
         <v>500</v>
@@ -14302,13 +14311,13 @@
         <v>19</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" s="7" t="b">
         <v>0</v>
@@ -14326,24 +14335,24 @@
         <v>19</v>
       </c>
       <c r="N95" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O95" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
-        <v>31</v>
+        <v>216</v>
       </c>
       <c r="B96" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C96" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D96">
         <v>500</v>
@@ -14352,19 +14361,19 @@
         <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G96" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I96" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J96" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1" t="s">
         <v>21</v>
@@ -14376,24 +14385,24 @@
         <v>19</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A97" s="6" t="s">
-        <v>219</v>
+      <c r="A97" t="s">
+        <v>31</v>
       </c>
       <c r="B97" t="s">
         <v>17</v>
       </c>
       <c r="C97" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D97">
         <v>500</v>
@@ -14405,16 +14414,16 @@
         <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>185</v>
+        <v>33</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I97" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J97" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>21</v>
@@ -14436,14 +14445,14 @@
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A98" t="s">
-        <v>221</v>
+      <c r="A98" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="B98" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C98" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D98">
         <v>500</v>
@@ -14452,13 +14461,13 @@
         <v>19</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="H98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" s="7" t="b">
         <v>0</v>
@@ -14476,24 +14485,24 @@
         <v>19</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C99" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D99">
         <v>500</v>
@@ -14505,10 +14514,10 @@
         <v>21</v>
       </c>
       <c r="G99" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I99" s="7" t="b">
         <v>0</v>
@@ -14526,24 +14535,24 @@
         <v>19</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D100">
         <v>500</v>
@@ -14587,13 +14596,13 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B101" t="s">
         <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D101">
         <v>500</v>
@@ -14637,13 +14646,13 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D102">
         <v>500</v>
@@ -14687,13 +14696,13 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D103">
         <v>500</v>
@@ -14737,13 +14746,13 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D104">
         <v>500</v>
@@ -14787,13 +14796,13 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D105">
         <v>500</v>
@@ -14835,15 +14844,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="106" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A106" s="6" t="s">
-        <v>238</v>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A106" t="s">
+        <v>236</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D106">
         <v>500</v>
@@ -14852,10 +14861,10 @@
         <v>19</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G106" t="s">
-        <v>42</v>
+        <v>225</v>
       </c>
       <c r="H106">
         <v>0</v>
@@ -14885,15 +14894,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>2808</v>
+        <v>239</v>
       </c>
       <c r="D107">
         <v>500</v>
@@ -14937,13 +14946,13 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A108" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
+      </c>
+      <c r="B108" t="s">
+        <v>17</v>
+      </c>
+      <c r="C108" t="s">
+        <v>2808</v>
       </c>
       <c r="D108">
         <v>500</v>
@@ -14952,13 +14961,13 @@
         <v>19</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G108" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I108" s="7" t="b">
         <v>0</v>
@@ -14982,33 +14991,33 @@
         <v>21</v>
       </c>
       <c r="P108" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A109" t="s">
-        <v>244</v>
-      </c>
-      <c r="B109" t="s">
-        <v>17</v>
-      </c>
-      <c r="C109" t="s">
-        <v>2861</v>
+      <c r="A109" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>243</v>
       </c>
       <c r="D109">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G109" t="s">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="H109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I109" s="7" t="b">
         <v>0</v>
@@ -15017,10 +15026,10 @@
         <v>0</v>
       </c>
       <c r="K109" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M109" s="1" t="s">
         <v>19</v>
@@ -15029,24 +15038,24 @@
         <v>19</v>
       </c>
       <c r="O109" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>247</v>
+        <v>2861</v>
       </c>
       <c r="D110">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>19</v>
@@ -15087,16 +15096,16 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D111">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>19</v>
@@ -15117,7 +15126,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L111" s="1" t="s">
         <v>21</v>
@@ -15137,16 +15146,16 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D112">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>19</v>
@@ -15167,7 +15176,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>21</v>
@@ -15187,16 +15196,16 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D113">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>19</v>
@@ -15217,7 +15226,7 @@
         <v>0</v>
       </c>
       <c r="K113" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L113" s="1" t="s">
         <v>21</v>
@@ -15237,16 +15246,16 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D114">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>19</v>
@@ -15267,7 +15276,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>21</v>
@@ -15287,16 +15296,16 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>2820</v>
+        <v>254</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>2821</v>
+        <v>255</v>
       </c>
       <c r="D115">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>19</v>
@@ -15305,22 +15314,22 @@
         <v>19</v>
       </c>
       <c r="G115" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="H115">
         <v>0</v>
       </c>
-      <c r="I115" s="2" t="b">
+      <c r="I115" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J115" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L115" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>19</v>
@@ -15329,7 +15338,7 @@
         <v>19</v>
       </c>
       <c r="O115" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P115" s="1" t="s">
         <v>19</v>
@@ -15337,25 +15346,25 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
-        <v>2851</v>
+        <v>2820</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>2924</v>
+        <v>2821</v>
       </c>
       <c r="D116">
         <v>500</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G116" t="s">
-        <v>2852</v>
+        <v>20</v>
       </c>
       <c r="H116">
         <v>0</v>
@@ -15387,13 +15396,13 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
-        <v>2922</v>
+        <v>2851</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>2925</v>
+        <v>2924</v>
       </c>
       <c r="D117">
         <v>500</v>
@@ -15405,7 +15414,7 @@
         <v>19</v>
       </c>
       <c r="G117" t="s">
-        <v>2923</v>
+        <v>2852</v>
       </c>
       <c r="H117">
         <v>0</v>
@@ -15413,11 +15422,11 @@
       <c r="I117" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J117" s="2" t="b">
+      <c r="J117" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>19</v>
@@ -15437,25 +15446,25 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>2930</v>
+        <v>2922</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>2931</v>
+        <v>2925</v>
       </c>
       <c r="D118">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G118" t="s">
-        <v>47</v>
+        <v>2923</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -15467,7 +15476,7 @@
         <v>0</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>19</v>
@@ -15482,23 +15491,73 @@
         <v>21</v>
       </c>
       <c r="P118" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A119" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B119" t="s">
+        <v>17</v>
+      </c>
+      <c r="C119" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D119">
+        <v>650</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119" t="s">
+        <v>47</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J119" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P119" s="1" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J115:P116">
+  <conditionalFormatting sqref="J116:P117">
     <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",J115)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",J116)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:P51 E1:F114 I2:J51 I52:P114">
+  <conditionalFormatting sqref="E1:F115 I53:P115 I2:J52 K1:P52">
     <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M117:P117">
+  <conditionalFormatting sqref="M118:P118">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",M117)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",M118)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED3E2B93-9EF5-D14B-B7E1-E788B50AC516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D4B6B9C-92BD-644A-A81A-222AFF9310FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15620" yWindow="500" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7100" yWindow="1360" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10368" uniqueCount="2979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10407" uniqueCount="2992">
   <si>
     <t>tag</t>
   </si>
@@ -8978,7 +8978,46 @@
     <t>att_cloneid</t>
   </si>
   <si>
-    <t>Clone Identifier</t>
+    <t>att_ptm_enrichment</t>
+  </si>
+  <si>
+    <t>PTM Enrichment Strategy</t>
+  </si>
+  <si>
+    <t>antibody</t>
+  </si>
+  <si>
+    <t>Antibody</t>
+  </si>
+  <si>
+    <t>An enrichment strategy for PTMs that is based on an antibody such pTyr, Acetylation or Ubiquitination.</t>
+  </si>
+  <si>
+    <t>metal</t>
+  </si>
+  <si>
+    <t>Metal</t>
+  </si>
+  <si>
+    <t>PTM enrichment strategy based on a metal interacting with the PTM such as IMAC or TiO2 enrichment for phospho peptides.</t>
+  </si>
+  <si>
+    <t>Ion Chromatography</t>
+  </si>
+  <si>
+    <t>Ion chromatography to enrich for PTMs such as Strong cation or anion exchange chromatography.</t>
+  </si>
+  <si>
+    <t>ionchromatography</t>
+  </si>
+  <si>
+    <t>att_protein_input</t>
+  </si>
+  <si>
+    <t>Protein amount [µg]</t>
+  </si>
+  <si>
+    <t>Clone ID</t>
   </si>
 </sst>
 </file>
@@ -9570,7 +9609,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH119"/>
+  <dimension ref="A1:AMH121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -9755,7 +9794,7 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
@@ -10152,7 +10191,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>2978</v>
+        <v>2991</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -14096,63 +14135,63 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
-        <v>206</v>
-      </c>
-      <c r="B91" t="s">
-        <v>129</v>
-      </c>
-      <c r="C91" t="s">
-        <v>207</v>
+        <v>2989</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>2990</v>
       </c>
       <c r="D91">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G91" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="H91">
         <v>0</v>
       </c>
       <c r="I91" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B92" t="s">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="C92" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D92">
         <v>500</v>
@@ -14195,14 +14234,14 @@
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A93" s="6" t="s">
-        <v>210</v>
+      <c r="A93" t="s">
+        <v>208</v>
       </c>
       <c r="B93" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C93" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D93">
         <v>500</v>
@@ -14214,16 +14253,16 @@
         <v>19</v>
       </c>
       <c r="G93" t="s">
-        <v>33</v>
+        <v>132</v>
       </c>
       <c r="H93">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I93" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J93" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>21</v>
@@ -14232,27 +14271,27 @@
         <v>19</v>
       </c>
       <c r="M93" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P93" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A94" s="6" t="s">
-        <v>211</v>
+      <c r="A94" t="s">
+        <v>2978</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>213</v>
+        <v>2979</v>
       </c>
       <c r="D94">
         <v>500</v>
@@ -14264,16 +14303,16 @@
         <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I94" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J94" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K94" s="1" t="s">
         <v>21</v>
@@ -14282,13 +14321,13 @@
         <v>19</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P94" s="1" t="s">
         <v>19</v>
@@ -14296,13 +14335,13 @@
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A95" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B95" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="B95" t="s">
+        <v>211</v>
+      </c>
+      <c r="C95" t="s">
+        <v>212</v>
       </c>
       <c r="D95">
         <v>500</v>
@@ -14314,16 +14353,16 @@
         <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I95" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J95" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>21</v>
@@ -14345,14 +14384,14 @@
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A96" t="s">
-        <v>216</v>
+      <c r="A96" s="6" t="s">
+        <v>211</v>
       </c>
       <c r="B96" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C96" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="D96">
         <v>500</v>
@@ -14361,19 +14400,19 @@
         <v>19</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G96" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I96" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J96" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K96" s="1" t="s">
         <v>21</v>
@@ -14385,27 +14424,27 @@
         <v>19</v>
       </c>
       <c r="N96" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O96" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A97" t="s">
-        <v>31</v>
-      </c>
-      <c r="B97" t="s">
-        <v>17</v>
-      </c>
-      <c r="C97" t="s">
-        <v>218</v>
+      <c r="A97" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="D97">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>19</v>
@@ -14414,16 +14453,16 @@
         <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I97" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J97" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>21</v>
@@ -14445,14 +14484,14 @@
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A98" s="6" t="s">
-        <v>219</v>
+      <c r="A98" t="s">
+        <v>216</v>
       </c>
       <c r="B98" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C98" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D98">
         <v>500</v>
@@ -14461,13 +14500,13 @@
         <v>19</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G98" t="s">
-        <v>185</v>
+        <v>25</v>
       </c>
       <c r="H98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I98" s="7" t="b">
         <v>0</v>
@@ -14485,24 +14524,24 @@
         <v>19</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
-        <v>221</v>
+        <v>31</v>
       </c>
       <c r="B99" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D99">
         <v>500</v>
@@ -14511,19 +14550,19 @@
         <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I99" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J99" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>21</v>
@@ -14535,24 +14574,24 @@
         <v>19</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A100" t="s">
-        <v>223</v>
+      <c r="A100" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D100">
         <v>500</v>
@@ -14561,13 +14600,13 @@
         <v>19</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I100" s="7" t="b">
         <v>0</v>
@@ -14596,13 +14635,13 @@
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B101" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C101" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D101">
         <v>500</v>
@@ -14614,10 +14653,10 @@
         <v>21</v>
       </c>
       <c r="G101" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I101" s="7" t="b">
         <v>0</v>
@@ -14635,24 +14674,24 @@
         <v>19</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="B102" t="s">
         <v>17</v>
       </c>
       <c r="C102" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D102">
         <v>500</v>
@@ -14696,13 +14735,13 @@
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D103">
         <v>500</v>
@@ -14746,13 +14785,13 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D104">
         <v>500</v>
@@ -14796,13 +14835,13 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D105">
         <v>500</v>
@@ -14846,13 +14885,13 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D106">
         <v>500</v>
@@ -14894,15 +14933,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A107" s="6" t="s">
-        <v>238</v>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A107" t="s">
+        <v>234</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D107">
         <v>500</v>
@@ -14911,10 +14950,10 @@
         <v>19</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G107" t="s">
-        <v>42</v>
+        <v>225</v>
       </c>
       <c r="H107">
         <v>0</v>
@@ -14945,14 +14984,14 @@
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A108" s="6" t="s">
-        <v>240</v>
+      <c r="A108" t="s">
+        <v>236</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>2808</v>
+        <v>237</v>
       </c>
       <c r="D108">
         <v>500</v>
@@ -14961,10 +15000,10 @@
         <v>19</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G108" t="s">
-        <v>42</v>
+        <v>225</v>
       </c>
       <c r="H108">
         <v>0</v>
@@ -14994,15 +15033,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>243</v>
+        <v>238</v>
+      </c>
+      <c r="B109" t="s">
+        <v>17</v>
+      </c>
+      <c r="C109" t="s">
+        <v>239</v>
       </c>
       <c r="D109">
         <v>500</v>
@@ -15011,13 +15050,13 @@
         <v>19</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G109" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I109" s="7" t="b">
         <v>0</v>
@@ -15041,21 +15080,21 @@
         <v>21</v>
       </c>
       <c r="P109" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A110" t="s">
-        <v>244</v>
+      <c r="A110" s="6" t="s">
+        <v>240</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>2861</v>
+        <v>2808</v>
       </c>
       <c r="D110">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>19</v>
@@ -15064,7 +15103,7 @@
         <v>19</v>
       </c>
       <c r="G110" t="s">
-        <v>245</v>
+        <v>42</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -15076,10 +15115,10 @@
         <v>0</v>
       </c>
       <c r="K110" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M110" s="1" t="s">
         <v>19</v>
@@ -15088,36 +15127,36 @@
         <v>19</v>
       </c>
       <c r="O110" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P110" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A111" t="s">
-        <v>246</v>
-      </c>
-      <c r="B111" t="s">
-        <v>17</v>
-      </c>
-      <c r="C111" t="s">
-        <v>247</v>
+      <c r="A111" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>243</v>
       </c>
       <c r="D111">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G111" t="s">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="H111">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I111" s="7" t="b">
         <v>0</v>
@@ -15126,10 +15165,10 @@
         <v>0</v>
       </c>
       <c r="K111" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M111" s="1" t="s">
         <v>19</v>
@@ -15138,24 +15177,24 @@
         <v>19</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>249</v>
+        <v>2861</v>
       </c>
       <c r="D112">
-        <v>550</v>
+        <v>800</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>19</v>
@@ -15176,7 +15215,7 @@
         <v>0</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L112" s="1" t="s">
         <v>21</v>
@@ -15196,16 +15235,16 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D113">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>19</v>
@@ -15246,16 +15285,16 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="D114">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>19</v>
@@ -15296,16 +15335,16 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D115">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>19</v>
@@ -15346,13 +15385,13 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
-        <v>2820</v>
+        <v>252</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>2821</v>
+        <v>253</v>
       </c>
       <c r="D116">
         <v>500</v>
@@ -15364,12 +15403,12 @@
         <v>19</v>
       </c>
       <c r="G116" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="H116">
         <v>0</v>
       </c>
-      <c r="I116" s="2" t="b">
+      <c r="I116" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J116" s="7" t="b">
@@ -15379,7 +15418,7 @@
         <v>21</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>19</v>
@@ -15388,7 +15427,7 @@
         <v>19</v>
       </c>
       <c r="O116" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P116" s="1" t="s">
         <v>19</v>
@@ -15396,40 +15435,40 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
-        <v>2851</v>
+        <v>254</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>2924</v>
+        <v>255</v>
       </c>
       <c r="D117">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G117" t="s">
-        <v>2852</v>
+        <v>245</v>
       </c>
       <c r="H117">
         <v>0</v>
       </c>
-      <c r="I117" s="2" t="b">
+      <c r="I117" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J117" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>19</v>
@@ -15438,7 +15477,7 @@
         <v>19</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P117" s="1" t="s">
         <v>19</v>
@@ -15446,25 +15485,25 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>2922</v>
+        <v>2820</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>2925</v>
+        <v>2821</v>
       </c>
       <c r="D118">
         <v>500</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G118" t="s">
-        <v>2923</v>
+        <v>20</v>
       </c>
       <c r="H118">
         <v>0</v>
@@ -15472,11 +15511,11 @@
       <c r="I118" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J118" s="2" t="b">
+      <c r="J118" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L118" s="1" t="s">
         <v>19</v>
@@ -15496,25 +15535,25 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
-        <v>2930</v>
+        <v>2851</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>2931</v>
+        <v>2924</v>
       </c>
       <c r="D119">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G119" t="s">
-        <v>47</v>
+        <v>2852</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -15522,7 +15561,7 @@
       <c r="I119" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J119" s="2" t="b">
+      <c r="J119" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K119" s="1" t="s">
@@ -15541,23 +15580,123 @@
         <v>21</v>
       </c>
       <c r="P119" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A120" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B120" t="s">
+        <v>17</v>
+      </c>
+      <c r="C120" t="s">
+        <v>2925</v>
+      </c>
+      <c r="D120">
+        <v>500</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G120" t="s">
+        <v>2923</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J120" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="L120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P120" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A121" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B121" t="s">
+        <v>17</v>
+      </c>
+      <c r="C121" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D121">
+        <v>650</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" t="s">
+        <v>47</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J121" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P121" s="1" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="J116:P117">
+  <conditionalFormatting sqref="J118:P119">
     <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",J116)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",J118)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E1:F115 I53:P115 I2:J52 K1:P52">
+  <conditionalFormatting sqref="E1:F117 I2:J52 K1:P52 I53:P117">
     <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M118:P118">
+  <conditionalFormatting sqref="M120:P120">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",M118)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",M120)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15567,7 +15706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ925"/>
+  <dimension ref="A1:AMJ928"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -31400,7 +31539,7 @@
         <v>196</v>
       </c>
       <c r="C754" s="8" t="str">
-        <f t="shared" ref="C754:C823" si="18">B754&amp;":"&amp;A754</f>
+        <f t="shared" ref="C754:C826" si="18">B754&amp;":"&amp;A754</f>
         <v>att_organism:UP000001940</v>
       </c>
       <c r="D754" s="8" t="s">
@@ -32379,7 +32518,7 @@
         <v>2327</v>
       </c>
     </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="801" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A801" s="8" t="s">
         <v>2328</v>
       </c>
@@ -32400,2604 +32539,5715 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="802" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A802" s="8" t="s">
-        <v>2331</v>
+        <v>2980</v>
       </c>
       <c r="B802" s="8" t="s">
-        <v>210</v>
+        <v>2978</v>
       </c>
       <c r="C802" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_quant_algorithm:directlfq</v>
+        <v>att_ptm_enrichment:antibody</v>
       </c>
       <c r="D802" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E802" s="8" t="s">
-        <v>2332</v>
-      </c>
-      <c r="F802" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2981</v>
+      </c>
+      <c r="F802" s="8" t="s">
+        <v>2982</v>
+      </c>
+      <c r="G802"/>
+      <c r="H802"/>
+      <c r="I802"/>
+      <c r="J802"/>
+      <c r="K802"/>
+      <c r="L802"/>
+      <c r="M802"/>
+      <c r="N802"/>
+      <c r="O802"/>
+      <c r="P802"/>
+      <c r="Q802"/>
+      <c r="R802"/>
+      <c r="S802"/>
+      <c r="T802"/>
+      <c r="U802"/>
+      <c r="V802"/>
+      <c r="W802"/>
+      <c r="X802"/>
+      <c r="Y802"/>
+      <c r="Z802"/>
+      <c r="AA802"/>
+      <c r="AB802"/>
+      <c r="AC802"/>
+      <c r="AD802"/>
+      <c r="AE802"/>
+      <c r="AF802"/>
+      <c r="AG802"/>
+      <c r="AH802"/>
+      <c r="AI802"/>
+      <c r="AJ802"/>
+      <c r="AK802"/>
+      <c r="AL802"/>
+      <c r="AM802"/>
+      <c r="AN802"/>
+      <c r="AO802"/>
+      <c r="AP802"/>
+      <c r="AQ802"/>
+      <c r="AR802"/>
+      <c r="AS802"/>
+      <c r="AT802"/>
+      <c r="AU802"/>
+      <c r="AV802"/>
+      <c r="AW802"/>
+      <c r="AX802"/>
+      <c r="AY802"/>
+      <c r="AZ802"/>
+      <c r="BA802"/>
+      <c r="BB802"/>
+      <c r="BC802"/>
+      <c r="BD802"/>
+      <c r="BE802"/>
+      <c r="BF802"/>
+      <c r="BG802"/>
+      <c r="BH802"/>
+      <c r="BI802"/>
+      <c r="BJ802"/>
+      <c r="BK802"/>
+      <c r="BL802"/>
+      <c r="BM802"/>
+      <c r="BN802"/>
+      <c r="BO802"/>
+      <c r="BP802"/>
+      <c r="BQ802"/>
+      <c r="BR802"/>
+      <c r="BS802"/>
+      <c r="BT802"/>
+      <c r="BU802"/>
+      <c r="BV802"/>
+      <c r="BW802"/>
+      <c r="BX802"/>
+      <c r="BY802"/>
+      <c r="BZ802"/>
+      <c r="CA802"/>
+      <c r="CB802"/>
+      <c r="CC802"/>
+      <c r="CD802"/>
+      <c r="CE802"/>
+      <c r="CF802"/>
+      <c r="CG802"/>
+      <c r="CH802"/>
+      <c r="CI802"/>
+      <c r="CJ802"/>
+      <c r="CK802"/>
+      <c r="CL802"/>
+      <c r="CM802"/>
+      <c r="CN802"/>
+      <c r="CO802"/>
+      <c r="CP802"/>
+      <c r="CQ802"/>
+      <c r="CR802"/>
+      <c r="CS802"/>
+      <c r="CT802"/>
+      <c r="CU802"/>
+      <c r="CV802"/>
+      <c r="CW802"/>
+      <c r="CX802"/>
+      <c r="CY802"/>
+      <c r="CZ802"/>
+      <c r="DA802"/>
+      <c r="DB802"/>
+      <c r="DC802"/>
+      <c r="DD802"/>
+      <c r="DE802"/>
+      <c r="DF802"/>
+      <c r="DG802"/>
+      <c r="DH802"/>
+      <c r="DI802"/>
+      <c r="DJ802"/>
+      <c r="DK802"/>
+      <c r="DL802"/>
+      <c r="DM802"/>
+      <c r="DN802"/>
+      <c r="DO802"/>
+      <c r="DP802"/>
+      <c r="DQ802"/>
+      <c r="DR802"/>
+      <c r="DS802"/>
+      <c r="DT802"/>
+      <c r="DU802"/>
+      <c r="DV802"/>
+      <c r="DW802"/>
+      <c r="DX802"/>
+      <c r="DY802"/>
+      <c r="DZ802"/>
+      <c r="EA802"/>
+      <c r="EB802"/>
+      <c r="EC802"/>
+      <c r="ED802"/>
+      <c r="EE802"/>
+      <c r="EF802"/>
+      <c r="EG802"/>
+      <c r="EH802"/>
+      <c r="EI802"/>
+      <c r="EJ802"/>
+      <c r="EK802"/>
+      <c r="EL802"/>
+      <c r="EM802"/>
+      <c r="EN802"/>
+      <c r="EO802"/>
+      <c r="EP802"/>
+      <c r="EQ802"/>
+      <c r="ER802"/>
+      <c r="ES802"/>
+      <c r="ET802"/>
+      <c r="EU802"/>
+      <c r="EV802"/>
+      <c r="EW802"/>
+      <c r="EX802"/>
+      <c r="EY802"/>
+      <c r="EZ802"/>
+      <c r="FA802"/>
+      <c r="FB802"/>
+      <c r="FC802"/>
+      <c r="FD802"/>
+      <c r="FE802"/>
+      <c r="FF802"/>
+      <c r="FG802"/>
+      <c r="FH802"/>
+      <c r="FI802"/>
+      <c r="FJ802"/>
+      <c r="FK802"/>
+      <c r="FL802"/>
+      <c r="FM802"/>
+      <c r="FN802"/>
+      <c r="FO802"/>
+      <c r="FP802"/>
+      <c r="FQ802"/>
+      <c r="FR802"/>
+      <c r="FS802"/>
+      <c r="FT802"/>
+      <c r="FU802"/>
+      <c r="FV802"/>
+      <c r="FW802"/>
+      <c r="FX802"/>
+      <c r="FY802"/>
+      <c r="FZ802"/>
+      <c r="GA802"/>
+      <c r="GB802"/>
+      <c r="GC802"/>
+      <c r="GD802"/>
+      <c r="GE802"/>
+      <c r="GF802"/>
+      <c r="GG802"/>
+      <c r="GH802"/>
+      <c r="GI802"/>
+      <c r="GJ802"/>
+      <c r="GK802"/>
+      <c r="GL802"/>
+      <c r="GM802"/>
+      <c r="GN802"/>
+      <c r="GO802"/>
+      <c r="GP802"/>
+      <c r="GQ802"/>
+      <c r="GR802"/>
+      <c r="GS802"/>
+      <c r="GT802"/>
+      <c r="GU802"/>
+      <c r="GV802"/>
+      <c r="GW802"/>
+      <c r="GX802"/>
+      <c r="GY802"/>
+      <c r="GZ802"/>
+      <c r="HA802"/>
+      <c r="HB802"/>
+      <c r="HC802"/>
+      <c r="HD802"/>
+      <c r="HE802"/>
+      <c r="HF802"/>
+      <c r="HG802"/>
+      <c r="HH802"/>
+      <c r="HI802"/>
+      <c r="HJ802"/>
+      <c r="HK802"/>
+      <c r="HL802"/>
+      <c r="HM802"/>
+      <c r="HN802"/>
+      <c r="HO802"/>
+      <c r="HP802"/>
+      <c r="HQ802"/>
+      <c r="HR802"/>
+      <c r="HS802"/>
+      <c r="HT802"/>
+      <c r="HU802"/>
+      <c r="HV802"/>
+      <c r="HW802"/>
+      <c r="HX802"/>
+      <c r="HY802"/>
+      <c r="HZ802"/>
+      <c r="IA802"/>
+      <c r="IB802"/>
+      <c r="IC802"/>
+      <c r="ID802"/>
+      <c r="IE802"/>
+      <c r="IF802"/>
+      <c r="IG802"/>
+      <c r="IH802"/>
+      <c r="II802"/>
+      <c r="IJ802"/>
+      <c r="IK802"/>
+      <c r="IL802"/>
+      <c r="IM802"/>
+      <c r="IN802"/>
+      <c r="IO802"/>
+      <c r="IP802"/>
+      <c r="IQ802"/>
+      <c r="IR802"/>
+      <c r="IS802"/>
+      <c r="IT802"/>
+      <c r="IU802"/>
+      <c r="IV802"/>
+      <c r="IW802"/>
+      <c r="IX802"/>
+      <c r="IY802"/>
+      <c r="IZ802"/>
+      <c r="JA802"/>
+      <c r="JB802"/>
+      <c r="JC802"/>
+      <c r="JD802"/>
+      <c r="JE802"/>
+      <c r="JF802"/>
+      <c r="JG802"/>
+      <c r="JH802"/>
+      <c r="JI802"/>
+      <c r="JJ802"/>
+      <c r="JK802"/>
+      <c r="JL802"/>
+      <c r="JM802"/>
+      <c r="JN802"/>
+      <c r="JO802"/>
+      <c r="JP802"/>
+      <c r="JQ802"/>
+      <c r="JR802"/>
+      <c r="JS802"/>
+      <c r="JT802"/>
+      <c r="JU802"/>
+      <c r="JV802"/>
+      <c r="JW802"/>
+      <c r="JX802"/>
+      <c r="JY802"/>
+      <c r="JZ802"/>
+      <c r="KA802"/>
+      <c r="KB802"/>
+      <c r="KC802"/>
+      <c r="KD802"/>
+      <c r="KE802"/>
+      <c r="KF802"/>
+      <c r="KG802"/>
+      <c r="KH802"/>
+      <c r="KI802"/>
+      <c r="KJ802"/>
+      <c r="KK802"/>
+      <c r="KL802"/>
+      <c r="KM802"/>
+      <c r="KN802"/>
+      <c r="KO802"/>
+      <c r="KP802"/>
+      <c r="KQ802"/>
+      <c r="KR802"/>
+      <c r="KS802"/>
+      <c r="KT802"/>
+      <c r="KU802"/>
+      <c r="KV802"/>
+      <c r="KW802"/>
+      <c r="KX802"/>
+      <c r="KY802"/>
+      <c r="KZ802"/>
+      <c r="LA802"/>
+      <c r="LB802"/>
+      <c r="LC802"/>
+      <c r="LD802"/>
+      <c r="LE802"/>
+      <c r="LF802"/>
+      <c r="LG802"/>
+      <c r="LH802"/>
+      <c r="LI802"/>
+      <c r="LJ802"/>
+      <c r="LK802"/>
+      <c r="LL802"/>
+      <c r="LM802"/>
+      <c r="LN802"/>
+      <c r="LO802"/>
+      <c r="LP802"/>
+      <c r="LQ802"/>
+      <c r="LR802"/>
+      <c r="LS802"/>
+      <c r="LT802"/>
+      <c r="LU802"/>
+      <c r="LV802"/>
+      <c r="LW802"/>
+      <c r="LX802"/>
+      <c r="LY802"/>
+      <c r="LZ802"/>
+      <c r="MA802"/>
+      <c r="MB802"/>
+      <c r="MC802"/>
+      <c r="MD802"/>
+      <c r="ME802"/>
+      <c r="MF802"/>
+      <c r="MG802"/>
+      <c r="MH802"/>
+      <c r="MI802"/>
+      <c r="MJ802"/>
+      <c r="MK802"/>
+      <c r="ML802"/>
+      <c r="MM802"/>
+      <c r="MN802"/>
+      <c r="MO802"/>
+      <c r="MP802"/>
+      <c r="MQ802"/>
+      <c r="MR802"/>
+      <c r="MS802"/>
+      <c r="MT802"/>
+      <c r="MU802"/>
+      <c r="MV802"/>
+      <c r="MW802"/>
+      <c r="MX802"/>
+      <c r="MY802"/>
+      <c r="MZ802"/>
+      <c r="NA802"/>
+      <c r="NB802"/>
+      <c r="NC802"/>
+      <c r="ND802"/>
+      <c r="NE802"/>
+      <c r="NF802"/>
+      <c r="NG802"/>
+      <c r="NH802"/>
+      <c r="NI802"/>
+      <c r="NJ802"/>
+      <c r="NK802"/>
+      <c r="NL802"/>
+      <c r="NM802"/>
+      <c r="NN802"/>
+      <c r="NO802"/>
+      <c r="NP802"/>
+      <c r="NQ802"/>
+      <c r="NR802"/>
+      <c r="NS802"/>
+      <c r="NT802"/>
+      <c r="NU802"/>
+      <c r="NV802"/>
+      <c r="NW802"/>
+      <c r="NX802"/>
+      <c r="NY802"/>
+      <c r="NZ802"/>
+      <c r="OA802"/>
+      <c r="OB802"/>
+      <c r="OC802"/>
+      <c r="OD802"/>
+      <c r="OE802"/>
+      <c r="OF802"/>
+      <c r="OG802"/>
+      <c r="OH802"/>
+      <c r="OI802"/>
+      <c r="OJ802"/>
+      <c r="OK802"/>
+      <c r="OL802"/>
+      <c r="OM802"/>
+      <c r="ON802"/>
+      <c r="OO802"/>
+      <c r="OP802"/>
+      <c r="OQ802"/>
+      <c r="OR802"/>
+      <c r="OS802"/>
+      <c r="OT802"/>
+      <c r="OU802"/>
+      <c r="OV802"/>
+      <c r="OW802"/>
+      <c r="OX802"/>
+      <c r="OY802"/>
+      <c r="OZ802"/>
+      <c r="PA802"/>
+      <c r="PB802"/>
+      <c r="PC802"/>
+      <c r="PD802"/>
+      <c r="PE802"/>
+      <c r="PF802"/>
+      <c r="PG802"/>
+      <c r="PH802"/>
+      <c r="PI802"/>
+      <c r="PJ802"/>
+      <c r="PK802"/>
+      <c r="PL802"/>
+      <c r="PM802"/>
+      <c r="PN802"/>
+      <c r="PO802"/>
+      <c r="PP802"/>
+      <c r="PQ802"/>
+      <c r="PR802"/>
+      <c r="PS802"/>
+      <c r="PT802"/>
+      <c r="PU802"/>
+      <c r="PV802"/>
+      <c r="PW802"/>
+      <c r="PX802"/>
+      <c r="PY802"/>
+      <c r="PZ802"/>
+      <c r="QA802"/>
+      <c r="QB802"/>
+      <c r="QC802"/>
+      <c r="QD802"/>
+      <c r="QE802"/>
+      <c r="QF802"/>
+      <c r="QG802"/>
+      <c r="QH802"/>
+      <c r="QI802"/>
+      <c r="QJ802"/>
+      <c r="QK802"/>
+      <c r="QL802"/>
+      <c r="QM802"/>
+      <c r="QN802"/>
+      <c r="QO802"/>
+      <c r="QP802"/>
+      <c r="QQ802"/>
+      <c r="QR802"/>
+      <c r="QS802"/>
+      <c r="QT802"/>
+      <c r="QU802"/>
+      <c r="QV802"/>
+      <c r="QW802"/>
+      <c r="QX802"/>
+      <c r="QY802"/>
+      <c r="QZ802"/>
+      <c r="RA802"/>
+      <c r="RB802"/>
+      <c r="RC802"/>
+      <c r="RD802"/>
+      <c r="RE802"/>
+      <c r="RF802"/>
+      <c r="RG802"/>
+      <c r="RH802"/>
+      <c r="RI802"/>
+      <c r="RJ802"/>
+      <c r="RK802"/>
+      <c r="RL802"/>
+      <c r="RM802"/>
+      <c r="RN802"/>
+      <c r="RO802"/>
+      <c r="RP802"/>
+      <c r="RQ802"/>
+      <c r="RR802"/>
+      <c r="RS802"/>
+      <c r="RT802"/>
+      <c r="RU802"/>
+      <c r="RV802"/>
+      <c r="RW802"/>
+      <c r="RX802"/>
+      <c r="RY802"/>
+      <c r="RZ802"/>
+      <c r="SA802"/>
+      <c r="SB802"/>
+      <c r="SC802"/>
+      <c r="SD802"/>
+      <c r="SE802"/>
+      <c r="SF802"/>
+      <c r="SG802"/>
+      <c r="SH802"/>
+      <c r="SI802"/>
+      <c r="SJ802"/>
+      <c r="SK802"/>
+      <c r="SL802"/>
+      <c r="SM802"/>
+      <c r="SN802"/>
+      <c r="SO802"/>
+      <c r="SP802"/>
+      <c r="SQ802"/>
+      <c r="SR802"/>
+      <c r="SS802"/>
+      <c r="ST802"/>
+      <c r="SU802"/>
+      <c r="SV802"/>
+      <c r="SW802"/>
+      <c r="SX802"/>
+      <c r="SY802"/>
+      <c r="SZ802"/>
+      <c r="TA802"/>
+      <c r="TB802"/>
+      <c r="TC802"/>
+      <c r="TD802"/>
+      <c r="TE802"/>
+      <c r="TF802"/>
+      <c r="TG802"/>
+      <c r="TH802"/>
+      <c r="TI802"/>
+      <c r="TJ802"/>
+      <c r="TK802"/>
+      <c r="TL802"/>
+      <c r="TM802"/>
+      <c r="TN802"/>
+      <c r="TO802"/>
+      <c r="TP802"/>
+      <c r="TQ802"/>
+      <c r="TR802"/>
+      <c r="TS802"/>
+      <c r="TT802"/>
+      <c r="TU802"/>
+      <c r="TV802"/>
+      <c r="TW802"/>
+      <c r="TX802"/>
+      <c r="TY802"/>
+      <c r="TZ802"/>
+      <c r="UA802"/>
+      <c r="UB802"/>
+      <c r="UC802"/>
+      <c r="UD802"/>
+      <c r="UE802"/>
+      <c r="UF802"/>
+      <c r="UG802"/>
+      <c r="UH802"/>
+      <c r="UI802"/>
+      <c r="UJ802"/>
+      <c r="UK802"/>
+      <c r="UL802"/>
+      <c r="UM802"/>
+      <c r="UN802"/>
+      <c r="UO802"/>
+      <c r="UP802"/>
+      <c r="UQ802"/>
+      <c r="UR802"/>
+      <c r="US802"/>
+      <c r="UT802"/>
+      <c r="UU802"/>
+      <c r="UV802"/>
+      <c r="UW802"/>
+      <c r="UX802"/>
+      <c r="UY802"/>
+      <c r="UZ802"/>
+      <c r="VA802"/>
+      <c r="VB802"/>
+      <c r="VC802"/>
+      <c r="VD802"/>
+      <c r="VE802"/>
+      <c r="VF802"/>
+      <c r="VG802"/>
+      <c r="VH802"/>
+      <c r="VI802"/>
+      <c r="VJ802"/>
+      <c r="VK802"/>
+      <c r="VL802"/>
+      <c r="VM802"/>
+      <c r="VN802"/>
+      <c r="VO802"/>
+      <c r="VP802"/>
+      <c r="VQ802"/>
+      <c r="VR802"/>
+      <c r="VS802"/>
+      <c r="VT802"/>
+      <c r="VU802"/>
+      <c r="VV802"/>
+      <c r="VW802"/>
+      <c r="VX802"/>
+      <c r="VY802"/>
+      <c r="VZ802"/>
+      <c r="WA802"/>
+      <c r="WB802"/>
+      <c r="WC802"/>
+      <c r="WD802"/>
+      <c r="WE802"/>
+      <c r="WF802"/>
+      <c r="WG802"/>
+      <c r="WH802"/>
+      <c r="WI802"/>
+      <c r="WJ802"/>
+      <c r="WK802"/>
+      <c r="WL802"/>
+      <c r="WM802"/>
+      <c r="WN802"/>
+      <c r="WO802"/>
+      <c r="WP802"/>
+      <c r="WQ802"/>
+      <c r="WR802"/>
+      <c r="WS802"/>
+      <c r="WT802"/>
+      <c r="WU802"/>
+      <c r="WV802"/>
+      <c r="WW802"/>
+      <c r="WX802"/>
+      <c r="WY802"/>
+      <c r="WZ802"/>
+      <c r="XA802"/>
+      <c r="XB802"/>
+      <c r="XC802"/>
+      <c r="XD802"/>
+      <c r="XE802"/>
+      <c r="XF802"/>
+      <c r="XG802"/>
+      <c r="XH802"/>
+      <c r="XI802"/>
+      <c r="XJ802"/>
+      <c r="XK802"/>
+      <c r="XL802"/>
+      <c r="XM802"/>
+      <c r="XN802"/>
+      <c r="XO802"/>
+      <c r="XP802"/>
+      <c r="XQ802"/>
+      <c r="XR802"/>
+      <c r="XS802"/>
+      <c r="XT802"/>
+      <c r="XU802"/>
+      <c r="XV802"/>
+      <c r="XW802"/>
+      <c r="XX802"/>
+      <c r="XY802"/>
+      <c r="XZ802"/>
+      <c r="YA802"/>
+      <c r="YB802"/>
+      <c r="YC802"/>
+      <c r="YD802"/>
+      <c r="YE802"/>
+      <c r="YF802"/>
+      <c r="YG802"/>
+      <c r="YH802"/>
+      <c r="YI802"/>
+      <c r="YJ802"/>
+      <c r="YK802"/>
+      <c r="YL802"/>
+      <c r="YM802"/>
+      <c r="YN802"/>
+      <c r="YO802"/>
+      <c r="YP802"/>
+      <c r="YQ802"/>
+      <c r="YR802"/>
+      <c r="YS802"/>
+      <c r="YT802"/>
+      <c r="YU802"/>
+      <c r="YV802"/>
+      <c r="YW802"/>
+      <c r="YX802"/>
+      <c r="YY802"/>
+      <c r="YZ802"/>
+      <c r="ZA802"/>
+      <c r="ZB802"/>
+      <c r="ZC802"/>
+      <c r="ZD802"/>
+      <c r="ZE802"/>
+      <c r="ZF802"/>
+      <c r="ZG802"/>
+      <c r="ZH802"/>
+      <c r="ZI802"/>
+      <c r="ZJ802"/>
+      <c r="ZK802"/>
+      <c r="ZL802"/>
+      <c r="ZM802"/>
+      <c r="ZN802"/>
+      <c r="ZO802"/>
+      <c r="ZP802"/>
+      <c r="ZQ802"/>
+      <c r="ZR802"/>
+      <c r="ZS802"/>
+      <c r="ZT802"/>
+      <c r="ZU802"/>
+      <c r="ZV802"/>
+      <c r="ZW802"/>
+      <c r="ZX802"/>
+      <c r="ZY802"/>
+      <c r="ZZ802"/>
+      <c r="AAA802"/>
+      <c r="AAB802"/>
+      <c r="AAC802"/>
+      <c r="AAD802"/>
+      <c r="AAE802"/>
+      <c r="AAF802"/>
+      <c r="AAG802"/>
+      <c r="AAH802"/>
+      <c r="AAI802"/>
+      <c r="AAJ802"/>
+      <c r="AAK802"/>
+      <c r="AAL802"/>
+      <c r="AAM802"/>
+      <c r="AAN802"/>
+      <c r="AAO802"/>
+      <c r="AAP802"/>
+      <c r="AAQ802"/>
+      <c r="AAR802"/>
+      <c r="AAS802"/>
+      <c r="AAT802"/>
+      <c r="AAU802"/>
+      <c r="AAV802"/>
+      <c r="AAW802"/>
+      <c r="AAX802"/>
+      <c r="AAY802"/>
+      <c r="AAZ802"/>
+      <c r="ABA802"/>
+      <c r="ABB802"/>
+      <c r="ABC802"/>
+      <c r="ABD802"/>
+      <c r="ABE802"/>
+      <c r="ABF802"/>
+      <c r="ABG802"/>
+      <c r="ABH802"/>
+      <c r="ABI802"/>
+      <c r="ABJ802"/>
+      <c r="ABK802"/>
+      <c r="ABL802"/>
+      <c r="ABM802"/>
+      <c r="ABN802"/>
+      <c r="ABO802"/>
+      <c r="ABP802"/>
+      <c r="ABQ802"/>
+      <c r="ABR802"/>
+      <c r="ABS802"/>
+      <c r="ABT802"/>
+      <c r="ABU802"/>
+      <c r="ABV802"/>
+      <c r="ABW802"/>
+      <c r="ABX802"/>
+      <c r="ABY802"/>
+      <c r="ABZ802"/>
+      <c r="ACA802"/>
+      <c r="ACB802"/>
+      <c r="ACC802"/>
+      <c r="ACD802"/>
+      <c r="ACE802"/>
+      <c r="ACF802"/>
+      <c r="ACG802"/>
+      <c r="ACH802"/>
+      <c r="ACI802"/>
+      <c r="ACJ802"/>
+      <c r="ACK802"/>
+      <c r="ACL802"/>
+      <c r="ACM802"/>
+      <c r="ACN802"/>
+      <c r="ACO802"/>
+      <c r="ACP802"/>
+      <c r="ACQ802"/>
+      <c r="ACR802"/>
+      <c r="ACS802"/>
+      <c r="ACT802"/>
+      <c r="ACU802"/>
+      <c r="ACV802"/>
+      <c r="ACW802"/>
+      <c r="ACX802"/>
+      <c r="ACY802"/>
+      <c r="ACZ802"/>
+      <c r="ADA802"/>
+      <c r="ADB802"/>
+      <c r="ADC802"/>
+      <c r="ADD802"/>
+      <c r="ADE802"/>
+      <c r="ADF802"/>
+      <c r="ADG802"/>
+      <c r="ADH802"/>
+      <c r="ADI802"/>
+      <c r="ADJ802"/>
+      <c r="ADK802"/>
+      <c r="ADL802"/>
+      <c r="ADM802"/>
+      <c r="ADN802"/>
+      <c r="ADO802"/>
+      <c r="ADP802"/>
+      <c r="ADQ802"/>
+      <c r="ADR802"/>
+      <c r="ADS802"/>
+      <c r="ADT802"/>
+      <c r="ADU802"/>
+      <c r="ADV802"/>
+      <c r="ADW802"/>
+      <c r="ADX802"/>
+      <c r="ADY802"/>
+      <c r="ADZ802"/>
+      <c r="AEA802"/>
+      <c r="AEB802"/>
+      <c r="AEC802"/>
+      <c r="AED802"/>
+      <c r="AEE802"/>
+      <c r="AEF802"/>
+      <c r="AEG802"/>
+      <c r="AEH802"/>
+      <c r="AEI802"/>
+      <c r="AEJ802"/>
+      <c r="AEK802"/>
+      <c r="AEL802"/>
+      <c r="AEM802"/>
+      <c r="AEN802"/>
+      <c r="AEO802"/>
+      <c r="AEP802"/>
+      <c r="AEQ802"/>
+      <c r="AER802"/>
+      <c r="AES802"/>
+      <c r="AET802"/>
+      <c r="AEU802"/>
+      <c r="AEV802"/>
+      <c r="AEW802"/>
+      <c r="AEX802"/>
+      <c r="AEY802"/>
+      <c r="AEZ802"/>
+      <c r="AFA802"/>
+      <c r="AFB802"/>
+      <c r="AFC802"/>
+      <c r="AFD802"/>
+      <c r="AFE802"/>
+      <c r="AFF802"/>
+      <c r="AFG802"/>
+      <c r="AFH802"/>
+      <c r="AFI802"/>
+      <c r="AFJ802"/>
+      <c r="AFK802"/>
+      <c r="AFL802"/>
+      <c r="AFM802"/>
+      <c r="AFN802"/>
+      <c r="AFO802"/>
+      <c r="AFP802"/>
+      <c r="AFQ802"/>
+      <c r="AFR802"/>
+      <c r="AFS802"/>
+      <c r="AFT802"/>
+      <c r="AFU802"/>
+      <c r="AFV802"/>
+      <c r="AFW802"/>
+      <c r="AFX802"/>
+      <c r="AFY802"/>
+      <c r="AFZ802"/>
+      <c r="AGA802"/>
+      <c r="AGB802"/>
+      <c r="AGC802"/>
+      <c r="AGD802"/>
+      <c r="AGE802"/>
+      <c r="AGF802"/>
+      <c r="AGG802"/>
+      <c r="AGH802"/>
+      <c r="AGI802"/>
+      <c r="AGJ802"/>
+      <c r="AGK802"/>
+      <c r="AGL802"/>
+      <c r="AGM802"/>
+      <c r="AGN802"/>
+      <c r="AGO802"/>
+      <c r="AGP802"/>
+      <c r="AGQ802"/>
+      <c r="AGR802"/>
+      <c r="AGS802"/>
+      <c r="AGT802"/>
+      <c r="AGU802"/>
+      <c r="AGV802"/>
+      <c r="AGW802"/>
+      <c r="AGX802"/>
+      <c r="AGY802"/>
+      <c r="AGZ802"/>
+      <c r="AHA802"/>
+      <c r="AHB802"/>
+      <c r="AHC802"/>
+      <c r="AHD802"/>
+      <c r="AHE802"/>
+      <c r="AHF802"/>
+      <c r="AHG802"/>
+      <c r="AHH802"/>
+      <c r="AHI802"/>
+      <c r="AHJ802"/>
+      <c r="AHK802"/>
+      <c r="AHL802"/>
+      <c r="AHM802"/>
+      <c r="AHN802"/>
+      <c r="AHO802"/>
+      <c r="AHP802"/>
+      <c r="AHQ802"/>
+      <c r="AHR802"/>
+      <c r="AHS802"/>
+      <c r="AHT802"/>
+      <c r="AHU802"/>
+      <c r="AHV802"/>
+      <c r="AHW802"/>
+      <c r="AHX802"/>
+      <c r="AHY802"/>
+      <c r="AHZ802"/>
+      <c r="AIA802"/>
+      <c r="AIB802"/>
+      <c r="AIC802"/>
+      <c r="AID802"/>
+      <c r="AIE802"/>
+      <c r="AIF802"/>
+      <c r="AIG802"/>
+      <c r="AIH802"/>
+      <c r="AII802"/>
+      <c r="AIJ802"/>
+      <c r="AIK802"/>
+      <c r="AIL802"/>
+      <c r="AIM802"/>
+      <c r="AIN802"/>
+      <c r="AIO802"/>
+      <c r="AIP802"/>
+      <c r="AIQ802"/>
+      <c r="AIR802"/>
+      <c r="AIS802"/>
+      <c r="AIT802"/>
+      <c r="AIU802"/>
+      <c r="AIV802"/>
+      <c r="AIW802"/>
+      <c r="AIX802"/>
+      <c r="AIY802"/>
+      <c r="AIZ802"/>
+      <c r="AJA802"/>
+      <c r="AJB802"/>
+      <c r="AJC802"/>
+      <c r="AJD802"/>
+      <c r="AJE802"/>
+      <c r="AJF802"/>
+      <c r="AJG802"/>
+      <c r="AJH802"/>
+      <c r="AJI802"/>
+      <c r="AJJ802"/>
+      <c r="AJK802"/>
+      <c r="AJL802"/>
+      <c r="AJM802"/>
+      <c r="AJN802"/>
+      <c r="AJO802"/>
+      <c r="AJP802"/>
+      <c r="AJQ802"/>
+      <c r="AJR802"/>
+      <c r="AJS802"/>
+      <c r="AJT802"/>
+      <c r="AJU802"/>
+      <c r="AJV802"/>
+      <c r="AJW802"/>
+      <c r="AJX802"/>
+      <c r="AJY802"/>
+      <c r="AJZ802"/>
+      <c r="AKA802"/>
+      <c r="AKB802"/>
+      <c r="AKC802"/>
+      <c r="AKD802"/>
+      <c r="AKE802"/>
+      <c r="AKF802"/>
+      <c r="AKG802"/>
+      <c r="AKH802"/>
+      <c r="AKI802"/>
+      <c r="AKJ802"/>
+      <c r="AKK802"/>
+      <c r="AKL802"/>
+      <c r="AKM802"/>
+      <c r="AKN802"/>
+      <c r="AKO802"/>
+      <c r="AKP802"/>
+      <c r="AKQ802"/>
+      <c r="AKR802"/>
+      <c r="AKS802"/>
+      <c r="AKT802"/>
+      <c r="AKU802"/>
+      <c r="AKV802"/>
+      <c r="AKW802"/>
+      <c r="AKX802"/>
+      <c r="AKY802"/>
+      <c r="AKZ802"/>
+      <c r="ALA802"/>
+      <c r="ALB802"/>
+      <c r="ALC802"/>
+      <c r="ALD802"/>
+      <c r="ALE802"/>
+      <c r="ALF802"/>
+      <c r="ALG802"/>
+      <c r="ALH802"/>
+      <c r="ALI802"/>
+      <c r="ALJ802"/>
+      <c r="ALK802"/>
+      <c r="ALL802"/>
+      <c r="ALM802"/>
+      <c r="ALN802"/>
+      <c r="ALO802"/>
+      <c r="ALP802"/>
+      <c r="ALQ802"/>
+      <c r="ALR802"/>
+      <c r="ALS802"/>
+      <c r="ALT802"/>
+      <c r="ALU802"/>
+      <c r="ALV802"/>
+      <c r="ALW802"/>
+      <c r="ALX802"/>
+      <c r="ALY802"/>
+      <c r="ALZ802"/>
+      <c r="AMA802"/>
+      <c r="AMB802"/>
+      <c r="AMC802"/>
+      <c r="AMD802"/>
+      <c r="AME802"/>
+      <c r="AMF802"/>
+      <c r="AMG802"/>
+      <c r="AMH802"/>
+    </row>
+    <row r="803" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A803" s="8" t="s">
-        <v>2333</v>
+        <v>2983</v>
       </c>
       <c r="B803" s="8" t="s">
-        <v>210</v>
+        <v>2978</v>
       </c>
       <c r="C803" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_quant_algorithm:maxlfq</v>
+        <v>att_ptm_enrichment:metal</v>
       </c>
       <c r="D803" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E803" s="8" t="s">
-        <v>2334</v>
-      </c>
-      <c r="F803" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2984</v>
+      </c>
+      <c r="F803" s="8" t="s">
+        <v>2985</v>
+      </c>
+      <c r="G803"/>
+      <c r="H803"/>
+      <c r="I803"/>
+      <c r="J803"/>
+      <c r="K803"/>
+      <c r="L803"/>
+      <c r="M803"/>
+      <c r="N803"/>
+      <c r="O803"/>
+      <c r="P803"/>
+      <c r="Q803"/>
+      <c r="R803"/>
+      <c r="S803"/>
+      <c r="T803"/>
+      <c r="U803"/>
+      <c r="V803"/>
+      <c r="W803"/>
+      <c r="X803"/>
+      <c r="Y803"/>
+      <c r="Z803"/>
+      <c r="AA803"/>
+      <c r="AB803"/>
+      <c r="AC803"/>
+      <c r="AD803"/>
+      <c r="AE803"/>
+      <c r="AF803"/>
+      <c r="AG803"/>
+      <c r="AH803"/>
+      <c r="AI803"/>
+      <c r="AJ803"/>
+      <c r="AK803"/>
+      <c r="AL803"/>
+      <c r="AM803"/>
+      <c r="AN803"/>
+      <c r="AO803"/>
+      <c r="AP803"/>
+      <c r="AQ803"/>
+      <c r="AR803"/>
+      <c r="AS803"/>
+      <c r="AT803"/>
+      <c r="AU803"/>
+      <c r="AV803"/>
+      <c r="AW803"/>
+      <c r="AX803"/>
+      <c r="AY803"/>
+      <c r="AZ803"/>
+      <c r="BA803"/>
+      <c r="BB803"/>
+      <c r="BC803"/>
+      <c r="BD803"/>
+      <c r="BE803"/>
+      <c r="BF803"/>
+      <c r="BG803"/>
+      <c r="BH803"/>
+      <c r="BI803"/>
+      <c r="BJ803"/>
+      <c r="BK803"/>
+      <c r="BL803"/>
+      <c r="BM803"/>
+      <c r="BN803"/>
+      <c r="BO803"/>
+      <c r="BP803"/>
+      <c r="BQ803"/>
+      <c r="BR803"/>
+      <c r="BS803"/>
+      <c r="BT803"/>
+      <c r="BU803"/>
+      <c r="BV803"/>
+      <c r="BW803"/>
+      <c r="BX803"/>
+      <c r="BY803"/>
+      <c r="BZ803"/>
+      <c r="CA803"/>
+      <c r="CB803"/>
+      <c r="CC803"/>
+      <c r="CD803"/>
+      <c r="CE803"/>
+      <c r="CF803"/>
+      <c r="CG803"/>
+      <c r="CH803"/>
+      <c r="CI803"/>
+      <c r="CJ803"/>
+      <c r="CK803"/>
+      <c r="CL803"/>
+      <c r="CM803"/>
+      <c r="CN803"/>
+      <c r="CO803"/>
+      <c r="CP803"/>
+      <c r="CQ803"/>
+      <c r="CR803"/>
+      <c r="CS803"/>
+      <c r="CT803"/>
+      <c r="CU803"/>
+      <c r="CV803"/>
+      <c r="CW803"/>
+      <c r="CX803"/>
+      <c r="CY803"/>
+      <c r="CZ803"/>
+      <c r="DA803"/>
+      <c r="DB803"/>
+      <c r="DC803"/>
+      <c r="DD803"/>
+      <c r="DE803"/>
+      <c r="DF803"/>
+      <c r="DG803"/>
+      <c r="DH803"/>
+      <c r="DI803"/>
+      <c r="DJ803"/>
+      <c r="DK803"/>
+      <c r="DL803"/>
+      <c r="DM803"/>
+      <c r="DN803"/>
+      <c r="DO803"/>
+      <c r="DP803"/>
+      <c r="DQ803"/>
+      <c r="DR803"/>
+      <c r="DS803"/>
+      <c r="DT803"/>
+      <c r="DU803"/>
+      <c r="DV803"/>
+      <c r="DW803"/>
+      <c r="DX803"/>
+      <c r="DY803"/>
+      <c r="DZ803"/>
+      <c r="EA803"/>
+      <c r="EB803"/>
+      <c r="EC803"/>
+      <c r="ED803"/>
+      <c r="EE803"/>
+      <c r="EF803"/>
+      <c r="EG803"/>
+      <c r="EH803"/>
+      <c r="EI803"/>
+      <c r="EJ803"/>
+      <c r="EK803"/>
+      <c r="EL803"/>
+      <c r="EM803"/>
+      <c r="EN803"/>
+      <c r="EO803"/>
+      <c r="EP803"/>
+      <c r="EQ803"/>
+      <c r="ER803"/>
+      <c r="ES803"/>
+      <c r="ET803"/>
+      <c r="EU803"/>
+      <c r="EV803"/>
+      <c r="EW803"/>
+      <c r="EX803"/>
+      <c r="EY803"/>
+      <c r="EZ803"/>
+      <c r="FA803"/>
+      <c r="FB803"/>
+      <c r="FC803"/>
+      <c r="FD803"/>
+      <c r="FE803"/>
+      <c r="FF803"/>
+      <c r="FG803"/>
+      <c r="FH803"/>
+      <c r="FI803"/>
+      <c r="FJ803"/>
+      <c r="FK803"/>
+      <c r="FL803"/>
+      <c r="FM803"/>
+      <c r="FN803"/>
+      <c r="FO803"/>
+      <c r="FP803"/>
+      <c r="FQ803"/>
+      <c r="FR803"/>
+      <c r="FS803"/>
+      <c r="FT803"/>
+      <c r="FU803"/>
+      <c r="FV803"/>
+      <c r="FW803"/>
+      <c r="FX803"/>
+      <c r="FY803"/>
+      <c r="FZ803"/>
+      <c r="GA803"/>
+      <c r="GB803"/>
+      <c r="GC803"/>
+      <c r="GD803"/>
+      <c r="GE803"/>
+      <c r="GF803"/>
+      <c r="GG803"/>
+      <c r="GH803"/>
+      <c r="GI803"/>
+      <c r="GJ803"/>
+      <c r="GK803"/>
+      <c r="GL803"/>
+      <c r="GM803"/>
+      <c r="GN803"/>
+      <c r="GO803"/>
+      <c r="GP803"/>
+      <c r="GQ803"/>
+      <c r="GR803"/>
+      <c r="GS803"/>
+      <c r="GT803"/>
+      <c r="GU803"/>
+      <c r="GV803"/>
+      <c r="GW803"/>
+      <c r="GX803"/>
+      <c r="GY803"/>
+      <c r="GZ803"/>
+      <c r="HA803"/>
+      <c r="HB803"/>
+      <c r="HC803"/>
+      <c r="HD803"/>
+      <c r="HE803"/>
+      <c r="HF803"/>
+      <c r="HG803"/>
+      <c r="HH803"/>
+      <c r="HI803"/>
+      <c r="HJ803"/>
+      <c r="HK803"/>
+      <c r="HL803"/>
+      <c r="HM803"/>
+      <c r="HN803"/>
+      <c r="HO803"/>
+      <c r="HP803"/>
+      <c r="HQ803"/>
+      <c r="HR803"/>
+      <c r="HS803"/>
+      <c r="HT803"/>
+      <c r="HU803"/>
+      <c r="HV803"/>
+      <c r="HW803"/>
+      <c r="HX803"/>
+      <c r="HY803"/>
+      <c r="HZ803"/>
+      <c r="IA803"/>
+      <c r="IB803"/>
+      <c r="IC803"/>
+      <c r="ID803"/>
+      <c r="IE803"/>
+      <c r="IF803"/>
+      <c r="IG803"/>
+      <c r="IH803"/>
+      <c r="II803"/>
+      <c r="IJ803"/>
+      <c r="IK803"/>
+      <c r="IL803"/>
+      <c r="IM803"/>
+      <c r="IN803"/>
+      <c r="IO803"/>
+      <c r="IP803"/>
+      <c r="IQ803"/>
+      <c r="IR803"/>
+      <c r="IS803"/>
+      <c r="IT803"/>
+      <c r="IU803"/>
+      <c r="IV803"/>
+      <c r="IW803"/>
+      <c r="IX803"/>
+      <c r="IY803"/>
+      <c r="IZ803"/>
+      <c r="JA803"/>
+      <c r="JB803"/>
+      <c r="JC803"/>
+      <c r="JD803"/>
+      <c r="JE803"/>
+      <c r="JF803"/>
+      <c r="JG803"/>
+      <c r="JH803"/>
+      <c r="JI803"/>
+      <c r="JJ803"/>
+      <c r="JK803"/>
+      <c r="JL803"/>
+      <c r="JM803"/>
+      <c r="JN803"/>
+      <c r="JO803"/>
+      <c r="JP803"/>
+      <c r="JQ803"/>
+      <c r="JR803"/>
+      <c r="JS803"/>
+      <c r="JT803"/>
+      <c r="JU803"/>
+      <c r="JV803"/>
+      <c r="JW803"/>
+      <c r="JX803"/>
+      <c r="JY803"/>
+      <c r="JZ803"/>
+      <c r="KA803"/>
+      <c r="KB803"/>
+      <c r="KC803"/>
+      <c r="KD803"/>
+      <c r="KE803"/>
+      <c r="KF803"/>
+      <c r="KG803"/>
+      <c r="KH803"/>
+      <c r="KI803"/>
+      <c r="KJ803"/>
+      <c r="KK803"/>
+      <c r="KL803"/>
+      <c r="KM803"/>
+      <c r="KN803"/>
+      <c r="KO803"/>
+      <c r="KP803"/>
+      <c r="KQ803"/>
+      <c r="KR803"/>
+      <c r="KS803"/>
+      <c r="KT803"/>
+      <c r="KU803"/>
+      <c r="KV803"/>
+      <c r="KW803"/>
+      <c r="KX803"/>
+      <c r="KY803"/>
+      <c r="KZ803"/>
+      <c r="LA803"/>
+      <c r="LB803"/>
+      <c r="LC803"/>
+      <c r="LD803"/>
+      <c r="LE803"/>
+      <c r="LF803"/>
+      <c r="LG803"/>
+      <c r="LH803"/>
+      <c r="LI803"/>
+      <c r="LJ803"/>
+      <c r="LK803"/>
+      <c r="LL803"/>
+      <c r="LM803"/>
+      <c r="LN803"/>
+      <c r="LO803"/>
+      <c r="LP803"/>
+      <c r="LQ803"/>
+      <c r="LR803"/>
+      <c r="LS803"/>
+      <c r="LT803"/>
+      <c r="LU803"/>
+      <c r="LV803"/>
+      <c r="LW803"/>
+      <c r="LX803"/>
+      <c r="LY803"/>
+      <c r="LZ803"/>
+      <c r="MA803"/>
+      <c r="MB803"/>
+      <c r="MC803"/>
+      <c r="MD803"/>
+      <c r="ME803"/>
+      <c r="MF803"/>
+      <c r="MG803"/>
+      <c r="MH803"/>
+      <c r="MI803"/>
+      <c r="MJ803"/>
+      <c r="MK803"/>
+      <c r="ML803"/>
+      <c r="MM803"/>
+      <c r="MN803"/>
+      <c r="MO803"/>
+      <c r="MP803"/>
+      <c r="MQ803"/>
+      <c r="MR803"/>
+      <c r="MS803"/>
+      <c r="MT803"/>
+      <c r="MU803"/>
+      <c r="MV803"/>
+      <c r="MW803"/>
+      <c r="MX803"/>
+      <c r="MY803"/>
+      <c r="MZ803"/>
+      <c r="NA803"/>
+      <c r="NB803"/>
+      <c r="NC803"/>
+      <c r="ND803"/>
+      <c r="NE803"/>
+      <c r="NF803"/>
+      <c r="NG803"/>
+      <c r="NH803"/>
+      <c r="NI803"/>
+      <c r="NJ803"/>
+      <c r="NK803"/>
+      <c r="NL803"/>
+      <c r="NM803"/>
+      <c r="NN803"/>
+      <c r="NO803"/>
+      <c r="NP803"/>
+      <c r="NQ803"/>
+      <c r="NR803"/>
+      <c r="NS803"/>
+      <c r="NT803"/>
+      <c r="NU803"/>
+      <c r="NV803"/>
+      <c r="NW803"/>
+      <c r="NX803"/>
+      <c r="NY803"/>
+      <c r="NZ803"/>
+      <c r="OA803"/>
+      <c r="OB803"/>
+      <c r="OC803"/>
+      <c r="OD803"/>
+      <c r="OE803"/>
+      <c r="OF803"/>
+      <c r="OG803"/>
+      <c r="OH803"/>
+      <c r="OI803"/>
+      <c r="OJ803"/>
+      <c r="OK803"/>
+      <c r="OL803"/>
+      <c r="OM803"/>
+      <c r="ON803"/>
+      <c r="OO803"/>
+      <c r="OP803"/>
+      <c r="OQ803"/>
+      <c r="OR803"/>
+      <c r="OS803"/>
+      <c r="OT803"/>
+      <c r="OU803"/>
+      <c r="OV803"/>
+      <c r="OW803"/>
+      <c r="OX803"/>
+      <c r="OY803"/>
+      <c r="OZ803"/>
+      <c r="PA803"/>
+      <c r="PB803"/>
+      <c r="PC803"/>
+      <c r="PD803"/>
+      <c r="PE803"/>
+      <c r="PF803"/>
+      <c r="PG803"/>
+      <c r="PH803"/>
+      <c r="PI803"/>
+      <c r="PJ803"/>
+      <c r="PK803"/>
+      <c r="PL803"/>
+      <c r="PM803"/>
+      <c r="PN803"/>
+      <c r="PO803"/>
+      <c r="PP803"/>
+      <c r="PQ803"/>
+      <c r="PR803"/>
+      <c r="PS803"/>
+      <c r="PT803"/>
+      <c r="PU803"/>
+      <c r="PV803"/>
+      <c r="PW803"/>
+      <c r="PX803"/>
+      <c r="PY803"/>
+      <c r="PZ803"/>
+      <c r="QA803"/>
+      <c r="QB803"/>
+      <c r="QC803"/>
+      <c r="QD803"/>
+      <c r="QE803"/>
+      <c r="QF803"/>
+      <c r="QG803"/>
+      <c r="QH803"/>
+      <c r="QI803"/>
+      <c r="QJ803"/>
+      <c r="QK803"/>
+      <c r="QL803"/>
+      <c r="QM803"/>
+      <c r="QN803"/>
+      <c r="QO803"/>
+      <c r="QP803"/>
+      <c r="QQ803"/>
+      <c r="QR803"/>
+      <c r="QS803"/>
+      <c r="QT803"/>
+      <c r="QU803"/>
+      <c r="QV803"/>
+      <c r="QW803"/>
+      <c r="QX803"/>
+      <c r="QY803"/>
+      <c r="QZ803"/>
+      <c r="RA803"/>
+      <c r="RB803"/>
+      <c r="RC803"/>
+      <c r="RD803"/>
+      <c r="RE803"/>
+      <c r="RF803"/>
+      <c r="RG803"/>
+      <c r="RH803"/>
+      <c r="RI803"/>
+      <c r="RJ803"/>
+      <c r="RK803"/>
+      <c r="RL803"/>
+      <c r="RM803"/>
+      <c r="RN803"/>
+      <c r="RO803"/>
+      <c r="RP803"/>
+      <c r="RQ803"/>
+      <c r="RR803"/>
+      <c r="RS803"/>
+      <c r="RT803"/>
+      <c r="RU803"/>
+      <c r="RV803"/>
+      <c r="RW803"/>
+      <c r="RX803"/>
+      <c r="RY803"/>
+      <c r="RZ803"/>
+      <c r="SA803"/>
+      <c r="SB803"/>
+      <c r="SC803"/>
+      <c r="SD803"/>
+      <c r="SE803"/>
+      <c r="SF803"/>
+      <c r="SG803"/>
+      <c r="SH803"/>
+      <c r="SI803"/>
+      <c r="SJ803"/>
+      <c r="SK803"/>
+      <c r="SL803"/>
+      <c r="SM803"/>
+      <c r="SN803"/>
+      <c r="SO803"/>
+      <c r="SP803"/>
+      <c r="SQ803"/>
+      <c r="SR803"/>
+      <c r="SS803"/>
+      <c r="ST803"/>
+      <c r="SU803"/>
+      <c r="SV803"/>
+      <c r="SW803"/>
+      <c r="SX803"/>
+      <c r="SY803"/>
+      <c r="SZ803"/>
+      <c r="TA803"/>
+      <c r="TB803"/>
+      <c r="TC803"/>
+      <c r="TD803"/>
+      <c r="TE803"/>
+      <c r="TF803"/>
+      <c r="TG803"/>
+      <c r="TH803"/>
+      <c r="TI803"/>
+      <c r="TJ803"/>
+      <c r="TK803"/>
+      <c r="TL803"/>
+      <c r="TM803"/>
+      <c r="TN803"/>
+      <c r="TO803"/>
+      <c r="TP803"/>
+      <c r="TQ803"/>
+      <c r="TR803"/>
+      <c r="TS803"/>
+      <c r="TT803"/>
+      <c r="TU803"/>
+      <c r="TV803"/>
+      <c r="TW803"/>
+      <c r="TX803"/>
+      <c r="TY803"/>
+      <c r="TZ803"/>
+      <c r="UA803"/>
+      <c r="UB803"/>
+      <c r="UC803"/>
+      <c r="UD803"/>
+      <c r="UE803"/>
+      <c r="UF803"/>
+      <c r="UG803"/>
+      <c r="UH803"/>
+      <c r="UI803"/>
+      <c r="UJ803"/>
+      <c r="UK803"/>
+      <c r="UL803"/>
+      <c r="UM803"/>
+      <c r="UN803"/>
+      <c r="UO803"/>
+      <c r="UP803"/>
+      <c r="UQ803"/>
+      <c r="UR803"/>
+      <c r="US803"/>
+      <c r="UT803"/>
+      <c r="UU803"/>
+      <c r="UV803"/>
+      <c r="UW803"/>
+      <c r="UX803"/>
+      <c r="UY803"/>
+      <c r="UZ803"/>
+      <c r="VA803"/>
+      <c r="VB803"/>
+      <c r="VC803"/>
+      <c r="VD803"/>
+      <c r="VE803"/>
+      <c r="VF803"/>
+      <c r="VG803"/>
+      <c r="VH803"/>
+      <c r="VI803"/>
+      <c r="VJ803"/>
+      <c r="VK803"/>
+      <c r="VL803"/>
+      <c r="VM803"/>
+      <c r="VN803"/>
+      <c r="VO803"/>
+      <c r="VP803"/>
+      <c r="VQ803"/>
+      <c r="VR803"/>
+      <c r="VS803"/>
+      <c r="VT803"/>
+      <c r="VU803"/>
+      <c r="VV803"/>
+      <c r="VW803"/>
+      <c r="VX803"/>
+      <c r="VY803"/>
+      <c r="VZ803"/>
+      <c r="WA803"/>
+      <c r="WB803"/>
+      <c r="WC803"/>
+      <c r="WD803"/>
+      <c r="WE803"/>
+      <c r="WF803"/>
+      <c r="WG803"/>
+      <c r="WH803"/>
+      <c r="WI803"/>
+      <c r="WJ803"/>
+      <c r="WK803"/>
+      <c r="WL803"/>
+      <c r="WM803"/>
+      <c r="WN803"/>
+      <c r="WO803"/>
+      <c r="WP803"/>
+      <c r="WQ803"/>
+      <c r="WR803"/>
+      <c r="WS803"/>
+      <c r="WT803"/>
+      <c r="WU803"/>
+      <c r="WV803"/>
+      <c r="WW803"/>
+      <c r="WX803"/>
+      <c r="WY803"/>
+      <c r="WZ803"/>
+      <c r="XA803"/>
+      <c r="XB803"/>
+      <c r="XC803"/>
+      <c r="XD803"/>
+      <c r="XE803"/>
+      <c r="XF803"/>
+      <c r="XG803"/>
+      <c r="XH803"/>
+      <c r="XI803"/>
+      <c r="XJ803"/>
+      <c r="XK803"/>
+      <c r="XL803"/>
+      <c r="XM803"/>
+      <c r="XN803"/>
+      <c r="XO803"/>
+      <c r="XP803"/>
+      <c r="XQ803"/>
+      <c r="XR803"/>
+      <c r="XS803"/>
+      <c r="XT803"/>
+      <c r="XU803"/>
+      <c r="XV803"/>
+      <c r="XW803"/>
+      <c r="XX803"/>
+      <c r="XY803"/>
+      <c r="XZ803"/>
+      <c r="YA803"/>
+      <c r="YB803"/>
+      <c r="YC803"/>
+      <c r="YD803"/>
+      <c r="YE803"/>
+      <c r="YF803"/>
+      <c r="YG803"/>
+      <c r="YH803"/>
+      <c r="YI803"/>
+      <c r="YJ803"/>
+      <c r="YK803"/>
+      <c r="YL803"/>
+      <c r="YM803"/>
+      <c r="YN803"/>
+      <c r="YO803"/>
+      <c r="YP803"/>
+      <c r="YQ803"/>
+      <c r="YR803"/>
+      <c r="YS803"/>
+      <c r="YT803"/>
+      <c r="YU803"/>
+      <c r="YV803"/>
+      <c r="YW803"/>
+      <c r="YX803"/>
+      <c r="YY803"/>
+      <c r="YZ803"/>
+      <c r="ZA803"/>
+      <c r="ZB803"/>
+      <c r="ZC803"/>
+      <c r="ZD803"/>
+      <c r="ZE803"/>
+      <c r="ZF803"/>
+      <c r="ZG803"/>
+      <c r="ZH803"/>
+      <c r="ZI803"/>
+      <c r="ZJ803"/>
+      <c r="ZK803"/>
+      <c r="ZL803"/>
+      <c r="ZM803"/>
+      <c r="ZN803"/>
+      <c r="ZO803"/>
+      <c r="ZP803"/>
+      <c r="ZQ803"/>
+      <c r="ZR803"/>
+      <c r="ZS803"/>
+      <c r="ZT803"/>
+      <c r="ZU803"/>
+      <c r="ZV803"/>
+      <c r="ZW803"/>
+      <c r="ZX803"/>
+      <c r="ZY803"/>
+      <c r="ZZ803"/>
+      <c r="AAA803"/>
+      <c r="AAB803"/>
+      <c r="AAC803"/>
+      <c r="AAD803"/>
+      <c r="AAE803"/>
+      <c r="AAF803"/>
+      <c r="AAG803"/>
+      <c r="AAH803"/>
+      <c r="AAI803"/>
+      <c r="AAJ803"/>
+      <c r="AAK803"/>
+      <c r="AAL803"/>
+      <c r="AAM803"/>
+      <c r="AAN803"/>
+      <c r="AAO803"/>
+      <c r="AAP803"/>
+      <c r="AAQ803"/>
+      <c r="AAR803"/>
+      <c r="AAS803"/>
+      <c r="AAT803"/>
+      <c r="AAU803"/>
+      <c r="AAV803"/>
+      <c r="AAW803"/>
+      <c r="AAX803"/>
+      <c r="AAY803"/>
+      <c r="AAZ803"/>
+      <c r="ABA803"/>
+      <c r="ABB803"/>
+      <c r="ABC803"/>
+      <c r="ABD803"/>
+      <c r="ABE803"/>
+      <c r="ABF803"/>
+      <c r="ABG803"/>
+      <c r="ABH803"/>
+      <c r="ABI803"/>
+      <c r="ABJ803"/>
+      <c r="ABK803"/>
+      <c r="ABL803"/>
+      <c r="ABM803"/>
+      <c r="ABN803"/>
+      <c r="ABO803"/>
+      <c r="ABP803"/>
+      <c r="ABQ803"/>
+      <c r="ABR803"/>
+      <c r="ABS803"/>
+      <c r="ABT803"/>
+      <c r="ABU803"/>
+      <c r="ABV803"/>
+      <c r="ABW803"/>
+      <c r="ABX803"/>
+      <c r="ABY803"/>
+      <c r="ABZ803"/>
+      <c r="ACA803"/>
+      <c r="ACB803"/>
+      <c r="ACC803"/>
+      <c r="ACD803"/>
+      <c r="ACE803"/>
+      <c r="ACF803"/>
+      <c r="ACG803"/>
+      <c r="ACH803"/>
+      <c r="ACI803"/>
+      <c r="ACJ803"/>
+      <c r="ACK803"/>
+      <c r="ACL803"/>
+      <c r="ACM803"/>
+      <c r="ACN803"/>
+      <c r="ACO803"/>
+      <c r="ACP803"/>
+      <c r="ACQ803"/>
+      <c r="ACR803"/>
+      <c r="ACS803"/>
+      <c r="ACT803"/>
+      <c r="ACU803"/>
+      <c r="ACV803"/>
+      <c r="ACW803"/>
+      <c r="ACX803"/>
+      <c r="ACY803"/>
+      <c r="ACZ803"/>
+      <c r="ADA803"/>
+      <c r="ADB803"/>
+      <c r="ADC803"/>
+      <c r="ADD803"/>
+      <c r="ADE803"/>
+      <c r="ADF803"/>
+      <c r="ADG803"/>
+      <c r="ADH803"/>
+      <c r="ADI803"/>
+      <c r="ADJ803"/>
+      <c r="ADK803"/>
+      <c r="ADL803"/>
+      <c r="ADM803"/>
+      <c r="ADN803"/>
+      <c r="ADO803"/>
+      <c r="ADP803"/>
+      <c r="ADQ803"/>
+      <c r="ADR803"/>
+      <c r="ADS803"/>
+      <c r="ADT803"/>
+      <c r="ADU803"/>
+      <c r="ADV803"/>
+      <c r="ADW803"/>
+      <c r="ADX803"/>
+      <c r="ADY803"/>
+      <c r="ADZ803"/>
+      <c r="AEA803"/>
+      <c r="AEB803"/>
+      <c r="AEC803"/>
+      <c r="AED803"/>
+      <c r="AEE803"/>
+      <c r="AEF803"/>
+      <c r="AEG803"/>
+      <c r="AEH803"/>
+      <c r="AEI803"/>
+      <c r="AEJ803"/>
+      <c r="AEK803"/>
+      <c r="AEL803"/>
+      <c r="AEM803"/>
+      <c r="AEN803"/>
+      <c r="AEO803"/>
+      <c r="AEP803"/>
+      <c r="AEQ803"/>
+      <c r="AER803"/>
+      <c r="AES803"/>
+      <c r="AET803"/>
+      <c r="AEU803"/>
+      <c r="AEV803"/>
+      <c r="AEW803"/>
+      <c r="AEX803"/>
+      <c r="AEY803"/>
+      <c r="AEZ803"/>
+      <c r="AFA803"/>
+      <c r="AFB803"/>
+      <c r="AFC803"/>
+      <c r="AFD803"/>
+      <c r="AFE803"/>
+      <c r="AFF803"/>
+      <c r="AFG803"/>
+      <c r="AFH803"/>
+      <c r="AFI803"/>
+      <c r="AFJ803"/>
+      <c r="AFK803"/>
+      <c r="AFL803"/>
+      <c r="AFM803"/>
+      <c r="AFN803"/>
+      <c r="AFO803"/>
+      <c r="AFP803"/>
+      <c r="AFQ803"/>
+      <c r="AFR803"/>
+      <c r="AFS803"/>
+      <c r="AFT803"/>
+      <c r="AFU803"/>
+      <c r="AFV803"/>
+      <c r="AFW803"/>
+      <c r="AFX803"/>
+      <c r="AFY803"/>
+      <c r="AFZ803"/>
+      <c r="AGA803"/>
+      <c r="AGB803"/>
+      <c r="AGC803"/>
+      <c r="AGD803"/>
+      <c r="AGE803"/>
+      <c r="AGF803"/>
+      <c r="AGG803"/>
+      <c r="AGH803"/>
+      <c r="AGI803"/>
+      <c r="AGJ803"/>
+      <c r="AGK803"/>
+      <c r="AGL803"/>
+      <c r="AGM803"/>
+      <c r="AGN803"/>
+      <c r="AGO803"/>
+      <c r="AGP803"/>
+      <c r="AGQ803"/>
+      <c r="AGR803"/>
+      <c r="AGS803"/>
+      <c r="AGT803"/>
+      <c r="AGU803"/>
+      <c r="AGV803"/>
+      <c r="AGW803"/>
+      <c r="AGX803"/>
+      <c r="AGY803"/>
+      <c r="AGZ803"/>
+      <c r="AHA803"/>
+      <c r="AHB803"/>
+      <c r="AHC803"/>
+      <c r="AHD803"/>
+      <c r="AHE803"/>
+      <c r="AHF803"/>
+      <c r="AHG803"/>
+      <c r="AHH803"/>
+      <c r="AHI803"/>
+      <c r="AHJ803"/>
+      <c r="AHK803"/>
+      <c r="AHL803"/>
+      <c r="AHM803"/>
+      <c r="AHN803"/>
+      <c r="AHO803"/>
+      <c r="AHP803"/>
+      <c r="AHQ803"/>
+      <c r="AHR803"/>
+      <c r="AHS803"/>
+      <c r="AHT803"/>
+      <c r="AHU803"/>
+      <c r="AHV803"/>
+      <c r="AHW803"/>
+      <c r="AHX803"/>
+      <c r="AHY803"/>
+      <c r="AHZ803"/>
+      <c r="AIA803"/>
+      <c r="AIB803"/>
+      <c r="AIC803"/>
+      <c r="AID803"/>
+      <c r="AIE803"/>
+      <c r="AIF803"/>
+      <c r="AIG803"/>
+      <c r="AIH803"/>
+      <c r="AII803"/>
+      <c r="AIJ803"/>
+      <c r="AIK803"/>
+      <c r="AIL803"/>
+      <c r="AIM803"/>
+      <c r="AIN803"/>
+      <c r="AIO803"/>
+      <c r="AIP803"/>
+      <c r="AIQ803"/>
+      <c r="AIR803"/>
+      <c r="AIS803"/>
+      <c r="AIT803"/>
+      <c r="AIU803"/>
+      <c r="AIV803"/>
+      <c r="AIW803"/>
+      <c r="AIX803"/>
+      <c r="AIY803"/>
+      <c r="AIZ803"/>
+      <c r="AJA803"/>
+      <c r="AJB803"/>
+      <c r="AJC803"/>
+      <c r="AJD803"/>
+      <c r="AJE803"/>
+      <c r="AJF803"/>
+      <c r="AJG803"/>
+      <c r="AJH803"/>
+      <c r="AJI803"/>
+      <c r="AJJ803"/>
+      <c r="AJK803"/>
+      <c r="AJL803"/>
+      <c r="AJM803"/>
+      <c r="AJN803"/>
+      <c r="AJO803"/>
+      <c r="AJP803"/>
+      <c r="AJQ803"/>
+      <c r="AJR803"/>
+      <c r="AJS803"/>
+      <c r="AJT803"/>
+      <c r="AJU803"/>
+      <c r="AJV803"/>
+      <c r="AJW803"/>
+      <c r="AJX803"/>
+      <c r="AJY803"/>
+      <c r="AJZ803"/>
+      <c r="AKA803"/>
+      <c r="AKB803"/>
+      <c r="AKC803"/>
+      <c r="AKD803"/>
+      <c r="AKE803"/>
+      <c r="AKF803"/>
+      <c r="AKG803"/>
+      <c r="AKH803"/>
+      <c r="AKI803"/>
+      <c r="AKJ803"/>
+      <c r="AKK803"/>
+      <c r="AKL803"/>
+      <c r="AKM803"/>
+      <c r="AKN803"/>
+      <c r="AKO803"/>
+      <c r="AKP803"/>
+      <c r="AKQ803"/>
+      <c r="AKR803"/>
+      <c r="AKS803"/>
+      <c r="AKT803"/>
+      <c r="AKU803"/>
+      <c r="AKV803"/>
+      <c r="AKW803"/>
+      <c r="AKX803"/>
+      <c r="AKY803"/>
+      <c r="AKZ803"/>
+      <c r="ALA803"/>
+      <c r="ALB803"/>
+      <c r="ALC803"/>
+      <c r="ALD803"/>
+      <c r="ALE803"/>
+      <c r="ALF803"/>
+      <c r="ALG803"/>
+      <c r="ALH803"/>
+      <c r="ALI803"/>
+      <c r="ALJ803"/>
+      <c r="ALK803"/>
+      <c r="ALL803"/>
+      <c r="ALM803"/>
+      <c r="ALN803"/>
+      <c r="ALO803"/>
+      <c r="ALP803"/>
+      <c r="ALQ803"/>
+      <c r="ALR803"/>
+      <c r="ALS803"/>
+      <c r="ALT803"/>
+      <c r="ALU803"/>
+      <c r="ALV803"/>
+      <c r="ALW803"/>
+      <c r="ALX803"/>
+      <c r="ALY803"/>
+      <c r="ALZ803"/>
+      <c r="AMA803"/>
+      <c r="AMB803"/>
+      <c r="AMC803"/>
+      <c r="AMD803"/>
+      <c r="AME803"/>
+      <c r="AMF803"/>
+      <c r="AMG803"/>
+      <c r="AMH803"/>
+    </row>
+    <row r="804" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A804" s="8" t="s">
-        <v>2335</v>
+        <v>2988</v>
       </c>
       <c r="B804" s="8" t="s">
-        <v>210</v>
+        <v>2978</v>
       </c>
       <c r="C804" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_quant_algorithm:speccount</v>
+        <v>att_ptm_enrichment:ionchromatography</v>
       </c>
       <c r="D804" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E804" s="8" t="s">
-        <v>2336</v>
-      </c>
-      <c r="F804" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2986</v>
+      </c>
+      <c r="F804" s="8" t="s">
+        <v>2987</v>
+      </c>
+      <c r="G804"/>
+      <c r="H804"/>
+      <c r="I804"/>
+      <c r="J804"/>
+      <c r="K804"/>
+      <c r="L804"/>
+      <c r="M804"/>
+      <c r="N804"/>
+      <c r="O804"/>
+      <c r="P804"/>
+      <c r="Q804"/>
+      <c r="R804"/>
+      <c r="S804"/>
+      <c r="T804"/>
+      <c r="U804"/>
+      <c r="V804"/>
+      <c r="W804"/>
+      <c r="X804"/>
+      <c r="Y804"/>
+      <c r="Z804"/>
+      <c r="AA804"/>
+      <c r="AB804"/>
+      <c r="AC804"/>
+      <c r="AD804"/>
+      <c r="AE804"/>
+      <c r="AF804"/>
+      <c r="AG804"/>
+      <c r="AH804"/>
+      <c r="AI804"/>
+      <c r="AJ804"/>
+      <c r="AK804"/>
+      <c r="AL804"/>
+      <c r="AM804"/>
+      <c r="AN804"/>
+      <c r="AO804"/>
+      <c r="AP804"/>
+      <c r="AQ804"/>
+      <c r="AR804"/>
+      <c r="AS804"/>
+      <c r="AT804"/>
+      <c r="AU804"/>
+      <c r="AV804"/>
+      <c r="AW804"/>
+      <c r="AX804"/>
+      <c r="AY804"/>
+      <c r="AZ804"/>
+      <c r="BA804"/>
+      <c r="BB804"/>
+      <c r="BC804"/>
+      <c r="BD804"/>
+      <c r="BE804"/>
+      <c r="BF804"/>
+      <c r="BG804"/>
+      <c r="BH804"/>
+      <c r="BI804"/>
+      <c r="BJ804"/>
+      <c r="BK804"/>
+      <c r="BL804"/>
+      <c r="BM804"/>
+      <c r="BN804"/>
+      <c r="BO804"/>
+      <c r="BP804"/>
+      <c r="BQ804"/>
+      <c r="BR804"/>
+      <c r="BS804"/>
+      <c r="BT804"/>
+      <c r="BU804"/>
+      <c r="BV804"/>
+      <c r="BW804"/>
+      <c r="BX804"/>
+      <c r="BY804"/>
+      <c r="BZ804"/>
+      <c r="CA804"/>
+      <c r="CB804"/>
+      <c r="CC804"/>
+      <c r="CD804"/>
+      <c r="CE804"/>
+      <c r="CF804"/>
+      <c r="CG804"/>
+      <c r="CH804"/>
+      <c r="CI804"/>
+      <c r="CJ804"/>
+      <c r="CK804"/>
+      <c r="CL804"/>
+      <c r="CM804"/>
+      <c r="CN804"/>
+      <c r="CO804"/>
+      <c r="CP804"/>
+      <c r="CQ804"/>
+      <c r="CR804"/>
+      <c r="CS804"/>
+      <c r="CT804"/>
+      <c r="CU804"/>
+      <c r="CV804"/>
+      <c r="CW804"/>
+      <c r="CX804"/>
+      <c r="CY804"/>
+      <c r="CZ804"/>
+      <c r="DA804"/>
+      <c r="DB804"/>
+      <c r="DC804"/>
+      <c r="DD804"/>
+      <c r="DE804"/>
+      <c r="DF804"/>
+      <c r="DG804"/>
+      <c r="DH804"/>
+      <c r="DI804"/>
+      <c r="DJ804"/>
+      <c r="DK804"/>
+      <c r="DL804"/>
+      <c r="DM804"/>
+      <c r="DN804"/>
+      <c r="DO804"/>
+      <c r="DP804"/>
+      <c r="DQ804"/>
+      <c r="DR804"/>
+      <c r="DS804"/>
+      <c r="DT804"/>
+      <c r="DU804"/>
+      <c r="DV804"/>
+      <c r="DW804"/>
+      <c r="DX804"/>
+      <c r="DY804"/>
+      <c r="DZ804"/>
+      <c r="EA804"/>
+      <c r="EB804"/>
+      <c r="EC804"/>
+      <c r="ED804"/>
+      <c r="EE804"/>
+      <c r="EF804"/>
+      <c r="EG804"/>
+      <c r="EH804"/>
+      <c r="EI804"/>
+      <c r="EJ804"/>
+      <c r="EK804"/>
+      <c r="EL804"/>
+      <c r="EM804"/>
+      <c r="EN804"/>
+      <c r="EO804"/>
+      <c r="EP804"/>
+      <c r="EQ804"/>
+      <c r="ER804"/>
+      <c r="ES804"/>
+      <c r="ET804"/>
+      <c r="EU804"/>
+      <c r="EV804"/>
+      <c r="EW804"/>
+      <c r="EX804"/>
+      <c r="EY804"/>
+      <c r="EZ804"/>
+      <c r="FA804"/>
+      <c r="FB804"/>
+      <c r="FC804"/>
+      <c r="FD804"/>
+      <c r="FE804"/>
+      <c r="FF804"/>
+      <c r="FG804"/>
+      <c r="FH804"/>
+      <c r="FI804"/>
+      <c r="FJ804"/>
+      <c r="FK804"/>
+      <c r="FL804"/>
+      <c r="FM804"/>
+      <c r="FN804"/>
+      <c r="FO804"/>
+      <c r="FP804"/>
+      <c r="FQ804"/>
+      <c r="FR804"/>
+      <c r="FS804"/>
+      <c r="FT804"/>
+      <c r="FU804"/>
+      <c r="FV804"/>
+      <c r="FW804"/>
+      <c r="FX804"/>
+      <c r="FY804"/>
+      <c r="FZ804"/>
+      <c r="GA804"/>
+      <c r="GB804"/>
+      <c r="GC804"/>
+      <c r="GD804"/>
+      <c r="GE804"/>
+      <c r="GF804"/>
+      <c r="GG804"/>
+      <c r="GH804"/>
+      <c r="GI804"/>
+      <c r="GJ804"/>
+      <c r="GK804"/>
+      <c r="GL804"/>
+      <c r="GM804"/>
+      <c r="GN804"/>
+      <c r="GO804"/>
+      <c r="GP804"/>
+      <c r="GQ804"/>
+      <c r="GR804"/>
+      <c r="GS804"/>
+      <c r="GT804"/>
+      <c r="GU804"/>
+      <c r="GV804"/>
+      <c r="GW804"/>
+      <c r="GX804"/>
+      <c r="GY804"/>
+      <c r="GZ804"/>
+      <c r="HA804"/>
+      <c r="HB804"/>
+      <c r="HC804"/>
+      <c r="HD804"/>
+      <c r="HE804"/>
+      <c r="HF804"/>
+      <c r="HG804"/>
+      <c r="HH804"/>
+      <c r="HI804"/>
+      <c r="HJ804"/>
+      <c r="HK804"/>
+      <c r="HL804"/>
+      <c r="HM804"/>
+      <c r="HN804"/>
+      <c r="HO804"/>
+      <c r="HP804"/>
+      <c r="HQ804"/>
+      <c r="HR804"/>
+      <c r="HS804"/>
+      <c r="HT804"/>
+      <c r="HU804"/>
+      <c r="HV804"/>
+      <c r="HW804"/>
+      <c r="HX804"/>
+      <c r="HY804"/>
+      <c r="HZ804"/>
+      <c r="IA804"/>
+      <c r="IB804"/>
+      <c r="IC804"/>
+      <c r="ID804"/>
+      <c r="IE804"/>
+      <c r="IF804"/>
+      <c r="IG804"/>
+      <c r="IH804"/>
+      <c r="II804"/>
+      <c r="IJ804"/>
+      <c r="IK804"/>
+      <c r="IL804"/>
+      <c r="IM804"/>
+      <c r="IN804"/>
+      <c r="IO804"/>
+      <c r="IP804"/>
+      <c r="IQ804"/>
+      <c r="IR804"/>
+      <c r="IS804"/>
+      <c r="IT804"/>
+      <c r="IU804"/>
+      <c r="IV804"/>
+      <c r="IW804"/>
+      <c r="IX804"/>
+      <c r="IY804"/>
+      <c r="IZ804"/>
+      <c r="JA804"/>
+      <c r="JB804"/>
+      <c r="JC804"/>
+      <c r="JD804"/>
+      <c r="JE804"/>
+      <c r="JF804"/>
+      <c r="JG804"/>
+      <c r="JH804"/>
+      <c r="JI804"/>
+      <c r="JJ804"/>
+      <c r="JK804"/>
+      <c r="JL804"/>
+      <c r="JM804"/>
+      <c r="JN804"/>
+      <c r="JO804"/>
+      <c r="JP804"/>
+      <c r="JQ804"/>
+      <c r="JR804"/>
+      <c r="JS804"/>
+      <c r="JT804"/>
+      <c r="JU804"/>
+      <c r="JV804"/>
+      <c r="JW804"/>
+      <c r="JX804"/>
+      <c r="JY804"/>
+      <c r="JZ804"/>
+      <c r="KA804"/>
+      <c r="KB804"/>
+      <c r="KC804"/>
+      <c r="KD804"/>
+      <c r="KE804"/>
+      <c r="KF804"/>
+      <c r="KG804"/>
+      <c r="KH804"/>
+      <c r="KI804"/>
+      <c r="KJ804"/>
+      <c r="KK804"/>
+      <c r="KL804"/>
+      <c r="KM804"/>
+      <c r="KN804"/>
+      <c r="KO804"/>
+      <c r="KP804"/>
+      <c r="KQ804"/>
+      <c r="KR804"/>
+      <c r="KS804"/>
+      <c r="KT804"/>
+      <c r="KU804"/>
+      <c r="KV804"/>
+      <c r="KW804"/>
+      <c r="KX804"/>
+      <c r="KY804"/>
+      <c r="KZ804"/>
+      <c r="LA804"/>
+      <c r="LB804"/>
+      <c r="LC804"/>
+      <c r="LD804"/>
+      <c r="LE804"/>
+      <c r="LF804"/>
+      <c r="LG804"/>
+      <c r="LH804"/>
+      <c r="LI804"/>
+      <c r="LJ804"/>
+      <c r="LK804"/>
+      <c r="LL804"/>
+      <c r="LM804"/>
+      <c r="LN804"/>
+      <c r="LO804"/>
+      <c r="LP804"/>
+      <c r="LQ804"/>
+      <c r="LR804"/>
+      <c r="LS804"/>
+      <c r="LT804"/>
+      <c r="LU804"/>
+      <c r="LV804"/>
+      <c r="LW804"/>
+      <c r="LX804"/>
+      <c r="LY804"/>
+      <c r="LZ804"/>
+      <c r="MA804"/>
+      <c r="MB804"/>
+      <c r="MC804"/>
+      <c r="MD804"/>
+      <c r="ME804"/>
+      <c r="MF804"/>
+      <c r="MG804"/>
+      <c r="MH804"/>
+      <c r="MI804"/>
+      <c r="MJ804"/>
+      <c r="MK804"/>
+      <c r="ML804"/>
+      <c r="MM804"/>
+      <c r="MN804"/>
+      <c r="MO804"/>
+      <c r="MP804"/>
+      <c r="MQ804"/>
+      <c r="MR804"/>
+      <c r="MS804"/>
+      <c r="MT804"/>
+      <c r="MU804"/>
+      <c r="MV804"/>
+      <c r="MW804"/>
+      <c r="MX804"/>
+      <c r="MY804"/>
+      <c r="MZ804"/>
+      <c r="NA804"/>
+      <c r="NB804"/>
+      <c r="NC804"/>
+      <c r="ND804"/>
+      <c r="NE804"/>
+      <c r="NF804"/>
+      <c r="NG804"/>
+      <c r="NH804"/>
+      <c r="NI804"/>
+      <c r="NJ804"/>
+      <c r="NK804"/>
+      <c r="NL804"/>
+      <c r="NM804"/>
+      <c r="NN804"/>
+      <c r="NO804"/>
+      <c r="NP804"/>
+      <c r="NQ804"/>
+      <c r="NR804"/>
+      <c r="NS804"/>
+      <c r="NT804"/>
+      <c r="NU804"/>
+      <c r="NV804"/>
+      <c r="NW804"/>
+      <c r="NX804"/>
+      <c r="NY804"/>
+      <c r="NZ804"/>
+      <c r="OA804"/>
+      <c r="OB804"/>
+      <c r="OC804"/>
+      <c r="OD804"/>
+      <c r="OE804"/>
+      <c r="OF804"/>
+      <c r="OG804"/>
+      <c r="OH804"/>
+      <c r="OI804"/>
+      <c r="OJ804"/>
+      <c r="OK804"/>
+      <c r="OL804"/>
+      <c r="OM804"/>
+      <c r="ON804"/>
+      <c r="OO804"/>
+      <c r="OP804"/>
+      <c r="OQ804"/>
+      <c r="OR804"/>
+      <c r="OS804"/>
+      <c r="OT804"/>
+      <c r="OU804"/>
+      <c r="OV804"/>
+      <c r="OW804"/>
+      <c r="OX804"/>
+      <c r="OY804"/>
+      <c r="OZ804"/>
+      <c r="PA804"/>
+      <c r="PB804"/>
+      <c r="PC804"/>
+      <c r="PD804"/>
+      <c r="PE804"/>
+      <c r="PF804"/>
+      <c r="PG804"/>
+      <c r="PH804"/>
+      <c r="PI804"/>
+      <c r="PJ804"/>
+      <c r="PK804"/>
+      <c r="PL804"/>
+      <c r="PM804"/>
+      <c r="PN804"/>
+      <c r="PO804"/>
+      <c r="PP804"/>
+      <c r="PQ804"/>
+      <c r="PR804"/>
+      <c r="PS804"/>
+      <c r="PT804"/>
+      <c r="PU804"/>
+      <c r="PV804"/>
+      <c r="PW804"/>
+      <c r="PX804"/>
+      <c r="PY804"/>
+      <c r="PZ804"/>
+      <c r="QA804"/>
+      <c r="QB804"/>
+      <c r="QC804"/>
+      <c r="QD804"/>
+      <c r="QE804"/>
+      <c r="QF804"/>
+      <c r="QG804"/>
+      <c r="QH804"/>
+      <c r="QI804"/>
+      <c r="QJ804"/>
+      <c r="QK804"/>
+      <c r="QL804"/>
+      <c r="QM804"/>
+      <c r="QN804"/>
+      <c r="QO804"/>
+      <c r="QP804"/>
+      <c r="QQ804"/>
+      <c r="QR804"/>
+      <c r="QS804"/>
+      <c r="QT804"/>
+      <c r="QU804"/>
+      <c r="QV804"/>
+      <c r="QW804"/>
+      <c r="QX804"/>
+      <c r="QY804"/>
+      <c r="QZ804"/>
+      <c r="RA804"/>
+      <c r="RB804"/>
+      <c r="RC804"/>
+      <c r="RD804"/>
+      <c r="RE804"/>
+      <c r="RF804"/>
+      <c r="RG804"/>
+      <c r="RH804"/>
+      <c r="RI804"/>
+      <c r="RJ804"/>
+      <c r="RK804"/>
+      <c r="RL804"/>
+      <c r="RM804"/>
+      <c r="RN804"/>
+      <c r="RO804"/>
+      <c r="RP804"/>
+      <c r="RQ804"/>
+      <c r="RR804"/>
+      <c r="RS804"/>
+      <c r="RT804"/>
+      <c r="RU804"/>
+      <c r="RV804"/>
+      <c r="RW804"/>
+      <c r="RX804"/>
+      <c r="RY804"/>
+      <c r="RZ804"/>
+      <c r="SA804"/>
+      <c r="SB804"/>
+      <c r="SC804"/>
+      <c r="SD804"/>
+      <c r="SE804"/>
+      <c r="SF804"/>
+      <c r="SG804"/>
+      <c r="SH804"/>
+      <c r="SI804"/>
+      <c r="SJ804"/>
+      <c r="SK804"/>
+      <c r="SL804"/>
+      <c r="SM804"/>
+      <c r="SN804"/>
+      <c r="SO804"/>
+      <c r="SP804"/>
+      <c r="SQ804"/>
+      <c r="SR804"/>
+      <c r="SS804"/>
+      <c r="ST804"/>
+      <c r="SU804"/>
+      <c r="SV804"/>
+      <c r="SW804"/>
+      <c r="SX804"/>
+      <c r="SY804"/>
+      <c r="SZ804"/>
+      <c r="TA804"/>
+      <c r="TB804"/>
+      <c r="TC804"/>
+      <c r="TD804"/>
+      <c r="TE804"/>
+      <c r="TF804"/>
+      <c r="TG804"/>
+      <c r="TH804"/>
+      <c r="TI804"/>
+      <c r="TJ804"/>
+      <c r="TK804"/>
+      <c r="TL804"/>
+      <c r="TM804"/>
+      <c r="TN804"/>
+      <c r="TO804"/>
+      <c r="TP804"/>
+      <c r="TQ804"/>
+      <c r="TR804"/>
+      <c r="TS804"/>
+      <c r="TT804"/>
+      <c r="TU804"/>
+      <c r="TV804"/>
+      <c r="TW804"/>
+      <c r="TX804"/>
+      <c r="TY804"/>
+      <c r="TZ804"/>
+      <c r="UA804"/>
+      <c r="UB804"/>
+      <c r="UC804"/>
+      <c r="UD804"/>
+      <c r="UE804"/>
+      <c r="UF804"/>
+      <c r="UG804"/>
+      <c r="UH804"/>
+      <c r="UI804"/>
+      <c r="UJ804"/>
+      <c r="UK804"/>
+      <c r="UL804"/>
+      <c r="UM804"/>
+      <c r="UN804"/>
+      <c r="UO804"/>
+      <c r="UP804"/>
+      <c r="UQ804"/>
+      <c r="UR804"/>
+      <c r="US804"/>
+      <c r="UT804"/>
+      <c r="UU804"/>
+      <c r="UV804"/>
+      <c r="UW804"/>
+      <c r="UX804"/>
+      <c r="UY804"/>
+      <c r="UZ804"/>
+      <c r="VA804"/>
+      <c r="VB804"/>
+      <c r="VC804"/>
+      <c r="VD804"/>
+      <c r="VE804"/>
+      <c r="VF804"/>
+      <c r="VG804"/>
+      <c r="VH804"/>
+      <c r="VI804"/>
+      <c r="VJ804"/>
+      <c r="VK804"/>
+      <c r="VL804"/>
+      <c r="VM804"/>
+      <c r="VN804"/>
+      <c r="VO804"/>
+      <c r="VP804"/>
+      <c r="VQ804"/>
+      <c r="VR804"/>
+      <c r="VS804"/>
+      <c r="VT804"/>
+      <c r="VU804"/>
+      <c r="VV804"/>
+      <c r="VW804"/>
+      <c r="VX804"/>
+      <c r="VY804"/>
+      <c r="VZ804"/>
+      <c r="WA804"/>
+      <c r="WB804"/>
+      <c r="WC804"/>
+      <c r="WD804"/>
+      <c r="WE804"/>
+      <c r="WF804"/>
+      <c r="WG804"/>
+      <c r="WH804"/>
+      <c r="WI804"/>
+      <c r="WJ804"/>
+      <c r="WK804"/>
+      <c r="WL804"/>
+      <c r="WM804"/>
+      <c r="WN804"/>
+      <c r="WO804"/>
+      <c r="WP804"/>
+      <c r="WQ804"/>
+      <c r="WR804"/>
+      <c r="WS804"/>
+      <c r="WT804"/>
+      <c r="WU804"/>
+      <c r="WV804"/>
+      <c r="WW804"/>
+      <c r="WX804"/>
+      <c r="WY804"/>
+      <c r="WZ804"/>
+      <c r="XA804"/>
+      <c r="XB804"/>
+      <c r="XC804"/>
+      <c r="XD804"/>
+      <c r="XE804"/>
+      <c r="XF804"/>
+      <c r="XG804"/>
+      <c r="XH804"/>
+      <c r="XI804"/>
+      <c r="XJ804"/>
+      <c r="XK804"/>
+      <c r="XL804"/>
+      <c r="XM804"/>
+      <c r="XN804"/>
+      <c r="XO804"/>
+      <c r="XP804"/>
+      <c r="XQ804"/>
+      <c r="XR804"/>
+      <c r="XS804"/>
+      <c r="XT804"/>
+      <c r="XU804"/>
+      <c r="XV804"/>
+      <c r="XW804"/>
+      <c r="XX804"/>
+      <c r="XY804"/>
+      <c r="XZ804"/>
+      <c r="YA804"/>
+      <c r="YB804"/>
+      <c r="YC804"/>
+      <c r="YD804"/>
+      <c r="YE804"/>
+      <c r="YF804"/>
+      <c r="YG804"/>
+      <c r="YH804"/>
+      <c r="YI804"/>
+      <c r="YJ804"/>
+      <c r="YK804"/>
+      <c r="YL804"/>
+      <c r="YM804"/>
+      <c r="YN804"/>
+      <c r="YO804"/>
+      <c r="YP804"/>
+      <c r="YQ804"/>
+      <c r="YR804"/>
+      <c r="YS804"/>
+      <c r="YT804"/>
+      <c r="YU804"/>
+      <c r="YV804"/>
+      <c r="YW804"/>
+      <c r="YX804"/>
+      <c r="YY804"/>
+      <c r="YZ804"/>
+      <c r="ZA804"/>
+      <c r="ZB804"/>
+      <c r="ZC804"/>
+      <c r="ZD804"/>
+      <c r="ZE804"/>
+      <c r="ZF804"/>
+      <c r="ZG804"/>
+      <c r="ZH804"/>
+      <c r="ZI804"/>
+      <c r="ZJ804"/>
+      <c r="ZK804"/>
+      <c r="ZL804"/>
+      <c r="ZM804"/>
+      <c r="ZN804"/>
+      <c r="ZO804"/>
+      <c r="ZP804"/>
+      <c r="ZQ804"/>
+      <c r="ZR804"/>
+      <c r="ZS804"/>
+      <c r="ZT804"/>
+      <c r="ZU804"/>
+      <c r="ZV804"/>
+      <c r="ZW804"/>
+      <c r="ZX804"/>
+      <c r="ZY804"/>
+      <c r="ZZ804"/>
+      <c r="AAA804"/>
+      <c r="AAB804"/>
+      <c r="AAC804"/>
+      <c r="AAD804"/>
+      <c r="AAE804"/>
+      <c r="AAF804"/>
+      <c r="AAG804"/>
+      <c r="AAH804"/>
+      <c r="AAI804"/>
+      <c r="AAJ804"/>
+      <c r="AAK804"/>
+      <c r="AAL804"/>
+      <c r="AAM804"/>
+      <c r="AAN804"/>
+      <c r="AAO804"/>
+      <c r="AAP804"/>
+      <c r="AAQ804"/>
+      <c r="AAR804"/>
+      <c r="AAS804"/>
+      <c r="AAT804"/>
+      <c r="AAU804"/>
+      <c r="AAV804"/>
+      <c r="AAW804"/>
+      <c r="AAX804"/>
+      <c r="AAY804"/>
+      <c r="AAZ804"/>
+      <c r="ABA804"/>
+      <c r="ABB804"/>
+      <c r="ABC804"/>
+      <c r="ABD804"/>
+      <c r="ABE804"/>
+      <c r="ABF804"/>
+      <c r="ABG804"/>
+      <c r="ABH804"/>
+      <c r="ABI804"/>
+      <c r="ABJ804"/>
+      <c r="ABK804"/>
+      <c r="ABL804"/>
+      <c r="ABM804"/>
+      <c r="ABN804"/>
+      <c r="ABO804"/>
+      <c r="ABP804"/>
+      <c r="ABQ804"/>
+      <c r="ABR804"/>
+      <c r="ABS804"/>
+      <c r="ABT804"/>
+      <c r="ABU804"/>
+      <c r="ABV804"/>
+      <c r="ABW804"/>
+      <c r="ABX804"/>
+      <c r="ABY804"/>
+      <c r="ABZ804"/>
+      <c r="ACA804"/>
+      <c r="ACB804"/>
+      <c r="ACC804"/>
+      <c r="ACD804"/>
+      <c r="ACE804"/>
+      <c r="ACF804"/>
+      <c r="ACG804"/>
+      <c r="ACH804"/>
+      <c r="ACI804"/>
+      <c r="ACJ804"/>
+      <c r="ACK804"/>
+      <c r="ACL804"/>
+      <c r="ACM804"/>
+      <c r="ACN804"/>
+      <c r="ACO804"/>
+      <c r="ACP804"/>
+      <c r="ACQ804"/>
+      <c r="ACR804"/>
+      <c r="ACS804"/>
+      <c r="ACT804"/>
+      <c r="ACU804"/>
+      <c r="ACV804"/>
+      <c r="ACW804"/>
+      <c r="ACX804"/>
+      <c r="ACY804"/>
+      <c r="ACZ804"/>
+      <c r="ADA804"/>
+      <c r="ADB804"/>
+      <c r="ADC804"/>
+      <c r="ADD804"/>
+      <c r="ADE804"/>
+      <c r="ADF804"/>
+      <c r="ADG804"/>
+      <c r="ADH804"/>
+      <c r="ADI804"/>
+      <c r="ADJ804"/>
+      <c r="ADK804"/>
+      <c r="ADL804"/>
+      <c r="ADM804"/>
+      <c r="ADN804"/>
+      <c r="ADO804"/>
+      <c r="ADP804"/>
+      <c r="ADQ804"/>
+      <c r="ADR804"/>
+      <c r="ADS804"/>
+      <c r="ADT804"/>
+      <c r="ADU804"/>
+      <c r="ADV804"/>
+      <c r="ADW804"/>
+      <c r="ADX804"/>
+      <c r="ADY804"/>
+      <c r="ADZ804"/>
+      <c r="AEA804"/>
+      <c r="AEB804"/>
+      <c r="AEC804"/>
+      <c r="AED804"/>
+      <c r="AEE804"/>
+      <c r="AEF804"/>
+      <c r="AEG804"/>
+      <c r="AEH804"/>
+      <c r="AEI804"/>
+      <c r="AEJ804"/>
+      <c r="AEK804"/>
+      <c r="AEL804"/>
+      <c r="AEM804"/>
+      <c r="AEN804"/>
+      <c r="AEO804"/>
+      <c r="AEP804"/>
+      <c r="AEQ804"/>
+      <c r="AER804"/>
+      <c r="AES804"/>
+      <c r="AET804"/>
+      <c r="AEU804"/>
+      <c r="AEV804"/>
+      <c r="AEW804"/>
+      <c r="AEX804"/>
+      <c r="AEY804"/>
+      <c r="AEZ804"/>
+      <c r="AFA804"/>
+      <c r="AFB804"/>
+      <c r="AFC804"/>
+      <c r="AFD804"/>
+      <c r="AFE804"/>
+      <c r="AFF804"/>
+      <c r="AFG804"/>
+      <c r="AFH804"/>
+      <c r="AFI804"/>
+      <c r="AFJ804"/>
+      <c r="AFK804"/>
+      <c r="AFL804"/>
+      <c r="AFM804"/>
+      <c r="AFN804"/>
+      <c r="AFO804"/>
+      <c r="AFP804"/>
+      <c r="AFQ804"/>
+      <c r="AFR804"/>
+      <c r="AFS804"/>
+      <c r="AFT804"/>
+      <c r="AFU804"/>
+      <c r="AFV804"/>
+      <c r="AFW804"/>
+      <c r="AFX804"/>
+      <c r="AFY804"/>
+      <c r="AFZ804"/>
+      <c r="AGA804"/>
+      <c r="AGB804"/>
+      <c r="AGC804"/>
+      <c r="AGD804"/>
+      <c r="AGE804"/>
+      <c r="AGF804"/>
+      <c r="AGG804"/>
+      <c r="AGH804"/>
+      <c r="AGI804"/>
+      <c r="AGJ804"/>
+      <c r="AGK804"/>
+      <c r="AGL804"/>
+      <c r="AGM804"/>
+      <c r="AGN804"/>
+      <c r="AGO804"/>
+      <c r="AGP804"/>
+      <c r="AGQ804"/>
+      <c r="AGR804"/>
+      <c r="AGS804"/>
+      <c r="AGT804"/>
+      <c r="AGU804"/>
+      <c r="AGV804"/>
+      <c r="AGW804"/>
+      <c r="AGX804"/>
+      <c r="AGY804"/>
+      <c r="AGZ804"/>
+      <c r="AHA804"/>
+      <c r="AHB804"/>
+      <c r="AHC804"/>
+      <c r="AHD804"/>
+      <c r="AHE804"/>
+      <c r="AHF804"/>
+      <c r="AHG804"/>
+      <c r="AHH804"/>
+      <c r="AHI804"/>
+      <c r="AHJ804"/>
+      <c r="AHK804"/>
+      <c r="AHL804"/>
+      <c r="AHM804"/>
+      <c r="AHN804"/>
+      <c r="AHO804"/>
+      <c r="AHP804"/>
+      <c r="AHQ804"/>
+      <c r="AHR804"/>
+      <c r="AHS804"/>
+      <c r="AHT804"/>
+      <c r="AHU804"/>
+      <c r="AHV804"/>
+      <c r="AHW804"/>
+      <c r="AHX804"/>
+      <c r="AHY804"/>
+      <c r="AHZ804"/>
+      <c r="AIA804"/>
+      <c r="AIB804"/>
+      <c r="AIC804"/>
+      <c r="AID804"/>
+      <c r="AIE804"/>
+      <c r="AIF804"/>
+      <c r="AIG804"/>
+      <c r="AIH804"/>
+      <c r="AII804"/>
+      <c r="AIJ804"/>
+      <c r="AIK804"/>
+      <c r="AIL804"/>
+      <c r="AIM804"/>
+      <c r="AIN804"/>
+      <c r="AIO804"/>
+      <c r="AIP804"/>
+      <c r="AIQ804"/>
+      <c r="AIR804"/>
+      <c r="AIS804"/>
+      <c r="AIT804"/>
+      <c r="AIU804"/>
+      <c r="AIV804"/>
+      <c r="AIW804"/>
+      <c r="AIX804"/>
+      <c r="AIY804"/>
+      <c r="AIZ804"/>
+      <c r="AJA804"/>
+      <c r="AJB804"/>
+      <c r="AJC804"/>
+      <c r="AJD804"/>
+      <c r="AJE804"/>
+      <c r="AJF804"/>
+      <c r="AJG804"/>
+      <c r="AJH804"/>
+      <c r="AJI804"/>
+      <c r="AJJ804"/>
+      <c r="AJK804"/>
+      <c r="AJL804"/>
+      <c r="AJM804"/>
+      <c r="AJN804"/>
+      <c r="AJO804"/>
+      <c r="AJP804"/>
+      <c r="AJQ804"/>
+      <c r="AJR804"/>
+      <c r="AJS804"/>
+      <c r="AJT804"/>
+      <c r="AJU804"/>
+      <c r="AJV804"/>
+      <c r="AJW804"/>
+      <c r="AJX804"/>
+      <c r="AJY804"/>
+      <c r="AJZ804"/>
+      <c r="AKA804"/>
+      <c r="AKB804"/>
+      <c r="AKC804"/>
+      <c r="AKD804"/>
+      <c r="AKE804"/>
+      <c r="AKF804"/>
+      <c r="AKG804"/>
+      <c r="AKH804"/>
+      <c r="AKI804"/>
+      <c r="AKJ804"/>
+      <c r="AKK804"/>
+      <c r="AKL804"/>
+      <c r="AKM804"/>
+      <c r="AKN804"/>
+      <c r="AKO804"/>
+      <c r="AKP804"/>
+      <c r="AKQ804"/>
+      <c r="AKR804"/>
+      <c r="AKS804"/>
+      <c r="AKT804"/>
+      <c r="AKU804"/>
+      <c r="AKV804"/>
+      <c r="AKW804"/>
+      <c r="AKX804"/>
+      <c r="AKY804"/>
+      <c r="AKZ804"/>
+      <c r="ALA804"/>
+      <c r="ALB804"/>
+      <c r="ALC804"/>
+      <c r="ALD804"/>
+      <c r="ALE804"/>
+      <c r="ALF804"/>
+      <c r="ALG804"/>
+      <c r="ALH804"/>
+      <c r="ALI804"/>
+      <c r="ALJ804"/>
+      <c r="ALK804"/>
+      <c r="ALL804"/>
+      <c r="ALM804"/>
+      <c r="ALN804"/>
+      <c r="ALO804"/>
+      <c r="ALP804"/>
+      <c r="ALQ804"/>
+      <c r="ALR804"/>
+      <c r="ALS804"/>
+      <c r="ALT804"/>
+      <c r="ALU804"/>
+      <c r="ALV804"/>
+      <c r="ALW804"/>
+      <c r="ALX804"/>
+      <c r="ALY804"/>
+      <c r="ALZ804"/>
+      <c r="AMA804"/>
+      <c r="AMB804"/>
+      <c r="AMC804"/>
+      <c r="AMD804"/>
+      <c r="AME804"/>
+      <c r="AMF804"/>
+      <c r="AMG804"/>
+      <c r="AMH804"/>
+    </row>
+    <row r="805" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A805" s="8" t="s">
-        <v>2337</v>
+        <v>2331</v>
       </c>
       <c r="B805" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C805" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_quantification:isobaric</v>
+        <v>att_quant_algorithm:directlfq</v>
       </c>
       <c r="D805" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E805" s="8" t="s">
-        <v>2337</v>
-      </c>
-      <c r="F805" s="8" t="s">
-        <v>2338</v>
-      </c>
-    </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2332</v>
+      </c>
+      <c r="F805" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="806" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A806" s="8" t="s">
-        <v>2339</v>
+        <v>2333</v>
       </c>
       <c r="B806" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C806" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_quantification:istopic</v>
+        <v>att_quant_algorithm:maxlfq</v>
       </c>
       <c r="D806" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E806" s="8" t="s">
-        <v>2339</v>
-      </c>
-      <c r="F806" s="8" t="s">
-        <v>2340</v>
-      </c>
-    </row>
-    <row r="807" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2334</v>
+      </c>
+      <c r="F806" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="807" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A807" s="8" t="s">
-        <v>2341</v>
+        <v>2335</v>
       </c>
       <c r="B807" s="8" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C807" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_quantification:label_free</v>
+        <v>att_quant_algorithm:speccount</v>
       </c>
       <c r="D807" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E807" s="8" t="s">
-        <v>2342</v>
-      </c>
-      <c r="F807" s="8" t="s">
-        <v>2343</v>
-      </c>
-    </row>
-    <row r="808" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2336</v>
+      </c>
+      <c r="F807" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="808" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A808" s="8" t="s">
-        <v>2344</v>
+        <v>2337</v>
       </c>
       <c r="B808" s="8" t="s">
         <v>211</v>
       </c>
       <c r="C808" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_quantification:silac</v>
+        <v>att_quantification:isobaric</v>
       </c>
       <c r="D808" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E808" s="8" t="s">
-        <v>2344</v>
+        <v>2337</v>
       </c>
       <c r="F808" s="8" t="s">
-        <v>2345</v>
-      </c>
-    </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="809" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A809" s="8" t="s">
-        <v>2346</v>
+        <v>2339</v>
       </c>
       <c r="B809" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C809" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_reduction:dtt</v>
+        <v>att_quantification:istopic</v>
       </c>
       <c r="D809" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E809" s="8" t="s">
-        <v>2347</v>
+        <v>2339</v>
       </c>
       <c r="F809" s="8" t="s">
-        <v>2348</v>
-      </c>
-    </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2340</v>
+      </c>
+    </row>
+    <row r="810" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A810" s="8" t="s">
-        <v>342</v>
+        <v>2341</v>
       </c>
       <c r="B810" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C810" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_reduction:none</v>
+        <v>att_quantification:label_free</v>
       </c>
       <c r="D810" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E810" s="8" t="s">
-        <v>343</v>
+        <v>2342</v>
       </c>
       <c r="F810" s="8" t="s">
-        <v>2349</v>
-      </c>
-    </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2343</v>
+      </c>
+    </row>
+    <row r="811" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A811" s="8" t="s">
-        <v>2350</v>
+        <v>2344</v>
       </c>
       <c r="B811" s="8" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C811" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_reduction:tcep</v>
+        <v>att_quantification:silac</v>
       </c>
       <c r="D811" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E811" s="8" t="s">
-        <v>2351</v>
+        <v>2344</v>
       </c>
       <c r="F811" s="8" t="s">
-        <v>2352</v>
-      </c>
-    </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2345</v>
+      </c>
+    </row>
+    <row r="812" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A812" s="8" t="s">
-        <v>1417</v>
+        <v>2346</v>
       </c>
       <c r="B812" s="8" t="s">
-        <v>2353</v>
+        <v>214</v>
       </c>
       <c r="C812" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:apoptosis</v>
+        <v>att_reduction:dtt</v>
       </c>
       <c r="D812" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E812" s="8" t="s">
-        <v>1418</v>
+        <v>2347</v>
       </c>
       <c r="F812" s="8" t="s">
-        <v>2354</v>
-      </c>
-    </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="813" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A813" s="8" t="s">
-        <v>2355</v>
+        <v>342</v>
       </c>
       <c r="B813" s="8" t="s">
-        <v>2353</v>
+        <v>214</v>
       </c>
       <c r="C813" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:autocrine</v>
+        <v>att_reduction:none</v>
       </c>
       <c r="D813" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E813" s="8" t="s">
-        <v>2356</v>
+        <v>343</v>
       </c>
       <c r="F813" s="8" t="s">
-        <v>2357</v>
-      </c>
-    </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2349</v>
+      </c>
+    </row>
+    <row r="814" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A814" s="8" t="s">
-        <v>2358</v>
+        <v>2350</v>
       </c>
       <c r="B814" s="8" t="s">
-        <v>2353</v>
+        <v>214</v>
       </c>
       <c r="C814" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:complement</v>
+        <v>att_reduction:tcep</v>
       </c>
       <c r="D814" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E814" s="8" t="s">
-        <v>2359</v>
+        <v>2351</v>
       </c>
       <c r="F814" s="8" t="s">
-        <v>2360</v>
-      </c>
-    </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2352</v>
+      </c>
+    </row>
+    <row r="815" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A815" s="8" t="s">
-        <v>2361</v>
+        <v>1417</v>
       </c>
       <c r="B815" s="8" t="s">
         <v>2353</v>
       </c>
       <c r="C815" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:cytokines</v>
+        <v>att_signalling:apoptosis</v>
       </c>
       <c r="D815" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E815" s="8" t="s">
-        <v>2362</v>
+        <v>1418</v>
       </c>
       <c r="F815" s="8" t="s">
-        <v>2363</v>
-      </c>
-    </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.15">
+        <v>2354</v>
+      </c>
+    </row>
+    <row r="816" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A816" s="8" t="s">
-        <v>2364</v>
+        <v>2355</v>
       </c>
       <c r="B816" s="8" t="s">
         <v>2353</v>
       </c>
       <c r="C816" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:inflammation</v>
+        <v>att_signalling:autocrine</v>
       </c>
       <c r="D816" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E816" s="8" t="s">
-        <v>2365</v>
+        <v>2356</v>
       </c>
       <c r="F816" s="8" t="s">
-        <v>2366</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A817" s="8" t="s">
-        <v>2367</v>
+        <v>2358</v>
       </c>
       <c r="B817" s="8" t="s">
         <v>2353</v>
       </c>
       <c r="C817" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:insulin</v>
+        <v>att_signalling:complement</v>
       </c>
       <c r="D817" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E817" s="8" t="s">
-        <v>2368</v>
+        <v>2359</v>
       </c>
       <c r="F817" s="8" t="s">
-        <v>2369</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A818" s="8" t="s">
-        <v>2370</v>
+        <v>2361</v>
       </c>
       <c r="B818" s="8" t="s">
         <v>2353</v>
       </c>
       <c r="C818" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:juxtacrine</v>
+        <v>att_signalling:cytokines</v>
       </c>
       <c r="D818" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E818" s="8" t="s">
-        <v>2371</v>
+        <v>2362</v>
       </c>
       <c r="F818" s="8" t="s">
-        <v>2372</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A819" s="8" t="s">
-        <v>2373</v>
+        <v>2364</v>
       </c>
       <c r="B819" s="8" t="s">
         <v>2353</v>
       </c>
       <c r="C819" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:necrosis</v>
+        <v>att_signalling:inflammation</v>
       </c>
       <c r="D819" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E819" s="8" t="s">
-        <v>2374</v>
+        <v>2365</v>
       </c>
       <c r="F819" s="8" t="s">
-        <v>2375</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A820" s="8" t="s">
-        <v>2376</v>
+        <v>2367</v>
       </c>
       <c r="B820" s="8" t="s">
         <v>2353</v>
       </c>
       <c r="C820" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:paracrine</v>
+        <v>att_signalling:insulin</v>
       </c>
       <c r="D820" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E820" s="8" t="s">
-        <v>2377</v>
+        <v>2368</v>
       </c>
       <c r="F820" s="8" t="s">
-        <v>2378</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A821" s="8" t="s">
-        <v>1765</v>
+        <v>2370</v>
       </c>
       <c r="B821" s="8" t="s">
         <v>2353</v>
       </c>
       <c r="C821" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_signalling:signaling</v>
+        <v>att_signalling:juxtacrine</v>
       </c>
       <c r="D821" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E821" s="8" t="s">
-        <v>1766</v>
+        <v>2371</v>
       </c>
       <c r="F821" s="8" t="s">
-        <v>2379</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="822" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A822" s="8" t="s">
-        <v>2380</v>
+        <v>2373</v>
       </c>
       <c r="B822" s="8" t="s">
-        <v>31</v>
+        <v>2353</v>
       </c>
       <c r="C822" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_software:diann</v>
+        <v>att_signalling:necrosis</v>
       </c>
       <c r="D822" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E822" s="8" t="s">
-        <v>2381</v>
+        <v>2374</v>
       </c>
       <c r="F822" s="8" t="s">
-        <v>2382</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A823" s="8" t="s">
-        <v>2383</v>
+        <v>2376</v>
       </c>
       <c r="B823" s="8" t="s">
-        <v>31</v>
+        <v>2353</v>
       </c>
       <c r="C823" s="8" t="str">
         <f t="shared" si="18"/>
-        <v>att_software:maxquant</v>
+        <v>att_signalling:paracrine</v>
       </c>
       <c r="D823" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E823" s="8" t="s">
-        <v>2384</v>
+        <v>2377</v>
       </c>
       <c r="F823" s="8" t="s">
-        <v>2385</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A824" s="8" t="s">
-        <v>2386</v>
+        <v>1765</v>
       </c>
       <c r="B824" s="8" t="s">
-        <v>31</v>
+        <v>2353</v>
       </c>
       <c r="C824" s="8" t="str">
-        <f t="shared" ref="C824:C895" si="20">B824&amp;":"&amp;A824</f>
-        <v>att_software:metamorpheus</v>
+        <f t="shared" si="18"/>
+        <v>att_signalling:signaling</v>
       </c>
       <c r="D824" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E824" s="8" t="s">
-        <v>2387</v>
+        <v>1766</v>
       </c>
       <c r="F824" s="8" t="s">
-        <v>2388</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="825" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A825" s="8" t="s">
-        <v>2389</v>
+        <v>2380</v>
       </c>
       <c r="B825" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C825" s="8" t="str">
+        <f t="shared" si="18"/>
+        <v>att_software:diann</v>
+      </c>
+      <c r="D825" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E825" s="8" t="s">
+        <v>2381</v>
+      </c>
+      <c r="F825" s="8" t="s">
+        <v>2382</v>
+      </c>
+    </row>
+    <row r="826" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A826" s="8" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B826" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C826" s="8" t="str">
+        <f t="shared" si="18"/>
+        <v>att_software:maxquant</v>
+      </c>
+      <c r="D826" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E826" s="8" t="s">
+        <v>2384</v>
+      </c>
+      <c r="F826" s="8" t="s">
+        <v>2385</v>
+      </c>
+    </row>
+    <row r="827" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A827" s="8" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B827" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C827" s="8" t="str">
+        <f t="shared" ref="C827:C898" si="20">B827&amp;":"&amp;A827</f>
+        <v>att_software:metamorpheus</v>
+      </c>
+      <c r="D827" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E827" s="8" t="s">
+        <v>2387</v>
+      </c>
+      <c r="F827" s="8" t="s">
+        <v>2388</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A828" s="8" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B828" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C828" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_software:minora</v>
       </c>
-      <c r="D825" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E825" s="8" t="s">
+      <c r="D828" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E828" s="8" t="s">
         <v>2390</v>
       </c>
-      <c r="F825" s="8" t="s">
+      <c r="F828" s="8" t="s">
         <v>2391</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A826" s="8" t="s">
+    <row r="829" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A829" s="8" t="s">
         <v>2392</v>
       </c>
-      <c r="B826" s="8" t="s">
+      <c r="B829" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C826" s="8" t="str">
+      <c r="C829" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_software:msfragger</v>
       </c>
-      <c r="D826" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E826" s="8" t="s">
+      <c r="D829" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E829" s="8" t="s">
         <v>2393</v>
       </c>
-      <c r="F826" s="8" t="s">
+      <c r="F829" s="8" t="s">
         <v>2394</v>
       </c>
     </row>
-    <row r="827" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A827" s="8" t="s">
+    <row r="830" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A830" s="8" t="s">
         <v>2395</v>
       </c>
-      <c r="B827" s="8" t="s">
+      <c r="B830" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C827" s="8" t="str">
+      <c r="C830" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_software:msgf</v>
       </c>
-      <c r="D827" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E827" s="8" t="s">
+      <c r="D830" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E830" s="8" t="s">
         <v>2396</v>
       </c>
-      <c r="F827" s="8" t="s">
+      <c r="F830" s="8" t="s">
         <v>2397</v>
       </c>
     </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A828" s="8" t="s">
+    <row r="831" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A831" s="8" t="s">
         <v>2398</v>
       </c>
-      <c r="B828" s="8" t="s">
+      <c r="B831" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C828" s="8" t="str">
+      <c r="C831" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_software:spectronaut</v>
       </c>
-      <c r="D828" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E828" s="8" t="s">
+      <c r="D831" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E831" s="8" t="s">
         <v>2399</v>
       </c>
-      <c r="F828" s="8" t="s">
+      <c r="F831" s="8" t="s">
         <v>2400</v>
       </c>
     </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A829" s="8" t="s">
+    <row r="832" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A832" s="8" t="s">
         <v>2932</v>
       </c>
-      <c r="B829" s="8" t="s">
+      <c r="B832" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C829" s="8" t="str">
+      <c r="C832" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_subcellular_compartment:wc</v>
       </c>
-      <c r="D829" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E829" s="8" t="s">
+      <c r="D832" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E832" s="8" t="s">
         <v>2933</v>
       </c>
-      <c r="F829" s="8" t="s">
+      <c r="F832" s="8" t="s">
         <v>2934</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A830" s="8" t="s">
+    <row r="833" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A833" s="8" t="s">
         <v>2936</v>
       </c>
-      <c r="B830" s="8" t="s">
+      <c r="B833" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C830" s="8" t="str">
+      <c r="C833" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_subcellular_compartment:membrane</v>
       </c>
-      <c r="D830" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E830" s="8" t="s">
+      <c r="D833" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E833" s="8" t="s">
         <v>2937</v>
       </c>
-      <c r="F830" s="8" t="s">
+      <c r="F833" s="8" t="s">
         <v>2938</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A831" s="8" t="s">
+    <row r="834" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A834" s="8" t="s">
         <v>2935</v>
       </c>
-      <c r="B831" s="8" t="s">
+      <c r="B834" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C831" s="8" t="str">
-        <f t="shared" ref="C831" si="21">B831&amp;":"&amp;A831</f>
+      <c r="C834" s="8" t="str">
+        <f t="shared" ref="C834" si="21">B834&amp;":"&amp;A834</f>
         <v>att_subcellular_compartment:mitochondria</v>
       </c>
-      <c r="D831" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E831" s="8" t="s">
+      <c r="D834" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E834" s="8" t="s">
         <v>2952</v>
       </c>
-      <c r="F831" s="8" t="s">
+      <c r="F834" s="8" t="s">
         <v>2951</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A832" s="8" t="s">
+    <row r="835" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A835" s="8" t="s">
         <v>2965</v>
       </c>
-      <c r="B832" s="8" t="s">
+      <c r="B835" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C832" s="8" t="str">
-        <f t="shared" ref="C832" si="22">B832&amp;":"&amp;A832</f>
+      <c r="C835" s="8" t="str">
+        <f t="shared" ref="C835" si="22">B835&amp;":"&amp;A835</f>
         <v>att_subcellular_compartment:mitochondriapk</v>
       </c>
-      <c r="D832" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E832" s="8" t="s">
+      <c r="D835" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E835" s="8" t="s">
         <v>2963</v>
       </c>
-      <c r="F832" s="8" t="s">
+      <c r="F835" s="8" t="s">
         <v>2964</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A833" s="8" t="s">
+    <row r="836" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A836" s="8" t="s">
         <v>2939</v>
       </c>
-      <c r="B833" s="8" t="s">
+      <c r="B836" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C833" s="8" t="str">
+      <c r="C836" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_subcellular_compartment:golgi</v>
       </c>
-      <c r="D833" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E833" s="8" t="s">
+      <c r="D836" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E836" s="8" t="s">
         <v>2940</v>
       </c>
-      <c r="F833" s="8" t="s">
+      <c r="F836" s="8" t="s">
         <v>2941</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A834" s="8" t="s">
+    <row r="837" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A837" s="8" t="s">
         <v>2942</v>
       </c>
-      <c r="B834" s="8" t="s">
+      <c r="B837" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C834" s="8" t="str">
-        <f t="shared" ref="C834:C836" si="23">B834&amp;":"&amp;A834</f>
+      <c r="C837" s="8" t="str">
+        <f t="shared" ref="C837:C839" si="23">B837&amp;":"&amp;A837</f>
         <v>att_subcellular_compartment:plasmamembrane</v>
       </c>
-      <c r="D834" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E834" s="8" t="s">
+      <c r="D837" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E837" s="8" t="s">
         <v>2950</v>
       </c>
-      <c r="F834" s="8" t="s">
+      <c r="F837" s="8" t="s">
         <v>2943</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A835" s="8" t="s">
+    <row r="838" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A838" s="8" t="s">
         <v>2944</v>
       </c>
-      <c r="B835" s="8" t="s">
+      <c r="B838" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C835" s="8" t="str">
+      <c r="C838" s="8" t="str">
         <f t="shared" si="23"/>
         <v>att_subcellular_compartment:nucleus</v>
       </c>
-      <c r="D835" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E835" s="8" t="s">
+      <c r="D838" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E838" s="8" t="s">
         <v>2945</v>
       </c>
-      <c r="F835" s="8" t="s">
+      <c r="F838" s="8" t="s">
         <v>2946</v>
       </c>
     </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A836" s="8" t="s">
+    <row r="839" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A839" s="8" t="s">
         <v>2947</v>
       </c>
-      <c r="B836" s="8" t="s">
+      <c r="B839" s="8" t="s">
         <v>2930</v>
       </c>
-      <c r="C836" s="8" t="str">
+      <c r="C839" s="8" t="str">
         <f t="shared" si="23"/>
         <v>att_subcellular_compartment:cytosol</v>
       </c>
-      <c r="D836" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E836" s="8" t="s">
+      <c r="D839" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E839" s="8" t="s">
         <v>2948</v>
       </c>
-      <c r="F836" s="8" t="s">
+      <c r="F839" s="8" t="s">
         <v>2949</v>
       </c>
     </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A837" s="8" t="s">
+    <row r="840" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A840" s="8" t="s">
         <v>2401</v>
       </c>
-      <c r="B837" s="8" t="s">
+      <c r="B840" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C837" s="8" t="str">
+      <c r="C840" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:adipose</v>
       </c>
-      <c r="D837" s="8" t="s">
+      <c r="D840" s="8" t="s">
         <v>2401</v>
       </c>
-      <c r="E837" s="8" t="s">
+      <c r="E840" s="8" t="s">
         <v>2402</v>
       </c>
-      <c r="F837" s="8" t="s">
+      <c r="F840" s="8" t="s">
         <v>2403</v>
       </c>
     </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A838" s="8" t="s">
+    <row r="841" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A841" s="8" t="s">
         <v>2404</v>
       </c>
-      <c r="B838" s="8" t="s">
+      <c r="B841" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C838" s="8" t="str">
+      <c r="C841" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:areolar</v>
       </c>
-      <c r="D838" s="8" t="s">
+      <c r="D841" s="8" t="s">
         <v>2404</v>
       </c>
-      <c r="E838" s="8" t="s">
+      <c r="E841" s="8" t="s">
         <v>2405</v>
       </c>
-      <c r="F838" s="8" t="s">
+      <c r="F841" s="8" t="s">
         <v>2406</v>
       </c>
     </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A839" s="8" t="s">
+    <row r="842" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A842" s="8" t="s">
         <v>2407</v>
       </c>
-      <c r="B839" s="8" t="s">
+      <c r="B842" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C839" s="8" t="str">
+      <c r="C842" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:blood</v>
       </c>
-      <c r="D839" s="8" t="s">
+      <c r="D842" s="8" t="s">
         <v>2407</v>
       </c>
-      <c r="E839" s="8" t="s">
+      <c r="E842" s="8" t="s">
         <v>2408</v>
       </c>
-      <c r="F839" s="8" t="s">
+      <c r="F842" s="8" t="s">
         <v>2408</v>
       </c>
     </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A840" s="8" t="s">
+    <row r="843" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A843" s="8" t="s">
         <v>2409</v>
       </c>
-      <c r="B840" s="8" t="s">
+      <c r="B843" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C840" s="8" t="str">
+      <c r="C843" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:connective</v>
       </c>
-      <c r="D840" s="8" t="s">
+      <c r="D843" s="8" t="s">
         <v>2409</v>
       </c>
-      <c r="E840" s="8" t="s">
+      <c r="E843" s="8" t="s">
         <v>2410</v>
       </c>
-      <c r="F840" s="8" t="s">
+      <c r="F843" s="8" t="s">
         <v>2411</v>
       </c>
     </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A841" s="8" t="s">
+    <row r="844" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A844" s="8" t="s">
         <v>2412</v>
       </c>
-      <c r="B841" s="8" t="s">
+      <c r="B844" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C841" s="8" t="str">
+      <c r="C844" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:dermis</v>
       </c>
-      <c r="D841" s="8" t="s">
+      <c r="D844" s="8" t="s">
         <v>2412</v>
       </c>
-      <c r="E841" s="8" t="s">
+      <c r="E844" s="8" t="s">
         <v>2413</v>
       </c>
-      <c r="F841" s="8" t="s">
+      <c r="F844" s="8" t="s">
         <v>2413</v>
       </c>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A842" s="8" t="s">
+    <row r="845" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A845" s="8" t="s">
         <v>2414</v>
       </c>
-      <c r="B842" s="8" t="s">
+      <c r="B845" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C842" s="8" t="str">
+      <c r="C845" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:epidermis</v>
       </c>
-      <c r="D842" s="8" t="s">
+      <c r="D845" s="8" t="s">
         <v>2414</v>
       </c>
-      <c r="E842" s="8" t="s">
+      <c r="E845" s="8" t="s">
         <v>2415</v>
       </c>
-      <c r="F842" s="8" t="s">
+      <c r="F845" s="8" t="s">
         <v>2415</v>
       </c>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A843" s="8" t="s">
+    <row r="846" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A846" s="8" t="s">
         <v>2416</v>
       </c>
-      <c r="B843" s="8" t="s">
+      <c r="B846" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C843" s="8" t="str">
+      <c r="C846" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:epithelial</v>
       </c>
-      <c r="D843" s="8" t="s">
+      <c r="D846" s="8" t="s">
         <v>2416</v>
       </c>
-      <c r="E843" s="8" t="s">
+      <c r="E846" s="8" t="s">
         <v>2417</v>
       </c>
-      <c r="F843" s="8" t="s">
+      <c r="F846" s="8" t="s">
         <v>2418</v>
       </c>
     </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A844" s="8" t="s">
+    <row r="847" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A847" s="8" t="s">
         <v>2419</v>
       </c>
-      <c r="B844" s="8" t="s">
+      <c r="B847" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C844" s="8" t="str">
+      <c r="C847" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:hypodermis</v>
       </c>
-      <c r="D844" s="8" t="s">
+      <c r="D847" s="8" t="s">
         <v>2419</v>
       </c>
-      <c r="E844" s="8" t="s">
+      <c r="E847" s="8" t="s">
         <v>2420</v>
       </c>
-      <c r="F844" s="8" t="s">
+      <c r="F847" s="8" t="s">
         <v>2420</v>
       </c>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A845" s="8" t="s">
+    <row r="848" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A848" s="8" t="s">
         <v>2421</v>
       </c>
-      <c r="B845" s="8" t="s">
+      <c r="B848" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C845" s="8" t="str">
+      <c r="C848" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:muscle</v>
       </c>
-      <c r="D845" s="8" t="s">
+      <c r="D848" s="8" t="s">
         <v>2421</v>
       </c>
-      <c r="E845" s="8" t="s">
+      <c r="E848" s="8" t="s">
         <v>2819</v>
       </c>
-      <c r="F845" s="8" t="s">
+      <c r="F848" s="8" t="s">
         <v>2422</v>
       </c>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A846" s="8" t="s">
+    <row r="849" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A849" s="8" t="s">
         <v>2423</v>
       </c>
-      <c r="B846" s="8" t="s">
+      <c r="B849" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C846" s="8" t="str">
+      <c r="C849" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:nervous</v>
       </c>
-      <c r="D846" s="8" t="s">
+      <c r="D849" s="8" t="s">
         <v>2423</v>
       </c>
-      <c r="E846" s="8" t="s">
+      <c r="E849" s="8" t="s">
         <v>2242</v>
       </c>
-      <c r="F846" s="8" t="s">
+      <c r="F849" s="8" t="s">
         <v>2424</v>
       </c>
     </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A847" s="8" t="s">
+    <row r="850" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A850" s="8" t="s">
         <v>2425</v>
       </c>
-      <c r="B847" s="8" t="s">
+      <c r="B850" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C847" s="8" t="str">
+      <c r="C850" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:reticular</v>
       </c>
-      <c r="D847" s="8" t="s">
+      <c r="D850" s="8" t="s">
         <v>2425</v>
       </c>
-      <c r="E847" s="8" t="s">
+      <c r="E850" s="8" t="s">
         <v>2426</v>
       </c>
-      <c r="F847" s="8" t="s">
+      <c r="F850" s="8" t="s">
         <v>2427</v>
       </c>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A848" s="8" t="s">
+    <row r="851" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A851" s="8" t="s">
         <v>2428</v>
       </c>
-      <c r="B848" s="8" t="s">
+      <c r="B851" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="C848" s="8" t="str">
+      <c r="C851" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tissue:stromal</v>
       </c>
-      <c r="D848" s="8" t="s">
+      <c r="D851" s="8" t="s">
         <v>2428</v>
       </c>
-      <c r="E848" s="8" t="s">
+      <c r="E851" s="8" t="s">
         <v>2429</v>
       </c>
-      <c r="F848" s="8" t="s">
+      <c r="F851" s="8" t="s">
         <v>2430</v>
       </c>
     </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A849" s="8" t="s">
+    <row r="852" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A852" s="8" t="s">
         <v>2431</v>
       </c>
-      <c r="B849" s="8" t="s">
+      <c r="B852" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C849" s="8" t="str">
+      <c r="C852" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_126</v>
       </c>
-      <c r="D849" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E849" s="8">
+      <c r="D852" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E852" s="8">
         <v>126</v>
       </c>
-      <c r="F849" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A850" s="8" t="s">
+      <c r="F852" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="853" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A853" s="8" t="s">
         <v>2432</v>
       </c>
-      <c r="B850" s="8" t="s">
+      <c r="B853" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C850" s="8" t="str">
+      <c r="C853" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_127C</v>
       </c>
-      <c r="D850" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E850" s="8" t="s">
+      <c r="D853" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E853" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F850" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A851" s="8" t="s">
+      <c r="F853" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="854" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A854" s="8" t="s">
         <v>2434</v>
       </c>
-      <c r="B851" s="8" t="s">
+      <c r="B854" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C851" s="8" t="str">
+      <c r="C854" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_127N</v>
       </c>
-      <c r="D851" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E851" s="8" t="s">
+      <c r="D854" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E854" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F851" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A852" s="8" t="s">
+      <c r="F854" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="855" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A855" s="8" t="s">
         <v>2436</v>
       </c>
-      <c r="B852" s="8" t="s">
+      <c r="B855" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C852" s="8" t="str">
+      <c r="C855" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_128C</v>
       </c>
-      <c r="D852" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E852" s="8" t="s">
+      <c r="D855" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E855" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F852" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A853" s="8" t="s">
+      <c r="F855" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="856" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A856" s="8" t="s">
         <v>2438</v>
       </c>
-      <c r="B853" s="8" t="s">
+      <c r="B856" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C853" s="8" t="str">
+      <c r="C856" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_128N</v>
       </c>
-      <c r="D853" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E853" s="8" t="s">
+      <c r="D856" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E856" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F853" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A854" s="8" t="s">
+      <c r="F856" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="857" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A857" s="8" t="s">
         <v>2440</v>
       </c>
-      <c r="B854" s="8" t="s">
+      <c r="B857" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C854" s="8" t="str">
+      <c r="C857" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_129C</v>
       </c>
-      <c r="D854" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E854" s="8" t="s">
+      <c r="D857" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E857" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F854" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A855" s="8" t="s">
+      <c r="F857" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="858" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A858" s="8" t="s">
         <v>2442</v>
       </c>
-      <c r="B855" s="8" t="s">
+      <c r="B858" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C855" s="8" t="str">
+      <c r="C858" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_129N</v>
       </c>
-      <c r="D855" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E855" s="8" t="s">
+      <c r="D858" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E858" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F855" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A856" s="8" t="s">
+      <c r="F858" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="859" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A859" s="8" t="s">
         <v>2444</v>
       </c>
-      <c r="B856" s="8" t="s">
+      <c r="B859" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C856" s="8" t="str">
+      <c r="C859" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_130C</v>
       </c>
-      <c r="D856" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E856" s="8" t="s">
+      <c r="D859" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E859" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F856" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A857" s="8" t="s">
+      <c r="F859" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="860" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A860" s="8" t="s">
         <v>2446</v>
       </c>
-      <c r="B857" s="8" t="s">
+      <c r="B860" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C857" s="8" t="str">
+      <c r="C860" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_130N</v>
       </c>
-      <c r="D857" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E857" s="8" t="s">
+      <c r="D860" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E860" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F857" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A858" s="8" t="s">
+      <c r="F860" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="861" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A861" s="8" t="s">
         <v>2448</v>
       </c>
-      <c r="B858" s="8" t="s">
+      <c r="B861" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C858" s="8" t="str">
+      <c r="C861" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt10_131</v>
       </c>
-      <c r="D858" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E858" s="8">
+      <c r="D861" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E861" s="8">
         <v>131</v>
       </c>
-      <c r="F858" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A859" s="8" t="s">
+      <c r="F861" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="862" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A862" s="8" t="s">
         <v>2449</v>
       </c>
-      <c r="B859" s="8" t="s">
+      <c r="B862" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C859" s="8" t="str">
+      <c r="C862" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_126</v>
       </c>
-      <c r="D859" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E859" s="8">
+      <c r="D862" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E862" s="8">
         <v>126</v>
       </c>
-      <c r="F859" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A860" s="8" t="s">
+      <c r="F862" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="863" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A863" s="8" t="s">
         <v>2450</v>
       </c>
-      <c r="B860" s="8" t="s">
+      <c r="B863" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C860" s="8" t="str">
+      <c r="C863" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_127C</v>
       </c>
-      <c r="D860" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E860" s="8" t="s">
+      <c r="D863" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E863" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F860" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A861" s="8" t="s">
+      <c r="F863" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="864" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A864" s="8" t="s">
         <v>2451</v>
       </c>
-      <c r="B861" s="8" t="s">
+      <c r="B864" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C861" s="8" t="str">
+      <c r="C864" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_127N</v>
       </c>
-      <c r="D861" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E861" s="8" t="s">
+      <c r="D864" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E864" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F861" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A862" s="8" t="s">
+      <c r="F864" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="865" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A865" s="8" t="s">
         <v>2452</v>
       </c>
-      <c r="B862" s="8" t="s">
+      <c r="B865" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C862" s="8" t="str">
+      <c r="C865" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_128C</v>
       </c>
-      <c r="D862" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E862" s="8" t="s">
+      <c r="D865" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E865" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F862" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A863" s="8" t="s">
+      <c r="F865" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="866" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A866" s="8" t="s">
         <v>2453</v>
       </c>
-      <c r="B863" s="8" t="s">
+      <c r="B866" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C863" s="8" t="str">
+      <c r="C866" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_128N</v>
       </c>
-      <c r="D863" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E863" s="8" t="s">
+      <c r="D866" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E866" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F863" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A864" s="8" t="s">
+      <c r="F866" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="867" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A867" s="8" t="s">
         <v>2454</v>
       </c>
-      <c r="B864" s="8" t="s">
+      <c r="B867" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C864" s="8" t="str">
+      <c r="C867" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_129C</v>
       </c>
-      <c r="D864" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E864" s="8" t="s">
+      <c r="D867" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E867" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F864" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A865" s="8" t="s">
+      <c r="F867" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="868" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A868" s="8" t="s">
         <v>2455</v>
       </c>
-      <c r="B865" s="8" t="s">
+      <c r="B868" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C865" s="8" t="str">
+      <c r="C868" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_129N</v>
       </c>
-      <c r="D865" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E865" s="8" t="s">
+      <c r="D868" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E868" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F865" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="866" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A866" s="8" t="s">
+      <c r="F868" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="869" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A869" s="8" t="s">
         <v>2456</v>
       </c>
-      <c r="B866" s="8" t="s">
+      <c r="B869" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C866" s="8" t="str">
+      <c r="C869" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_130C</v>
       </c>
-      <c r="D866" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E866" s="8" t="s">
+      <c r="D869" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E869" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F866" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A867" s="8" t="s">
+      <c r="F869" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="870" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A870" s="8" t="s">
         <v>2457</v>
       </c>
-      <c r="B867" s="8" t="s">
+      <c r="B870" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C867" s="8" t="str">
+      <c r="C870" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_130N</v>
       </c>
-      <c r="D867" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E867" s="8" t="s">
+      <c r="D870" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E870" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F867" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A868" s="8" t="s">
+      <c r="F870" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="871" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A871" s="8" t="s">
         <v>2458</v>
       </c>
-      <c r="B868" s="8" t="s">
+      <c r="B871" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C868" s="8" t="str">
+      <c r="C871" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_131C</v>
       </c>
-      <c r="D868" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E868" s="8" t="s">
+      <c r="D871" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E871" s="8" t="s">
         <v>2459</v>
       </c>
-      <c r="F868" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A869" s="8" t="s">
+      <c r="F871" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="872" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A872" s="8" t="s">
         <v>2460</v>
       </c>
-      <c r="B869" s="8" t="s">
+      <c r="B872" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C869" s="8" t="str">
+      <c r="C872" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt11_131N</v>
       </c>
-      <c r="D869" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E869" s="8" t="s">
+      <c r="D872" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E872" s="8" t="s">
         <v>2461</v>
       </c>
-      <c r="F869" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A870" s="8" t="s">
+      <c r="F872" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="873" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A873" s="8" t="s">
         <v>2462</v>
       </c>
-      <c r="B870" s="8" t="s">
+      <c r="B873" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C870" s="8" t="str">
+      <c r="C873" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_126</v>
       </c>
-      <c r="D870" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E870" s="8">
+      <c r="D873" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E873" s="8">
         <v>126</v>
       </c>
-      <c r="F870" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="871" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A871" s="8" t="s">
+      <c r="F873" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="874" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A874" s="8" t="s">
         <v>2463</v>
       </c>
-      <c r="B871" s="8" t="s">
+      <c r="B874" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C871" s="8" t="str">
+      <c r="C874" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_127C</v>
       </c>
-      <c r="D871" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E871" s="8" t="s">
+      <c r="D874" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E874" s="8" t="s">
         <v>2433</v>
       </c>
-      <c r="F871" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A872" s="8" t="s">
+      <c r="F874" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="875" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A875" s="8" t="s">
         <v>2464</v>
       </c>
-      <c r="B872" s="8" t="s">
+      <c r="B875" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C872" s="8" t="str">
+      <c r="C875" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_127N</v>
       </c>
-      <c r="D872" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E872" s="8" t="s">
+      <c r="D875" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E875" s="8" t="s">
         <v>2435</v>
       </c>
-      <c r="F872" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A873" s="8" t="s">
+      <c r="F875" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="876" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A876" s="8" t="s">
         <v>2465</v>
       </c>
-      <c r="B873" s="8" t="s">
+      <c r="B876" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C873" s="8" t="str">
+      <c r="C876" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_128C</v>
       </c>
-      <c r="D873" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E873" s="8" t="s">
+      <c r="D876" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E876" s="8" t="s">
         <v>2437</v>
       </c>
-      <c r="F873" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A874" s="8" t="s">
+      <c r="F876" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="877" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A877" s="8" t="s">
         <v>2466</v>
       </c>
-      <c r="B874" s="8" t="s">
+      <c r="B877" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C874" s="8" t="str">
+      <c r="C877" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_128N</v>
       </c>
-      <c r="D874" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E874" s="8" t="s">
+      <c r="D877" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E877" s="8" t="s">
         <v>2439</v>
       </c>
-      <c r="F874" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A875" s="8" t="s">
+      <c r="F877" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="878" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A878" s="8" t="s">
         <v>2467</v>
       </c>
-      <c r="B875" s="8" t="s">
+      <c r="B878" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C875" s="8" t="str">
+      <c r="C878" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_129C</v>
       </c>
-      <c r="D875" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E875" s="8" t="s">
+      <c r="D878" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E878" s="8" t="s">
         <v>2441</v>
       </c>
-      <c r="F875" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A876" s="8" t="s">
+      <c r="F878" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="879" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A879" s="8" t="s">
         <v>2468</v>
       </c>
-      <c r="B876" s="8" t="s">
+      <c r="B879" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C876" s="8" t="str">
+      <c r="C879" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_129N</v>
       </c>
-      <c r="D876" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E876" s="8" t="s">
+      <c r="D879" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E879" s="8" t="s">
         <v>2443</v>
       </c>
-      <c r="F876" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A877" s="8" t="s">
+      <c r="F879" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="880" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A880" s="8" t="s">
         <v>2469</v>
       </c>
-      <c r="B877" s="8" t="s">
+      <c r="B880" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C877" s="8" t="str">
+      <c r="C880" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_130C</v>
       </c>
-      <c r="D877" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E877" s="8" t="s">
+      <c r="D880" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E880" s="8" t="s">
         <v>2445</v>
       </c>
-      <c r="F877" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A878" s="8" t="s">
+      <c r="F880" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="881" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A881" s="8" t="s">
         <v>2470</v>
       </c>
-      <c r="B878" s="8" t="s">
+      <c r="B881" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C878" s="8" t="str">
+      <c r="C881" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_130N</v>
       </c>
-      <c r="D878" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E878" s="8" t="s">
+      <c r="D881" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E881" s="8" t="s">
         <v>2447</v>
       </c>
-      <c r="F878" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A879" s="8" t="s">
+      <c r="F881" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="882" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A882" s="8" t="s">
         <v>2471</v>
       </c>
-      <c r="B879" s="8" t="s">
+      <c r="B882" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C879" s="8" t="str">
+      <c r="C882" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_131C</v>
       </c>
-      <c r="D879" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E879" s="8" t="s">
+      <c r="D882" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E882" s="8" t="s">
         <v>2459</v>
       </c>
-      <c r="F879" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A880" s="8" t="s">
+      <c r="F882" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="883" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A883" s="8" t="s">
         <v>2472</v>
       </c>
-      <c r="B880" s="8" t="s">
+      <c r="B883" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C880" s="8" t="str">
+      <c r="C883" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_131N</v>
       </c>
-      <c r="D880" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E880" s="8" t="s">
+      <c r="D883" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E883" s="8" t="s">
         <v>2461</v>
       </c>
-      <c r="F880" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A881" s="8" t="s">
+      <c r="F883" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="884" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A884" s="8" t="s">
         <v>2473</v>
       </c>
-      <c r="B881" s="8" t="s">
+      <c r="B884" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C881" s="8" t="str">
+      <c r="C884" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_132C</v>
       </c>
-      <c r="D881" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E881" s="8" t="s">
+      <c r="D884" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E884" s="8" t="s">
         <v>2474</v>
       </c>
-      <c r="F881" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="882" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A882" s="8" t="s">
+      <c r="F884" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="885" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A885" s="8" t="s">
         <v>2475</v>
       </c>
-      <c r="B882" s="8" t="s">
+      <c r="B885" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C882" s="8" t="str">
+      <c r="C885" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_132N</v>
       </c>
-      <c r="D882" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E882" s="8" t="s">
+      <c r="D885" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E885" s="8" t="s">
         <v>2476</v>
       </c>
-      <c r="F882" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A883" s="8" t="s">
+      <c r="F885" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="886" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A886" s="8" t="s">
         <v>2477</v>
       </c>
-      <c r="B883" s="8" t="s">
+      <c r="B886" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C883" s="8" t="str">
+      <c r="C886" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_133C</v>
       </c>
-      <c r="D883" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E883" s="8" t="s">
+      <c r="D886" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E886" s="8" t="s">
         <v>2478</v>
       </c>
-      <c r="F883" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A884" s="8" t="s">
+      <c r="F886" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="887" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A887" s="8" t="s">
         <v>2479</v>
       </c>
-      <c r="B884" s="8" t="s">
+      <c r="B887" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C884" s="8" t="str">
+      <c r="C887" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_133N</v>
       </c>
-      <c r="D884" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E884" s="8" t="s">
+      <c r="D887" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E887" s="8" t="s">
         <v>2480</v>
       </c>
-      <c r="F884" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A885" s="8" t="s">
+      <c r="F887" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="888" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A888" s="8" t="s">
         <v>2481</v>
       </c>
-      <c r="B885" s="8" t="s">
+      <c r="B888" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C885" s="8" t="str">
+      <c r="C888" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_134C</v>
       </c>
-      <c r="D885" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E885" s="8" t="s">
+      <c r="D888" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E888" s="8" t="s">
         <v>2482</v>
       </c>
-      <c r="F885" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A886" s="8" t="s">
+      <c r="F888" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="889" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A889" s="8" t="s">
         <v>2483</v>
       </c>
-      <c r="B886" s="8" t="s">
+      <c r="B889" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C886" s="8" t="str">
+      <c r="C889" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_134N</v>
       </c>
-      <c r="D886" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E886" s="8" t="s">
+      <c r="D889" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E889" s="8" t="s">
         <v>2484</v>
       </c>
-      <c r="F886" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A887" s="8" t="s">
+      <c r="F889" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="890" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A890" s="8" t="s">
         <v>2485</v>
       </c>
-      <c r="B887" s="8" t="s">
+      <c r="B890" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C887" s="8" t="str">
+      <c r="C890" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt18_135N</v>
       </c>
-      <c r="D887" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E887" s="8" t="s">
+      <c r="D890" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E890" s="8" t="s">
         <v>2486</v>
       </c>
-      <c r="F887" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A888" s="8" t="s">
+      <c r="F890" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="891" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A891" s="8" t="s">
         <v>2487</v>
       </c>
-      <c r="B888" s="8" t="s">
+      <c r="B891" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C888" s="8" t="str">
+      <c r="C891" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt6_126</v>
       </c>
-      <c r="D888" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E888" s="8">
+      <c r="D891" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E891" s="8">
         <v>126</v>
       </c>
-      <c r="F888" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A889" s="8" t="s">
+      <c r="F891" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="892" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A892" s="8" t="s">
         <v>2488</v>
       </c>
-      <c r="B889" s="8" t="s">
+      <c r="B892" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C889" s="8" t="str">
+      <c r="C892" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt6_127</v>
       </c>
-      <c r="D889" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E889" s="8">
+      <c r="D892" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E892" s="8">
         <v>127</v>
       </c>
-      <c r="F889" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="890" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A890" s="8" t="s">
+      <c r="F892" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="893" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A893" s="8" t="s">
         <v>2489</v>
       </c>
-      <c r="B890" s="8" t="s">
+      <c r="B893" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C890" s="8" t="str">
+      <c r="C893" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt6_128</v>
       </c>
-      <c r="D890" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E890" s="8">
+      <c r="D893" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E893" s="8">
         <v>128</v>
       </c>
-      <c r="F890" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A891" s="8" t="s">
+      <c r="F893" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="894" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A894" s="8" t="s">
         <v>2490</v>
       </c>
-      <c r="B891" s="8" t="s">
+      <c r="B894" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C891" s="8" t="str">
+      <c r="C894" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt6_129</v>
       </c>
-      <c r="D891" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E891" s="8">
+      <c r="D894" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E894" s="8">
         <v>129</v>
       </c>
-      <c r="F891" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A892" s="8" t="s">
+      <c r="F894" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="895" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A895" s="8" t="s">
         <v>2491</v>
       </c>
-      <c r="B892" s="8" t="s">
+      <c r="B895" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C892" s="8" t="str">
+      <c r="C895" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt6_130</v>
       </c>
-      <c r="D892" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E892" s="8">
+      <c r="D895" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E895" s="8">
         <v>130</v>
       </c>
-      <c r="F892" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="893" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A893" s="8" t="s">
+      <c r="F895" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="896" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A896" s="8" t="s">
         <v>2492</v>
       </c>
-      <c r="B893" s="8" t="s">
+      <c r="B896" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="C893" s="8" t="str">
+      <c r="C896" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_tmt_channel:tmt6_131</v>
       </c>
-      <c r="D893" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E893" s="8">
+      <c r="D896" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E896" s="8">
         <v>131</v>
       </c>
-      <c r="F893" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A894" s="8" t="s">
+      <c r="F896" s="9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="897" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A897" s="8" t="s">
         <v>2493</v>
       </c>
-      <c r="B894" s="8" t="s">
+      <c r="B897" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C894" s="8" t="str">
+      <c r="C897" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_user_institute:biochem</v>
       </c>
-      <c r="D894" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E894" s="8" t="s">
+      <c r="D897" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E897" s="8" t="s">
         <v>2494</v>
       </c>
-      <c r="F894" s="8" t="s">
+      <c r="F897" s="8" t="s">
         <v>2495</v>
       </c>
     </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A895" s="8" t="s">
+    <row r="898" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A898" s="8" t="s">
         <v>2496</v>
       </c>
-      <c r="B895" s="8" t="s">
+      <c r="B898" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C895" s="8" t="str">
+      <c r="C898" s="8" t="str">
         <f t="shared" si="20"/>
         <v>att_user_institute:cecad</v>
       </c>
-      <c r="D895" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E895" s="8" t="s">
+      <c r="D898" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E898" s="8" t="s">
         <v>2497</v>
       </c>
-      <c r="F895" s="8" t="s">
+      <c r="F898" s="8" t="s">
         <v>2498</v>
       </c>
     </row>
-    <row r="896" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A896" s="8" t="s">
+    <row r="899" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A899" s="8" t="s">
         <v>2499</v>
       </c>
-      <c r="B896" s="8" t="s">
+      <c r="B899" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C896" s="8" t="str">
-        <f t="shared" ref="C896:C925" si="24">B896&amp;":"&amp;A896</f>
+      <c r="C899" s="8" t="str">
+        <f t="shared" ref="C899:C928" si="24">B899&amp;":"&amp;A899</f>
         <v>att_user_institute:mpiage</v>
       </c>
-      <c r="D896" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E896" s="8" t="s">
+      <c r="D899" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E899" s="8" t="s">
         <v>2500</v>
       </c>
-      <c r="F896" s="8" t="s">
+      <c r="F899" s="8" t="s">
         <v>2501</v>
       </c>
     </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A897" s="8" t="s">
+    <row r="900" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A900" s="8" t="s">
         <v>2502</v>
       </c>
-      <c r="B897" s="8" t="s">
+      <c r="B900" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C897" s="8" t="str">
+      <c r="C900" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_institute:mpimetab</v>
       </c>
-      <c r="D897" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="E897" s="8" t="s">
+      <c r="D900" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E900" s="8" t="s">
         <v>2503</v>
       </c>
-      <c r="F897" s="8" t="s">
+      <c r="F900" s="8" t="s">
         <v>2504</v>
       </c>
     </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A898" s="8" t="s">
+    <row r="901" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A901" s="8" t="s">
         <v>2493</v>
       </c>
-      <c r="B898" s="8" t="s">
+      <c r="B901" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C898" s="8" t="str">
+      <c r="C901" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_institute:biochem</v>
       </c>
-      <c r="D898" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E898" s="8" t="s">
+      <c r="D901" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E901" s="8" t="s">
         <v>2494</v>
       </c>
-      <c r="F898" s="8" t="s">
+      <c r="F901" s="8" t="s">
         <v>2495</v>
       </c>
     </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A899" s="8" t="s">
+    <row r="902" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A902" s="8" t="s">
         <v>2496</v>
       </c>
-      <c r="B899" s="8" t="s">
+      <c r="B902" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C899" s="8" t="str">
+      <c r="C902" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_institute:cecad</v>
       </c>
-      <c r="D899" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E899" s="8" t="s">
+      <c r="D902" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E902" s="8" t="s">
         <v>2497</v>
       </c>
-      <c r="F899" s="8" t="s">
+      <c r="F902" s="8" t="s">
         <v>2498</v>
       </c>
     </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A900" s="8" t="s">
+    <row r="903" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A903" s="8" t="s">
         <v>2499</v>
       </c>
-      <c r="B900" s="8" t="s">
+      <c r="B903" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C900" s="8" t="str">
+      <c r="C903" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_institute:mpiage</v>
       </c>
-      <c r="D900" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E900" s="8" t="s">
+      <c r="D903" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E903" s="8" t="s">
         <v>2500</v>
       </c>
-      <c r="F900" s="8" t="s">
+      <c r="F903" s="8" t="s">
         <v>2501</v>
       </c>
     </row>
-    <row r="901" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A901" s="8" t="s">
+    <row r="904" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A904" s="8" t="s">
         <v>2502</v>
       </c>
-      <c r="B901" s="8" t="s">
+      <c r="B904" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="C901" s="8" t="str">
+      <c r="C904" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_institute:mpimetab</v>
       </c>
-      <c r="D901" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E901" s="8" t="s">
+      <c r="D904" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E904" s="8" t="s">
         <v>2503</v>
       </c>
-      <c r="F901" s="8" t="s">
+      <c r="F904" s="8" t="s">
         <v>2504</v>
       </c>
     </row>
-    <row r="902" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A902" s="8" t="s">
+    <row r="905" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A905" s="8" t="s">
         <v>2505</v>
       </c>
-      <c r="B902" s="8" t="s">
+      <c r="B905" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C902" s="8" t="str">
+      <c r="C905" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:mitoprotea</v>
       </c>
-      <c r="D902" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E902" s="8" t="s">
+      <c r="D905" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E905" s="8" t="s">
         <v>2506</v>
       </c>
-      <c r="F902" s="8" t="s">
+      <c r="F905" s="8" t="s">
         <v>2507</v>
       </c>
     </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A903" s="8" t="s">
+    <row r="906" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A906" s="8" t="s">
         <v>2508</v>
       </c>
-      <c r="B903" s="8" t="s">
+      <c r="B906" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C903" s="8" t="str">
+      <c r="C906" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:molageing</v>
       </c>
-      <c r="D903" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E903" s="8" t="s">
+      <c r="D906" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E906" s="8" t="s">
         <v>2509</v>
       </c>
-      <c r="F903" s="8" t="s">
+      <c r="F906" s="8" t="s">
         <v>2510</v>
       </c>
     </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A904" s="8" t="s">
+    <row r="907" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A907" s="8" t="s">
         <v>2874</v>
       </c>
-      <c r="B904" s="8" t="s">
+      <c r="B907" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C904" s="8" t="str">
+      <c r="C907" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:ProtFa</v>
       </c>
-      <c r="D904" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E904" s="8" t="s">
+      <c r="D907" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E907" s="8" t="s">
         <v>2875</v>
       </c>
-      <c r="F904" s="8" t="s">
+      <c r="F907" s="8" t="s">
         <v>2876</v>
       </c>
     </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A905" s="8" t="s">
+    <row r="908" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A908" s="8" t="s">
         <v>2877</v>
       </c>
-      <c r="B905" s="8" t="s">
+      <c r="B908" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C905" s="8" t="str">
+      <c r="C908" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:frezza</v>
       </c>
-      <c r="D905" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E905" s="8" t="s">
+      <c r="D908" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E908" s="8" t="s">
         <v>2878</v>
       </c>
-      <c r="F905" s="8" t="s">
+      <c r="F908" s="8" t="s">
         <v>2879</v>
       </c>
     </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A906" s="8" t="s">
+    <row r="909" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A909" s="8" t="s">
         <v>2880</v>
       </c>
-      <c r="B906" s="8" t="s">
+      <c r="B909" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C906" s="8" t="str">
+      <c r="C909" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:krueger</v>
       </c>
-      <c r="D906" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E906" s="8" t="s">
+      <c r="D909" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E909" s="8" t="s">
         <v>2881</v>
       </c>
-      <c r="F906" s="8" t="s">
+      <c r="F909" s="8" t="s">
         <v>2882</v>
       </c>
     </row>
-    <row r="907" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A907" s="8" t="s">
+    <row r="910" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A910" s="8" t="s">
         <v>2883</v>
       </c>
-      <c r="B907" s="8" t="s">
+      <c r="B910" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C907" s="8" t="str">
+      <c r="C910" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:rugarli</v>
       </c>
-      <c r="D907" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E907" s="8" t="s">
+      <c r="D910" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E910" s="8" t="s">
         <v>2884</v>
       </c>
-      <c r="F907" s="8" t="s">
+      <c r="F910" s="8" t="s">
         <v>2882</v>
       </c>
     </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A908" s="8" t="s">
+    <row r="911" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A911" s="8" t="s">
         <v>2885</v>
       </c>
-      <c r="B908" s="8" t="s">
+      <c r="B911" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C908" s="8" t="str">
+      <c r="C911" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:trifunovic</v>
       </c>
-      <c r="D908" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E908" s="8" t="s">
+      <c r="D911" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E911" s="8" t="s">
         <v>2886</v>
       </c>
-      <c r="F908" s="8" t="s">
+      <c r="F911" s="8" t="s">
         <v>2887</v>
       </c>
     </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A909" s="8" t="s">
+    <row r="912" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A912" s="8" t="s">
         <v>2888</v>
       </c>
-      <c r="B909" s="8" t="s">
+      <c r="B912" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C909" s="8" t="str">
+      <c r="C912" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:niessen</v>
       </c>
-      <c r="D909" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E909" s="8" t="s">
+      <c r="D912" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E912" s="8" t="s">
         <v>2889</v>
       </c>
-      <c r="F909" s="8" t="s">
+      <c r="F912" s="8" t="s">
         <v>2497</v>
       </c>
     </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A910" s="8" t="s">
+    <row r="913" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A913" s="8" t="s">
         <v>2890</v>
       </c>
-      <c r="B910" s="8" t="s">
+      <c r="B913" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C910" s="8" t="str">
+      <c r="C913" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:gloeckner</v>
       </c>
-      <c r="D910" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E910" s="8" t="s">
+      <c r="D913" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E913" s="8" t="s">
         <v>2891</v>
       </c>
-      <c r="F910" s="8" t="s">
+      <c r="F913" s="8" t="s">
         <v>2892</v>
       </c>
     </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A911" s="8" t="s">
+    <row r="914" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A914" s="8" t="s">
         <v>2893</v>
       </c>
-      <c r="B911" s="8" t="s">
+      <c r="B914" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C911" s="8" t="str">
+      <c r="C914" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:bazzi</v>
       </c>
-      <c r="D911" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E911" s="8" t="s">
+      <c r="D914" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E914" s="8" t="s">
         <v>2894</v>
       </c>
-      <c r="F911" s="8" t="s">
+      <c r="F914" s="8" t="s">
         <v>2895</v>
       </c>
     </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A912" s="8" t="s">
+    <row r="915" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A915" s="8" t="s">
         <v>2896</v>
       </c>
-      <c r="B912" s="8" t="s">
+      <c r="B915" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C912" s="8" t="str">
+      <c r="C915" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:hallek</v>
       </c>
-      <c r="D912" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E912" s="8" t="s">
+      <c r="D915" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E915" s="8" t="s">
         <v>2897</v>
       </c>
-      <c r="F912" s="8" t="s">
+      <c r="F915" s="8" t="s">
         <v>2898</v>
       </c>
     </row>
-    <row r="913" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A913" s="8" t="s">
+    <row r="916" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A916" s="8" t="s">
         <v>2899</v>
       </c>
-      <c r="B913" s="8" t="s">
+      <c r="B916" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C913" s="8" t="str">
+      <c r="C916" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:benzing</v>
       </c>
-      <c r="D913" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E913" s="8" t="s">
+      <c r="D916" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E916" s="8" t="s">
         <v>2900</v>
       </c>
-      <c r="F913" s="8" t="s">
+      <c r="F916" s="8" t="s">
         <v>2901</v>
       </c>
     </row>
-    <row r="914" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A914" s="8" t="s">
+    <row r="917" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A917" s="8" t="s">
         <v>2902</v>
       </c>
-      <c r="B914" s="8" t="s">
+      <c r="B917" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C914" s="8" t="str">
+      <c r="C917" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:hennies</v>
       </c>
-      <c r="D914" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E914" s="8" t="s">
+      <c r="D917" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E917" s="8" t="s">
         <v>2903</v>
       </c>
-      <c r="F914" s="8" t="s">
+      <c r="F917" s="8" t="s">
         <v>2904</v>
       </c>
     </row>
-    <row r="915" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A915" s="8" t="s">
+    <row r="918" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A918" s="8" t="s">
         <v>2905</v>
       </c>
-      <c r="B915" s="8" t="s">
+      <c r="B918" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C915" s="8" t="str">
+      <c r="C918" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:vonkarstedt</v>
       </c>
-      <c r="D915" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E915" s="8" t="s">
+      <c r="D918" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E918" s="8" t="s">
         <v>2906</v>
       </c>
-      <c r="F915" s="8" t="s">
+      <c r="F918" s="8" t="s">
         <v>2907</v>
       </c>
     </row>
-    <row r="916" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A916" s="8" t="s">
+    <row r="919" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A919" s="8" t="s">
         <v>2908</v>
       </c>
-      <c r="B916" s="8" t="s">
+      <c r="B919" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C916" s="8" t="str">
+      <c r="C919" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:laessig</v>
       </c>
-      <c r="D916" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E916" s="8" t="s">
+      <c r="D919" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E919" s="8" t="s">
         <v>2909</v>
       </c>
-      <c r="F916" s="8" t="s">
+      <c r="F919" s="8" t="s">
         <v>2910</v>
       </c>
     </row>
-    <row r="917" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A917" s="8" t="s">
+    <row r="920" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A920" s="8" t="s">
         <v>2911</v>
       </c>
-      <c r="B917" s="8" t="s">
+      <c r="B920" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C917" s="8" t="str">
+      <c r="C920" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:hoppe</v>
       </c>
-      <c r="D917" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E917" s="8" t="s">
+      <c r="D920" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E920" s="8" t="s">
         <v>2912</v>
       </c>
-      <c r="F917" s="8" t="s">
+      <c r="F920" s="8" t="s">
         <v>2913</v>
       </c>
     </row>
-    <row r="918" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A918" s="8" t="s">
+    <row r="921" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A921" s="8" t="s">
         <v>2914</v>
       </c>
-      <c r="B918" s="8" t="s">
+      <c r="B921" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C918" s="8" t="str">
+      <c r="C921" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:garcia</v>
       </c>
-      <c r="D918" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E918" s="8" t="s">
+      <c r="D921" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E921" s="8" t="s">
         <v>2915</v>
       </c>
-      <c r="F918" s="8" t="s">
+      <c r="F921" s="8" t="s">
         <v>2913</v>
       </c>
     </row>
-    <row r="919" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A919" s="8" t="s">
+    <row r="922" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A922" s="8" t="s">
         <v>2916</v>
       </c>
-      <c r="B919" s="8" t="s">
+      <c r="B922" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C919" s="8" t="str">
+      <c r="C922" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:khaskar</v>
       </c>
-      <c r="D919" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E919" s="8" t="s">
+      <c r="D922" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E922" s="8" t="s">
         <v>2917</v>
       </c>
-      <c r="F919" s="8" t="s">
+      <c r="F922" s="8" t="s">
         <v>2918</v>
       </c>
     </row>
-    <row r="920" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A920" s="8" t="s">
+    <row r="923" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A923" s="8" t="s">
         <v>2919</v>
       </c>
-      <c r="B920" s="8" t="s">
+      <c r="B923" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="C920" s="8" t="str">
+      <c r="C923" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_user_research_group:krieg</v>
       </c>
-      <c r="D920" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E920" s="8" t="s">
+      <c r="D923" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E923" s="8" t="s">
         <v>2920</v>
       </c>
-      <c r="F920" s="8" t="s">
+      <c r="F923" s="8" t="s">
         <v>2921</v>
       </c>
     </row>
-    <row r="921" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A921" s="8" t="s">
+    <row r="924" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A924" s="8" t="s">
         <v>2824</v>
       </c>
-      <c r="B921" s="22" t="s">
+      <c r="B924" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C921" s="8" t="str">
+      <c r="C924" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_diet:wd</v>
       </c>
-      <c r="D921" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E921" s="8" t="s">
+      <c r="D924" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E924" s="8" t="s">
         <v>2823</v>
       </c>
-      <c r="F921" s="8" t="s">
+      <c r="F924" s="8" t="s">
         <v>2822</v>
       </c>
     </row>
-    <row r="922" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A922" s="8" t="s">
+    <row r="925" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A925" s="8" t="s">
         <v>2825</v>
       </c>
-      <c r="B922" s="22" t="s">
+      <c r="B925" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C922" s="8" t="str">
+      <c r="C925" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_diet:sd</v>
       </c>
-      <c r="D922" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E922" s="8" t="s">
+      <c r="D925" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E925" s="8" t="s">
         <v>2826</v>
       </c>
     </row>
-    <row r="923" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A923" s="8" t="s">
+    <row r="926" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A926" s="8" t="s">
         <v>2827</v>
       </c>
-      <c r="B923" s="22" t="s">
+      <c r="B926" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C923" s="8" t="str">
+      <c r="C926" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_diet:veg</v>
       </c>
-      <c r="D923" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E923" s="8" t="s">
+      <c r="D926" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E926" s="8" t="s">
         <v>2828</v>
       </c>
-      <c r="F923" s="8" t="s">
+      <c r="F926" s="8" t="s">
         <v>2829</v>
       </c>
     </row>
-    <row r="924" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A924" s="8" t="s">
+    <row r="927" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A927" s="8" t="s">
         <v>2832</v>
       </c>
-      <c r="B924" s="22" t="s">
+      <c r="B927" s="22" t="s">
         <v>2820</v>
       </c>
-      <c r="C924" s="8" t="str">
+      <c r="C927" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_diet:hg</v>
       </c>
-      <c r="D924" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E924" s="8" t="s">
+      <c r="D927" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E927" s="8" t="s">
         <v>2830</v>
       </c>
-      <c r="F924" s="8" t="s">
+      <c r="F927" s="8" t="s">
         <v>2831</v>
       </c>
     </row>
-    <row r="925" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A925" s="8" t="s">
+    <row r="928" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A928" s="8" t="s">
         <v>2835</v>
       </c>
-      <c r="B925" s="8" t="s">
+      <c r="B928" s="8" t="s">
         <v>2820</v>
       </c>
-      <c r="C925" s="8" t="str">
+      <c r="C928" s="8" t="str">
         <f t="shared" si="24"/>
         <v>att_diet:hfd</v>
       </c>
-      <c r="D925" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E925" s="8" t="s">
+      <c r="D928" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E928" s="8" t="s">
         <v>2833</v>
       </c>
-      <c r="F925" s="8" t="s">
+      <c r="F928" s="8" t="s">
         <v>2834</v>
       </c>
     </row>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FBAB63-C07A-D64E-9B0E-7DEC8EE7C147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4164D8BE-81E0-3B4A-87EB-18F6662E310E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21640" yWindow="3460" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21640" yWindow="3460" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10494" uniqueCount="3039">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10484" uniqueCount="3040">
   <si>
     <t>tag</t>
   </si>
@@ -9159,6 +9159,9 @@
   </si>
   <si>
     <t>Easy nLC 1200, Thermo Fisher, SN: LC-030802</t>
+  </si>
+  <si>
+    <t>opentronsot2</t>
   </si>
 </sst>
 </file>
@@ -14461,7 +14464,7 @@
         <v>47</v>
       </c>
       <c r="H94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I94" s="7" t="b">
         <v>0</v>
@@ -14476,16 +14479,16 @@
         <v>19</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
@@ -15911,7 +15914,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ1061"/>
+  <dimension ref="A1:AMJ1059"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -25337,14 +25340,14 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A449" s="8" t="s">
-        <v>1363</v>
+        <v>3039</v>
       </c>
       <c r="B449" s="8" t="s">
         <v>150</v>
       </c>
       <c r="C449" s="8" t="str">
         <f t="shared" ref="C449" si="9">B449&amp;":"&amp;A449</f>
-        <v>att_liquid_handler:opentrons</v>
+        <v>att_liquid_handler:opentronsot2</v>
       </c>
       <c r="D449" s="8" t="s">
         <v>1363</v>
@@ -37879,7 +37882,7 @@
         <v>248</v>
       </c>
       <c r="C901" s="8" t="str">
-        <f t="shared" ref="C901:C943" si="24">B901&amp;":"&amp;A901</f>
+        <f t="shared" ref="C901:C941" si="24">B901&amp;":"&amp;A901</f>
         <v>att_user_institute:mpiage</v>
       </c>
       <c r="D901" s="9" t="s">
@@ -37915,864 +37918,828 @@
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A903" s="8" t="s">
-        <v>2492</v>
+        <v>2504</v>
       </c>
       <c r="B903" s="8" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C903" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_institute:biochem</v>
+        <v>att_user_research_group:mitoprotea</v>
       </c>
       <c r="D903" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E903" s="8" t="s">
-        <v>2493</v>
+        <v>2505</v>
       </c>
       <c r="F903" s="8" t="s">
-        <v>2494</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A904" s="8" t="s">
-        <v>2495</v>
+        <v>2507</v>
       </c>
       <c r="B904" s="8" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C904" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_institute:cecad</v>
+        <v>att_user_research_group:molageing</v>
       </c>
       <c r="D904" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E904" s="8" t="s">
-        <v>2496</v>
+        <v>2508</v>
       </c>
       <c r="F904" s="8" t="s">
-        <v>2497</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A905" s="8" t="s">
-        <v>2504</v>
+        <v>2872</v>
       </c>
       <c r="B905" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C905" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:mitoprotea</v>
+        <v>att_user_research_group:ProtFa</v>
       </c>
       <c r="D905" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E905" s="8" t="s">
-        <v>2505</v>
+        <v>2873</v>
       </c>
       <c r="F905" s="8" t="s">
-        <v>2506</v>
+        <v>2874</v>
       </c>
     </row>
     <row r="906" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A906" s="8" t="s">
-        <v>2507</v>
+        <v>2875</v>
       </c>
       <c r="B906" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C906" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:molageing</v>
+        <v>att_user_research_group:frezza</v>
       </c>
       <c r="D906" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E906" s="8" t="s">
-        <v>2508</v>
+        <v>2876</v>
       </c>
       <c r="F906" s="8" t="s">
-        <v>2509</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="907" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A907" s="8" t="s">
-        <v>2872</v>
+        <v>2878</v>
       </c>
       <c r="B907" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C907" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:ProtFa</v>
+        <v>att_user_research_group:krueger</v>
       </c>
       <c r="D907" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E907" s="8" t="s">
-        <v>2873</v>
+        <v>2879</v>
       </c>
       <c r="F907" s="8" t="s">
-        <v>2874</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="908" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A908" s="8" t="s">
-        <v>2875</v>
+        <v>2881</v>
       </c>
       <c r="B908" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C908" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:frezza</v>
+        <v>att_user_research_group:rugarli</v>
       </c>
       <c r="D908" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E908" s="8" t="s">
-        <v>2876</v>
+        <v>2882</v>
       </c>
       <c r="F908" s="8" t="s">
-        <v>2877</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A909" s="8" t="s">
-        <v>2878</v>
+        <v>2883</v>
       </c>
       <c r="B909" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C909" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:krueger</v>
+        <v>att_user_research_group:trifunovic</v>
       </c>
       <c r="D909" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E909" s="8" t="s">
-        <v>2879</v>
+        <v>2884</v>
       </c>
       <c r="F909" s="8" t="s">
-        <v>2880</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A910" s="8" t="s">
-        <v>2881</v>
+        <v>2886</v>
       </c>
       <c r="B910" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C910" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:rugarli</v>
+        <v>att_user_research_group:niessen</v>
       </c>
       <c r="D910" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E910" s="8" t="s">
-        <v>2882</v>
+        <v>2887</v>
       </c>
       <c r="F910" s="8" t="s">
-        <v>2880</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A911" s="8" t="s">
-        <v>2883</v>
+        <v>2888</v>
       </c>
       <c r="B911" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C911" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:trifunovic</v>
+        <v>att_user_research_group:gloeckner</v>
       </c>
       <c r="D911" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E911" s="8" t="s">
-        <v>2884</v>
+        <v>2889</v>
       </c>
       <c r="F911" s="8" t="s">
-        <v>2885</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A912" s="8" t="s">
-        <v>2886</v>
+        <v>2891</v>
       </c>
       <c r="B912" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C912" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:niessen</v>
+        <v>att_user_research_group:bazzi</v>
       </c>
       <c r="D912" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E912" s="8" t="s">
-        <v>2887</v>
+        <v>2892</v>
       </c>
       <c r="F912" s="8" t="s">
-        <v>2496</v>
+        <v>2893</v>
       </c>
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A913" s="8" t="s">
-        <v>2888</v>
+        <v>2894</v>
       </c>
       <c r="B913" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C913" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:gloeckner</v>
+        <v>att_user_research_group:hallek</v>
       </c>
       <c r="D913" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E913" s="8" t="s">
-        <v>2889</v>
+        <v>2895</v>
       </c>
       <c r="F913" s="8" t="s">
-        <v>2890</v>
+        <v>2896</v>
       </c>
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A914" s="8" t="s">
-        <v>2891</v>
+        <v>2897</v>
       </c>
       <c r="B914" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C914" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:bazzi</v>
+        <v>att_user_research_group:benzing</v>
       </c>
       <c r="D914" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E914" s="8" t="s">
-        <v>2892</v>
+        <v>2898</v>
       </c>
       <c r="F914" s="8" t="s">
-        <v>2893</v>
+        <v>2899</v>
       </c>
     </row>
     <row r="915" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A915" s="8" t="s">
-        <v>2894</v>
+        <v>2900</v>
       </c>
       <c r="B915" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C915" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:hallek</v>
+        <v>att_user_research_group:hennies</v>
       </c>
       <c r="D915" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E915" s="8" t="s">
-        <v>2895</v>
+        <v>2901</v>
       </c>
       <c r="F915" s="8" t="s">
-        <v>2896</v>
+        <v>2902</v>
       </c>
     </row>
     <row r="916" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A916" s="8" t="s">
-        <v>2897</v>
+        <v>2903</v>
       </c>
       <c r="B916" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C916" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:benzing</v>
+        <v>att_user_research_group:vonkarstedt</v>
       </c>
       <c r="D916" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E916" s="8" t="s">
-        <v>2898</v>
+        <v>2904</v>
       </c>
       <c r="F916" s="8" t="s">
-        <v>2899</v>
+        <v>2905</v>
       </c>
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A917" s="8" t="s">
-        <v>2900</v>
+        <v>2906</v>
       </c>
       <c r="B917" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C917" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:hennies</v>
+        <v>att_user_research_group:laessig</v>
       </c>
       <c r="D917" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E917" s="8" t="s">
-        <v>2901</v>
+        <v>2907</v>
       </c>
       <c r="F917" s="8" t="s">
-        <v>2902</v>
+        <v>2908</v>
       </c>
     </row>
     <row r="918" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A918" s="8" t="s">
-        <v>2903</v>
+        <v>2909</v>
       </c>
       <c r="B918" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C918" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:vonkarstedt</v>
+        <v>att_user_research_group:hoppe</v>
       </c>
       <c r="D918" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E918" s="8" t="s">
-        <v>2904</v>
+        <v>2910</v>
       </c>
       <c r="F918" s="8" t="s">
-        <v>2905</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="919" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A919" s="8" t="s">
-        <v>2906</v>
+        <v>2912</v>
       </c>
       <c r="B919" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C919" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:laessig</v>
+        <v>att_user_research_group:garcia</v>
       </c>
       <c r="D919" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E919" s="8" t="s">
-        <v>2907</v>
+        <v>2913</v>
       </c>
       <c r="F919" s="8" t="s">
-        <v>2908</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="920" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A920" s="8" t="s">
-        <v>2909</v>
+        <v>2914</v>
       </c>
       <c r="B920" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C920" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:hoppe</v>
+        <v>att_user_research_group:khaskar</v>
       </c>
       <c r="D920" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E920" s="8" t="s">
-        <v>2910</v>
+        <v>2915</v>
       </c>
       <c r="F920" s="8" t="s">
-        <v>2911</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="921" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A921" s="8" t="s">
-        <v>2912</v>
+        <v>2917</v>
       </c>
       <c r="B921" s="8" t="s">
         <v>252</v>
       </c>
       <c r="C921" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:garcia</v>
+        <v>att_user_research_group:krieg</v>
       </c>
       <c r="D921" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E921" s="8" t="s">
-        <v>2913</v>
+        <v>2918</v>
       </c>
       <c r="F921" s="8" t="s">
-        <v>2911</v>
+        <v>2919</v>
       </c>
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A922" s="8" t="s">
-        <v>2914</v>
-      </c>
-      <c r="B922" s="8" t="s">
-        <v>252</v>
+        <v>2823</v>
+      </c>
+      <c r="B922" s="22" t="s">
+        <v>2819</v>
       </c>
       <c r="C922" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:khaskar</v>
+        <v>att_diet:wd</v>
       </c>
       <c r="D922" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E922" s="8" t="s">
-        <v>2915</v>
+        <v>2822</v>
       </c>
       <c r="F922" s="8" t="s">
-        <v>2916</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A923" s="8" t="s">
-        <v>2917</v>
-      </c>
-      <c r="B923" s="8" t="s">
-        <v>252</v>
+        <v>2824</v>
+      </c>
+      <c r="B923" s="22" t="s">
+        <v>2819</v>
       </c>
       <c r="C923" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_user_research_group:krieg</v>
+        <v>att_diet:sd</v>
       </c>
       <c r="D923" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E923" s="8" t="s">
-        <v>2918</v>
-      </c>
-      <c r="F923" s="8" t="s">
-        <v>2919</v>
+        <v>2825</v>
       </c>
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A924" s="8" t="s">
-        <v>2823</v>
+        <v>2826</v>
       </c>
       <c r="B924" s="22" t="s">
         <v>2819</v>
       </c>
       <c r="C924" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_diet:wd</v>
+        <v>att_diet:veg</v>
       </c>
       <c r="D924" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E924" s="8" t="s">
-        <v>2822</v>
+        <v>2827</v>
       </c>
       <c r="F924" s="8" t="s">
-        <v>2821</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A925" s="8" t="s">
-        <v>2824</v>
+        <v>2831</v>
       </c>
       <c r="B925" s="22" t="s">
         <v>2819</v>
       </c>
       <c r="C925" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_diet:sd</v>
+        <v>att_diet:hg</v>
       </c>
       <c r="D925" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E925" s="8" t="s">
-        <v>2825</v>
+        <v>2829</v>
+      </c>
+      <c r="F925" s="8" t="s">
+        <v>2830</v>
       </c>
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A926" s="8" t="s">
-        <v>2826</v>
-      </c>
-      <c r="B926" s="22" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B926" s="8" t="s">
         <v>2819</v>
       </c>
       <c r="C926" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_diet:veg</v>
+        <v>att_diet:hfd</v>
       </c>
       <c r="D926" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E926" s="8" t="s">
-        <v>2827</v>
+        <v>2832</v>
       </c>
       <c r="F926" s="8" t="s">
-        <v>2828</v>
+        <v>2833</v>
       </c>
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A927" s="8" t="s">
-        <v>2831</v>
-      </c>
-      <c r="B927" s="22" t="s">
-        <v>2819</v>
+        <v>2564</v>
+      </c>
+      <c r="B927" s="8" t="s">
+        <v>69</v>
       </c>
       <c r="C927" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_diet:hg</v>
+        <v>att_compound:lps</v>
       </c>
       <c r="D927" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E927" s="8" t="s">
-        <v>2829</v>
+        <v>2565</v>
       </c>
       <c r="F927" s="8" t="s">
-        <v>2830</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A928" s="8" t="s">
-        <v>2834</v>
+        <v>2575</v>
       </c>
       <c r="B928" s="8" t="s">
-        <v>2819</v>
+        <v>69</v>
       </c>
       <c r="C928" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_diet:hfd</v>
+        <v>att_compound:r848</v>
       </c>
       <c r="D928" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E928" s="8" t="s">
-        <v>2832</v>
+        <v>2576</v>
       </c>
       <c r="F928" s="8" t="s">
-        <v>2833</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A929" s="8" t="s">
-        <v>2564</v>
+        <v>2991</v>
       </c>
       <c r="B929" s="8" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C929" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_compound:lps</v>
+        <v>att_cell:mdc</v>
       </c>
       <c r="D929" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E929" s="8" t="s">
-        <v>2565</v>
+        <v>3012</v>
       </c>
       <c r="F929" s="8" t="s">
-        <v>2566</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A930" s="8" t="s">
-        <v>2575</v>
+        <v>2992</v>
       </c>
       <c r="B930" s="8" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="C930" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_compound:r848</v>
+        <v>att_cell:mtregs</v>
       </c>
       <c r="D930" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E930" s="8" t="s">
-        <v>2576</v>
+        <v>3010</v>
       </c>
       <c r="F930" s="8" t="s">
-        <v>2990</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A931" s="8" t="s">
-        <v>2991</v>
+        <v>2993</v>
       </c>
       <c r="B931" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C931" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:mdc</v>
+        <v>att_cell:pdc</v>
       </c>
       <c r="D931" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E931" s="8" t="s">
-        <v>3012</v>
+        <v>3013</v>
       </c>
       <c r="F931" s="8" t="s">
-        <v>3011</v>
+        <v>3008</v>
       </c>
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A932" s="8" t="s">
-        <v>2992</v>
+        <v>2994</v>
       </c>
       <c r="B932" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C932" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:mtregs</v>
+        <v>att_cell:attregs</v>
       </c>
       <c r="D932" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E932" s="8" t="s">
-        <v>3010</v>
+        <v>3007</v>
       </c>
       <c r="F932" s="8" t="s">
-        <v>3009</v>
+        <v>3014</v>
       </c>
     </row>
     <row r="933" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A933" s="8" t="s">
-        <v>2993</v>
+        <v>2995</v>
       </c>
       <c r="B933" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C933" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:pdc</v>
+        <v>att_cell:infdc</v>
       </c>
       <c r="D933" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E933" s="8" t="s">
-        <v>3013</v>
+        <v>3006</v>
       </c>
       <c r="F933" s="8" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="934" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A934" s="8" t="s">
-        <v>2994</v>
+        <v>2996</v>
       </c>
       <c r="B934" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C934" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:attregs</v>
+        <v>att_cell:itgres</v>
       </c>
       <c r="D934" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E934" s="8" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="F934" s="8" t="s">
-        <v>3014</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="935" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A935" s="8" t="s">
-        <v>2995</v>
+        <v>2997</v>
       </c>
       <c r="B935" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C935" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:infdc</v>
+        <v>att_cell:dendritic</v>
       </c>
       <c r="D935" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E935" s="8" t="s">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="F935" s="8" t="s">
-        <v>3005</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A936" s="8" t="s">
-        <v>2996</v>
+        <v>2998</v>
       </c>
       <c r="B936" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C936" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:itgres</v>
+        <v>att_cell:ememcell</v>
       </c>
       <c r="D936" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E936" s="8" t="s">
-        <v>3004</v>
+        <v>3000</v>
       </c>
       <c r="F936" s="8" t="s">
-        <v>3003</v>
+        <v>2999</v>
       </c>
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A937" s="8" t="s">
-        <v>2997</v>
+        <v>3015</v>
       </c>
       <c r="B937" s="8" t="s">
-        <v>40</v>
+        <v>2928</v>
       </c>
       <c r="C937" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:dendritic</v>
+        <v>att_subcellular_compartment:supernatant</v>
       </c>
       <c r="D937" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E937" s="8" t="s">
-        <v>3002</v>
+        <v>3016</v>
       </c>
       <c r="F937" s="8" t="s">
-        <v>3001</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A938" s="8" t="s">
-        <v>2998</v>
+        <v>3020</v>
       </c>
       <c r="B938" s="8" t="s">
-        <v>40</v>
+        <v>3018</v>
       </c>
       <c r="C938" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_cell:ememcell</v>
+        <v>att_heart:leftatrium</v>
       </c>
       <c r="D938" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E938" s="8" t="s">
-        <v>3000</v>
+        <v>3021</v>
       </c>
       <c r="F938" s="8" t="s">
-        <v>2999</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A939" s="8" t="s">
-        <v>3015</v>
+        <v>3023</v>
       </c>
       <c r="B939" s="8" t="s">
-        <v>2928</v>
+        <v>3018</v>
       </c>
       <c r="C939" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_subcellular_compartment:supernatant</v>
+        <v>att_heart:rightatrium</v>
       </c>
       <c r="D939" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E939" s="8" t="s">
-        <v>3016</v>
+        <v>3024</v>
       </c>
       <c r="F939" s="8" t="s">
-        <v>3017</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A940" s="8" t="s">
-        <v>3020</v>
+        <v>3026</v>
       </c>
       <c r="B940" s="8" t="s">
         <v>3018</v>
       </c>
       <c r="C940" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_heart:leftatrium</v>
+        <v>att_heart:leftchamber</v>
       </c>
       <c r="D940" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E940" s="8" t="s">
-        <v>3021</v>
+        <v>3027</v>
       </c>
       <c r="F940" s="8" t="s">
-        <v>3022</v>
+        <v>3028</v>
       </c>
     </row>
     <row r="941" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A941" s="8" t="s">
-        <v>3023</v>
+        <v>3029</v>
       </c>
       <c r="B941" s="8" t="s">
         <v>3018</v>
       </c>
       <c r="C941" s="8" t="str">
         <f t="shared" si="24"/>
-        <v>att_heart:rightatrium</v>
+        <v>att_heart:rightchamber</v>
       </c>
       <c r="D941" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E941" s="8" t="s">
-        <v>3024</v>
+        <v>3030</v>
       </c>
       <c r="F941" s="8" t="s">
-        <v>3025</v>
-      </c>
-    </row>
-    <row r="942" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A942" s="8" t="s">
-        <v>3026</v>
-      </c>
-      <c r="B942" s="8" t="s">
-        <v>3018</v>
-      </c>
-      <c r="C942" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>att_heart:leftchamber</v>
-      </c>
-      <c r="D942" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E942" s="8" t="s">
-        <v>3027</v>
-      </c>
-      <c r="F942" s="8" t="s">
         <v>3028</v>
       </c>
     </row>
-    <row r="943" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A943" s="8" t="s">
-        <v>3029</v>
-      </c>
-      <c r="B943" s="8" t="s">
-        <v>3018</v>
-      </c>
-      <c r="C943" s="8" t="str">
-        <f t="shared" si="24"/>
-        <v>att_heart:rightchamber</v>
-      </c>
-      <c r="D943" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E943" s="8" t="s">
-        <v>3030</v>
-      </c>
-      <c r="F943" s="8" t="s">
-        <v>3028</v>
-      </c>
+    <row r="950" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B950" s="24"/>
+    </row>
+    <row r="951" spans="2:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="B951" s="25"/>
     </row>
     <row r="952" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B952" s="24"/>
+      <c r="B952" s="25"/>
     </row>
     <row r="953" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B953" s="25"/>
@@ -38793,16 +38760,16 @@
       <c r="B958" s="25"/>
     </row>
     <row r="959" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B959" s="25"/>
+      <c r="B959" s="24"/>
     </row>
     <row r="960" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B960" s="25"/>
+      <c r="B960" s="24"/>
     </row>
     <row r="961" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B961" s="24"/>
+      <c r="B961" s="25"/>
     </row>
     <row r="962" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B962" s="24"/>
+      <c r="B962" s="25"/>
     </row>
     <row r="963" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B963" s="25"/>
@@ -38823,16 +38790,16 @@
       <c r="B968" s="25"/>
     </row>
     <row r="969" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B969" s="25"/>
+      <c r="B969" s="24"/>
     </row>
     <row r="970" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B970" s="25"/>
+      <c r="B970" s="24"/>
     </row>
     <row r="971" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B971" s="24"/>
+      <c r="B971" s="25"/>
     </row>
     <row r="972" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B972" s="24"/>
+      <c r="B972" s="25"/>
     </row>
     <row r="973" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B973" s="25"/>
@@ -38853,16 +38820,16 @@
       <c r="B978" s="25"/>
     </row>
     <row r="979" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B979" s="25"/>
+      <c r="B979" s="24"/>
     </row>
     <row r="980" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B980" s="25"/>
+      <c r="B980" s="24"/>
     </row>
     <row r="981" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B981" s="24"/>
+      <c r="B981" s="25"/>
     </row>
     <row r="982" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B982" s="24"/>
+      <c r="B982" s="25"/>
     </row>
     <row r="983" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B983" s="25"/>
@@ -38883,16 +38850,16 @@
       <c r="B988" s="25"/>
     </row>
     <row r="989" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B989" s="25"/>
+      <c r="B989" s="24"/>
     </row>
     <row r="990" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B990" s="25"/>
+      <c r="B990" s="24"/>
     </row>
     <row r="991" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B991" s="24"/>
+      <c r="B991" s="25"/>
     </row>
     <row r="992" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B992" s="24"/>
+      <c r="B992" s="25"/>
     </row>
     <row r="993" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B993" s="25"/>
@@ -38913,16 +38880,16 @@
       <c r="B998" s="25"/>
     </row>
     <row r="999" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B999" s="25"/>
+      <c r="B999" s="24"/>
     </row>
     <row r="1000" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1000" s="25"/>
+      <c r="B1000" s="24"/>
     </row>
     <row r="1001" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1001" s="24"/>
+      <c r="B1001" s="25"/>
     </row>
     <row r="1002" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1002" s="24"/>
+      <c r="B1002" s="25"/>
     </row>
     <row r="1003" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1003" s="25"/>
@@ -38943,16 +38910,16 @@
       <c r="B1008" s="25"/>
     </row>
     <row r="1009" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1009" s="25"/>
+      <c r="B1009" s="24"/>
     </row>
     <row r="1010" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1010" s="25"/>
+      <c r="B1010" s="24"/>
     </row>
     <row r="1011" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1011" s="24"/>
+      <c r="B1011" s="25"/>
     </row>
     <row r="1012" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1012" s="24"/>
+      <c r="B1012" s="25"/>
     </row>
     <row r="1013" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1013" s="25"/>
@@ -38973,16 +38940,16 @@
       <c r="B1018" s="25"/>
     </row>
     <row r="1019" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1019" s="25"/>
+      <c r="B1019" s="24"/>
     </row>
     <row r="1020" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1020" s="25"/>
+      <c r="B1020" s="24"/>
     </row>
     <row r="1021" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1021" s="24"/>
+      <c r="B1021" s="25"/>
     </row>
     <row r="1022" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1022" s="24"/>
+      <c r="B1022" s="25"/>
     </row>
     <row r="1023" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1023" s="25"/>
@@ -39003,16 +38970,16 @@
       <c r="B1028" s="25"/>
     </row>
     <row r="1029" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1029" s="25"/>
+      <c r="B1029" s="24"/>
     </row>
     <row r="1030" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1030" s="25"/>
+      <c r="B1030" s="24"/>
     </row>
     <row r="1031" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1031" s="24"/>
+      <c r="B1031" s="25"/>
     </row>
     <row r="1032" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1032" s="24"/>
+      <c r="B1032" s="25"/>
     </row>
     <row r="1033" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1033" s="25"/>
@@ -39033,16 +39000,16 @@
       <c r="B1038" s="25"/>
     </row>
     <row r="1039" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1039" s="25"/>
+      <c r="B1039" s="24"/>
     </row>
     <row r="1040" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1040" s="25"/>
+      <c r="B1040" s="24"/>
     </row>
     <row r="1041" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1041" s="24"/>
+      <c r="B1041" s="25"/>
     </row>
     <row r="1042" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1042" s="24"/>
+      <c r="B1042" s="25"/>
     </row>
     <row r="1043" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1043" s="25"/>
@@ -39063,16 +39030,16 @@
       <c r="B1048" s="25"/>
     </row>
     <row r="1049" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1049" s="25"/>
+      <c r="B1049" s="24"/>
     </row>
     <row r="1050" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1050" s="25"/>
+      <c r="B1050" s="24"/>
     </row>
     <row r="1051" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1051" s="24"/>
+      <c r="B1051" s="25"/>
     </row>
     <row r="1052" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1052" s="24"/>
+      <c r="B1052" s="25"/>
     </row>
     <row r="1053" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1053" s="25"/>
@@ -39093,13 +39060,7 @@
       <c r="B1058" s="25"/>
     </row>
     <row r="1059" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1059" s="25"/>
-    </row>
-    <row r="1060" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1060" s="25"/>
-    </row>
-    <row r="1061" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1061" s="24"/>
+      <c r="B1059" s="24"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="F331:F339 E240 F9:F329">

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4164D8BE-81E0-3B4A-87EB-18F6662E310E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86233F73-4C5D-924C-BEB7-F363BAC3DC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21640" yWindow="3460" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10484" uniqueCount="3040">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10496" uniqueCount="3042">
   <si>
     <t>tag</t>
   </si>
@@ -9162,6 +9162,12 @@
   </si>
   <si>
     <t>opentronsot2</t>
+  </si>
+  <si>
+    <t>att_genotype</t>
+  </si>
+  <si>
+    <t>Genotype</t>
   </si>
 </sst>
 </file>
@@ -9767,7 +9773,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH122"/>
+  <dimension ref="A1:AMH123"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -12442,29 +12448,29 @@
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A54" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>138</v>
+      <c r="A54" t="s">
+        <v>3040</v>
+      </c>
+      <c r="B54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54" t="s">
+        <v>3041</v>
       </c>
       <c r="D54">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I54" s="7" t="b">
         <v>0</v>
@@ -12473,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>19</v>
@@ -12485,36 +12491,36 @@
         <v>19</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A55" t="s">
-        <v>139</v>
+      <c r="A55" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>3031</v>
+        <v>138</v>
       </c>
       <c r="D55">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G55" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I55" s="7" t="b">
         <v>0</v>
@@ -12538,24 +12544,24 @@
         <v>21</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A56" s="6" t="s">
+      <c r="A56" t="s">
+        <v>139</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B56" t="s">
-        <v>17</v>
-      </c>
-      <c r="C56" t="s">
-        <v>2848</v>
+      <c r="C56" s="6" t="s">
+        <v>3031</v>
       </c>
       <c r="D56">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>19</v>
@@ -12592,14 +12598,14 @@
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A57" t="s">
-        <v>143</v>
+      <c r="A57" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="B57" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="C57" t="s">
-        <v>145</v>
+        <v>2848</v>
       </c>
       <c r="D57">
         <v>500</v>
@@ -12608,13 +12614,13 @@
         <v>19</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G57" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="H57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I57" s="7" t="b">
         <v>0</v>
@@ -12623,7 +12629,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L57" s="1" t="s">
         <v>19</v>
@@ -12632,24 +12638,24 @@
         <v>19</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O57" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B58" t="s">
         <v>144</v>
       </c>
       <c r="C58" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D58">
         <v>500</v>
@@ -12658,7 +12664,7 @@
         <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G58" t="s">
         <v>55</v>
@@ -12670,7 +12676,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K58" s="1" t="s">
         <v>19</v>
@@ -12693,13 +12699,13 @@
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B59" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>2805</v>
+        <v>147</v>
       </c>
       <c r="D59">
         <v>500</v>
@@ -12723,7 +12729,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L59" s="1" t="s">
         <v>19</v>
@@ -12743,13 +12749,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>2806</v>
+        <v>2805</v>
       </c>
       <c r="D60">
         <v>500</v>
@@ -12792,17 +12798,17 @@
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A61" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B61" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>151</v>
+      <c r="A61" t="s">
+        <v>144</v>
+      </c>
+      <c r="B61" t="s">
+        <v>148</v>
+      </c>
+      <c r="C61" t="s">
+        <v>2806</v>
       </c>
       <c r="D61">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>19</v>
@@ -12811,16 +12817,16 @@
         <v>19</v>
       </c>
       <c r="G61" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I61" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J61" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" s="1" t="s">
         <v>21</v>
@@ -12832,27 +12838,27 @@
         <v>19</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O61" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A62" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" t="s">
-        <v>153</v>
+        <v>27</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="D62">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>19</v>
@@ -12861,7 +12867,7 @@
         <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -12893,13 +12899,13 @@
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A63" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B63" t="s">
-        <v>17</v>
-      </c>
       <c r="C63" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D63">
         <v>500</v>
@@ -12943,13 +12949,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A64" s="6" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D64">
         <v>500</v>
@@ -12961,10 +12967,10 @@
         <v>19</v>
       </c>
       <c r="G64" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="H64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="7" t="b">
         <v>0</v>
@@ -12992,14 +12998,14 @@
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A65" t="s">
-        <v>157</v>
+      <c r="A65" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D65">
         <v>500</v>
@@ -13011,7 +13017,7 @@
         <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="H65">
         <v>0</v>
@@ -13043,13 +13049,13 @@
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D66">
         <v>500</v>
@@ -13061,7 +13067,7 @@
         <v>19</v>
       </c>
       <c r="G66" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -13092,14 +13098,14 @@
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A67" s="6" t="s">
-        <v>2970</v>
+      <c r="A67" t="s">
+        <v>160</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>2974</v>
+        <v>161</v>
       </c>
       <c r="D67">
         <v>500</v>
@@ -13108,7 +13114,7 @@
         <v>19</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G67" t="s">
         <v>42</v>
@@ -13123,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L67" s="1" t="s">
         <v>19</v>
@@ -13138,18 +13144,18 @@
         <v>21</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A68" t="s">
-        <v>23</v>
+      <c r="A68" s="6" t="s">
+        <v>2970</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>162</v>
+        <v>2974</v>
       </c>
       <c r="D68">
         <v>500</v>
@@ -13158,22 +13164,22 @@
         <v>19</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G68" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H68">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J68" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L68" s="1" t="s">
         <v>19</v>
@@ -13182,7 +13188,7 @@
         <v>19</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O68" s="1" t="s">
         <v>21</v>
@@ -13192,14 +13198,14 @@
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A69" s="6" t="s">
-        <v>116</v>
+      <c r="A69" t="s">
+        <v>23</v>
       </c>
       <c r="B69" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D69">
         <v>500</v>
@@ -13220,7 +13226,7 @@
         <v>0</v>
       </c>
       <c r="J69" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K69" s="1" t="s">
         <v>21</v>
@@ -13232,7 +13238,7 @@
         <v>19</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O69" s="1" t="s">
         <v>21</v>
@@ -13242,14 +13248,14 @@
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A70" t="s">
-        <v>38</v>
+      <c r="A70" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="C70" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D70">
         <v>500</v>
@@ -13270,7 +13276,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
         <v>21</v>
@@ -13282,7 +13288,7 @@
         <v>19</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>21</v>
@@ -13293,13 +13299,13 @@
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" t="s">
         <v>164</v>
       </c>
-      <c r="B71" t="s">
-        <v>23</v>
-      </c>
       <c r="C71" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D71">
         <v>500</v>
@@ -13342,14 +13348,14 @@
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A72" s="6" t="s">
-        <v>167</v>
+      <c r="A72" t="s">
+        <v>164</v>
       </c>
       <c r="B72" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D72">
         <v>500</v>
@@ -13358,7 +13364,7 @@
         <v>19</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G72" t="s">
         <v>25</v>
@@ -13370,7 +13376,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>21</v>
@@ -13382,7 +13388,7 @@
         <v>19</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>21</v>
@@ -13393,13 +13399,13 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A73" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B73" t="s">
         <v>168</v>
       </c>
       <c r="C73" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D73">
         <v>500</v>
@@ -13442,14 +13448,14 @@
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A74" t="s">
+      <c r="A74" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B74" t="s">
         <v>168</v>
       </c>
-      <c r="B74" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>172</v>
+      <c r="C74" t="s">
+        <v>171</v>
       </c>
       <c r="D74">
         <v>500</v>
@@ -13492,14 +13498,14 @@
       </c>
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A75" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B75" t="s">
-        <v>174</v>
-      </c>
-      <c r="C75" t="s">
-        <v>175</v>
+      <c r="A75" t="s">
+        <v>168</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="D75">
         <v>500</v>
@@ -13543,13 +13549,13 @@
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A76" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B76" t="s">
         <v>174</v>
       </c>
       <c r="C76" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D76">
         <v>500</v>
@@ -13592,14 +13598,14 @@
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A77" t="s">
+      <c r="A77" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B77" t="s">
         <v>174</v>
       </c>
-      <c r="B77" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>178</v>
+      <c r="C77" t="s">
+        <v>177</v>
       </c>
       <c r="D77">
         <v>500</v>
@@ -13643,13 +13649,13 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
-        <v>179</v>
-      </c>
-      <c r="B78" t="s">
-        <v>180</v>
-      </c>
-      <c r="C78" t="s">
-        <v>2804</v>
+        <v>174</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>178</v>
       </c>
       <c r="D78">
         <v>500</v>
@@ -13658,13 +13664,13 @@
         <v>19</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G78" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I78" s="7" t="b">
         <v>0</v>
@@ -13688,33 +13694,33 @@
         <v>21</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A79" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>184</v>
+      <c r="A79" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" t="s">
+        <v>180</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2804</v>
       </c>
       <c r="D79">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G79" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79" s="7" t="b">
         <v>0</v>
@@ -13743,13 +13749,13 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D80">
         <v>400</v>
@@ -13773,7 +13779,7 @@
         <v>0</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L80" s="1" t="s">
         <v>19</v>
@@ -13785,21 +13791,21 @@
         <v>19</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P80" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B81" t="s">
-        <v>17</v>
-      </c>
-      <c r="C81" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="D81">
         <v>400</v>
@@ -13808,7 +13814,7 @@
         <v>19</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G81" t="s">
         <v>185</v>
@@ -13823,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L81" s="1" t="s">
         <v>19</v>
@@ -13835,21 +13841,21 @@
         <v>19</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P81" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A82" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B82" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C82" s="6" t="s">
-        <v>191</v>
+      <c r="B82" t="s">
+        <v>17</v>
+      </c>
+      <c r="C82" t="s">
+        <v>189</v>
       </c>
       <c r="D82">
         <v>400</v>
@@ -13858,7 +13864,7 @@
         <v>19</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G82" t="s">
         <v>185</v>
@@ -13893,13 +13899,13 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>183</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>2861</v>
+        <v>191</v>
       </c>
       <c r="D83">
         <v>400</v>
@@ -13942,35 +13948,35 @@
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A84" t="s">
-        <v>193</v>
-      </c>
-      <c r="B84" t="s">
-        <v>17</v>
-      </c>
-      <c r="C84" t="s">
-        <v>194</v>
+      <c r="A84" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>2861</v>
       </c>
       <c r="D84">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G84" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="H84">
+        <v>1</v>
+      </c>
+      <c r="I84" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="I84" s="7" t="b">
-        <v>1</v>
-      </c>
       <c r="J84" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K84" s="1" t="s">
         <v>21</v>
@@ -13993,13 +13999,13 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B85" t="s">
         <v>17</v>
       </c>
       <c r="C85" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D85">
         <v>500</v>
@@ -14011,16 +14017,16 @@
         <v>19</v>
       </c>
       <c r="G85" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="H85">
         <v>0</v>
       </c>
       <c r="I85" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J85" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K85" s="1" t="s">
         <v>21</v>
@@ -14042,14 +14048,14 @@
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A86" s="6" t="s">
-        <v>196</v>
+      <c r="A86" t="s">
+        <v>180</v>
       </c>
       <c r="B86" t="s">
         <v>17</v>
       </c>
       <c r="C86" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D86">
         <v>500</v>
@@ -14067,7 +14073,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J86" s="7" t="b">
         <v>0</v>
@@ -14092,14 +14098,14 @@
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A87" t="s">
-        <v>198</v>
+      <c r="A87" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="B87" t="s">
         <v>17</v>
       </c>
       <c r="C87" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D87">
         <v>500</v>
@@ -14117,7 +14123,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J87" s="7" t="b">
         <v>0</v>
@@ -14143,34 +14149,34 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B88" t="s">
         <v>17</v>
       </c>
       <c r="C88" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D88">
         <v>500</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G88" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="H88">
         <v>0</v>
       </c>
       <c r="I88" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J88" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88" s="1" t="s">
         <v>21</v>
@@ -14192,32 +14198,32 @@
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A89" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>204</v>
+      <c r="A89" t="s">
+        <v>200</v>
+      </c>
+      <c r="B89" t="s">
+        <v>17</v>
+      </c>
+      <c r="C89" t="s">
+        <v>201</v>
       </c>
       <c r="D89">
         <v>500</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G89" t="s">
-        <v>29</v>
+        <v>202</v>
       </c>
       <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89" s="7" t="b">
         <v>1</v>
-      </c>
-      <c r="I89" s="7" t="b">
-        <v>0</v>
       </c>
       <c r="J89" s="7" t="b">
         <v>1</v>
@@ -14242,35 +14248,35 @@
       </c>
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A90" t="s">
-        <v>134</v>
-      </c>
-      <c r="B90" t="s">
-        <v>17</v>
+      <c r="A90" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D90">
         <v>500</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="H90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I90" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J90" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>21</v>
@@ -14279,13 +14285,13 @@
         <v>19</v>
       </c>
       <c r="M90" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N90" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P90" s="1" t="s">
         <v>19</v>
@@ -14293,25 +14299,25 @@
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
-        <v>2987</v>
-      </c>
-      <c r="B91" s="6" t="s">
-        <v>27</v>
+        <v>134</v>
+      </c>
+      <c r="B91" t="s">
+        <v>17</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>2988</v>
+        <v>205</v>
       </c>
       <c r="D91">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G91" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="H91">
         <v>0</v>
@@ -14320,48 +14326,48 @@
         <v>0</v>
       </c>
       <c r="J91" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M91" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
-        <v>206</v>
-      </c>
-      <c r="B92" t="s">
-        <v>129</v>
-      </c>
-      <c r="C92" t="s">
-        <v>207</v>
+        <v>2987</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>2988</v>
       </c>
       <c r="D92">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G92" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="H92">
         <v>0</v>
@@ -14370,36 +14376,36 @@
         <v>0</v>
       </c>
       <c r="J92" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B93" t="s">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D93">
         <v>500</v>
@@ -14443,13 +14449,13 @@
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
-        <v>2976</v>
+        <v>208</v>
       </c>
       <c r="B94" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="C94" t="s">
-        <v>2977</v>
+        <v>209</v>
       </c>
       <c r="D94">
         <v>500</v>
@@ -14461,10 +14467,10 @@
         <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="H94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I94" s="7" t="b">
         <v>0</v>
@@ -14479,27 +14485,27 @@
         <v>19</v>
       </c>
       <c r="M94" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P94" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A95" s="6" t="s">
-        <v>210</v>
+      <c r="A95" t="s">
+        <v>2976</v>
       </c>
       <c r="B95" t="s">
-        <v>211</v>
+        <v>17</v>
       </c>
       <c r="C95" t="s">
-        <v>212</v>
+        <v>2977</v>
       </c>
       <c r="D95">
         <v>500</v>
@@ -14511,16 +14517,16 @@
         <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H95">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I95" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J95" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>21</v>
@@ -14538,18 +14544,18 @@
         <v>21</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A96" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B96" t="s">
         <v>211</v>
       </c>
-      <c r="B96" t="s">
-        <v>17</v>
-      </c>
       <c r="C96" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D96">
         <v>500</v>
@@ -14593,16 +14599,16 @@
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A97" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B97" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
+      </c>
+      <c r="B97" t="s">
+        <v>17</v>
+      </c>
+      <c r="C97" t="s">
+        <v>213</v>
       </c>
       <c r="D97">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>19</v>
@@ -14611,16 +14617,16 @@
         <v>19</v>
       </c>
       <c r="G97" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I97" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J97" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" s="1" t="s">
         <v>21</v>
@@ -14642,29 +14648,29 @@
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A98" t="s">
-        <v>216</v>
-      </c>
-      <c r="B98" t="s">
-        <v>23</v>
-      </c>
-      <c r="C98" t="s">
-        <v>217</v>
+      <c r="A98" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="D98">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G98" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I98" s="7" t="b">
         <v>0</v>
@@ -14682,24 +14688,24 @@
         <v>19</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O98" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
-        <v>31</v>
+        <v>216</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C99" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D99">
         <v>500</v>
@@ -14708,19 +14714,19 @@
         <v>19</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G99" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I99" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J99" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K99" s="1" t="s">
         <v>21</v>
@@ -14732,24 +14738,24 @@
         <v>19</v>
       </c>
       <c r="N99" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O99" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A100" s="6" t="s">
-        <v>219</v>
+      <c r="A100" t="s">
+        <v>31</v>
       </c>
       <c r="B100" t="s">
         <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D100">
         <v>500</v>
@@ -14761,16 +14767,16 @@
         <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>185</v>
+        <v>33</v>
       </c>
       <c r="H100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I100" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J100" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K100" s="1" t="s">
         <v>21</v>
@@ -14792,14 +14798,14 @@
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A101" t="s">
-        <v>221</v>
+      <c r="A101" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="B101" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C101" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D101">
         <v>500</v>
@@ -14808,13 +14814,13 @@
         <v>19</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G101" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="H101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I101" s="7" t="b">
         <v>0</v>
@@ -14832,24 +14838,24 @@
         <v>19</v>
       </c>
       <c r="N101" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O101" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B102" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C102" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D102">
         <v>500</v>
@@ -14861,10 +14867,10 @@
         <v>21</v>
       </c>
       <c r="G102" t="s">
-        <v>225</v>
+        <v>25</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I102" s="7" t="b">
         <v>0</v>
@@ -14882,24 +14888,24 @@
         <v>19</v>
       </c>
       <c r="N102" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O102" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P102" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="B103" t="s">
         <v>17</v>
       </c>
       <c r="C103" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D103">
         <v>500</v>
@@ -14943,13 +14949,13 @@
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B104" t="s">
         <v>17</v>
       </c>
       <c r="C104" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D104">
         <v>500</v>
@@ -14993,13 +14999,13 @@
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D105">
         <v>500</v>
@@ -15043,13 +15049,13 @@
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B106" t="s">
         <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D106">
         <v>500</v>
@@ -15093,13 +15099,13 @@
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B107" t="s">
         <v>17</v>
       </c>
       <c r="C107" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="D107">
         <v>500</v>
@@ -15143,13 +15149,13 @@
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D108">
         <v>500</v>
@@ -15191,15 +15197,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="109" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A109" s="6" t="s">
-        <v>238</v>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A109" t="s">
+        <v>236</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D109">
         <v>500</v>
@@ -15208,10 +15214,10 @@
         <v>19</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G109" t="s">
-        <v>42</v>
+        <v>225</v>
       </c>
       <c r="H109">
         <v>0</v>
@@ -15241,15 +15247,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>2807</v>
+        <v>239</v>
       </c>
       <c r="D110">
         <v>500</v>
@@ -15293,13 +15299,13 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A111" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>243</v>
+        <v>240</v>
+      </c>
+      <c r="B111" t="s">
+        <v>17</v>
+      </c>
+      <c r="C111" t="s">
+        <v>2807</v>
       </c>
       <c r="D111">
         <v>500</v>
@@ -15308,13 +15314,13 @@
         <v>19</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G111" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I111" s="7" t="b">
         <v>0</v>
@@ -15338,33 +15344,33 @@
         <v>21</v>
       </c>
       <c r="P111" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A112" t="s">
-        <v>244</v>
-      </c>
-      <c r="B112" t="s">
-        <v>17</v>
-      </c>
-      <c r="C112" t="s">
-        <v>2859</v>
+      <c r="A112" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>243</v>
       </c>
       <c r="D112">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G112" t="s">
-        <v>245</v>
+        <v>25</v>
       </c>
       <c r="H112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I112" s="7" t="b">
         <v>0</v>
@@ -15373,10 +15379,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="M112" s="1" t="s">
         <v>19</v>
@@ -15385,24 +15391,24 @@
         <v>19</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P112" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>247</v>
+        <v>2859</v>
       </c>
       <c r="D113">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>19</v>
@@ -15443,16 +15449,16 @@
     </row>
     <row r="114" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D114">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>19</v>
@@ -15473,7 +15479,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>21</v>
@@ -15493,16 +15499,16 @@
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D115">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>19</v>
@@ -15523,7 +15529,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L115" s="1" t="s">
         <v>21</v>
@@ -15543,16 +15549,16 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B116" t="s">
         <v>17</v>
       </c>
       <c r="C116" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D116">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>19</v>
@@ -15573,7 +15579,7 @@
         <v>0</v>
       </c>
       <c r="K116" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L116" s="1" t="s">
         <v>21</v>
@@ -15593,16 +15599,16 @@
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B117" t="s">
         <v>17</v>
       </c>
       <c r="C117" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D117">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>19</v>
@@ -15623,7 +15629,7 @@
         <v>0</v>
       </c>
       <c r="K117" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L117" s="1" t="s">
         <v>21</v>
@@ -15643,16 +15649,16 @@
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>2819</v>
+        <v>254</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>2820</v>
+        <v>255</v>
       </c>
       <c r="D118">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>19</v>
@@ -15661,22 +15667,22 @@
         <v>19</v>
       </c>
       <c r="G118" t="s">
-        <v>20</v>
+        <v>245</v>
       </c>
       <c r="H118">
         <v>0</v>
       </c>
-      <c r="I118" s="2" t="b">
+      <c r="I118" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J118" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K118" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>19</v>
@@ -15685,7 +15691,7 @@
         <v>19</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P118" s="1" t="s">
         <v>19</v>
@@ -15693,25 +15699,25 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
-        <v>2849</v>
+        <v>2819</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>2922</v>
+        <v>2820</v>
       </c>
       <c r="D119">
         <v>500</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G119" t="s">
-        <v>2850</v>
+        <v>20</v>
       </c>
       <c r="H119">
         <v>0</v>
@@ -15743,13 +15749,13 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
-        <v>2920</v>
+        <v>2849</v>
       </c>
       <c r="B120" t="s">
         <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>2923</v>
+        <v>2922</v>
       </c>
       <c r="D120">
         <v>500</v>
@@ -15761,7 +15767,7 @@
         <v>19</v>
       </c>
       <c r="G120" t="s">
-        <v>2921</v>
+        <v>2850</v>
       </c>
       <c r="H120">
         <v>0</v>
@@ -15769,11 +15775,11 @@
       <c r="I120" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J120" s="2" t="b">
+      <c r="J120" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>19</v>
@@ -15793,25 +15799,25 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
-        <v>2928</v>
+        <v>2920</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
       </c>
       <c r="C121" t="s">
-        <v>2929</v>
+        <v>2923</v>
       </c>
       <c r="D121">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G121" t="s">
-        <v>47</v>
+        <v>2921</v>
       </c>
       <c r="H121">
         <v>0</v>
@@ -15823,7 +15829,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>19</v>
@@ -15838,21 +15844,21 @@
         <v>21</v>
       </c>
       <c r="P121" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
-        <v>3018</v>
+        <v>2928</v>
       </c>
       <c r="B122" t="s">
         <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>3019</v>
+        <v>2929</v>
       </c>
       <c r="D122">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>19</v>
@@ -15861,7 +15867,7 @@
         <v>19</v>
       </c>
       <c r="G122" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H122">
         <v>0</v>
@@ -15891,20 +15897,70 @@
         <v>21</v>
       </c>
     </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A123" t="s">
+        <v>3018</v>
+      </c>
+      <c r="B123" t="s">
+        <v>17</v>
+      </c>
+      <c r="C123" t="s">
+        <v>3019</v>
+      </c>
+      <c r="D123">
+        <v>500</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" t="s">
+        <v>42</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J123" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O123" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P123" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J118:P119">
+  <conditionalFormatting sqref="J119:P120">
     <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",J118)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",J119)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:P52 E1:F117 I2:J52 I53:P117">
+  <conditionalFormatting sqref="K1:P52 E1:F118 I2:J52 I53:P118">
     <cfRule type="containsText" dxfId="6" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M120:P120">
+  <conditionalFormatting sqref="M121:P121">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",M120)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",M121)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96AB22C0-FF8D-1244-98B3-7F93760C0EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{449D9F10-BBCB-1440-8F28-BB6755B1B3B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18820" yWindow="2300" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18820" yWindow="2300" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10749" uniqueCount="3175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10749" uniqueCount="3174">
   <si>
     <t>tag</t>
   </si>
@@ -9379,9 +9379,6 @@
   </si>
   <si>
     <t>Muscle Fiber Type</t>
-  </si>
-  <si>
-    <t>FALSe</t>
   </si>
   <si>
     <t>type1</t>
@@ -14149,13 +14146,13 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="6" t="s">
-        <v>3146</v>
+        <v>3145</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>3161</v>
+        <v>3160</v>
       </c>
       <c r="D80">
         <v>500</v>
@@ -14199,13 +14196,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="6" t="s">
-        <v>3147</v>
+        <v>3146</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>3162</v>
+        <v>3161</v>
       </c>
       <c r="D81">
         <v>500</v>
@@ -14311,7 +14308,7 @@
         <v>500</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>3112</v>
+        <v>19</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>19</v>
@@ -20893,7 +20890,7 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A206" s="8" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>53</v>
@@ -20903,18 +20900,18 @@
         <v>att_column_type:pepsep</v>
       </c>
       <c r="D206" s="9" t="s">
+        <v>3147</v>
+      </c>
+      <c r="E206" s="8" t="s">
         <v>3148</v>
       </c>
-      <c r="E206" s="8" t="s">
+      <c r="F206" s="8" t="s">
         <v>3149</v>
-      </c>
-      <c r="F206" s="8" t="s">
-        <v>3150</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A207" s="8" t="s">
-        <v>3151</v>
+        <v>3150</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>53</v>
@@ -20924,18 +20921,18 @@
         <v>att_column_type:pepsepultra</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="E207" s="8" t="s">
-        <v>3152</v>
+        <v>3151</v>
       </c>
       <c r="F207" s="8" t="s">
-        <v>3160</v>
+        <v>3159</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A208" s="8" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="B208" s="8" t="s">
         <v>53</v>
@@ -20945,18 +20942,18 @@
         <v>att_column_type:pepsepmax</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="F208" s="8" t="s">
-        <v>3159</v>
+        <v>3158</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A209" s="8" t="s">
-        <v>3155</v>
+        <v>3154</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>53</v>
@@ -20966,13 +20963,13 @@
         <v>att_column_type:pepsepmaxht</v>
       </c>
       <c r="D209" s="9" t="s">
+        <v>3155</v>
+      </c>
+      <c r="E209" s="8" t="s">
         <v>3156</v>
       </c>
-      <c r="E209" s="8" t="s">
+      <c r="F209" s="8" t="s">
         <v>3157</v>
-      </c>
-      <c r="F209" s="8" t="s">
-        <v>3158</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
@@ -30192,7 +30189,7 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A649" s="8" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
       <c r="B649" s="8" t="s">
         <v>38</v>
@@ -30202,18 +30199,18 @@
         <v>att_ms_ionsource:captivespray</v>
       </c>
       <c r="D649" s="9" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
       <c r="E649" s="8" t="s">
-        <v>3168</v>
+        <v>3167</v>
       </c>
       <c r="F649" s="8" t="s">
-        <v>3170</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A650" s="8" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
       <c r="B650" s="8" t="s">
         <v>38</v>
@@ -30223,18 +30220,18 @@
         <v>att_ms_ionsource:captivespraytwo</v>
       </c>
       <c r="D650" s="9" t="s">
+        <v>3165</v>
+      </c>
+      <c r="E650" s="8" t="s">
         <v>3166</v>
       </c>
-      <c r="E650" s="8" t="s">
-        <v>3167</v>
-      </c>
       <c r="F650" s="8" t="s">
-        <v>3169</v>
+        <v>3168</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A651" s="8" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="B651" s="8" t="s">
         <v>38</v>
@@ -30244,13 +30241,13 @@
         <v>att_ms_ionsource:captiivespraypro</v>
       </c>
       <c r="D651" s="9" t="s">
+        <v>3171</v>
+      </c>
+      <c r="E651" s="8" t="s">
         <v>3172</v>
       </c>
-      <c r="E651" s="8" t="s">
+      <c r="F651" s="8" t="s">
         <v>3173</v>
-      </c>
-      <c r="F651" s="8" t="s">
-        <v>3174</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.15">
@@ -39873,7 +39870,7 @@
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A965" s="8" t="s">
-        <v>3113</v>
+        <v>3112</v>
       </c>
       <c r="B965" s="8" t="s">
         <v>3110</v>
@@ -39886,15 +39883,15 @@
         <v>17</v>
       </c>
       <c r="E965" s="8" t="s">
-        <v>3131</v>
+        <v>3130</v>
       </c>
       <c r="F965" s="8" t="s">
-        <v>3136</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A966" s="8" t="s">
-        <v>3114</v>
+        <v>3113</v>
       </c>
       <c r="B966" s="8" t="s">
         <v>3110</v>
@@ -39907,15 +39904,15 @@
         <v>17</v>
       </c>
       <c r="E966" s="8" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
       <c r="F966" s="8" t="s">
-        <v>3137</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="967" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A967" s="8" t="s">
-        <v>3115</v>
+        <v>3114</v>
       </c>
       <c r="B967" s="8" t="s">
         <v>3110</v>
@@ -39928,15 +39925,15 @@
         <v>17</v>
       </c>
       <c r="E967" s="8" t="s">
-        <v>3133</v>
+        <v>3132</v>
       </c>
       <c r="F967" s="8" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A968" s="8" t="s">
-        <v>3116</v>
+        <v>3115</v>
       </c>
       <c r="B968" s="8" t="s">
         <v>3110</v>
@@ -39949,15 +39946,15 @@
         <v>17</v>
       </c>
       <c r="E968" s="8" t="s">
-        <v>3134</v>
+        <v>3133</v>
       </c>
       <c r="F968" s="8" t="s">
-        <v>3139</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="969" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A969" s="8" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
       <c r="B969" s="8" t="s">
         <v>3110</v>
@@ -39970,15 +39967,15 @@
         <v>17</v>
       </c>
       <c r="E969" s="8" t="s">
-        <v>3135</v>
+        <v>3134</v>
       </c>
       <c r="F969" s="8" t="s">
-        <v>3118</v>
+        <v>3117</v>
       </c>
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A970" s="8" t="s">
-        <v>3119</v>
+        <v>3118</v>
       </c>
       <c r="B970" s="8" t="s">
         <v>3110</v>
@@ -39991,15 +39988,15 @@
         <v>17</v>
       </c>
       <c r="E970" s="8" t="s">
-        <v>3120</v>
+        <v>3119</v>
       </c>
       <c r="F970" s="8" t="s">
-        <v>3141</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A971" s="8" t="s">
-        <v>3121</v>
+        <v>3120</v>
       </c>
       <c r="B971" s="8" t="s">
         <v>3110</v>
@@ -40012,15 +40009,15 @@
         <v>17</v>
       </c>
       <c r="E971" s="8" t="s">
-        <v>3122</v>
+        <v>3121</v>
       </c>
       <c r="F971" s="8" t="s">
-        <v>3140</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A972" s="8" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
       <c r="B972" s="8" t="s">
         <v>3110</v>
@@ -40033,15 +40030,15 @@
         <v>17</v>
       </c>
       <c r="E972" s="8" t="s">
-        <v>3124</v>
+        <v>3123</v>
       </c>
       <c r="F972" s="8" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A973" s="8" t="s">
-        <v>3125</v>
+        <v>3124</v>
       </c>
       <c r="B973" s="8" t="s">
         <v>3110</v>
@@ -40054,15 +40051,15 @@
         <v>17</v>
       </c>
       <c r="E973" s="8" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
       <c r="F973" s="8" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A974" s="8" t="s">
-        <v>3127</v>
+        <v>3126</v>
       </c>
       <c r="B974" s="8" t="s">
         <v>3110</v>
@@ -40075,15 +40072,15 @@
         <v>17</v>
       </c>
       <c r="E974" s="8" t="s">
-        <v>3128</v>
+        <v>3127</v>
       </c>
       <c r="F974" s="8" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A975" s="8" t="s">
-        <v>3129</v>
+        <v>3128</v>
       </c>
       <c r="B975" s="8" t="s">
         <v>3110</v>
@@ -40096,10 +40093,10 @@
         <v>17</v>
       </c>
       <c r="E975" s="8" t="s">
-        <v>3130</v>
+        <v>3129</v>
       </c>
       <c r="F975" s="8" t="s">
-        <v>3145</v>
+        <v>3144</v>
       </c>
     </row>
     <row r="976" spans="1:6" ht="16" x14ac:dyDescent="0.2">

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DCF4EC-2119-594F-9519-F1644363CDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8A2CB4-2C74-1D42-AAFA-39DCBE9B1C98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5460" yWindow="980" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8655,15 +8655,6 @@
     <t>Epoxomicin is a naturally occurring selective proteasome inhibitor.</t>
   </si>
   <si>
-    <t>ProtFa</t>
-  </si>
-  <si>
-    <t>CECAD Proteomics Facility</t>
-  </si>
-  <si>
-    <t>CECAD Proteomics facility</t>
-  </si>
-  <si>
     <t>frezza</t>
   </si>
   <si>
@@ -9562,6 +9553,15 @@
   </si>
   <si>
     <t>CaptiveSpray Pro Source by Bruker for timsTOF</t>
+  </si>
+  <si>
+    <t>Z Project 02 (CRC1218)</t>
+  </si>
+  <si>
+    <t>ZO2 Project (Proteomics)</t>
+  </si>
+  <si>
+    <t>protfa</t>
   </si>
 </sst>
 </file>
@@ -10743,13 +10743,13 @@
     </row>
     <row r="12" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A12" s="6" t="s">
-        <v>2970</v>
+        <v>2967</v>
       </c>
       <c r="B12" t="s">
         <v>17</v>
       </c>
       <c r="C12" t="s">
-        <v>2984</v>
+        <v>2981</v>
       </c>
       <c r="D12">
         <v>500</v>
@@ -12793,13 +12793,13 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>2960</v>
+        <v>2957</v>
       </c>
       <c r="D53">
         <v>550</v>
@@ -12843,13 +12843,13 @@
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>3030</v>
+        <v>3027</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>3031</v>
+        <v>3028</v>
       </c>
       <c r="D54">
         <v>600</v>
@@ -12949,7 +12949,7 @@
         <v>140</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>3021</v>
+        <v>3018</v>
       </c>
       <c r="D56">
         <v>650</v>
@@ -13543,13 +13543,13 @@
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A68" s="6" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>3080</v>
+        <v>3077</v>
       </c>
       <c r="D68">
         <v>600</v>
@@ -13593,13 +13593,13 @@
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A69" s="6" t="s">
-        <v>2965</v>
+        <v>2962</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>2969</v>
+        <v>2966</v>
       </c>
       <c r="D69">
         <v>500</v>
@@ -14143,13 +14143,13 @@
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A80" s="6" t="s">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>3159</v>
+        <v>3156</v>
       </c>
       <c r="D80">
         <v>500</v>
@@ -14193,13 +14193,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="6" t="s">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>3160</v>
+        <v>3157</v>
       </c>
       <c r="D81">
         <v>500</v>
@@ -14293,13 +14293,13 @@
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="B83" t="s">
         <v>179</v>
       </c>
       <c r="C83" t="s">
-        <v>3110</v>
+        <v>3107</v>
       </c>
       <c r="D83">
         <v>500</v>
@@ -14943,13 +14943,13 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
-        <v>2982</v>
+        <v>2979</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>27</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>2983</v>
+        <v>2980</v>
       </c>
       <c r="D96">
         <v>600</v>
@@ -15093,13 +15093,13 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
-        <v>2971</v>
+        <v>2968</v>
       </c>
       <c r="B99" t="s">
         <v>17</v>
       </c>
       <c r="C99" t="s">
-        <v>2972</v>
+        <v>2969</v>
       </c>
       <c r="D99">
         <v>500</v>
@@ -16349,7 +16349,7 @@
         <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>2917</v>
+        <v>2914</v>
       </c>
       <c r="D124">
         <v>500</v>
@@ -16393,13 +16393,13 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B125" t="s">
+        <v>17</v>
+      </c>
+      <c r="C125" t="s">
         <v>2915</v>
-      </c>
-      <c r="B125" t="s">
-        <v>17</v>
-      </c>
-      <c r="C125" t="s">
-        <v>2918</v>
       </c>
       <c r="D125">
         <v>500</v>
@@ -16411,7 +16411,7 @@
         <v>19</v>
       </c>
       <c r="G125" t="s">
-        <v>2916</v>
+        <v>2913</v>
       </c>
       <c r="H125">
         <v>0</v>
@@ -16443,13 +16443,13 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>2924</v>
+        <v>2921</v>
       </c>
       <c r="D126">
         <v>650</v>
@@ -16493,13 +16493,13 @@
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="B127" t="s">
         <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>3042</v>
+        <v>3039</v>
       </c>
       <c r="D127">
         <v>500</v>
@@ -17498,10 +17498,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>3107</v>
+        <v>3104</v>
       </c>
       <c r="F44" s="8" t="s">
-        <v>3108</v>
+        <v>3105</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.15">
@@ -20588,12 +20588,12 @@
         <v>5</v>
       </c>
       <c r="F191" s="8" t="s">
-        <v>3098</v>
+        <v>3095</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A192" s="8" t="s">
-        <v>3097</v>
+        <v>3094</v>
       </c>
       <c r="B192" s="8" t="s">
         <v>56</v>
@@ -20609,7 +20609,7 @@
         <v>40</v>
       </c>
       <c r="F192" s="8" t="s">
-        <v>3099</v>
+        <v>3096</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.15">
@@ -20630,12 +20630,12 @@
         <v>40</v>
       </c>
       <c r="F193" s="9" t="s">
-        <v>3101</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A194" s="8" t="s">
-        <v>3100</v>
+        <v>3097</v>
       </c>
       <c r="B194" s="8" t="s">
         <v>60</v>
@@ -20651,7 +20651,7 @@
         <v>50</v>
       </c>
       <c r="F194" s="9" t="s">
-        <v>3102</v>
+        <v>3099</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.15">
@@ -20672,7 +20672,7 @@
         <v>55</v>
       </c>
       <c r="F195" s="9" t="s">
-        <v>3103</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.15">
@@ -20887,7 +20887,7 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A206" s="8" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="B206" s="8" t="s">
         <v>53</v>
@@ -20897,18 +20897,18 @@
         <v>att_column_type:pepsep</v>
       </c>
       <c r="D206" s="9" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="E206" s="8" t="s">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="F206" s="8" t="s">
-        <v>3148</v>
+        <v>3145</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A207" s="8" t="s">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="B207" s="8" t="s">
         <v>53</v>
@@ -20918,18 +20918,18 @@
         <v>att_column_type:pepsepultra</v>
       </c>
       <c r="D207" s="9" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="E207" s="8" t="s">
-        <v>3150</v>
+        <v>3147</v>
       </c>
       <c r="F207" s="8" t="s">
-        <v>3158</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A208" s="8" t="s">
-        <v>3151</v>
+        <v>3148</v>
       </c>
       <c r="B208" s="8" t="s">
         <v>53</v>
@@ -20939,18 +20939,18 @@
         <v>att_column_type:pepsepmax</v>
       </c>
       <c r="D208" s="9" t="s">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="E208" s="8" t="s">
-        <v>3152</v>
+        <v>3149</v>
       </c>
       <c r="F208" s="8" t="s">
-        <v>3157</v>
+        <v>3154</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A209" s="8" t="s">
-        <v>3153</v>
+        <v>3150</v>
       </c>
       <c r="B209" s="8" t="s">
         <v>53</v>
@@ -20960,13 +20960,13 @@
         <v>att_column_type:pepsepmaxht</v>
       </c>
       <c r="D209" s="9" t="s">
-        <v>3154</v>
+        <v>3151</v>
       </c>
       <c r="E209" s="8" t="s">
-        <v>3155</v>
+        <v>3152</v>
       </c>
       <c r="F209" s="8" t="s">
-        <v>3156</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.15">
@@ -25150,7 +25150,7 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A409" s="8" t="s">
-        <v>2966</v>
+        <v>2963</v>
       </c>
       <c r="B409" s="8" t="s">
         <v>129</v>
@@ -25163,10 +25163,10 @@
         <v>17</v>
       </c>
       <c r="E409" s="8" t="s">
-        <v>2967</v>
+        <v>2964</v>
       </c>
       <c r="F409" s="8" t="s">
-        <v>2968</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.15">
@@ -25465,7 +25465,7 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A424" s="8" t="s">
-        <v>3032</v>
+        <v>3029</v>
       </c>
       <c r="B424" s="8" t="s">
         <v>130</v>
@@ -25478,10 +25478,10 @@
         <v>17</v>
       </c>
       <c r="E424" s="8" t="s">
-        <v>3033</v>
+        <v>3030</v>
       </c>
       <c r="F424" s="8" t="s">
-        <v>3034</v>
+        <v>3031</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.15">
@@ -25507,10 +25507,10 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A426" s="8" t="s">
-        <v>2961</v>
+        <v>2958</v>
       </c>
       <c r="B426" s="8" t="s">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="C426" s="8" t="str">
         <f t="shared" si="13"/>
@@ -25520,18 +25520,18 @@
         <v>17</v>
       </c>
       <c r="E426" s="8" t="s">
-        <v>2962</v>
+        <v>2959</v>
       </c>
       <c r="F426" s="8" t="s">
-        <v>2962</v>
+        <v>2959</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A427" s="8" t="s">
-        <v>2963</v>
+        <v>2960</v>
       </c>
       <c r="B427" s="8" t="s">
-        <v>2959</v>
+        <v>2956</v>
       </c>
       <c r="C427" s="8" t="str">
         <f t="shared" si="13"/>
@@ -25541,10 +25541,10 @@
         <v>17</v>
       </c>
       <c r="E427" s="8" t="s">
-        <v>2964</v>
+        <v>2961</v>
       </c>
       <c r="F427" s="8" t="s">
-        <v>2964</v>
+        <v>2961</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.15">
@@ -25562,10 +25562,10 @@
         <v>17</v>
       </c>
       <c r="E428" s="8" t="s">
-        <v>3076</v>
+        <v>3073</v>
       </c>
       <c r="F428" s="8" t="s">
-        <v>3077</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.15">
@@ -25583,10 +25583,10 @@
         <v>17</v>
       </c>
       <c r="E429" s="8" t="s">
+        <v>3072</v>
+      </c>
+      <c r="F429" s="8" t="s">
         <v>3075</v>
-      </c>
-      <c r="F429" s="8" t="s">
-        <v>3078</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.15">
@@ -25604,10 +25604,10 @@
         <v>17</v>
       </c>
       <c r="E430" s="8" t="s">
-        <v>3073</v>
+        <v>3070</v>
       </c>
       <c r="F430" s="8" t="s">
-        <v>3074</v>
+        <v>3071</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.15">
@@ -25948,7 +25948,7 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A447" s="8" t="s">
-        <v>3026</v>
+        <v>3023</v>
       </c>
       <c r="B447" s="8" t="s">
         <v>144</v>
@@ -25961,10 +25961,10 @@
         <v>17</v>
       </c>
       <c r="E447" s="8" t="s">
-        <v>3027</v>
+        <v>3024</v>
       </c>
       <c r="F447" s="8" t="s">
-        <v>3028</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.15">
@@ -26200,7 +26200,7 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A459" s="8" t="s">
-        <v>3029</v>
+        <v>3026</v>
       </c>
       <c r="B459" s="8" t="s">
         <v>150</v>
@@ -26510,7 +26510,7 @@
         <v>1396</v>
       </c>
       <c r="F473" s="9" t="s">
-        <v>2946</v>
+        <v>2943</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.15">
@@ -26578,7 +26578,7 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A477" s="8" t="s">
-        <v>2948</v>
+        <v>2945</v>
       </c>
       <c r="B477" s="8" t="s">
         <v>155</v>
@@ -26591,15 +26591,15 @@
         <v>17</v>
       </c>
       <c r="E477" s="8" t="s">
-        <v>2947</v>
+        <v>2944</v>
       </c>
       <c r="F477" s="8" t="s">
-        <v>2955</v>
+        <v>2952</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A478" s="8" t="s">
-        <v>2949</v>
+        <v>2946</v>
       </c>
       <c r="B478" s="8" t="s">
         <v>155</v>
@@ -26610,15 +26610,15 @@
       </c>
       <c r="D478" s="9"/>
       <c r="E478" s="8" t="s">
-        <v>2950</v>
+        <v>2947</v>
       </c>
       <c r="F478" s="8" t="s">
-        <v>2954</v>
+        <v>2951</v>
       </c>
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A479" s="8" t="s">
-        <v>2951</v>
+        <v>2948</v>
       </c>
       <c r="B479" s="8" t="s">
         <v>155</v>
@@ -26629,10 +26629,10 @@
       </c>
       <c r="D479" s="9"/>
       <c r="E479" s="8" t="s">
-        <v>2952</v>
+        <v>2949</v>
       </c>
       <c r="F479" s="8" t="s">
-        <v>2953</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.15">
@@ -29787,10 +29787,10 @@
     </row>
     <row r="630" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A630" s="8" t="s">
-        <v>3082</v>
+        <v>3079</v>
       </c>
       <c r="B630" s="8" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="C630" s="8" t="str">
         <f t="shared" si="22"/>
@@ -29800,18 +29800,18 @@
         <v>17</v>
       </c>
       <c r="E630" s="8" t="s">
-        <v>3081</v>
+        <v>3078</v>
       </c>
       <c r="F630" s="8" t="s">
-        <v>3094</v>
+        <v>3091</v>
       </c>
     </row>
     <row r="631" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A631" s="8" t="s">
-        <v>3084</v>
+        <v>3081</v>
       </c>
       <c r="B631" s="8" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="C631" s="8" t="str">
         <f t="shared" si="22"/>
@@ -29821,18 +29821,18 @@
         <v>17</v>
       </c>
       <c r="E631" s="8" t="s">
-        <v>3083</v>
+        <v>3080</v>
       </c>
       <c r="F631" s="8" t="s">
-        <v>3093</v>
+        <v>3090</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A632" s="8" t="s">
-        <v>3087</v>
+        <v>3084</v>
       </c>
       <c r="B632" s="8" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="C632" s="8" t="str">
         <f t="shared" si="22"/>
@@ -29842,10 +29842,10 @@
         <v>17</v>
       </c>
       <c r="E632" s="8" t="s">
-        <v>3086</v>
+        <v>3083</v>
       </c>
       <c r="F632" s="8" t="s">
-        <v>3085</v>
+        <v>3082</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.15">
@@ -29853,7 +29853,7 @@
         <v>2527</v>
       </c>
       <c r="B633" s="8" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="C633" s="8" t="str">
         <f t="shared" si="22"/>
@@ -29863,18 +29863,18 @@
         <v>17</v>
       </c>
       <c r="E633" s="8" t="s">
-        <v>3088</v>
+        <v>3085</v>
       </c>
       <c r="F633" s="8" t="s">
-        <v>3092</v>
+        <v>3089</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A634" s="8" t="s">
-        <v>3089</v>
+        <v>3086</v>
       </c>
       <c r="B634" s="8" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="C634" s="8" t="str">
         <f t="shared" ref="C634:C635" si="23">B634&amp;":"&amp;A634</f>
@@ -29884,10 +29884,10 @@
         <v>17</v>
       </c>
       <c r="E634" s="8" t="s">
-        <v>3090</v>
+        <v>3087</v>
       </c>
       <c r="F634" s="8" t="s">
-        <v>3091</v>
+        <v>3088</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.15">
@@ -29895,7 +29895,7 @@
         <v>2524</v>
       </c>
       <c r="B635" s="8" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="C635" s="8" t="str">
         <f t="shared" si="23"/>
@@ -29905,18 +29905,18 @@
         <v>17</v>
       </c>
       <c r="E635" s="8" t="s">
-        <v>3095</v>
+        <v>3092</v>
       </c>
       <c r="F635" s="8" t="s">
-        <v>3096</v>
+        <v>3093</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A636" s="8" t="s">
-        <v>3104</v>
+        <v>3101</v>
       </c>
       <c r="B636" s="8" t="s">
-        <v>3079</v>
+        <v>3076</v>
       </c>
       <c r="C636" s="8" t="str">
         <f t="shared" ref="C636" si="24">B636&amp;":"&amp;A636</f>
@@ -29926,10 +29926,10 @@
         <v>17</v>
       </c>
       <c r="E636" s="8" t="s">
-        <v>3105</v>
+        <v>3102</v>
       </c>
       <c r="F636" s="8" t="s">
-        <v>3106</v>
+        <v>3103</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.15">
@@ -30186,7 +30186,7 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A649" s="8" t="s">
-        <v>3162</v>
+        <v>3159</v>
       </c>
       <c r="B649" s="8" t="s">
         <v>38</v>
@@ -30196,18 +30196,18 @@
         <v>att_ms_ionsource:captivespray</v>
       </c>
       <c r="D649" s="9" t="s">
-        <v>3161</v>
+        <v>3158</v>
       </c>
       <c r="E649" s="8" t="s">
-        <v>3166</v>
+        <v>3163</v>
       </c>
       <c r="F649" s="8" t="s">
-        <v>3168</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A650" s="8" t="s">
-        <v>3163</v>
+        <v>3160</v>
       </c>
       <c r="B650" s="8" t="s">
         <v>38</v>
@@ -30217,18 +30217,18 @@
         <v>att_ms_ionsource:captivespraytwo</v>
       </c>
       <c r="D650" s="9" t="s">
+        <v>3161</v>
+      </c>
+      <c r="E650" s="8" t="s">
+        <v>3162</v>
+      </c>
+      <c r="F650" s="8" t="s">
         <v>3164</v>
-      </c>
-      <c r="E650" s="8" t="s">
-        <v>3165</v>
-      </c>
-      <c r="F650" s="8" t="s">
-        <v>3167</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A651" s="8" t="s">
-        <v>3169</v>
+        <v>3166</v>
       </c>
       <c r="B651" s="8" t="s">
         <v>38</v>
@@ -30238,13 +30238,13 @@
         <v>att_ms_ionsource:captiivespraypro</v>
       </c>
       <c r="D651" s="9" t="s">
-        <v>3170</v>
+        <v>3167</v>
       </c>
       <c r="E651" s="8" t="s">
-        <v>3171</v>
+        <v>3168</v>
       </c>
       <c r="F651" s="8" t="s">
-        <v>3172</v>
+        <v>3169</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.15">
@@ -30307,12 +30307,12 @@
         <v>1890</v>
       </c>
       <c r="F654" s="8" t="s">
-        <v>3025</v>
+        <v>3022</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A655" s="8" t="s">
-        <v>3022</v>
+        <v>3019</v>
       </c>
       <c r="B655" s="8" t="s">
         <v>164</v>
@@ -30325,10 +30325,10 @@
         <v>17</v>
       </c>
       <c r="E655" s="8" t="s">
-        <v>3023</v>
+        <v>3020</v>
       </c>
       <c r="F655" s="8" t="s">
-        <v>3024</v>
+        <v>3021</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.15">
@@ -32937,7 +32937,7 @@
     </row>
     <row r="780" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A780" s="8" t="s">
-        <v>2922</v>
+        <v>2919</v>
       </c>
       <c r="B780" s="8" t="s">
         <v>196</v>
@@ -32947,13 +32947,13 @@
         <v>att_organism:controls</v>
       </c>
       <c r="D780" s="8" t="s">
-        <v>2919</v>
+        <v>2916</v>
       </c>
       <c r="E780" s="8" t="s">
-        <v>2920</v>
+        <v>2917</v>
       </c>
       <c r="F780" s="8" t="s">
-        <v>2921</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="781" spans="1:6" x14ac:dyDescent="0.15">
@@ -33861,10 +33861,10 @@
     </row>
     <row r="824" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A824" s="8" t="s">
-        <v>2973</v>
+        <v>2970</v>
       </c>
       <c r="B824" s="8" t="s">
-        <v>2971</v>
+        <v>2968</v>
       </c>
       <c r="C824" s="8" t="str">
         <f t="shared" si="28"/>
@@ -33874,10 +33874,10 @@
         <v>17</v>
       </c>
       <c r="E824" s="8" t="s">
-        <v>2974</v>
+        <v>2971</v>
       </c>
       <c r="F824" s="8" t="s">
-        <v>2975</v>
+        <v>2972</v>
       </c>
       <c r="G824"/>
       <c r="H824"/>
@@ -34898,10 +34898,10 @@
     </row>
     <row r="825" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A825" s="8" t="s">
-        <v>2976</v>
+        <v>2973</v>
       </c>
       <c r="B825" s="8" t="s">
-        <v>2971</v>
+        <v>2968</v>
       </c>
       <c r="C825" s="8" t="str">
         <f t="shared" si="28"/>
@@ -34911,10 +34911,10 @@
         <v>17</v>
       </c>
       <c r="E825" s="8" t="s">
-        <v>2977</v>
+        <v>2974</v>
       </c>
       <c r="F825" s="8" t="s">
-        <v>2978</v>
+        <v>2975</v>
       </c>
       <c r="G825"/>
       <c r="H825"/>
@@ -35935,10 +35935,10 @@
     </row>
     <row r="826" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A826" s="8" t="s">
-        <v>2981</v>
+        <v>2978</v>
       </c>
       <c r="B826" s="8" t="s">
-        <v>2971</v>
+        <v>2968</v>
       </c>
       <c r="C826" s="8" t="str">
         <f t="shared" si="28"/>
@@ -35948,10 +35948,10 @@
         <v>17</v>
       </c>
       <c r="E826" s="8" t="s">
-        <v>2979</v>
+        <v>2976</v>
       </c>
       <c r="F826" s="8" t="s">
-        <v>2980</v>
+        <v>2977</v>
       </c>
       <c r="G826"/>
       <c r="H826"/>
@@ -37539,10 +37539,10 @@
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A854" s="8" t="s">
-        <v>2925</v>
+        <v>2922</v>
       </c>
       <c r="B854" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C854" s="8" t="str">
         <f t="shared" si="30"/>
@@ -37552,18 +37552,18 @@
         <v>17</v>
       </c>
       <c r="E854" s="8" t="s">
-        <v>2926</v>
+        <v>2923</v>
       </c>
       <c r="F854" s="8" t="s">
-        <v>2927</v>
+        <v>2924</v>
       </c>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A855" s="8" t="s">
-        <v>2929</v>
+        <v>2926</v>
       </c>
       <c r="B855" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C855" s="8" t="str">
         <f t="shared" si="30"/>
@@ -37573,18 +37573,18 @@
         <v>17</v>
       </c>
       <c r="E855" s="8" t="s">
-        <v>2930</v>
+        <v>2927</v>
       </c>
       <c r="F855" s="8" t="s">
-        <v>2931</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A856" s="8" t="s">
-        <v>2928</v>
+        <v>2925</v>
       </c>
       <c r="B856" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C856" s="8" t="str">
         <f t="shared" ref="C856" si="31">B856&amp;":"&amp;A856</f>
@@ -37594,18 +37594,18 @@
         <v>17</v>
       </c>
       <c r="E856" s="8" t="s">
-        <v>2945</v>
+        <v>2942</v>
       </c>
       <c r="F856" s="8" t="s">
-        <v>2944</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A857" s="8" t="s">
-        <v>2958</v>
+        <v>2955</v>
       </c>
       <c r="B857" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C857" s="8" t="str">
         <f t="shared" ref="C857" si="32">B857&amp;":"&amp;A857</f>
@@ -37615,18 +37615,18 @@
         <v>17</v>
       </c>
       <c r="E857" s="8" t="s">
-        <v>2956</v>
+        <v>2953</v>
       </c>
       <c r="F857" s="8" t="s">
-        <v>2957</v>
+        <v>2954</v>
       </c>
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A858" s="8" t="s">
-        <v>2932</v>
+        <v>2929</v>
       </c>
       <c r="B858" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C858" s="8" t="str">
         <f t="shared" si="30"/>
@@ -37636,18 +37636,18 @@
         <v>17</v>
       </c>
       <c r="E858" s="8" t="s">
-        <v>2933</v>
+        <v>2930</v>
       </c>
       <c r="F858" s="8" t="s">
-        <v>2934</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A859" s="8" t="s">
-        <v>2935</v>
+        <v>2932</v>
       </c>
       <c r="B859" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C859" s="8" t="str">
         <f t="shared" ref="C859:C861" si="33">B859&amp;":"&amp;A859</f>
@@ -37657,18 +37657,18 @@
         <v>17</v>
       </c>
       <c r="E859" s="8" t="s">
-        <v>2943</v>
+        <v>2940</v>
       </c>
       <c r="F859" s="8" t="s">
-        <v>2936</v>
+        <v>2933</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A860" s="8" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
       <c r="B860" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C860" s="8" t="str">
         <f t="shared" si="33"/>
@@ -37678,18 +37678,18 @@
         <v>17</v>
       </c>
       <c r="E860" s="8" t="s">
-        <v>2938</v>
+        <v>2935</v>
       </c>
       <c r="F860" s="8" t="s">
-        <v>2939</v>
+        <v>2936</v>
       </c>
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A861" s="8" t="s">
-        <v>2940</v>
+        <v>2937</v>
       </c>
       <c r="B861" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C861" s="8" t="str">
         <f t="shared" si="33"/>
@@ -37699,10 +37699,10 @@
         <v>17</v>
       </c>
       <c r="E861" s="8" t="s">
-        <v>2941</v>
+        <v>2938</v>
       </c>
       <c r="F861" s="8" t="s">
-        <v>2942</v>
+        <v>2939</v>
       </c>
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.15">
@@ -38988,7 +38988,7 @@
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A923" s="8" t="s">
-        <v>3069</v>
+        <v>3066</v>
       </c>
       <c r="B923" s="8" t="s">
         <v>247</v>
@@ -39001,10 +39001,10 @@
         <v>17</v>
       </c>
       <c r="E923" s="8" t="s">
-        <v>3070</v>
+        <v>3067</v>
       </c>
       <c r="F923" s="8" t="s">
-        <v>3070</v>
+        <v>3067</v>
       </c>
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.15">
@@ -39051,28 +39051,28 @@
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A926" s="8" t="s">
-        <v>2870</v>
+        <v>3172</v>
       </c>
       <c r="B926" s="8" t="s">
         <v>251</v>
       </c>
       <c r="C926" s="8" t="str">
         <f t="shared" si="34"/>
-        <v>att_user_research_group:ProtFa</v>
+        <v>att_user_research_group:protfa</v>
       </c>
       <c r="D926" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E926" s="8" t="s">
-        <v>2871</v>
+        <v>3171</v>
       </c>
       <c r="F926" s="8" t="s">
-        <v>2872</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A927" s="8" t="s">
-        <v>2873</v>
+        <v>2870</v>
       </c>
       <c r="B927" s="8" t="s">
         <v>251</v>
@@ -39085,15 +39085,15 @@
         <v>17</v>
       </c>
       <c r="E927" s="8" t="s">
-        <v>2874</v>
+        <v>2871</v>
       </c>
       <c r="F927" s="8" t="s">
-        <v>2875</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A928" s="8" t="s">
-        <v>2876</v>
+        <v>2873</v>
       </c>
       <c r="B928" s="8" t="s">
         <v>251</v>
@@ -39106,15 +39106,15 @@
         <v>17</v>
       </c>
       <c r="E928" s="8" t="s">
-        <v>2877</v>
+        <v>2874</v>
       </c>
       <c r="F928" s="8" t="s">
-        <v>2878</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A929" s="8" t="s">
-        <v>2879</v>
+        <v>2876</v>
       </c>
       <c r="B929" s="8" t="s">
         <v>251</v>
@@ -39127,15 +39127,15 @@
         <v>17</v>
       </c>
       <c r="E929" s="8" t="s">
-        <v>2880</v>
+        <v>2877</v>
       </c>
       <c r="F929" s="8" t="s">
-        <v>2878</v>
+        <v>2875</v>
       </c>
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A930" s="8" t="s">
-        <v>2881</v>
+        <v>2878</v>
       </c>
       <c r="B930" s="8" t="s">
         <v>251</v>
@@ -39148,15 +39148,15 @@
         <v>17</v>
       </c>
       <c r="E930" s="8" t="s">
-        <v>2882</v>
+        <v>2879</v>
       </c>
       <c r="F930" s="8" t="s">
-        <v>2883</v>
+        <v>2880</v>
       </c>
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A931" s="8" t="s">
-        <v>3043</v>
+        <v>3040</v>
       </c>
       <c r="B931" s="8" t="s">
         <v>251</v>
@@ -39169,15 +39169,15 @@
         <v>17</v>
       </c>
       <c r="E931" s="8" t="s">
-        <v>3051</v>
+        <v>3048</v>
       </c>
       <c r="F931" s="8" t="s">
-        <v>3061</v>
+        <v>3058</v>
       </c>
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A932" s="8" t="s">
-        <v>3044</v>
+        <v>3041</v>
       </c>
       <c r="B932" s="8" t="s">
         <v>251</v>
@@ -39190,15 +39190,15 @@
         <v>17</v>
       </c>
       <c r="E932" s="8" t="s">
-        <v>3052</v>
+        <v>3049</v>
       </c>
       <c r="F932" s="8" t="s">
-        <v>3062</v>
+        <v>3059</v>
       </c>
     </row>
     <row r="933" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A933" s="8" t="s">
-        <v>3045</v>
+        <v>3042</v>
       </c>
       <c r="B933" s="8" t="s">
         <v>251</v>
@@ -39211,15 +39211,15 @@
         <v>17</v>
       </c>
       <c r="E933" s="8" t="s">
-        <v>3053</v>
+        <v>3050</v>
       </c>
       <c r="F933" s="8" t="s">
-        <v>3068</v>
+        <v>3065</v>
       </c>
     </row>
     <row r="934" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A934" s="8" t="s">
-        <v>3046</v>
+        <v>3043</v>
       </c>
       <c r="B934" s="8" t="s">
         <v>251</v>
@@ -39232,15 +39232,15 @@
         <v>17</v>
       </c>
       <c r="E934" s="8" t="s">
-        <v>3066</v>
+        <v>3063</v>
       </c>
       <c r="F934" s="8" t="s">
-        <v>3065</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="935" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A935" s="8" t="s">
-        <v>3055</v>
+        <v>3052</v>
       </c>
       <c r="B935" s="8" t="s">
         <v>251</v>
@@ -39253,15 +39253,15 @@
         <v>17</v>
       </c>
       <c r="E935" s="8" t="s">
-        <v>3054</v>
+        <v>3051</v>
       </c>
       <c r="F935" s="8" t="s">
-        <v>3063</v>
+        <v>3060</v>
       </c>
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A936" s="8" t="s">
-        <v>2910</v>
+        <v>2907</v>
       </c>
       <c r="B936" s="8" t="s">
         <v>251</v>
@@ -39274,15 +39274,15 @@
         <v>17</v>
       </c>
       <c r="E936" s="8" t="s">
-        <v>2911</v>
+        <v>2908</v>
       </c>
       <c r="F936" s="8" t="s">
-        <v>3064</v>
+        <v>3061</v>
       </c>
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A937" s="8" t="s">
-        <v>3047</v>
+        <v>3044</v>
       </c>
       <c r="B937" s="8" t="s">
         <v>251</v>
@@ -39295,15 +39295,15 @@
         <v>17</v>
       </c>
       <c r="E937" s="8" t="s">
-        <v>3056</v>
+        <v>3053</v>
       </c>
       <c r="F937" s="8" t="s">
-        <v>3071</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A938" s="8" t="s">
-        <v>3048</v>
+        <v>3045</v>
       </c>
       <c r="B938" s="8" t="s">
         <v>251</v>
@@ -39316,15 +39316,15 @@
         <v>17</v>
       </c>
       <c r="E938" s="8" t="s">
-        <v>3057</v>
+        <v>3054</v>
       </c>
       <c r="F938" s="8" t="s">
-        <v>3067</v>
+        <v>3064</v>
       </c>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A939" s="8" t="s">
-        <v>3049</v>
+        <v>3046</v>
       </c>
       <c r="B939" s="8" t="s">
         <v>251</v>
@@ -39337,15 +39337,15 @@
         <v>17</v>
       </c>
       <c r="E939" s="8" t="s">
-        <v>3058</v>
+        <v>3055</v>
       </c>
       <c r="F939" s="8" t="s">
-        <v>3072</v>
+        <v>3069</v>
       </c>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A940" s="8" t="s">
-        <v>3050</v>
+        <v>3047</v>
       </c>
       <c r="B940" s="8" t="s">
         <v>251</v>
@@ -39358,15 +39358,15 @@
         <v>17</v>
       </c>
       <c r="E940" s="8" t="s">
-        <v>3059</v>
+        <v>3056</v>
       </c>
       <c r="F940" s="8" t="s">
-        <v>3060</v>
+        <v>3057</v>
       </c>
     </row>
     <row r="941" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A941" s="8" t="s">
-        <v>2907</v>
+        <v>2904</v>
       </c>
       <c r="B941" s="8" t="s">
         <v>251</v>
@@ -39379,15 +39379,15 @@
         <v>17</v>
       </c>
       <c r="E941" s="8" t="s">
-        <v>2908</v>
+        <v>2905</v>
       </c>
       <c r="F941" s="8" t="s">
-        <v>2909</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="942" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A942" s="8" t="s">
-        <v>2910</v>
+        <v>2907</v>
       </c>
       <c r="B942" s="8" t="s">
         <v>251</v>
@@ -39400,15 +39400,15 @@
         <v>17</v>
       </c>
       <c r="E942" s="8" t="s">
-        <v>2911</v>
+        <v>2908</v>
       </c>
       <c r="F942" s="8" t="s">
-        <v>2909</v>
+        <v>2906</v>
       </c>
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A943" s="8" t="s">
-        <v>2912</v>
+        <v>2909</v>
       </c>
       <c r="B943" s="8" t="s">
         <v>251</v>
@@ -39421,15 +39421,15 @@
         <v>17</v>
       </c>
       <c r="E943" s="8" t="s">
-        <v>2913</v>
+        <v>2910</v>
       </c>
       <c r="F943" s="8" t="s">
-        <v>2914</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A944" s="8" t="s">
-        <v>3039</v>
+        <v>3036</v>
       </c>
       <c r="B944" s="8" t="s">
         <v>251</v>
@@ -39442,10 +39442,10 @@
         <v>17</v>
       </c>
       <c r="E944" s="8" t="s">
-        <v>3040</v>
+        <v>3037</v>
       </c>
       <c r="F944" s="8" t="s">
-        <v>3041</v>
+        <v>3038</v>
       </c>
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.15">
@@ -39589,12 +39589,12 @@
         <v>2574</v>
       </c>
       <c r="F951" s="8" t="s">
-        <v>2985</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A952" s="8" t="s">
-        <v>2986</v>
+        <v>2983</v>
       </c>
       <c r="B952" s="8" t="s">
         <v>40</v>
@@ -39607,15 +39607,15 @@
         <v>17</v>
       </c>
       <c r="E952" s="8" t="s">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="F952" s="8" t="s">
-        <v>3006</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A953" s="8" t="s">
-        <v>2987</v>
+        <v>2984</v>
       </c>
       <c r="B953" s="8" t="s">
         <v>40</v>
@@ -39628,15 +39628,15 @@
         <v>17</v>
       </c>
       <c r="E953" s="8" t="s">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="F953" s="8" t="s">
-        <v>3004</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="954" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A954" s="8" t="s">
-        <v>2988</v>
+        <v>2985</v>
       </c>
       <c r="B954" s="8" t="s">
         <v>40</v>
@@ -39649,15 +39649,15 @@
         <v>17</v>
       </c>
       <c r="E954" s="8" t="s">
-        <v>3008</v>
+        <v>3005</v>
       </c>
       <c r="F954" s="8" t="s">
-        <v>3003</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A955" s="8" t="s">
-        <v>2989</v>
+        <v>2986</v>
       </c>
       <c r="B955" s="8" t="s">
         <v>40</v>
@@ -39670,15 +39670,15 @@
         <v>17</v>
       </c>
       <c r="E955" s="8" t="s">
-        <v>3002</v>
+        <v>2999</v>
       </c>
       <c r="F955" s="8" t="s">
-        <v>3009</v>
+        <v>3006</v>
       </c>
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A956" s="8" t="s">
-        <v>2990</v>
+        <v>2987</v>
       </c>
       <c r="B956" s="8" t="s">
         <v>40</v>
@@ -39691,15 +39691,15 @@
         <v>17</v>
       </c>
       <c r="E956" s="8" t="s">
-        <v>3001</v>
+        <v>2998</v>
       </c>
       <c r="F956" s="8" t="s">
-        <v>3000</v>
+        <v>2997</v>
       </c>
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A957" s="8" t="s">
-        <v>2991</v>
+        <v>2988</v>
       </c>
       <c r="B957" s="8" t="s">
         <v>40</v>
@@ -39712,15 +39712,15 @@
         <v>17</v>
       </c>
       <c r="E957" s="8" t="s">
-        <v>2999</v>
+        <v>2996</v>
       </c>
       <c r="F957" s="8" t="s">
-        <v>2998</v>
+        <v>2995</v>
       </c>
     </row>
     <row r="958" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A958" s="8" t="s">
-        <v>2992</v>
+        <v>2989</v>
       </c>
       <c r="B958" s="8" t="s">
         <v>40</v>
@@ -39733,15 +39733,15 @@
         <v>17</v>
       </c>
       <c r="E958" s="8" t="s">
-        <v>2997</v>
+        <v>2994</v>
       </c>
       <c r="F958" s="8" t="s">
-        <v>2996</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A959" s="8" t="s">
-        <v>2993</v>
+        <v>2990</v>
       </c>
       <c r="B959" s="8" t="s">
         <v>40</v>
@@ -39754,18 +39754,18 @@
         <v>17</v>
       </c>
       <c r="E959" s="8" t="s">
-        <v>2995</v>
+        <v>2992</v>
       </c>
       <c r="F959" s="8" t="s">
-        <v>2994</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A960" s="8" t="s">
-        <v>3010</v>
+        <v>3007</v>
       </c>
       <c r="B960" s="8" t="s">
-        <v>2923</v>
+        <v>2920</v>
       </c>
       <c r="C960" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39775,18 +39775,18 @@
         <v>17</v>
       </c>
       <c r="E960" s="8" t="s">
-        <v>3011</v>
+        <v>3008</v>
       </c>
       <c r="F960" s="8" t="s">
-        <v>3012</v>
+        <v>3009</v>
       </c>
     </row>
     <row r="961" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A961" s="8" t="s">
-        <v>3014</v>
+        <v>3011</v>
       </c>
       <c r="B961" s="8" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="C961" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39796,18 +39796,18 @@
         <v>17</v>
       </c>
       <c r="E961" s="8" t="s">
-        <v>3015</v>
+        <v>3012</v>
       </c>
       <c r="F961" s="8" t="s">
-        <v>3016</v>
+        <v>3013</v>
       </c>
     </row>
     <row r="962" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A962" s="8" t="s">
-        <v>3017</v>
+        <v>3014</v>
       </c>
       <c r="B962" s="8" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="C962" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39817,18 +39817,18 @@
         <v>17</v>
       </c>
       <c r="E962" s="8" t="s">
-        <v>3018</v>
+        <v>3015</v>
       </c>
       <c r="F962" s="8" t="s">
-        <v>3019</v>
+        <v>3016</v>
       </c>
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A963" s="8" t="s">
-        <v>3037</v>
+        <v>3034</v>
       </c>
       <c r="B963" s="8" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="C963" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39838,18 +39838,18 @@
         <v>17</v>
       </c>
       <c r="E963" s="8" t="s">
-        <v>3035</v>
+        <v>3032</v>
       </c>
       <c r="F963" s="8" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="964" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A964" s="8" t="s">
-        <v>3038</v>
+        <v>3035</v>
       </c>
       <c r="B964" s="8" t="s">
-        <v>3013</v>
+        <v>3010</v>
       </c>
       <c r="C964" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39859,18 +39859,18 @@
         <v>17</v>
       </c>
       <c r="E964" s="8" t="s">
-        <v>3036</v>
+        <v>3033</v>
       </c>
       <c r="F964" s="8" t="s">
-        <v>3020</v>
+        <v>3017</v>
       </c>
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A965" s="8" t="s">
-        <v>3111</v>
+        <v>3108</v>
       </c>
       <c r="B965" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C965" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39880,18 +39880,18 @@
         <v>17</v>
       </c>
       <c r="E965" s="8" t="s">
-        <v>3129</v>
+        <v>3126</v>
       </c>
       <c r="F965" s="8" t="s">
-        <v>3134</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A966" s="8" t="s">
-        <v>3112</v>
+        <v>3109</v>
       </c>
       <c r="B966" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C966" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39901,18 +39901,18 @@
         <v>17</v>
       </c>
       <c r="E966" s="8" t="s">
-        <v>3130</v>
+        <v>3127</v>
       </c>
       <c r="F966" s="8" t="s">
-        <v>3135</v>
+        <v>3132</v>
       </c>
     </row>
     <row r="967" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A967" s="8" t="s">
-        <v>3113</v>
+        <v>3110</v>
       </c>
       <c r="B967" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C967" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39922,18 +39922,18 @@
         <v>17</v>
       </c>
       <c r="E967" s="8" t="s">
-        <v>3131</v>
+        <v>3128</v>
       </c>
       <c r="F967" s="8" t="s">
-        <v>3136</v>
+        <v>3133</v>
       </c>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A968" s="8" t="s">
-        <v>3114</v>
+        <v>3111</v>
       </c>
       <c r="B968" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C968" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39943,18 +39943,18 @@
         <v>17</v>
       </c>
       <c r="E968" s="8" t="s">
-        <v>3132</v>
+        <v>3129</v>
       </c>
       <c r="F968" s="8" t="s">
-        <v>3137</v>
+        <v>3134</v>
       </c>
     </row>
     <row r="969" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A969" s="8" t="s">
-        <v>3115</v>
+        <v>3112</v>
       </c>
       <c r="B969" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C969" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39964,18 +39964,18 @@
         <v>17</v>
       </c>
       <c r="E969" s="8" t="s">
-        <v>3133</v>
+        <v>3130</v>
       </c>
       <c r="F969" s="8" t="s">
-        <v>3116</v>
+        <v>3113</v>
       </c>
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A970" s="8" t="s">
-        <v>3117</v>
+        <v>3114</v>
       </c>
       <c r="B970" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C970" s="8" t="str">
         <f t="shared" si="36"/>
@@ -39985,18 +39985,18 @@
         <v>17</v>
       </c>
       <c r="E970" s="8" t="s">
-        <v>3118</v>
+        <v>3115</v>
       </c>
       <c r="F970" s="8" t="s">
-        <v>3139</v>
+        <v>3136</v>
       </c>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A971" s="8" t="s">
-        <v>3119</v>
+        <v>3116</v>
       </c>
       <c r="B971" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C971" s="8" t="str">
         <f t="shared" si="36"/>
@@ -40006,18 +40006,18 @@
         <v>17</v>
       </c>
       <c r="E971" s="8" t="s">
-        <v>3120</v>
+        <v>3117</v>
       </c>
       <c r="F971" s="8" t="s">
-        <v>3138</v>
+        <v>3135</v>
       </c>
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A972" s="8" t="s">
-        <v>3121</v>
+        <v>3118</v>
       </c>
       <c r="B972" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C972" s="8" t="str">
         <f t="shared" si="36"/>
@@ -40027,18 +40027,18 @@
         <v>17</v>
       </c>
       <c r="E972" s="8" t="s">
-        <v>3122</v>
+        <v>3119</v>
       </c>
       <c r="F972" s="8" t="s">
-        <v>3140</v>
+        <v>3137</v>
       </c>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A973" s="8" t="s">
-        <v>3123</v>
+        <v>3120</v>
       </c>
       <c r="B973" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C973" s="8" t="str">
         <f t="shared" si="36"/>
@@ -40048,18 +40048,18 @@
         <v>17</v>
       </c>
       <c r="E973" s="8" t="s">
-        <v>3124</v>
+        <v>3121</v>
       </c>
       <c r="F973" s="8" t="s">
-        <v>3141</v>
+        <v>3138</v>
       </c>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A974" s="8" t="s">
-        <v>3125</v>
+        <v>3122</v>
       </c>
       <c r="B974" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C974" s="8" t="str">
         <f t="shared" si="36"/>
@@ -40069,18 +40069,18 @@
         <v>17</v>
       </c>
       <c r="E974" s="8" t="s">
-        <v>3126</v>
+        <v>3123</v>
       </c>
       <c r="F974" s="8" t="s">
-        <v>3142</v>
+        <v>3139</v>
       </c>
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A975" s="8" t="s">
-        <v>3127</v>
+        <v>3124</v>
       </c>
       <c r="B975" s="8" t="s">
-        <v>3109</v>
+        <v>3106</v>
       </c>
       <c r="C975" s="8" t="str">
         <f t="shared" si="36"/>
@@ -40090,10 +40090,10 @@
         <v>17</v>
       </c>
       <c r="E975" s="8" t="s">
-        <v>3128</v>
+        <v>3125</v>
       </c>
       <c r="F975" s="8" t="s">
-        <v>3143</v>
+        <v>3140</v>
       </c>
     </row>
     <row r="976" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -40445,7 +40445,7 @@
   <sheetData>
     <row r="1" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A1" s="8" t="s">
-        <v>2884</v>
+        <v>2881</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>251</v>
@@ -40458,7 +40458,7 @@
         <v>17</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>2885</v>
+        <v>2882</v>
       </c>
       <c r="F1" s="8" t="s">
         <v>2494</v>
@@ -41482,7 +41482,7 @@
     </row>
     <row r="2" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A2" s="8" t="s">
-        <v>2886</v>
+        <v>2883</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>251</v>
@@ -41495,10 +41495,10 @@
         <v>17</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>2887</v>
+        <v>2884</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>2888</v>
+        <v>2885</v>
       </c>
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
@@ -42519,7 +42519,7 @@
     </row>
     <row r="3" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A3" s="8" t="s">
-        <v>2889</v>
+        <v>2886</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>251</v>
@@ -42532,10 +42532,10 @@
         <v>17</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>2890</v>
+        <v>2887</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>2891</v>
+        <v>2888</v>
       </c>
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
@@ -43556,7 +43556,7 @@
     </row>
     <row r="4" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A4" s="8" t="s">
-        <v>2892</v>
+        <v>2889</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>251</v>
@@ -43569,10 +43569,10 @@
         <v>17</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>2893</v>
+        <v>2890</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>2894</v>
+        <v>2891</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
@@ -44593,7 +44593,7 @@
     </row>
     <row r="5" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A5" s="8" t="s">
-        <v>2895</v>
+        <v>2892</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>251</v>
@@ -44606,10 +44606,10 @@
         <v>17</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>2896</v>
+        <v>2893</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>2897</v>
+        <v>2894</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
@@ -45630,7 +45630,7 @@
     </row>
     <row r="6" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A6" s="8" t="s">
-        <v>2898</v>
+        <v>2895</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>251</v>
@@ -45643,10 +45643,10 @@
         <v>17</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>2899</v>
+        <v>2896</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>2900</v>
+        <v>2897</v>
       </c>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
@@ -46667,7 +46667,7 @@
     </row>
     <row r="7" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A7" s="8" t="s">
-        <v>2901</v>
+        <v>2898</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>251</v>
@@ -46680,10 +46680,10 @@
         <v>17</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>2902</v>
+        <v>2899</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>2903</v>
+        <v>2900</v>
       </c>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
@@ -47704,7 +47704,7 @@
     </row>
     <row r="8" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A8" s="8" t="s">
-        <v>2904</v>
+        <v>2901</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>251</v>
@@ -47717,10 +47717,10 @@
         <v>17</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>2905</v>
+        <v>2902</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>2906</v>
+        <v>2903</v>
       </c>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9B2E6DE-F156-E846-9081-2CC4BBADDE09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB290B4B-9CEB-F243-98E5-C35700181400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18840" yWindow="2300" windowWidth="29540" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18840" yWindow="2300" windowWidth="29540" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10813" uniqueCount="3192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10825" uniqueCount="3193">
   <si>
     <t>tag</t>
   </si>
@@ -9619,6 +9619,9 @@
   </si>
   <si>
     <t>RIPA cotaning SDS (0.1%) buffer (specify recipe in info).</t>
+  </si>
+  <si>
+    <t>Differential centrifugation fraction</t>
   </si>
 </sst>
 </file>
@@ -10231,7 +10234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH129"/>
+  <dimension ref="A1:AMH130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -12707,13 +12710,13 @@
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>129</v>
-      </c>
-      <c r="B50" t="s">
-        <v>130</v>
-      </c>
-      <c r="C50" t="s">
-        <v>131</v>
+        <v>1235</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>3192</v>
       </c>
       <c r="D50">
         <v>500</v>
@@ -12725,7 +12728,7 @@
         <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>132</v>
+        <v>47</v>
       </c>
       <c r="H50">
         <v>0</v>
@@ -12743,27 +12746,27 @@
         <v>19</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N50" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B51" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C51" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D51">
         <v>500</v>
@@ -12807,13 +12810,13 @@
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B52" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D52">
         <v>500</v>
@@ -12857,16 +12860,16 @@
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
-        <v>2952</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c r="C53" t="s">
-        <v>2953</v>
+        <v>136</v>
       </c>
       <c r="D53">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>19</v>
@@ -12875,7 +12878,7 @@
         <v>19</v>
       </c>
       <c r="G53" t="s">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="H53">
         <v>0</v>
@@ -12893,30 +12896,30 @@
         <v>19</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N53" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>3023</v>
+        <v>2952</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
       </c>
       <c r="C54" t="s">
-        <v>3024</v>
+        <v>2953</v>
       </c>
       <c r="D54">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>19</v>
@@ -12937,7 +12940,7 @@
         <v>0</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>19</v>
@@ -12949,36 +12952,36 @@
         <v>19</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A55" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>138</v>
+      <c r="A55" t="s">
+        <v>3023</v>
+      </c>
+      <c r="B55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55" t="s">
+        <v>3024</v>
       </c>
       <c r="D55">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G55" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I55" s="7" t="b">
         <v>0</v>
@@ -12987,7 +12990,7 @@
         <v>0</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L55" s="1" t="s">
         <v>19</v>
@@ -12999,36 +13002,36 @@
         <v>19</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A56" t="s">
-        <v>139</v>
+      <c r="A56" s="6" t="s">
+        <v>137</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>140</v>
+        <v>22</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>3014</v>
+        <v>138</v>
       </c>
       <c r="D56">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G56" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="H56">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I56" s="7" t="b">
         <v>0</v>
@@ -13052,24 +13055,24 @@
         <v>21</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A57" s="6" t="s">
+      <c r="A57" t="s">
+        <v>139</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B57" t="s">
-        <v>17</v>
-      </c>
-      <c r="C57" t="s">
-        <v>2845</v>
+      <c r="C57" s="6" t="s">
+        <v>3014</v>
       </c>
       <c r="D57">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>19</v>
@@ -13106,14 +13109,14 @@
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A58" t="s">
-        <v>143</v>
+      <c r="A58" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="B58" t="s">
-        <v>144</v>
+        <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>145</v>
+        <v>2845</v>
       </c>
       <c r="D58">
         <v>500</v>
@@ -13122,13 +13125,13 @@
         <v>19</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G58" t="s">
-        <v>55</v>
+        <v>141</v>
       </c>
       <c r="H58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I58" s="7" t="b">
         <v>0</v>
@@ -13137,7 +13140,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L58" s="1" t="s">
         <v>19</v>
@@ -13146,24 +13149,24 @@
         <v>19</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O58" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B59" t="s">
         <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D59">
         <v>500</v>
@@ -13184,7 +13187,7 @@
         <v>0</v>
       </c>
       <c r="J59" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K59" s="1" t="s">
         <v>19</v>
@@ -13207,13 +13210,13 @@
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B60" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="C60" t="s">
-        <v>2802</v>
+        <v>147</v>
       </c>
       <c r="D60">
         <v>500</v>
@@ -13222,7 +13225,7 @@
         <v>19</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G60" t="s">
         <v>55</v>
@@ -13237,7 +13240,7 @@
         <v>1</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L60" s="1" t="s">
         <v>19</v>
@@ -13257,13 +13260,13 @@
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
+        <v>17</v>
       </c>
       <c r="C61" t="s">
-        <v>2803</v>
+        <v>2802</v>
       </c>
       <c r="D61">
         <v>500</v>
@@ -13306,17 +13309,17 @@
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A62" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>151</v>
+      <c r="A62" t="s">
+        <v>144</v>
+      </c>
+      <c r="B62" t="s">
+        <v>148</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2803</v>
       </c>
       <c r="D62">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>19</v>
@@ -13325,16 +13328,16 @@
         <v>19</v>
       </c>
       <c r="G62" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="H62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I62" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J62" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>21</v>
@@ -13346,27 +13349,27 @@
         <v>19</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O62" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P62" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A63" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C63" t="s">
-        <v>153</v>
+        <v>27</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>151</v>
       </c>
       <c r="D63">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>19</v>
@@ -13375,7 +13378,7 @@
         <v>19</v>
       </c>
       <c r="G63" t="s">
-        <v>93</v>
+        <v>29</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -13407,13 +13410,13 @@
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A64" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B64" t="s">
-        <v>17</v>
-      </c>
       <c r="C64" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D64">
         <v>500</v>
@@ -13457,13 +13460,13 @@
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A65" s="6" t="s">
-        <v>155</v>
+        <v>91</v>
       </c>
       <c r="B65" t="s">
         <v>17</v>
       </c>
       <c r="C65" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D65">
         <v>500</v>
@@ -13475,10 +13478,10 @@
         <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>42</v>
+        <v>93</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I65" s="7" t="b">
         <v>0</v>
@@ -13506,14 +13509,14 @@
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A66" t="s">
-        <v>157</v>
+      <c r="A66" s="6" t="s">
+        <v>155</v>
       </c>
       <c r="B66" t="s">
         <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D66">
         <v>500</v>
@@ -13525,7 +13528,7 @@
         <v>19</v>
       </c>
       <c r="G66" t="s">
-        <v>159</v>
+        <v>42</v>
       </c>
       <c r="H66">
         <v>0</v>
@@ -13557,13 +13560,13 @@
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D67">
         <v>500</v>
@@ -13575,7 +13578,7 @@
         <v>19</v>
       </c>
       <c r="G67" t="s">
-        <v>42</v>
+        <v>159</v>
       </c>
       <c r="H67">
         <v>0</v>
@@ -13606,17 +13609,17 @@
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A68" s="6" t="s">
-        <v>3072</v>
+      <c r="A68" t="s">
+        <v>160</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>3073</v>
+        <v>161</v>
       </c>
       <c r="D68">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>19</v>
@@ -13652,27 +13655,27 @@
         <v>21</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A69" s="6" t="s">
-        <v>2958</v>
+        <v>3072</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>2962</v>
+        <v>3073</v>
       </c>
       <c r="D69">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G69" t="s">
         <v>42</v>
@@ -13687,7 +13690,7 @@
         <v>0</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L69" s="1" t="s">
         <v>19</v>
@@ -13706,14 +13709,14 @@
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A70" t="s">
-        <v>23</v>
+      <c r="A70" s="6" t="s">
+        <v>2958</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>162</v>
+        <v>2962</v>
       </c>
       <c r="D70">
         <v>500</v>
@@ -13722,22 +13725,22 @@
         <v>19</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G70" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J70" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L70" s="1" t="s">
         <v>19</v>
@@ -13746,7 +13749,7 @@
         <v>19</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O70" s="1" t="s">
         <v>21</v>
@@ -13756,14 +13759,14 @@
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A71" s="6" t="s">
-        <v>116</v>
+      <c r="A71" t="s">
+        <v>23</v>
       </c>
       <c r="B71" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C71" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D71">
         <v>500</v>
@@ -13784,7 +13787,7 @@
         <v>0</v>
       </c>
       <c r="J71" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K71" s="1" t="s">
         <v>21</v>
@@ -13796,7 +13799,7 @@
         <v>19</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O71" s="1" t="s">
         <v>21</v>
@@ -13806,14 +13809,14 @@
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A72" t="s">
-        <v>38</v>
+      <c r="A72" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="B72" t="s">
-        <v>164</v>
+        <v>23</v>
       </c>
       <c r="C72" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D72">
         <v>500</v>
@@ -13834,7 +13837,7 @@
         <v>0</v>
       </c>
       <c r="J72" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" s="1" t="s">
         <v>21</v>
@@ -13846,7 +13849,7 @@
         <v>19</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O72" s="1" t="s">
         <v>21</v>
@@ -13857,13 +13860,13 @@
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" t="s">
         <v>164</v>
       </c>
-      <c r="B73" t="s">
-        <v>23</v>
-      </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D73">
         <v>500</v>
@@ -13906,14 +13909,14 @@
       </c>
     </row>
     <row r="74" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A74" s="6" t="s">
-        <v>167</v>
+      <c r="A74" t="s">
+        <v>164</v>
       </c>
       <c r="B74" t="s">
-        <v>168</v>
+        <v>23</v>
       </c>
       <c r="C74" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D74">
         <v>500</v>
@@ -13922,7 +13925,7 @@
         <v>19</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G74" t="s">
         <v>25</v>
@@ -13934,7 +13937,7 @@
         <v>0</v>
       </c>
       <c r="J74" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K74" s="1" t="s">
         <v>21</v>
@@ -13946,7 +13949,7 @@
         <v>19</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O74" s="1" t="s">
         <v>21</v>
@@ -13957,13 +13960,13 @@
     </row>
     <row r="75" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A75" s="6" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B75" t="s">
         <v>168</v>
       </c>
       <c r="C75" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D75">
         <v>500</v>
@@ -14006,14 +14009,14 @@
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A76" t="s">
+      <c r="A76" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B76" t="s">
         <v>168</v>
       </c>
-      <c r="B76" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>172</v>
+      <c r="C76" t="s">
+        <v>171</v>
       </c>
       <c r="D76">
         <v>500</v>
@@ -14056,14 +14059,14 @@
       </c>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A77" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B77" t="s">
-        <v>174</v>
-      </c>
-      <c r="C77" t="s">
-        <v>175</v>
+      <c r="A77" t="s">
+        <v>168</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="D77">
         <v>500</v>
@@ -14107,13 +14110,13 @@
     </row>
     <row r="78" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A78" s="6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B78" t="s">
         <v>174</v>
       </c>
       <c r="C78" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D78">
         <v>500</v>
@@ -14156,14 +14159,14 @@
       </c>
     </row>
     <row r="79" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A79" t="s">
+      <c r="A79" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B79" t="s">
         <v>174</v>
       </c>
-      <c r="B79" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>178</v>
+      <c r="C79" t="s">
+        <v>177</v>
       </c>
       <c r="D79">
         <v>500</v>
@@ -14206,14 +14209,14 @@
       </c>
     </row>
     <row r="80" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A80" s="6" t="s">
-        <v>3137</v>
+      <c r="A80" t="s">
+        <v>174</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>3152</v>
+        <v>178</v>
       </c>
       <c r="D80">
         <v>500</v>
@@ -14257,13 +14260,13 @@
     </row>
     <row r="81" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A81" s="6" t="s">
-        <v>3138</v>
+        <v>3137</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>23</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>3153</v>
+        <v>3152</v>
       </c>
       <c r="D81">
         <v>500</v>
@@ -14306,14 +14309,14 @@
       </c>
     </row>
     <row r="82" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A82" t="s">
-        <v>179</v>
-      </c>
-      <c r="B82" t="s">
-        <v>180</v>
-      </c>
-      <c r="C82" t="s">
-        <v>2801</v>
+      <c r="A82" s="6" t="s">
+        <v>3138</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>3153</v>
       </c>
       <c r="D82">
         <v>500</v>
@@ -14322,13 +14325,13 @@
         <v>19</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G82" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" s="7" t="b">
         <v>0</v>
@@ -14352,18 +14355,18 @@
         <v>21</v>
       </c>
       <c r="P82" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
-        <v>3102</v>
+        <v>179</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
-        <v>3103</v>
+        <v>2801</v>
       </c>
       <c r="D83">
         <v>500</v>
@@ -14406,29 +14409,29 @@
       </c>
     </row>
     <row r="84" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A84" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B84" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>184</v>
+      <c r="A84" t="s">
+        <v>3102</v>
+      </c>
+      <c r="B84" t="s">
+        <v>179</v>
+      </c>
+      <c r="C84" t="s">
+        <v>3103</v>
       </c>
       <c r="D84">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G84" t="s">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="H84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" s="7" t="b">
         <v>0</v>
@@ -14457,13 +14460,13 @@
     </row>
     <row r="85" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A85" s="6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="D85">
         <v>400</v>
@@ -14487,7 +14490,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L85" s="1" t="s">
         <v>19</v>
@@ -14499,21 +14502,21 @@
         <v>19</v>
       </c>
       <c r="O85" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P85" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="P85" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A86" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="B86" t="s">
-        <v>17</v>
-      </c>
-      <c r="C86" t="s">
-        <v>189</v>
+        <v>186</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>188</v>
       </c>
       <c r="D86">
         <v>400</v>
@@ -14522,7 +14525,7 @@
         <v>19</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G86" t="s">
         <v>185</v>
@@ -14537,7 +14540,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L86" s="1" t="s">
         <v>19</v>
@@ -14549,21 +14552,21 @@
         <v>19</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A87" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="B87" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="C87" s="6" t="s">
-        <v>191</v>
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>189</v>
       </c>
       <c r="D87">
         <v>400</v>
@@ -14572,7 +14575,7 @@
         <v>19</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G87" t="s">
         <v>185</v>
@@ -14607,13 +14610,13 @@
     </row>
     <row r="88" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A88" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>183</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>2857</v>
+        <v>191</v>
       </c>
       <c r="D88">
         <v>400</v>
@@ -14656,35 +14659,35 @@
       </c>
     </row>
     <row r="89" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A89" t="s">
-        <v>193</v>
-      </c>
-      <c r="B89" t="s">
-        <v>17</v>
-      </c>
-      <c r="C89" t="s">
-        <v>194</v>
+      <c r="A89" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>2857</v>
       </c>
       <c r="D89">
-        <v>500</v>
+        <v>400</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G89" t="s">
-        <v>114</v>
+        <v>185</v>
       </c>
       <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="I89" s="7" t="b">
         <v>0</v>
       </c>
-      <c r="I89" s="7" t="b">
-        <v>1</v>
-      </c>
       <c r="J89" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K89" s="1" t="s">
         <v>21</v>
@@ -14707,13 +14710,13 @@
     </row>
     <row r="90" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B90" t="s">
         <v>17</v>
       </c>
       <c r="C90" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D90">
         <v>500</v>
@@ -14725,16 +14728,16 @@
         <v>19</v>
       </c>
       <c r="G90" t="s">
-        <v>42</v>
+        <v>114</v>
       </c>
       <c r="H90">
         <v>0</v>
       </c>
       <c r="I90" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90" s="1" t="s">
         <v>21</v>
@@ -14756,14 +14759,14 @@
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A91" s="6" t="s">
-        <v>196</v>
+      <c r="A91" t="s">
+        <v>180</v>
       </c>
       <c r="B91" t="s">
         <v>17</v>
       </c>
       <c r="C91" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D91">
         <v>500</v>
@@ -14781,7 +14784,7 @@
         <v>0</v>
       </c>
       <c r="I91" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J91" s="7" t="b">
         <v>0</v>
@@ -14806,14 +14809,14 @@
       </c>
     </row>
     <row r="92" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A92" t="s">
-        <v>198</v>
+      <c r="A92" s="6" t="s">
+        <v>196</v>
       </c>
       <c r="B92" t="s">
         <v>17</v>
       </c>
       <c r="C92" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D92">
         <v>500</v>
@@ -14831,7 +14834,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J92" s="7" t="b">
         <v>0</v>
@@ -14857,34 +14860,34 @@
     </row>
     <row r="93" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B93" t="s">
         <v>17</v>
       </c>
       <c r="C93" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D93">
         <v>500</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G93" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="H93">
         <v>0</v>
       </c>
       <c r="I93" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J93" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K93" s="1" t="s">
         <v>21</v>
@@ -14906,32 +14909,32 @@
       </c>
     </row>
     <row r="94" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A94" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B94" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>204</v>
+      <c r="A94" t="s">
+        <v>200</v>
+      </c>
+      <c r="B94" t="s">
+        <v>17</v>
+      </c>
+      <c r="C94" t="s">
+        <v>201</v>
       </c>
       <c r="D94">
         <v>500</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G94" t="s">
-        <v>29</v>
+        <v>202</v>
       </c>
       <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94" s="7" t="b">
         <v>1</v>
-      </c>
-      <c r="I94" s="7" t="b">
-        <v>0</v>
       </c>
       <c r="J94" s="7" t="b">
         <v>1</v>
@@ -14956,35 +14959,35 @@
       </c>
     </row>
     <row r="95" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A95" t="s">
-        <v>134</v>
-      </c>
-      <c r="B95" t="s">
-        <v>17</v>
+      <c r="A95" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>27</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D95">
         <v>500</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G95" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="H95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I95" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J95" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K95" s="1" t="s">
         <v>21</v>
@@ -14993,13 +14996,13 @@
         <v>19</v>
       </c>
       <c r="M95" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N95" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P95" s="1" t="s">
         <v>19</v>
@@ -15007,113 +15010,113 @@
     </row>
     <row r="96" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
-        <v>2975</v>
-      </c>
-      <c r="B96" s="6" t="s">
-        <v>27</v>
+        <v>134</v>
+      </c>
+      <c r="B96" t="s">
+        <v>17</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>2976</v>
+        <v>205</v>
       </c>
       <c r="D96">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="G96" t="s">
-        <v>29</v>
+        <v>132</v>
       </c>
       <c r="H96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I96" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J96" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L96" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M96" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N96" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
-        <v>206</v>
-      </c>
-      <c r="B97" t="s">
-        <v>129</v>
-      </c>
-      <c r="C97" t="s">
-        <v>207</v>
+        <v>2975</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>2976</v>
       </c>
       <c r="D97">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G97" t="s">
-        <v>132</v>
+        <v>29</v>
       </c>
       <c r="H97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I97" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J97" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K97" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L97" s="1" t="s">
         <v>19</v>
       </c>
       <c r="M97" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N97" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P97" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B98" t="s">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="C98" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D98">
         <v>500</v>
@@ -15157,13 +15160,13 @@
     </row>
     <row r="99" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
-        <v>2964</v>
+        <v>208</v>
       </c>
       <c r="B99" t="s">
-        <v>17</v>
+        <v>206</v>
       </c>
       <c r="C99" t="s">
-        <v>2965</v>
+        <v>209</v>
       </c>
       <c r="D99">
         <v>500</v>
@@ -15175,10 +15178,10 @@
         <v>19</v>
       </c>
       <c r="G99" t="s">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I99" s="7" t="b">
         <v>0</v>
@@ -15193,27 +15196,27 @@
         <v>19</v>
       </c>
       <c r="M99" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N99" s="1" t="s">
         <v>19</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A100" s="6" t="s">
-        <v>210</v>
+      <c r="A100" t="s">
+        <v>2964</v>
       </c>
       <c r="B100" t="s">
-        <v>211</v>
+        <v>17</v>
       </c>
       <c r="C100" t="s">
-        <v>212</v>
+        <v>2965</v>
       </c>
       <c r="D100">
         <v>500</v>
@@ -15225,16 +15228,16 @@
         <v>19</v>
       </c>
       <c r="G100" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I100" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J100" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" s="1" t="s">
         <v>21</v>
@@ -15252,18 +15255,18 @@
         <v>21</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A101" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B101" t="s">
         <v>211</v>
       </c>
-      <c r="B101" t="s">
-        <v>17</v>
-      </c>
       <c r="C101" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D101">
         <v>500</v>
@@ -15307,16 +15310,16 @@
     </row>
     <row r="102" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A102" s="6" t="s">
-        <v>214</v>
-      </c>
-      <c r="B102" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>215</v>
+        <v>211</v>
+      </c>
+      <c r="B102" t="s">
+        <v>17</v>
+      </c>
+      <c r="C102" t="s">
+        <v>213</v>
       </c>
       <c r="D102">
-        <v>550</v>
+        <v>500</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>19</v>
@@ -15325,16 +15328,16 @@
         <v>19</v>
       </c>
       <c r="G102" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I102" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J102" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K102" s="1" t="s">
         <v>21</v>
@@ -15356,29 +15359,29 @@
       </c>
     </row>
     <row r="103" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A103" t="s">
-        <v>216</v>
-      </c>
-      <c r="B103" t="s">
-        <v>23</v>
-      </c>
-      <c r="C103" t="s">
-        <v>217</v>
+      <c r="A103" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>215</v>
       </c>
       <c r="D103">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G103" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="H103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I103" s="7" t="b">
         <v>0</v>
@@ -15396,24 +15399,24 @@
         <v>19</v>
       </c>
       <c r="N103" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O103" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
-        <v>31</v>
+        <v>216</v>
       </c>
       <c r="B104" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C104" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D104">
         <v>500</v>
@@ -15422,19 +15425,19 @@
         <v>19</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G104" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I104" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J104" s="7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K104" s="1" t="s">
         <v>21</v>
@@ -15446,24 +15449,24 @@
         <v>19</v>
       </c>
       <c r="N104" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O104" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A105" s="6" t="s">
-        <v>219</v>
+      <c r="A105" t="s">
+        <v>31</v>
       </c>
       <c r="B105" t="s">
         <v>17</v>
       </c>
       <c r="C105" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D105">
         <v>500</v>
@@ -15475,16 +15478,16 @@
         <v>19</v>
       </c>
       <c r="G105" t="s">
-        <v>185</v>
+        <v>33</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I105" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J105" s="7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K105" s="1" t="s">
         <v>21</v>
@@ -15506,14 +15509,14 @@
       </c>
     </row>
     <row r="106" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A106" t="s">
-        <v>221</v>
+      <c r="A106" s="6" t="s">
+        <v>219</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C106" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D106">
         <v>500</v>
@@ -15522,13 +15525,13 @@
         <v>19</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G106" t="s">
-        <v>25</v>
+        <v>185</v>
       </c>
       <c r="H106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I106" s="7" t="b">
         <v>0</v>
@@ -15546,24 +15549,24 @@
         <v>19</v>
       </c>
       <c r="N106" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="O106" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P106" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B107" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C107" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D107">
         <v>500</v>
@@ -15575,10 +15578,10 @@
         <v>21</v>
       </c>
       <c r="G107" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I107" s="7" t="b">
         <v>0</v>
@@ -15587,7 +15590,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L107" s="1" t="s">
         <v>19</v>
@@ -15596,24 +15599,24 @@
         <v>19</v>
       </c>
       <c r="N107" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O107" s="1" t="s">
         <v>21</v>
       </c>
       <c r="P107" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="B108" t="s">
         <v>17</v>
       </c>
       <c r="C108" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D108">
         <v>500</v>
@@ -15657,13 +15660,13 @@
     </row>
     <row r="109" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B109" t="s">
         <v>17</v>
       </c>
       <c r="C109" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D109">
         <v>500</v>
@@ -15707,13 +15710,13 @@
     </row>
     <row r="110" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B110" t="s">
         <v>17</v>
       </c>
       <c r="C110" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D110">
         <v>500</v>
@@ -15757,13 +15760,13 @@
     </row>
     <row r="111" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B111" t="s">
         <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D111">
         <v>500</v>
@@ -15807,13 +15810,13 @@
     </row>
     <row r="112" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B112" t="s">
         <v>17</v>
       </c>
       <c r="C112" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D112">
         <v>500</v>
@@ -15857,13 +15860,13 @@
     </row>
     <row r="113" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B113" t="s">
         <v>17</v>
       </c>
       <c r="C113" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D113">
         <v>500</v>
@@ -15905,15 +15908,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="114" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A114" s="6" t="s">
-        <v>237</v>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A114" t="s">
+        <v>235</v>
       </c>
       <c r="B114" t="s">
         <v>17</v>
       </c>
       <c r="C114" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D114">
         <v>500</v>
@@ -15922,7 +15925,7 @@
         <v>19</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G114" t="s">
         <v>42</v>
@@ -15937,7 +15940,7 @@
         <v>0</v>
       </c>
       <c r="K114" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L114" s="1" t="s">
         <v>19</v>
@@ -15955,15 +15958,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B115" t="s">
         <v>17</v>
       </c>
       <c r="C115" t="s">
-        <v>2804</v>
+        <v>238</v>
       </c>
       <c r="D115">
         <v>500</v>
@@ -16007,13 +16010,13 @@
     </row>
     <row r="116" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A116" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>242</v>
+        <v>239</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2804</v>
       </c>
       <c r="D116">
         <v>500</v>
@@ -16022,13 +16025,13 @@
         <v>19</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G116" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="H116">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I116" s="7" t="b">
         <v>0</v>
@@ -16052,33 +16055,33 @@
         <v>21</v>
       </c>
       <c r="P116" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A117" t="s">
-        <v>243</v>
-      </c>
-      <c r="B117" t="s">
-        <v>17</v>
-      </c>
-      <c r="C117" t="s">
-        <v>2855</v>
+      <c r="A117" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>242</v>
       </c>
       <c r="D117">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G117" t="s">
-        <v>244</v>
+        <v>25</v>
       </c>
       <c r="H117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I117" s="7" t="b">
         <v>0</v>
@@ -16087,10 +16090,10 @@
         <v>0</v>
       </c>
       <c r="K117" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L117" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="L117" s="1" t="s">
-        <v>21</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>19</v>
@@ -16099,24 +16102,24 @@
         <v>19</v>
       </c>
       <c r="O117" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="P117" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B118" t="s">
         <v>17</v>
       </c>
       <c r="C118" t="s">
-        <v>246</v>
+        <v>2855</v>
       </c>
       <c r="D118">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>19</v>
@@ -16157,16 +16160,16 @@
     </row>
     <row r="119" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B119" t="s">
         <v>17</v>
       </c>
       <c r="C119" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D119">
-        <v>550</v>
+        <v>700</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>19</v>
@@ -16187,7 +16190,7 @@
         <v>0</v>
       </c>
       <c r="K119" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L119" s="1" t="s">
         <v>21</v>
@@ -16207,16 +16210,16 @@
     </row>
     <row r="120" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B120" t="s">
         <v>17</v>
       </c>
       <c r="C120" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D120">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>19</v>
@@ -16237,7 +16240,7 @@
         <v>0</v>
       </c>
       <c r="K120" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L120" s="1" t="s">
         <v>21</v>
@@ -16257,16 +16260,16 @@
     </row>
     <row r="121" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B121" t="s">
         <v>17</v>
       </c>
       <c r="C121" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D121">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>19</v>
@@ -16287,7 +16290,7 @@
         <v>0</v>
       </c>
       <c r="K121" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L121" s="1" t="s">
         <v>21</v>
@@ -16307,16 +16310,16 @@
     </row>
     <row r="122" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B122" t="s">
         <v>17</v>
       </c>
       <c r="C122" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D122">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>19</v>
@@ -16337,7 +16340,7 @@
         <v>0</v>
       </c>
       <c r="K122" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L122" s="1" t="s">
         <v>21</v>
@@ -16357,16 +16360,16 @@
     </row>
     <row r="123" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
-        <v>2816</v>
+        <v>253</v>
       </c>
       <c r="B123" t="s">
         <v>17</v>
       </c>
       <c r="C123" t="s">
-        <v>2817</v>
+        <v>254</v>
       </c>
       <c r="D123">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>19</v>
@@ -16375,22 +16378,22 @@
         <v>19</v>
       </c>
       <c r="G123" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="H123">
         <v>0</v>
       </c>
-      <c r="I123" s="2" t="b">
+      <c r="I123" s="7" t="b">
         <v>0</v>
       </c>
       <c r="J123" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K123" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M123" s="1" t="s">
         <v>19</v>
@@ -16399,7 +16402,7 @@
         <v>19</v>
       </c>
       <c r="O123" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P123" s="1" t="s">
         <v>19</v>
@@ -16407,25 +16410,25 @@
     </row>
     <row r="124" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
-        <v>2846</v>
+        <v>2816</v>
       </c>
       <c r="B124" t="s">
         <v>17</v>
       </c>
       <c r="C124" t="s">
-        <v>2911</v>
+        <v>2817</v>
       </c>
       <c r="D124">
         <v>500</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G124" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="H124">
         <v>0</v>
@@ -16457,13 +16460,13 @@
     </row>
     <row r="125" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
-        <v>2910</v>
+        <v>2846</v>
       </c>
       <c r="B125" t="s">
         <v>17</v>
       </c>
       <c r="C125" t="s">
-        <v>2912</v>
+        <v>2911</v>
       </c>
       <c r="D125">
         <v>500</v>
@@ -16483,11 +16486,11 @@
       <c r="I125" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J125" s="2" t="b">
+      <c r="J125" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K125" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L125" s="1" t="s">
         <v>19</v>
@@ -16507,25 +16510,25 @@
     </row>
     <row r="126" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
-        <v>2917</v>
+        <v>2910</v>
       </c>
       <c r="B126" t="s">
         <v>17</v>
       </c>
       <c r="C126" t="s">
-        <v>3180</v>
+        <v>2912</v>
       </c>
       <c r="D126">
-        <v>650</v>
+        <v>500</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>19</v>
       </c>
       <c r="G126" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H126">
         <v>0</v>
@@ -16537,7 +16540,7 @@
         <v>0</v>
       </c>
       <c r="K126" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L126" s="1" t="s">
         <v>19</v>
@@ -16552,21 +16555,21 @@
         <v>21</v>
       </c>
       <c r="P126" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="127" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
-        <v>3006</v>
+        <v>2917</v>
       </c>
       <c r="B127" t="s">
         <v>17</v>
       </c>
       <c r="C127" t="s">
-        <v>3035</v>
+        <v>3180</v>
       </c>
       <c r="D127">
-        <v>500</v>
+        <v>650</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>19</v>
@@ -16575,7 +16578,7 @@
         <v>19</v>
       </c>
       <c r="G127" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="H127">
         <v>0</v>
@@ -16607,19 +16610,19 @@
     </row>
     <row r="128" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
-        <v>3174</v>
+        <v>3006</v>
       </c>
       <c r="B128" t="s">
         <v>17</v>
       </c>
       <c r="C128" t="s">
-        <v>3175</v>
+        <v>3035</v>
       </c>
       <c r="D128">
         <v>500</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>19</v>
@@ -16633,7 +16636,7 @@
       <c r="I128" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J128" s="7" t="b">
+      <c r="J128" s="2" t="b">
         <v>0</v>
       </c>
       <c r="K128" s="1" t="s">
@@ -16657,19 +16660,19 @@
     </row>
     <row r="129" spans="1:16" x14ac:dyDescent="0.15">
       <c r="A129" t="s">
-        <v>3182</v>
+        <v>3174</v>
       </c>
       <c r="B129" t="s">
         <v>17</v>
       </c>
       <c r="C129" t="s">
-        <v>3181</v>
+        <v>3175</v>
       </c>
       <c r="D129">
         <v>500</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>19</v>
@@ -16683,7 +16686,7 @@
       <c r="I129" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="J129" s="2" t="b">
+      <c r="J129" s="7" t="b">
         <v>0</v>
       </c>
       <c r="K129" s="1" t="s">
@@ -16705,25 +16708,75 @@
         <v>21</v>
       </c>
     </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A130" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B130" t="s">
+        <v>17</v>
+      </c>
+      <c r="C130" t="s">
+        <v>3181</v>
+      </c>
+      <c r="D130">
+        <v>500</v>
+      </c>
+      <c r="E130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G130" t="s">
+        <v>42</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J130" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K130" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N130" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O130" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P130" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="J123:P124">
+  <conditionalFormatting sqref="J124:P125">
     <cfRule type="containsText" dxfId="8" priority="3" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",J123)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",J124)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:P52 I2:J52 E1:F122 I53:P122">
+  <conditionalFormatting sqref="I2:J53 E1:F123 I54:P123 K1:P53">
     <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M125:P125">
+  <conditionalFormatting sqref="M126:P126">
     <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",M125)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",M126)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J128:P128">
+  <conditionalFormatting sqref="J129:P129">
     <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",J128)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TRUE",J129)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F9226D-46E2-1745-A4AD-503CC05A3B49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB61181-1117-4A49-A24E-F6F7B4FAA7A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7280" yWindow="7440" windowWidth="29540" windowHeight="20300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7280" yWindow="7440" windowWidth="29540" windowHeight="20300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -9768,19 +9768,19 @@
     <t>att_cellculture_media</t>
   </si>
   <si>
-    <t>10% FBS added to the cell culture media.</t>
-  </si>
-  <si>
-    <t>No FBS used in the cell culture</t>
-  </si>
-  <si>
-    <t>Serum Starvation.</t>
-  </si>
-  <si>
-    <t>Normal' growth</t>
-  </si>
-  <si>
     <t>Cell culture conditions</t>
+  </si>
+  <si>
+    <t>Fetal bovine serum (FBS) is derived from the blood drawn from a bovine fetus via a closed system of collection at the slaughterhouse. Fetal bovine serum is the most widely used serum-supplement for the in vitro cell culture of eukaryotic cells. This is due to it having a very low level of antibodies and containing more growth factors, allowing for versatility in many different cell culture applications.</t>
+  </si>
+  <si>
+    <t>No FB serum has been added to the cell culture media.</t>
+  </si>
+  <si>
+    <t>FBS</t>
+  </si>
+  <si>
+    <t>No-FBS</t>
   </si>
 </sst>
 </file>
@@ -9791,7 +9791,7 @@
     <numFmt numFmtId="164" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -9869,6 +9869,14 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -9893,8 +9901,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -9960,11 +9969,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
@@ -17930,7 +17938,7 @@
         <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>3244</v>
+        <v>3240</v>
       </c>
       <c r="D135">
         <v>500</v>
@@ -17994,7 +18002,7 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",M129)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J127:P128 R2:R135">
+  <conditionalFormatting sqref="R2:R135 J127:P128">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J2)))</formula>
     </cfRule>
@@ -42924,10 +42932,10 @@
         <v>17</v>
       </c>
       <c r="E993" s="8" t="s">
-        <v>3240</v>
+        <v>3243</v>
       </c>
       <c r="F993" s="27" t="s">
-        <v>3243</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="994" spans="1:6" ht="16" x14ac:dyDescent="0.2">
@@ -42945,7 +42953,7 @@
         <v>17</v>
       </c>
       <c r="E994" s="8" t="s">
-        <v>3241</v>
+        <v>3244</v>
       </c>
       <c r="F994" s="8" t="s">
         <v>3242</v>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71BC0F64-A472-9D45-A0E9-0FCF77DF56BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309DA4F4-E53B-C041-BFB3-A24F596E16C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7280" yWindow="7440" windowWidth="29540" windowHeight="20300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7280" yWindow="7440" windowWidth="29540" windowHeight="20300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
-    <sheet name="attribute_values" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="7" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="6" r:id="rId4"/>
-    <sheet name="attribute_values_ar" sheetId="3" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId6"/>
-    <sheet name="STATES" sheetId="5" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId2"/>
+    <sheet name="attribute_values" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId5"/>
+    <sheet name="attribute_values_ar" sheetId="3" r:id="rId6"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId7"/>
+    <sheet name="STATES" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">attribute_values_ar!$A$1:$O$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">attribute_values_ar!$A$1:$O$365</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11100" uniqueCount="3254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11113" uniqueCount="3254">
   <si>
     <t>tag</t>
   </si>
@@ -10002,7 +10003,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="10">
     <dxf>
       <font>
         <color rgb="FFCC0000"/>
@@ -10022,6 +10023,20 @@
       <font>
         <color rgb="FFCC0000"/>
       </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC5E0B4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC5E0B4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -15663,13 +15678,13 @@
     </row>
     <row r="94" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A94" s="6" t="s">
-        <v>3191</v>
+        <v>192</v>
       </c>
       <c r="B94" t="s">
         <v>17</v>
       </c>
       <c r="C94" t="s">
-        <v>3190</v>
+        <v>193</v>
       </c>
       <c r="D94">
         <v>500</v>
@@ -18015,22 +18030,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="J132:P132">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J132)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:P1 E1:F126 I2:P126">
-    <cfRule type="containsText" dxfId="6" priority="6" operator="containsText" text="TRUE">
+  <conditionalFormatting sqref="K1:P1 I2:P126 E1:F126">
+    <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M129:P129">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",M129)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R135 J127:P128">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="TRUE">
+  <conditionalFormatting sqref="J127:P128 R2:R135">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J2)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18040,6 +18055,82 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3C9494-E4C4-B94F-80B4-F8F47233E318}">
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A1" s="6" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3190</v>
+      </c>
+      <c r="D1">
+        <v>500</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1">
+        <v>0</v>
+      </c>
+      <c r="I1" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J1" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="b">
+        <v>0</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E1:F1 I1:P1">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",R1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AMJ1093"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -43353,7 +43444,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39F04B9C-C859-AA4A-82A0-0191B0A5431A}">
   <dimension ref="A2:AMH6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -48548,7 +48639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74A045B7-985B-284A-BEE4-821C1E6602B3}">
   <dimension ref="A1:AMH8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -56854,7 +56945,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:AMJ569"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -79144,7 +79235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
@@ -79608,7 +79699,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{309DA4F4-E53B-C041-BFB3-A24F596E16C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE98EFEB-FA17-9F46-A638-131616B24636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7280" yWindow="7440" windowWidth="29540" windowHeight="20300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10580" yWindow="3940" windowWidth="29540" windowHeight="20300" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11113" uniqueCount="3254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11143" uniqueCount="3254">
   <si>
     <t>tag</t>
   </si>
@@ -43085,7 +43085,7 @@
         <v>3223</v>
       </c>
       <c r="C995" s="8" t="str">
-        <f t="shared" ref="C995:C997" si="47">B995&amp;":"&amp;A995</f>
+        <f t="shared" ref="C995:C1003" si="47">B995&amp;":"&amp;A995</f>
         <v>att_enrich_frac:wash</v>
       </c>
       <c r="D995" s="8" t="s">
@@ -43140,23 +43140,131 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="998" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B998" s="25"/>
-    </row>
-    <row r="999" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B999" s="25"/>
-    </row>
-    <row r="1000" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1000" s="25"/>
-    </row>
-    <row r="1001" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1001" s="25"/>
-    </row>
-    <row r="1002" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1002" s="25"/>
-    </row>
-    <row r="1003" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1003" s="24"/>
+    <row r="998" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A998" s="8" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B998" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C998" s="8" t="str">
+        <f t="shared" si="47"/>
+        <v>att_organism:UP000000589</v>
+      </c>
+      <c r="D998" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="E998" s="8" t="s">
+        <v>2188</v>
+      </c>
+      <c r="F998" s="8" t="s">
+        <v>2189</v>
+      </c>
+    </row>
+    <row r="999" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A999" s="8" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B999" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C999" s="8" t="str">
+        <f t="shared" si="47"/>
+        <v>att_organism:UP000001940</v>
+      </c>
+      <c r="D999" s="8" t="s">
+        <v>2191</v>
+      </c>
+      <c r="E999" s="8" t="s">
+        <v>2192</v>
+      </c>
+      <c r="F999" s="8" t="s">
+        <v>2193</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1000" s="8" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1000" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1000" s="8" t="str">
+        <f t="shared" si="47"/>
+        <v>att_organism:UP000002311</v>
+      </c>
+      <c r="D1000" s="8" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E1000" s="8" t="s">
+        <v>2196</v>
+      </c>
+      <c r="F1000" s="8" t="s">
+        <v>2197</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1001" s="8" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1001" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1001" s="8" t="str">
+        <f t="shared" si="47"/>
+        <v>att_organism:UP000002494</v>
+      </c>
+      <c r="D1001" s="8" t="s">
+        <v>2199</v>
+      </c>
+      <c r="E1001" s="8" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F1001" s="8" t="s">
+        <v>2201</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1002" s="8" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1002" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1002" s="8" t="str">
+        <f t="shared" si="47"/>
+        <v>att_organism:UP000005640</v>
+      </c>
+      <c r="D1002" s="8" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E1002" s="8" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F1002" s="8" t="s">
+        <v>2205</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1003" s="8" t="s">
+        <v>2907</v>
+      </c>
+      <c r="B1003" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C1003" s="8" t="str">
+        <f t="shared" si="47"/>
+        <v>att_organism:controls</v>
+      </c>
+      <c r="D1003" s="8" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E1003" s="8" t="s">
+        <v>2905</v>
+      </c>
+      <c r="F1003" s="8" t="s">
+        <v>2906</v>
+      </c>
     </row>
     <row r="1004" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B1004" s="24"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE98EFEB-FA17-9F46-A638-131616B24636}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09518947-7AB1-5443-95DD-61BBA0D37FE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10580" yWindow="3940" windowWidth="29540" windowHeight="20300" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11143" uniqueCount="3254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11138" uniqueCount="3254">
   <si>
     <t>tag</t>
   </si>
@@ -18034,7 +18034,7 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",J132)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:P1 I2:P126 E1:F126">
+  <conditionalFormatting sqref="K1:P1 E1:F126 I2:P126">
     <cfRule type="containsText" dxfId="8" priority="6" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
@@ -18044,7 +18044,7 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",M129)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J127:P128 R2:R135">
+  <conditionalFormatting sqref="R2:R135 J127:P128">
     <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J2)))</formula>
     </cfRule>
@@ -18132,7 +18132,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ1093"/>
+  <dimension ref="A1:AMJ1082"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -35792,926 +35792,1942 @@
     </row>
     <row r="793" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A793" s="8" t="s">
-        <v>2907</v>
+        <v>2206</v>
       </c>
       <c r="B793" s="8" t="s">
-        <v>192</v>
+        <v>2207</v>
       </c>
       <c r="C793" s="8" t="str">
-        <f t="shared" ref="C793:C824" si="35">B793&amp;":"&amp;A793</f>
-        <v>att_organism:controls</v>
-      </c>
-      <c r="D793" s="8" t="s">
-        <v>2904</v>
+        <f t="shared" ref="C793:C823" si="35">B793&amp;":"&amp;A793</f>
+        <v>att_organsystem:cardiovascular</v>
+      </c>
+      <c r="D793" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="E793" s="8" t="s">
-        <v>2905</v>
+        <v>2208</v>
       </c>
       <c r="F793" s="8" t="s">
-        <v>2906</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="794" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A794" s="8" t="s">
-        <v>2206</v>
+        <v>2210</v>
       </c>
       <c r="B794" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C794" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:cardiovascular</v>
+        <v>att_organsystem:digestive</v>
       </c>
       <c r="D794" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E794" s="8" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
       <c r="F794" s="8" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="795" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A795" s="8" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="B795" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C795" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:digestive</v>
+        <v>att_organsystem:endocrine</v>
       </c>
       <c r="D795" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E795" s="8" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="F795" s="8" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="796" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A796" s="8" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="B796" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C796" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:endocrine</v>
+        <v>att_organsystem:excretory</v>
       </c>
       <c r="D796" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E796" s="8" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="F796" s="8" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="797" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A797" s="8" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="B797" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C797" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:excretory</v>
+        <v>att_organsystem:integumentary</v>
       </c>
       <c r="D797" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E797" s="8" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F797" s="8" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="798" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A798" s="8" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="B798" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C798" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:integumentary</v>
+        <v>att_organsystem:lymphatic</v>
       </c>
       <c r="D798" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E798" s="8" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F798" s="8" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="799" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A799" s="8" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="B799" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C799" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:lymphatic</v>
+        <v>att_organsystem:muscular</v>
       </c>
       <c r="D799" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E799" s="8" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F799" s="8" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="800" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A800" s="8" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="B800" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C800" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:muscular</v>
+        <v>att_organsystem:nervous_system</v>
       </c>
       <c r="D800" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E800" s="8" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="F800" s="8" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="801" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A801" s="8" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="B801" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C801" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:nervous_system</v>
+        <v>att_organsystem:reproductive</v>
       </c>
       <c r="D801" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E801" s="8" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="F801" s="8" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="802" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A802" s="8" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="B802" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C802" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:reproductive</v>
+        <v>att_organsystem:respiratory</v>
       </c>
       <c r="D802" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E802" s="8" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="F802" s="8" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="803" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A803" s="8" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="B803" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C803" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:respiratory</v>
+        <v>att_organsystem:skeletal</v>
       </c>
       <c r="D803" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E803" s="8" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="F803" s="8" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="804" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A804" s="8" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="B804" s="8" t="s">
         <v>2207</v>
       </c>
       <c r="C804" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:skeletal</v>
+        <v>att_organsystem:urinary</v>
       </c>
       <c r="D804" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E804" s="8" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="F804" s="8" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="805" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A805" s="8" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="B805" s="8" t="s">
-        <v>2207</v>
+        <v>194</v>
       </c>
       <c r="C805" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_organsystem:urinary</v>
+        <v>att_phystraining:intervalcardio</v>
       </c>
       <c r="D805" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E805" s="8" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="F805" s="8" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="806" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A806" s="8" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
       <c r="B806" s="8" t="s">
         <v>194</v>
       </c>
       <c r="C806" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_phystraining:intervalcardio</v>
+        <v>att_phystraining:steadycardio</v>
       </c>
       <c r="D806" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E806" s="8" t="s">
-        <v>2244</v>
+        <v>2823</v>
       </c>
       <c r="F806" s="8" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="807" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A807" s="8" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="B807" s="8" t="s">
         <v>194</v>
       </c>
       <c r="C807" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_phystraining:steadycardio</v>
+        <v>att_phystraining:strength</v>
       </c>
       <c r="D807" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E807" s="8" t="s">
-        <v>2823</v>
+        <v>2249</v>
       </c>
       <c r="F807" s="8" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="808" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A808" s="8" t="s">
-        <v>2248</v>
+        <v>2824</v>
       </c>
       <c r="B808" s="8" t="s">
         <v>194</v>
       </c>
       <c r="C808" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_phystraining:strength</v>
+        <v>att_phystraining:hiit</v>
       </c>
       <c r="D808" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E808" s="8" t="s">
-        <v>2249</v>
+        <v>2825</v>
       </c>
       <c r="F808" s="8" t="s">
-        <v>2250</v>
+        <v>2826</v>
       </c>
     </row>
     <row r="809" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A809" s="8" t="s">
-        <v>2824</v>
+        <v>2251</v>
       </c>
       <c r="B809" s="8" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="C809" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_phystraining:hiit</v>
+        <v>att_protease:argc</v>
       </c>
       <c r="D809" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E809" s="8" t="s">
-        <v>2825</v>
+        <v>2252</v>
       </c>
       <c r="F809" s="8" t="s">
-        <v>2826</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="810" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A810" s="8" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="B810" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C810" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:argc</v>
+        <v>att_protease:aspn</v>
       </c>
       <c r="D810" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E810" s="8" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="F810" s="8" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="811" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A811" s="8" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="B811" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C811" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:aspn</v>
+        <v>att_protease:chymotrypsin</v>
       </c>
       <c r="D811" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E811" s="8" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
       <c r="F811" s="8" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="812" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A812" s="8" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="B812" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C812" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:chymotrypsin</v>
+        <v>att_protease:elastase</v>
       </c>
       <c r="D812" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E812" s="8" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
       <c r="F812" s="8" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="813" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A813" s="8" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="B813" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C813" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:elastase</v>
+        <v>att_protease:gluc</v>
       </c>
       <c r="D813" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E813" s="8" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="F813" s="8" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="814" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A814" s="8" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="B814" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C814" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:gluc</v>
+        <v>att_protease:lysc</v>
       </c>
       <c r="D814" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E814" s="8" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
       <c r="F814" s="8" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="815" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A815" s="8" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="B815" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C815" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:lysc</v>
+        <v>att_protease:raspn</v>
       </c>
       <c r="D815" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E815" s="8" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="F815" s="8" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="816" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A816" s="8" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="B816" s="8" t="s">
         <v>199</v>
       </c>
       <c r="C816" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:raspn</v>
+        <v>att_protease:trypsin</v>
       </c>
       <c r="D816" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E816" s="8" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="F816" s="8" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="817" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A817" s="8" t="s">
-        <v>2272</v>
+        <v>2827</v>
       </c>
       <c r="B817" s="8" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="C817" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protease:trypsin</v>
+        <v>att_protein_mutation:apex</v>
       </c>
       <c r="D817" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E817" s="8" t="s">
-        <v>2273</v>
+        <v>2828</v>
       </c>
       <c r="F817" s="8" t="s">
-        <v>2274</v>
+        <v>2829</v>
       </c>
     </row>
     <row r="818" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A818" s="8" t="s">
-        <v>2827</v>
+        <v>2830</v>
       </c>
       <c r="B818" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C818" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protein_mutation:apex</v>
+        <v>att_protein_mutation:bioid</v>
       </c>
       <c r="D818" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E818" s="8" t="s">
-        <v>2828</v>
+        <v>2831</v>
       </c>
       <c r="F818" s="8" t="s">
-        <v>2829</v>
+        <v>2832</v>
       </c>
     </row>
     <row r="819" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A819" s="8" t="s">
-        <v>2830</v>
+        <v>2833</v>
       </c>
       <c r="B819" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C819" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protein_mutation:bioid</v>
+        <v>att_protein_mutation:turboid</v>
       </c>
       <c r="D819" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E819" s="8" t="s">
-        <v>2831</v>
+        <v>2834</v>
       </c>
       <c r="F819" s="8" t="s">
-        <v>2832</v>
+        <v>2835</v>
       </c>
     </row>
     <row r="820" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A820" s="8" t="s">
-        <v>2833</v>
+        <v>1264</v>
       </c>
       <c r="B820" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C820" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protein_mutation:turboid</v>
+        <v>att_protein_mutation:deletion</v>
       </c>
       <c r="D820" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E820" s="8" t="s">
-        <v>2834</v>
+        <v>2275</v>
       </c>
       <c r="F820" s="8" t="s">
-        <v>2835</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="821" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A821" s="8" t="s">
-        <v>1264</v>
+        <v>2277</v>
       </c>
       <c r="B821" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C821" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protein_mutation:deletion</v>
+        <v>att_protein_mutation:flag</v>
       </c>
       <c r="D821" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E821" s="8" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="F821" s="8" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="822" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A822" s="8" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="B822" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C822" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protein_mutation:flag</v>
+        <v>att_protein_mutation:frameshift</v>
       </c>
       <c r="D822" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E822" s="8" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="F822" s="8" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="823" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A823" s="8" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="B823" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C823" s="8" t="str">
         <f t="shared" si="35"/>
-        <v>att_protein_mutation:frameshift</v>
+        <v>att_protein_mutation:gfp</v>
       </c>
       <c r="D823" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E823" s="8" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="F823" s="8" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="824" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A824" s="8" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="B824" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C824" s="8" t="str">
-        <f t="shared" si="35"/>
-        <v>att_protein_mutation:gfp</v>
+        <f t="shared" ref="C824:C829" si="36">B824&amp;":"&amp;A824</f>
+        <v>att_protein_mutation:ha</v>
       </c>
       <c r="D824" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E824" s="8" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="F824" s="8" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="825" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A825" s="8" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="B825" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C825" s="8" t="str">
-        <f t="shared" ref="C825:C830" si="36">B825&amp;":"&amp;A825</f>
-        <v>att_protein_mutation:ha</v>
+        <f t="shared" si="36"/>
+        <v>att_protein_mutation:his</v>
       </c>
       <c r="D825" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E825" s="8" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="F825" s="8" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="826" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A826" s="8" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="B826" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C826" s="8" t="str">
         <f t="shared" si="36"/>
-        <v>att_protein_mutation:his</v>
+        <v>att_protein_mutation:insertion</v>
       </c>
       <c r="D826" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E826" s="8" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="F826" s="8" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="827" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A827" s="8" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="B827" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C827" s="8" t="str">
         <f t="shared" si="36"/>
-        <v>att_protein_mutation:insertion</v>
+        <v>att_protein_mutation:myc</v>
       </c>
       <c r="D827" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E827" s="8" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="F827" s="8" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="828" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A828" s="8" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="B828" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C828" s="8" t="str">
         <f t="shared" si="36"/>
-        <v>att_protein_mutation:myc</v>
+        <v>att_protein_mutation:pep86</v>
       </c>
       <c r="D828" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E828" s="8" t="s">
-        <v>2296</v>
+        <v>2799</v>
       </c>
       <c r="F828" s="8" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="829" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A829" s="8" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="B829" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C829" s="8" t="str">
         <f t="shared" si="36"/>
-        <v>att_protein_mutation:pep86</v>
+        <v>att_protein_mutation:substitution</v>
       </c>
       <c r="D829" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E829" s="8" t="s">
-        <v>2799</v>
+        <v>2301</v>
       </c>
       <c r="F829" s="8" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="830" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A830" s="8" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="B830" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C830" s="8" t="str">
-        <f t="shared" si="36"/>
-        <v>att_protein_mutation:substitution</v>
+        <f t="shared" ref="C830" si="37">B830&amp;":"&amp;A830</f>
+        <v>att_protein_mutation:truncation</v>
       </c>
       <c r="D830" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E830" s="8" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="F830" s="8" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="831" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A831" s="8" t="s">
-        <v>2303</v>
+        <v>336</v>
       </c>
       <c r="B831" s="8" t="s">
         <v>202</v>
       </c>
       <c r="C831" s="8" t="str">
-        <f t="shared" ref="C831" si="37">B831&amp;":"&amp;A831</f>
-        <v>att_protein_mutation:truncation</v>
+        <f t="shared" ref="C831:C860" si="38">B831&amp;":"&amp;A831</f>
+        <v>att_protein_mutation:none</v>
       </c>
       <c r="D831" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E831" s="8" t="s">
-        <v>2304</v>
+        <v>1862</v>
       </c>
       <c r="F831" s="8" t="s">
-        <v>2305</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="832" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A832" s="8" t="s">
-        <v>336</v>
+        <v>2306</v>
       </c>
       <c r="B832" s="8" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C832" s="8" t="str">
-        <f t="shared" ref="C832:C861" si="38">B832&amp;":"&amp;A832</f>
-        <v>att_protein_mutation:none</v>
+        <f t="shared" si="38"/>
+        <v>att_protein_position:aa</v>
       </c>
       <c r="D832" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E832" s="8" t="s">
-        <v>1862</v>
+        <v>2307</v>
       </c>
       <c r="F832" s="8" t="s">
-        <v>2800</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="833" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A833" s="8" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="B833" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C833" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_protein_position:aa</v>
+        <v>att_protein_position:cterm</v>
       </c>
       <c r="D833" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E833" s="8" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
       <c r="F833" s="8" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="834" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A834" s="8" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="B834" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C834" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_protein_position:cterm</v>
+        <v>att_protein_position:nterm</v>
       </c>
       <c r="D834" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E834" s="8" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="F834" s="8" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="835" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A835" s="8" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="B835" s="8" t="s">
         <v>204</v>
       </c>
       <c r="C835" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_protein_position:nterm</v>
+        <v>att_protein_position:region</v>
       </c>
       <c r="D835" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E835" s="8" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="F835" s="8" t="s">
-        <v>2314</v>
-      </c>
+        <v>2317</v>
+      </c>
+      <c r="G835"/>
+      <c r="H835"/>
+      <c r="I835"/>
+      <c r="J835"/>
+      <c r="K835"/>
+      <c r="L835"/>
+      <c r="M835"/>
+      <c r="N835"/>
+      <c r="O835"/>
+      <c r="P835"/>
+      <c r="Q835"/>
+      <c r="R835"/>
+      <c r="S835"/>
+      <c r="T835"/>
+      <c r="U835"/>
+      <c r="V835"/>
+      <c r="W835"/>
+      <c r="X835"/>
+      <c r="Y835"/>
+      <c r="Z835"/>
+      <c r="AA835"/>
+      <c r="AB835"/>
+      <c r="AC835"/>
+      <c r="AD835"/>
+      <c r="AE835"/>
+      <c r="AF835"/>
+      <c r="AG835"/>
+      <c r="AH835"/>
+      <c r="AI835"/>
+      <c r="AJ835"/>
+      <c r="AK835"/>
+      <c r="AL835"/>
+      <c r="AM835"/>
+      <c r="AN835"/>
+      <c r="AO835"/>
+      <c r="AP835"/>
+      <c r="AQ835"/>
+      <c r="AR835"/>
+      <c r="AS835"/>
+      <c r="AT835"/>
+      <c r="AU835"/>
+      <c r="AV835"/>
+      <c r="AW835"/>
+      <c r="AX835"/>
+      <c r="AY835"/>
+      <c r="AZ835"/>
+      <c r="BA835"/>
+      <c r="BB835"/>
+      <c r="BC835"/>
+      <c r="BD835"/>
+      <c r="BE835"/>
+      <c r="BF835"/>
+      <c r="BG835"/>
+      <c r="BH835"/>
+      <c r="BI835"/>
+      <c r="BJ835"/>
+      <c r="BK835"/>
+      <c r="BL835"/>
+      <c r="BM835"/>
+      <c r="BN835"/>
+      <c r="BO835"/>
+      <c r="BP835"/>
+      <c r="BQ835"/>
+      <c r="BR835"/>
+      <c r="BS835"/>
+      <c r="BT835"/>
+      <c r="BU835"/>
+      <c r="BV835"/>
+      <c r="BW835"/>
+      <c r="BX835"/>
+      <c r="BY835"/>
+      <c r="BZ835"/>
+      <c r="CA835"/>
+      <c r="CB835"/>
+      <c r="CC835"/>
+      <c r="CD835"/>
+      <c r="CE835"/>
+      <c r="CF835"/>
+      <c r="CG835"/>
+      <c r="CH835"/>
+      <c r="CI835"/>
+      <c r="CJ835"/>
+      <c r="CK835"/>
+      <c r="CL835"/>
+      <c r="CM835"/>
+      <c r="CN835"/>
+      <c r="CO835"/>
+      <c r="CP835"/>
+      <c r="CQ835"/>
+      <c r="CR835"/>
+      <c r="CS835"/>
+      <c r="CT835"/>
+      <c r="CU835"/>
+      <c r="CV835"/>
+      <c r="CW835"/>
+      <c r="CX835"/>
+      <c r="CY835"/>
+      <c r="CZ835"/>
+      <c r="DA835"/>
+      <c r="DB835"/>
+      <c r="DC835"/>
+      <c r="DD835"/>
+      <c r="DE835"/>
+      <c r="DF835"/>
+      <c r="DG835"/>
+      <c r="DH835"/>
+      <c r="DI835"/>
+      <c r="DJ835"/>
+      <c r="DK835"/>
+      <c r="DL835"/>
+      <c r="DM835"/>
+      <c r="DN835"/>
+      <c r="DO835"/>
+      <c r="DP835"/>
+      <c r="DQ835"/>
+      <c r="DR835"/>
+      <c r="DS835"/>
+      <c r="DT835"/>
+      <c r="DU835"/>
+      <c r="DV835"/>
+      <c r="DW835"/>
+      <c r="DX835"/>
+      <c r="DY835"/>
+      <c r="DZ835"/>
+      <c r="EA835"/>
+      <c r="EB835"/>
+      <c r="EC835"/>
+      <c r="ED835"/>
+      <c r="EE835"/>
+      <c r="EF835"/>
+      <c r="EG835"/>
+      <c r="EH835"/>
+      <c r="EI835"/>
+      <c r="EJ835"/>
+      <c r="EK835"/>
+      <c r="EL835"/>
+      <c r="EM835"/>
+      <c r="EN835"/>
+      <c r="EO835"/>
+      <c r="EP835"/>
+      <c r="EQ835"/>
+      <c r="ER835"/>
+      <c r="ES835"/>
+      <c r="ET835"/>
+      <c r="EU835"/>
+      <c r="EV835"/>
+      <c r="EW835"/>
+      <c r="EX835"/>
+      <c r="EY835"/>
+      <c r="EZ835"/>
+      <c r="FA835"/>
+      <c r="FB835"/>
+      <c r="FC835"/>
+      <c r="FD835"/>
+      <c r="FE835"/>
+      <c r="FF835"/>
+      <c r="FG835"/>
+      <c r="FH835"/>
+      <c r="FI835"/>
+      <c r="FJ835"/>
+      <c r="FK835"/>
+      <c r="FL835"/>
+      <c r="FM835"/>
+      <c r="FN835"/>
+      <c r="FO835"/>
+      <c r="FP835"/>
+      <c r="FQ835"/>
+      <c r="FR835"/>
+      <c r="FS835"/>
+      <c r="FT835"/>
+      <c r="FU835"/>
+      <c r="FV835"/>
+      <c r="FW835"/>
+      <c r="FX835"/>
+      <c r="FY835"/>
+      <c r="FZ835"/>
+      <c r="GA835"/>
+      <c r="GB835"/>
+      <c r="GC835"/>
+      <c r="GD835"/>
+      <c r="GE835"/>
+      <c r="GF835"/>
+      <c r="GG835"/>
+      <c r="GH835"/>
+      <c r="GI835"/>
+      <c r="GJ835"/>
+      <c r="GK835"/>
+      <c r="GL835"/>
+      <c r="GM835"/>
+      <c r="GN835"/>
+      <c r="GO835"/>
+      <c r="GP835"/>
+      <c r="GQ835"/>
+      <c r="GR835"/>
+      <c r="GS835"/>
+      <c r="GT835"/>
+      <c r="GU835"/>
+      <c r="GV835"/>
+      <c r="GW835"/>
+      <c r="GX835"/>
+      <c r="GY835"/>
+      <c r="GZ835"/>
+      <c r="HA835"/>
+      <c r="HB835"/>
+      <c r="HC835"/>
+      <c r="HD835"/>
+      <c r="HE835"/>
+      <c r="HF835"/>
+      <c r="HG835"/>
+      <c r="HH835"/>
+      <c r="HI835"/>
+      <c r="HJ835"/>
+      <c r="HK835"/>
+      <c r="HL835"/>
+      <c r="HM835"/>
+      <c r="HN835"/>
+      <c r="HO835"/>
+      <c r="HP835"/>
+      <c r="HQ835"/>
+      <c r="HR835"/>
+      <c r="HS835"/>
+      <c r="HT835"/>
+      <c r="HU835"/>
+      <c r="HV835"/>
+      <c r="HW835"/>
+      <c r="HX835"/>
+      <c r="HY835"/>
+      <c r="HZ835"/>
+      <c r="IA835"/>
+      <c r="IB835"/>
+      <c r="IC835"/>
+      <c r="ID835"/>
+      <c r="IE835"/>
+      <c r="IF835"/>
+      <c r="IG835"/>
+      <c r="IH835"/>
+      <c r="II835"/>
+      <c r="IJ835"/>
+      <c r="IK835"/>
+      <c r="IL835"/>
+      <c r="IM835"/>
+      <c r="IN835"/>
+      <c r="IO835"/>
+      <c r="IP835"/>
+      <c r="IQ835"/>
+      <c r="IR835"/>
+      <c r="IS835"/>
+      <c r="IT835"/>
+      <c r="IU835"/>
+      <c r="IV835"/>
+      <c r="IW835"/>
+      <c r="IX835"/>
+      <c r="IY835"/>
+      <c r="IZ835"/>
+      <c r="JA835"/>
+      <c r="JB835"/>
+      <c r="JC835"/>
+      <c r="JD835"/>
+      <c r="JE835"/>
+      <c r="JF835"/>
+      <c r="JG835"/>
+      <c r="JH835"/>
+      <c r="JI835"/>
+      <c r="JJ835"/>
+      <c r="JK835"/>
+      <c r="JL835"/>
+      <c r="JM835"/>
+      <c r="JN835"/>
+      <c r="JO835"/>
+      <c r="JP835"/>
+      <c r="JQ835"/>
+      <c r="JR835"/>
+      <c r="JS835"/>
+      <c r="JT835"/>
+      <c r="JU835"/>
+      <c r="JV835"/>
+      <c r="JW835"/>
+      <c r="JX835"/>
+      <c r="JY835"/>
+      <c r="JZ835"/>
+      <c r="KA835"/>
+      <c r="KB835"/>
+      <c r="KC835"/>
+      <c r="KD835"/>
+      <c r="KE835"/>
+      <c r="KF835"/>
+      <c r="KG835"/>
+      <c r="KH835"/>
+      <c r="KI835"/>
+      <c r="KJ835"/>
+      <c r="KK835"/>
+      <c r="KL835"/>
+      <c r="KM835"/>
+      <c r="KN835"/>
+      <c r="KO835"/>
+      <c r="KP835"/>
+      <c r="KQ835"/>
+      <c r="KR835"/>
+      <c r="KS835"/>
+      <c r="KT835"/>
+      <c r="KU835"/>
+      <c r="KV835"/>
+      <c r="KW835"/>
+      <c r="KX835"/>
+      <c r="KY835"/>
+      <c r="KZ835"/>
+      <c r="LA835"/>
+      <c r="LB835"/>
+      <c r="LC835"/>
+      <c r="LD835"/>
+      <c r="LE835"/>
+      <c r="LF835"/>
+      <c r="LG835"/>
+      <c r="LH835"/>
+      <c r="LI835"/>
+      <c r="LJ835"/>
+      <c r="LK835"/>
+      <c r="LL835"/>
+      <c r="LM835"/>
+      <c r="LN835"/>
+      <c r="LO835"/>
+      <c r="LP835"/>
+      <c r="LQ835"/>
+      <c r="LR835"/>
+      <c r="LS835"/>
+      <c r="LT835"/>
+      <c r="LU835"/>
+      <c r="LV835"/>
+      <c r="LW835"/>
+      <c r="LX835"/>
+      <c r="LY835"/>
+      <c r="LZ835"/>
+      <c r="MA835"/>
+      <c r="MB835"/>
+      <c r="MC835"/>
+      <c r="MD835"/>
+      <c r="ME835"/>
+      <c r="MF835"/>
+      <c r="MG835"/>
+      <c r="MH835"/>
+      <c r="MI835"/>
+      <c r="MJ835"/>
+      <c r="MK835"/>
+      <c r="ML835"/>
+      <c r="MM835"/>
+      <c r="MN835"/>
+      <c r="MO835"/>
+      <c r="MP835"/>
+      <c r="MQ835"/>
+      <c r="MR835"/>
+      <c r="MS835"/>
+      <c r="MT835"/>
+      <c r="MU835"/>
+      <c r="MV835"/>
+      <c r="MW835"/>
+      <c r="MX835"/>
+      <c r="MY835"/>
+      <c r="MZ835"/>
+      <c r="NA835"/>
+      <c r="NB835"/>
+      <c r="NC835"/>
+      <c r="ND835"/>
+      <c r="NE835"/>
+      <c r="NF835"/>
+      <c r="NG835"/>
+      <c r="NH835"/>
+      <c r="NI835"/>
+      <c r="NJ835"/>
+      <c r="NK835"/>
+      <c r="NL835"/>
+      <c r="NM835"/>
+      <c r="NN835"/>
+      <c r="NO835"/>
+      <c r="NP835"/>
+      <c r="NQ835"/>
+      <c r="NR835"/>
+      <c r="NS835"/>
+      <c r="NT835"/>
+      <c r="NU835"/>
+      <c r="NV835"/>
+      <c r="NW835"/>
+      <c r="NX835"/>
+      <c r="NY835"/>
+      <c r="NZ835"/>
+      <c r="OA835"/>
+      <c r="OB835"/>
+      <c r="OC835"/>
+      <c r="OD835"/>
+      <c r="OE835"/>
+      <c r="OF835"/>
+      <c r="OG835"/>
+      <c r="OH835"/>
+      <c r="OI835"/>
+      <c r="OJ835"/>
+      <c r="OK835"/>
+      <c r="OL835"/>
+      <c r="OM835"/>
+      <c r="ON835"/>
+      <c r="OO835"/>
+      <c r="OP835"/>
+      <c r="OQ835"/>
+      <c r="OR835"/>
+      <c r="OS835"/>
+      <c r="OT835"/>
+      <c r="OU835"/>
+      <c r="OV835"/>
+      <c r="OW835"/>
+      <c r="OX835"/>
+      <c r="OY835"/>
+      <c r="OZ835"/>
+      <c r="PA835"/>
+      <c r="PB835"/>
+      <c r="PC835"/>
+      <c r="PD835"/>
+      <c r="PE835"/>
+      <c r="PF835"/>
+      <c r="PG835"/>
+      <c r="PH835"/>
+      <c r="PI835"/>
+      <c r="PJ835"/>
+      <c r="PK835"/>
+      <c r="PL835"/>
+      <c r="PM835"/>
+      <c r="PN835"/>
+      <c r="PO835"/>
+      <c r="PP835"/>
+      <c r="PQ835"/>
+      <c r="PR835"/>
+      <c r="PS835"/>
+      <c r="PT835"/>
+      <c r="PU835"/>
+      <c r="PV835"/>
+      <c r="PW835"/>
+      <c r="PX835"/>
+      <c r="PY835"/>
+      <c r="PZ835"/>
+      <c r="QA835"/>
+      <c r="QB835"/>
+      <c r="QC835"/>
+      <c r="QD835"/>
+      <c r="QE835"/>
+      <c r="QF835"/>
+      <c r="QG835"/>
+      <c r="QH835"/>
+      <c r="QI835"/>
+      <c r="QJ835"/>
+      <c r="QK835"/>
+      <c r="QL835"/>
+      <c r="QM835"/>
+      <c r="QN835"/>
+      <c r="QO835"/>
+      <c r="QP835"/>
+      <c r="QQ835"/>
+      <c r="QR835"/>
+      <c r="QS835"/>
+      <c r="QT835"/>
+      <c r="QU835"/>
+      <c r="QV835"/>
+      <c r="QW835"/>
+      <c r="QX835"/>
+      <c r="QY835"/>
+      <c r="QZ835"/>
+      <c r="RA835"/>
+      <c r="RB835"/>
+      <c r="RC835"/>
+      <c r="RD835"/>
+      <c r="RE835"/>
+      <c r="RF835"/>
+      <c r="RG835"/>
+      <c r="RH835"/>
+      <c r="RI835"/>
+      <c r="RJ835"/>
+      <c r="RK835"/>
+      <c r="RL835"/>
+      <c r="RM835"/>
+      <c r="RN835"/>
+      <c r="RO835"/>
+      <c r="RP835"/>
+      <c r="RQ835"/>
+      <c r="RR835"/>
+      <c r="RS835"/>
+      <c r="RT835"/>
+      <c r="RU835"/>
+      <c r="RV835"/>
+      <c r="RW835"/>
+      <c r="RX835"/>
+      <c r="RY835"/>
+      <c r="RZ835"/>
+      <c r="SA835"/>
+      <c r="SB835"/>
+      <c r="SC835"/>
+      <c r="SD835"/>
+      <c r="SE835"/>
+      <c r="SF835"/>
+      <c r="SG835"/>
+      <c r="SH835"/>
+      <c r="SI835"/>
+      <c r="SJ835"/>
+      <c r="SK835"/>
+      <c r="SL835"/>
+      <c r="SM835"/>
+      <c r="SN835"/>
+      <c r="SO835"/>
+      <c r="SP835"/>
+      <c r="SQ835"/>
+      <c r="SR835"/>
+      <c r="SS835"/>
+      <c r="ST835"/>
+      <c r="SU835"/>
+      <c r="SV835"/>
+      <c r="SW835"/>
+      <c r="SX835"/>
+      <c r="SY835"/>
+      <c r="SZ835"/>
+      <c r="TA835"/>
+      <c r="TB835"/>
+      <c r="TC835"/>
+      <c r="TD835"/>
+      <c r="TE835"/>
+      <c r="TF835"/>
+      <c r="TG835"/>
+      <c r="TH835"/>
+      <c r="TI835"/>
+      <c r="TJ835"/>
+      <c r="TK835"/>
+      <c r="TL835"/>
+      <c r="TM835"/>
+      <c r="TN835"/>
+      <c r="TO835"/>
+      <c r="TP835"/>
+      <c r="TQ835"/>
+      <c r="TR835"/>
+      <c r="TS835"/>
+      <c r="TT835"/>
+      <c r="TU835"/>
+      <c r="TV835"/>
+      <c r="TW835"/>
+      <c r="TX835"/>
+      <c r="TY835"/>
+      <c r="TZ835"/>
+      <c r="UA835"/>
+      <c r="UB835"/>
+      <c r="UC835"/>
+      <c r="UD835"/>
+      <c r="UE835"/>
+      <c r="UF835"/>
+      <c r="UG835"/>
+      <c r="UH835"/>
+      <c r="UI835"/>
+      <c r="UJ835"/>
+      <c r="UK835"/>
+      <c r="UL835"/>
+      <c r="UM835"/>
+      <c r="UN835"/>
+      <c r="UO835"/>
+      <c r="UP835"/>
+      <c r="UQ835"/>
+      <c r="UR835"/>
+      <c r="US835"/>
+      <c r="UT835"/>
+      <c r="UU835"/>
+      <c r="UV835"/>
+      <c r="UW835"/>
+      <c r="UX835"/>
+      <c r="UY835"/>
+      <c r="UZ835"/>
+      <c r="VA835"/>
+      <c r="VB835"/>
+      <c r="VC835"/>
+      <c r="VD835"/>
+      <c r="VE835"/>
+      <c r="VF835"/>
+      <c r="VG835"/>
+      <c r="VH835"/>
+      <c r="VI835"/>
+      <c r="VJ835"/>
+      <c r="VK835"/>
+      <c r="VL835"/>
+      <c r="VM835"/>
+      <c r="VN835"/>
+      <c r="VO835"/>
+      <c r="VP835"/>
+      <c r="VQ835"/>
+      <c r="VR835"/>
+      <c r="VS835"/>
+      <c r="VT835"/>
+      <c r="VU835"/>
+      <c r="VV835"/>
+      <c r="VW835"/>
+      <c r="VX835"/>
+      <c r="VY835"/>
+      <c r="VZ835"/>
+      <c r="WA835"/>
+      <c r="WB835"/>
+      <c r="WC835"/>
+      <c r="WD835"/>
+      <c r="WE835"/>
+      <c r="WF835"/>
+      <c r="WG835"/>
+      <c r="WH835"/>
+      <c r="WI835"/>
+      <c r="WJ835"/>
+      <c r="WK835"/>
+      <c r="WL835"/>
+      <c r="WM835"/>
+      <c r="WN835"/>
+      <c r="WO835"/>
+      <c r="WP835"/>
+      <c r="WQ835"/>
+      <c r="WR835"/>
+      <c r="WS835"/>
+      <c r="WT835"/>
+      <c r="WU835"/>
+      <c r="WV835"/>
+      <c r="WW835"/>
+      <c r="WX835"/>
+      <c r="WY835"/>
+      <c r="WZ835"/>
+      <c r="XA835"/>
+      <c r="XB835"/>
+      <c r="XC835"/>
+      <c r="XD835"/>
+      <c r="XE835"/>
+      <c r="XF835"/>
+      <c r="XG835"/>
+      <c r="XH835"/>
+      <c r="XI835"/>
+      <c r="XJ835"/>
+      <c r="XK835"/>
+      <c r="XL835"/>
+      <c r="XM835"/>
+      <c r="XN835"/>
+      <c r="XO835"/>
+      <c r="XP835"/>
+      <c r="XQ835"/>
+      <c r="XR835"/>
+      <c r="XS835"/>
+      <c r="XT835"/>
+      <c r="XU835"/>
+      <c r="XV835"/>
+      <c r="XW835"/>
+      <c r="XX835"/>
+      <c r="XY835"/>
+      <c r="XZ835"/>
+      <c r="YA835"/>
+      <c r="YB835"/>
+      <c r="YC835"/>
+      <c r="YD835"/>
+      <c r="YE835"/>
+      <c r="YF835"/>
+      <c r="YG835"/>
+      <c r="YH835"/>
+      <c r="YI835"/>
+      <c r="YJ835"/>
+      <c r="YK835"/>
+      <c r="YL835"/>
+      <c r="YM835"/>
+      <c r="YN835"/>
+      <c r="YO835"/>
+      <c r="YP835"/>
+      <c r="YQ835"/>
+      <c r="YR835"/>
+      <c r="YS835"/>
+      <c r="YT835"/>
+      <c r="YU835"/>
+      <c r="YV835"/>
+      <c r="YW835"/>
+      <c r="YX835"/>
+      <c r="YY835"/>
+      <c r="YZ835"/>
+      <c r="ZA835"/>
+      <c r="ZB835"/>
+      <c r="ZC835"/>
+      <c r="ZD835"/>
+      <c r="ZE835"/>
+      <c r="ZF835"/>
+      <c r="ZG835"/>
+      <c r="ZH835"/>
+      <c r="ZI835"/>
+      <c r="ZJ835"/>
+      <c r="ZK835"/>
+      <c r="ZL835"/>
+      <c r="ZM835"/>
+      <c r="ZN835"/>
+      <c r="ZO835"/>
+      <c r="ZP835"/>
+      <c r="ZQ835"/>
+      <c r="ZR835"/>
+      <c r="ZS835"/>
+      <c r="ZT835"/>
+      <c r="ZU835"/>
+      <c r="ZV835"/>
+      <c r="ZW835"/>
+      <c r="ZX835"/>
+      <c r="ZY835"/>
+      <c r="ZZ835"/>
+      <c r="AAA835"/>
+      <c r="AAB835"/>
+      <c r="AAC835"/>
+      <c r="AAD835"/>
+      <c r="AAE835"/>
+      <c r="AAF835"/>
+      <c r="AAG835"/>
+      <c r="AAH835"/>
+      <c r="AAI835"/>
+      <c r="AAJ835"/>
+      <c r="AAK835"/>
+      <c r="AAL835"/>
+      <c r="AAM835"/>
+      <c r="AAN835"/>
+      <c r="AAO835"/>
+      <c r="AAP835"/>
+      <c r="AAQ835"/>
+      <c r="AAR835"/>
+      <c r="AAS835"/>
+      <c r="AAT835"/>
+      <c r="AAU835"/>
+      <c r="AAV835"/>
+      <c r="AAW835"/>
+      <c r="AAX835"/>
+      <c r="AAY835"/>
+      <c r="AAZ835"/>
+      <c r="ABA835"/>
+      <c r="ABB835"/>
+      <c r="ABC835"/>
+      <c r="ABD835"/>
+      <c r="ABE835"/>
+      <c r="ABF835"/>
+      <c r="ABG835"/>
+      <c r="ABH835"/>
+      <c r="ABI835"/>
+      <c r="ABJ835"/>
+      <c r="ABK835"/>
+      <c r="ABL835"/>
+      <c r="ABM835"/>
+      <c r="ABN835"/>
+      <c r="ABO835"/>
+      <c r="ABP835"/>
+      <c r="ABQ835"/>
+      <c r="ABR835"/>
+      <c r="ABS835"/>
+      <c r="ABT835"/>
+      <c r="ABU835"/>
+      <c r="ABV835"/>
+      <c r="ABW835"/>
+      <c r="ABX835"/>
+      <c r="ABY835"/>
+      <c r="ABZ835"/>
+      <c r="ACA835"/>
+      <c r="ACB835"/>
+      <c r="ACC835"/>
+      <c r="ACD835"/>
+      <c r="ACE835"/>
+      <c r="ACF835"/>
+      <c r="ACG835"/>
+      <c r="ACH835"/>
+      <c r="ACI835"/>
+      <c r="ACJ835"/>
+      <c r="ACK835"/>
+      <c r="ACL835"/>
+      <c r="ACM835"/>
+      <c r="ACN835"/>
+      <c r="ACO835"/>
+      <c r="ACP835"/>
+      <c r="ACQ835"/>
+      <c r="ACR835"/>
+      <c r="ACS835"/>
+      <c r="ACT835"/>
+      <c r="ACU835"/>
+      <c r="ACV835"/>
+      <c r="ACW835"/>
+      <c r="ACX835"/>
+      <c r="ACY835"/>
+      <c r="ACZ835"/>
+      <c r="ADA835"/>
+      <c r="ADB835"/>
+      <c r="ADC835"/>
+      <c r="ADD835"/>
+      <c r="ADE835"/>
+      <c r="ADF835"/>
+      <c r="ADG835"/>
+      <c r="ADH835"/>
+      <c r="ADI835"/>
+      <c r="ADJ835"/>
+      <c r="ADK835"/>
+      <c r="ADL835"/>
+      <c r="ADM835"/>
+      <c r="ADN835"/>
+      <c r="ADO835"/>
+      <c r="ADP835"/>
+      <c r="ADQ835"/>
+      <c r="ADR835"/>
+      <c r="ADS835"/>
+      <c r="ADT835"/>
+      <c r="ADU835"/>
+      <c r="ADV835"/>
+      <c r="ADW835"/>
+      <c r="ADX835"/>
+      <c r="ADY835"/>
+      <c r="ADZ835"/>
+      <c r="AEA835"/>
+      <c r="AEB835"/>
+      <c r="AEC835"/>
+      <c r="AED835"/>
+      <c r="AEE835"/>
+      <c r="AEF835"/>
+      <c r="AEG835"/>
+      <c r="AEH835"/>
+      <c r="AEI835"/>
+      <c r="AEJ835"/>
+      <c r="AEK835"/>
+      <c r="AEL835"/>
+      <c r="AEM835"/>
+      <c r="AEN835"/>
+      <c r="AEO835"/>
+      <c r="AEP835"/>
+      <c r="AEQ835"/>
+      <c r="AER835"/>
+      <c r="AES835"/>
+      <c r="AET835"/>
+      <c r="AEU835"/>
+      <c r="AEV835"/>
+      <c r="AEW835"/>
+      <c r="AEX835"/>
+      <c r="AEY835"/>
+      <c r="AEZ835"/>
+      <c r="AFA835"/>
+      <c r="AFB835"/>
+      <c r="AFC835"/>
+      <c r="AFD835"/>
+      <c r="AFE835"/>
+      <c r="AFF835"/>
+      <c r="AFG835"/>
+      <c r="AFH835"/>
+      <c r="AFI835"/>
+      <c r="AFJ835"/>
+      <c r="AFK835"/>
+      <c r="AFL835"/>
+      <c r="AFM835"/>
+      <c r="AFN835"/>
+      <c r="AFO835"/>
+      <c r="AFP835"/>
+      <c r="AFQ835"/>
+      <c r="AFR835"/>
+      <c r="AFS835"/>
+      <c r="AFT835"/>
+      <c r="AFU835"/>
+      <c r="AFV835"/>
+      <c r="AFW835"/>
+      <c r="AFX835"/>
+      <c r="AFY835"/>
+      <c r="AFZ835"/>
+      <c r="AGA835"/>
+      <c r="AGB835"/>
+      <c r="AGC835"/>
+      <c r="AGD835"/>
+      <c r="AGE835"/>
+      <c r="AGF835"/>
+      <c r="AGG835"/>
+      <c r="AGH835"/>
+      <c r="AGI835"/>
+      <c r="AGJ835"/>
+      <c r="AGK835"/>
+      <c r="AGL835"/>
+      <c r="AGM835"/>
+      <c r="AGN835"/>
+      <c r="AGO835"/>
+      <c r="AGP835"/>
+      <c r="AGQ835"/>
+      <c r="AGR835"/>
+      <c r="AGS835"/>
+      <c r="AGT835"/>
+      <c r="AGU835"/>
+      <c r="AGV835"/>
+      <c r="AGW835"/>
+      <c r="AGX835"/>
+      <c r="AGY835"/>
+      <c r="AGZ835"/>
+      <c r="AHA835"/>
+      <c r="AHB835"/>
+      <c r="AHC835"/>
+      <c r="AHD835"/>
+      <c r="AHE835"/>
+      <c r="AHF835"/>
+      <c r="AHG835"/>
+      <c r="AHH835"/>
+      <c r="AHI835"/>
+      <c r="AHJ835"/>
+      <c r="AHK835"/>
+      <c r="AHL835"/>
+      <c r="AHM835"/>
+      <c r="AHN835"/>
+      <c r="AHO835"/>
+      <c r="AHP835"/>
+      <c r="AHQ835"/>
+      <c r="AHR835"/>
+      <c r="AHS835"/>
+      <c r="AHT835"/>
+      <c r="AHU835"/>
+      <c r="AHV835"/>
+      <c r="AHW835"/>
+      <c r="AHX835"/>
+      <c r="AHY835"/>
+      <c r="AHZ835"/>
+      <c r="AIA835"/>
+      <c r="AIB835"/>
+      <c r="AIC835"/>
+      <c r="AID835"/>
+      <c r="AIE835"/>
+      <c r="AIF835"/>
+      <c r="AIG835"/>
+      <c r="AIH835"/>
+      <c r="AII835"/>
+      <c r="AIJ835"/>
+      <c r="AIK835"/>
+      <c r="AIL835"/>
+      <c r="AIM835"/>
+      <c r="AIN835"/>
+      <c r="AIO835"/>
+      <c r="AIP835"/>
+      <c r="AIQ835"/>
+      <c r="AIR835"/>
+      <c r="AIS835"/>
+      <c r="AIT835"/>
+      <c r="AIU835"/>
+      <c r="AIV835"/>
+      <c r="AIW835"/>
+      <c r="AIX835"/>
+      <c r="AIY835"/>
+      <c r="AIZ835"/>
+      <c r="AJA835"/>
+      <c r="AJB835"/>
+      <c r="AJC835"/>
+      <c r="AJD835"/>
+      <c r="AJE835"/>
+      <c r="AJF835"/>
+      <c r="AJG835"/>
+      <c r="AJH835"/>
+      <c r="AJI835"/>
+      <c r="AJJ835"/>
+      <c r="AJK835"/>
+      <c r="AJL835"/>
+      <c r="AJM835"/>
+      <c r="AJN835"/>
+      <c r="AJO835"/>
+      <c r="AJP835"/>
+      <c r="AJQ835"/>
+      <c r="AJR835"/>
+      <c r="AJS835"/>
+      <c r="AJT835"/>
+      <c r="AJU835"/>
+      <c r="AJV835"/>
+      <c r="AJW835"/>
+      <c r="AJX835"/>
+      <c r="AJY835"/>
+      <c r="AJZ835"/>
+      <c r="AKA835"/>
+      <c r="AKB835"/>
+      <c r="AKC835"/>
+      <c r="AKD835"/>
+      <c r="AKE835"/>
+      <c r="AKF835"/>
+      <c r="AKG835"/>
+      <c r="AKH835"/>
+      <c r="AKI835"/>
+      <c r="AKJ835"/>
+      <c r="AKK835"/>
+      <c r="AKL835"/>
+      <c r="AKM835"/>
+      <c r="AKN835"/>
+      <c r="AKO835"/>
+      <c r="AKP835"/>
+      <c r="AKQ835"/>
+      <c r="AKR835"/>
+      <c r="AKS835"/>
+      <c r="AKT835"/>
+      <c r="AKU835"/>
+      <c r="AKV835"/>
+      <c r="AKW835"/>
+      <c r="AKX835"/>
+      <c r="AKY835"/>
+      <c r="AKZ835"/>
+      <c r="ALA835"/>
+      <c r="ALB835"/>
+      <c r="ALC835"/>
+      <c r="ALD835"/>
+      <c r="ALE835"/>
+      <c r="ALF835"/>
+      <c r="ALG835"/>
+      <c r="ALH835"/>
+      <c r="ALI835"/>
+      <c r="ALJ835"/>
+      <c r="ALK835"/>
+      <c r="ALL835"/>
+      <c r="ALM835"/>
+      <c r="ALN835"/>
+      <c r="ALO835"/>
+      <c r="ALP835"/>
+      <c r="ALQ835"/>
+      <c r="ALR835"/>
+      <c r="ALS835"/>
+      <c r="ALT835"/>
+      <c r="ALU835"/>
+      <c r="ALV835"/>
+      <c r="ALW835"/>
+      <c r="ALX835"/>
+      <c r="ALY835"/>
+      <c r="ALZ835"/>
+      <c r="AMA835"/>
+      <c r="AMB835"/>
+      <c r="AMC835"/>
+      <c r="AMD835"/>
+      <c r="AME835"/>
+      <c r="AMF835"/>
+      <c r="AMG835"/>
+      <c r="AMH835"/>
     </row>
     <row r="836" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A836" s="8" t="s">
-        <v>2315</v>
+        <v>2957</v>
       </c>
       <c r="B836" s="8" t="s">
-        <v>204</v>
+        <v>2955</v>
       </c>
       <c r="C836" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_protein_position:region</v>
+        <v>att_ptm_enrichment:antibody</v>
       </c>
       <c r="D836" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E836" s="8" t="s">
-        <v>2316</v>
+        <v>2958</v>
       </c>
       <c r="F836" s="8" t="s">
-        <v>2317</v>
+        <v>2959</v>
       </c>
       <c r="G836"/>
       <c r="H836"/>
@@ -37732,23 +38748,23 @@
     </row>
     <row r="837" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A837" s="8" t="s">
-        <v>2957</v>
+        <v>2960</v>
       </c>
       <c r="B837" s="8" t="s">
         <v>2955</v>
       </c>
       <c r="C837" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_ptm_enrichment:antibody</v>
+        <v>att_ptm_enrichment:metal</v>
       </c>
       <c r="D837" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E837" s="8" t="s">
-        <v>2958</v>
+        <v>2961</v>
       </c>
       <c r="F837" s="8" t="s">
-        <v>2959</v>
+        <v>2962</v>
       </c>
       <c r="G837"/>
       <c r="H837"/>
@@ -38769,1078 +39785,62 @@
     </row>
     <row r="838" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A838" s="8" t="s">
-        <v>2960</v>
+        <v>2965</v>
       </c>
       <c r="B838" s="8" t="s">
         <v>2955</v>
       </c>
       <c r="C838" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_ptm_enrichment:metal</v>
+        <v>att_ptm_enrichment:ionchromatography</v>
       </c>
       <c r="D838" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E838" s="8" t="s">
-        <v>2961</v>
+        <v>2963</v>
       </c>
       <c r="F838" s="8" t="s">
-        <v>2962</v>
-      </c>
-      <c r="G838"/>
-      <c r="H838"/>
-      <c r="I838"/>
-      <c r="J838"/>
-      <c r="K838"/>
-      <c r="L838"/>
-      <c r="M838"/>
-      <c r="N838"/>
-      <c r="O838"/>
-      <c r="P838"/>
-      <c r="Q838"/>
-      <c r="R838"/>
-      <c r="S838"/>
-      <c r="T838"/>
-      <c r="U838"/>
-      <c r="V838"/>
-      <c r="W838"/>
-      <c r="X838"/>
-      <c r="Y838"/>
-      <c r="Z838"/>
-      <c r="AA838"/>
-      <c r="AB838"/>
-      <c r="AC838"/>
-      <c r="AD838"/>
-      <c r="AE838"/>
-      <c r="AF838"/>
-      <c r="AG838"/>
-      <c r="AH838"/>
-      <c r="AI838"/>
-      <c r="AJ838"/>
-      <c r="AK838"/>
-      <c r="AL838"/>
-      <c r="AM838"/>
-      <c r="AN838"/>
-      <c r="AO838"/>
-      <c r="AP838"/>
-      <c r="AQ838"/>
-      <c r="AR838"/>
-      <c r="AS838"/>
-      <c r="AT838"/>
-      <c r="AU838"/>
-      <c r="AV838"/>
-      <c r="AW838"/>
-      <c r="AX838"/>
-      <c r="AY838"/>
-      <c r="AZ838"/>
-      <c r="BA838"/>
-      <c r="BB838"/>
-      <c r="BC838"/>
-      <c r="BD838"/>
-      <c r="BE838"/>
-      <c r="BF838"/>
-      <c r="BG838"/>
-      <c r="BH838"/>
-      <c r="BI838"/>
-      <c r="BJ838"/>
-      <c r="BK838"/>
-      <c r="BL838"/>
-      <c r="BM838"/>
-      <c r="BN838"/>
-      <c r="BO838"/>
-      <c r="BP838"/>
-      <c r="BQ838"/>
-      <c r="BR838"/>
-      <c r="BS838"/>
-      <c r="BT838"/>
-      <c r="BU838"/>
-      <c r="BV838"/>
-      <c r="BW838"/>
-      <c r="BX838"/>
-      <c r="BY838"/>
-      <c r="BZ838"/>
-      <c r="CA838"/>
-      <c r="CB838"/>
-      <c r="CC838"/>
-      <c r="CD838"/>
-      <c r="CE838"/>
-      <c r="CF838"/>
-      <c r="CG838"/>
-      <c r="CH838"/>
-      <c r="CI838"/>
-      <c r="CJ838"/>
-      <c r="CK838"/>
-      <c r="CL838"/>
-      <c r="CM838"/>
-      <c r="CN838"/>
-      <c r="CO838"/>
-      <c r="CP838"/>
-      <c r="CQ838"/>
-      <c r="CR838"/>
-      <c r="CS838"/>
-      <c r="CT838"/>
-      <c r="CU838"/>
-      <c r="CV838"/>
-      <c r="CW838"/>
-      <c r="CX838"/>
-      <c r="CY838"/>
-      <c r="CZ838"/>
-      <c r="DA838"/>
-      <c r="DB838"/>
-      <c r="DC838"/>
-      <c r="DD838"/>
-      <c r="DE838"/>
-      <c r="DF838"/>
-      <c r="DG838"/>
-      <c r="DH838"/>
-      <c r="DI838"/>
-      <c r="DJ838"/>
-      <c r="DK838"/>
-      <c r="DL838"/>
-      <c r="DM838"/>
-      <c r="DN838"/>
-      <c r="DO838"/>
-      <c r="DP838"/>
-      <c r="DQ838"/>
-      <c r="DR838"/>
-      <c r="DS838"/>
-      <c r="DT838"/>
-      <c r="DU838"/>
-      <c r="DV838"/>
-      <c r="DW838"/>
-      <c r="DX838"/>
-      <c r="DY838"/>
-      <c r="DZ838"/>
-      <c r="EA838"/>
-      <c r="EB838"/>
-      <c r="EC838"/>
-      <c r="ED838"/>
-      <c r="EE838"/>
-      <c r="EF838"/>
-      <c r="EG838"/>
-      <c r="EH838"/>
-      <c r="EI838"/>
-      <c r="EJ838"/>
-      <c r="EK838"/>
-      <c r="EL838"/>
-      <c r="EM838"/>
-      <c r="EN838"/>
-      <c r="EO838"/>
-      <c r="EP838"/>
-      <c r="EQ838"/>
-      <c r="ER838"/>
-      <c r="ES838"/>
-      <c r="ET838"/>
-      <c r="EU838"/>
-      <c r="EV838"/>
-      <c r="EW838"/>
-      <c r="EX838"/>
-      <c r="EY838"/>
-      <c r="EZ838"/>
-      <c r="FA838"/>
-      <c r="FB838"/>
-      <c r="FC838"/>
-      <c r="FD838"/>
-      <c r="FE838"/>
-      <c r="FF838"/>
-      <c r="FG838"/>
-      <c r="FH838"/>
-      <c r="FI838"/>
-      <c r="FJ838"/>
-      <c r="FK838"/>
-      <c r="FL838"/>
-      <c r="FM838"/>
-      <c r="FN838"/>
-      <c r="FO838"/>
-      <c r="FP838"/>
-      <c r="FQ838"/>
-      <c r="FR838"/>
-      <c r="FS838"/>
-      <c r="FT838"/>
-      <c r="FU838"/>
-      <c r="FV838"/>
-      <c r="FW838"/>
-      <c r="FX838"/>
-      <c r="FY838"/>
-      <c r="FZ838"/>
-      <c r="GA838"/>
-      <c r="GB838"/>
-      <c r="GC838"/>
-      <c r="GD838"/>
-      <c r="GE838"/>
-      <c r="GF838"/>
-      <c r="GG838"/>
-      <c r="GH838"/>
-      <c r="GI838"/>
-      <c r="GJ838"/>
-      <c r="GK838"/>
-      <c r="GL838"/>
-      <c r="GM838"/>
-      <c r="GN838"/>
-      <c r="GO838"/>
-      <c r="GP838"/>
-      <c r="GQ838"/>
-      <c r="GR838"/>
-      <c r="GS838"/>
-      <c r="GT838"/>
-      <c r="GU838"/>
-      <c r="GV838"/>
-      <c r="GW838"/>
-      <c r="GX838"/>
-      <c r="GY838"/>
-      <c r="GZ838"/>
-      <c r="HA838"/>
-      <c r="HB838"/>
-      <c r="HC838"/>
-      <c r="HD838"/>
-      <c r="HE838"/>
-      <c r="HF838"/>
-      <c r="HG838"/>
-      <c r="HH838"/>
-      <c r="HI838"/>
-      <c r="HJ838"/>
-      <c r="HK838"/>
-      <c r="HL838"/>
-      <c r="HM838"/>
-      <c r="HN838"/>
-      <c r="HO838"/>
-      <c r="HP838"/>
-      <c r="HQ838"/>
-      <c r="HR838"/>
-      <c r="HS838"/>
-      <c r="HT838"/>
-      <c r="HU838"/>
-      <c r="HV838"/>
-      <c r="HW838"/>
-      <c r="HX838"/>
-      <c r="HY838"/>
-      <c r="HZ838"/>
-      <c r="IA838"/>
-      <c r="IB838"/>
-      <c r="IC838"/>
-      <c r="ID838"/>
-      <c r="IE838"/>
-      <c r="IF838"/>
-      <c r="IG838"/>
-      <c r="IH838"/>
-      <c r="II838"/>
-      <c r="IJ838"/>
-      <c r="IK838"/>
-      <c r="IL838"/>
-      <c r="IM838"/>
-      <c r="IN838"/>
-      <c r="IO838"/>
-      <c r="IP838"/>
-      <c r="IQ838"/>
-      <c r="IR838"/>
-      <c r="IS838"/>
-      <c r="IT838"/>
-      <c r="IU838"/>
-      <c r="IV838"/>
-      <c r="IW838"/>
-      <c r="IX838"/>
-      <c r="IY838"/>
-      <c r="IZ838"/>
-      <c r="JA838"/>
-      <c r="JB838"/>
-      <c r="JC838"/>
-      <c r="JD838"/>
-      <c r="JE838"/>
-      <c r="JF838"/>
-      <c r="JG838"/>
-      <c r="JH838"/>
-      <c r="JI838"/>
-      <c r="JJ838"/>
-      <c r="JK838"/>
-      <c r="JL838"/>
-      <c r="JM838"/>
-      <c r="JN838"/>
-      <c r="JO838"/>
-      <c r="JP838"/>
-      <c r="JQ838"/>
-      <c r="JR838"/>
-      <c r="JS838"/>
-      <c r="JT838"/>
-      <c r="JU838"/>
-      <c r="JV838"/>
-      <c r="JW838"/>
-      <c r="JX838"/>
-      <c r="JY838"/>
-      <c r="JZ838"/>
-      <c r="KA838"/>
-      <c r="KB838"/>
-      <c r="KC838"/>
-      <c r="KD838"/>
-      <c r="KE838"/>
-      <c r="KF838"/>
-      <c r="KG838"/>
-      <c r="KH838"/>
-      <c r="KI838"/>
-      <c r="KJ838"/>
-      <c r="KK838"/>
-      <c r="KL838"/>
-      <c r="KM838"/>
-      <c r="KN838"/>
-      <c r="KO838"/>
-      <c r="KP838"/>
-      <c r="KQ838"/>
-      <c r="KR838"/>
-      <c r="KS838"/>
-      <c r="KT838"/>
-      <c r="KU838"/>
-      <c r="KV838"/>
-      <c r="KW838"/>
-      <c r="KX838"/>
-      <c r="KY838"/>
-      <c r="KZ838"/>
-      <c r="LA838"/>
-      <c r="LB838"/>
-      <c r="LC838"/>
-      <c r="LD838"/>
-      <c r="LE838"/>
-      <c r="LF838"/>
-      <c r="LG838"/>
-      <c r="LH838"/>
-      <c r="LI838"/>
-      <c r="LJ838"/>
-      <c r="LK838"/>
-      <c r="LL838"/>
-      <c r="LM838"/>
-      <c r="LN838"/>
-      <c r="LO838"/>
-      <c r="LP838"/>
-      <c r="LQ838"/>
-      <c r="LR838"/>
-      <c r="LS838"/>
-      <c r="LT838"/>
-      <c r="LU838"/>
-      <c r="LV838"/>
-      <c r="LW838"/>
-      <c r="LX838"/>
-      <c r="LY838"/>
-      <c r="LZ838"/>
-      <c r="MA838"/>
-      <c r="MB838"/>
-      <c r="MC838"/>
-      <c r="MD838"/>
-      <c r="ME838"/>
-      <c r="MF838"/>
-      <c r="MG838"/>
-      <c r="MH838"/>
-      <c r="MI838"/>
-      <c r="MJ838"/>
-      <c r="MK838"/>
-      <c r="ML838"/>
-      <c r="MM838"/>
-      <c r="MN838"/>
-      <c r="MO838"/>
-      <c r="MP838"/>
-      <c r="MQ838"/>
-      <c r="MR838"/>
-      <c r="MS838"/>
-      <c r="MT838"/>
-      <c r="MU838"/>
-      <c r="MV838"/>
-      <c r="MW838"/>
-      <c r="MX838"/>
-      <c r="MY838"/>
-      <c r="MZ838"/>
-      <c r="NA838"/>
-      <c r="NB838"/>
-      <c r="NC838"/>
-      <c r="ND838"/>
-      <c r="NE838"/>
-      <c r="NF838"/>
-      <c r="NG838"/>
-      <c r="NH838"/>
-      <c r="NI838"/>
-      <c r="NJ838"/>
-      <c r="NK838"/>
-      <c r="NL838"/>
-      <c r="NM838"/>
-      <c r="NN838"/>
-      <c r="NO838"/>
-      <c r="NP838"/>
-      <c r="NQ838"/>
-      <c r="NR838"/>
-      <c r="NS838"/>
-      <c r="NT838"/>
-      <c r="NU838"/>
-      <c r="NV838"/>
-      <c r="NW838"/>
-      <c r="NX838"/>
-      <c r="NY838"/>
-      <c r="NZ838"/>
-      <c r="OA838"/>
-      <c r="OB838"/>
-      <c r="OC838"/>
-      <c r="OD838"/>
-      <c r="OE838"/>
-      <c r="OF838"/>
-      <c r="OG838"/>
-      <c r="OH838"/>
-      <c r="OI838"/>
-      <c r="OJ838"/>
-      <c r="OK838"/>
-      <c r="OL838"/>
-      <c r="OM838"/>
-      <c r="ON838"/>
-      <c r="OO838"/>
-      <c r="OP838"/>
-      <c r="OQ838"/>
-      <c r="OR838"/>
-      <c r="OS838"/>
-      <c r="OT838"/>
-      <c r="OU838"/>
-      <c r="OV838"/>
-      <c r="OW838"/>
-      <c r="OX838"/>
-      <c r="OY838"/>
-      <c r="OZ838"/>
-      <c r="PA838"/>
-      <c r="PB838"/>
-      <c r="PC838"/>
-      <c r="PD838"/>
-      <c r="PE838"/>
-      <c r="PF838"/>
-      <c r="PG838"/>
-      <c r="PH838"/>
-      <c r="PI838"/>
-      <c r="PJ838"/>
-      <c r="PK838"/>
-      <c r="PL838"/>
-      <c r="PM838"/>
-      <c r="PN838"/>
-      <c r="PO838"/>
-      <c r="PP838"/>
-      <c r="PQ838"/>
-      <c r="PR838"/>
-      <c r="PS838"/>
-      <c r="PT838"/>
-      <c r="PU838"/>
-      <c r="PV838"/>
-      <c r="PW838"/>
-      <c r="PX838"/>
-      <c r="PY838"/>
-      <c r="PZ838"/>
-      <c r="QA838"/>
-      <c r="QB838"/>
-      <c r="QC838"/>
-      <c r="QD838"/>
-      <c r="QE838"/>
-      <c r="QF838"/>
-      <c r="QG838"/>
-      <c r="QH838"/>
-      <c r="QI838"/>
-      <c r="QJ838"/>
-      <c r="QK838"/>
-      <c r="QL838"/>
-      <c r="QM838"/>
-      <c r="QN838"/>
-      <c r="QO838"/>
-      <c r="QP838"/>
-      <c r="QQ838"/>
-      <c r="QR838"/>
-      <c r="QS838"/>
-      <c r="QT838"/>
-      <c r="QU838"/>
-      <c r="QV838"/>
-      <c r="QW838"/>
-      <c r="QX838"/>
-      <c r="QY838"/>
-      <c r="QZ838"/>
-      <c r="RA838"/>
-      <c r="RB838"/>
-      <c r="RC838"/>
-      <c r="RD838"/>
-      <c r="RE838"/>
-      <c r="RF838"/>
-      <c r="RG838"/>
-      <c r="RH838"/>
-      <c r="RI838"/>
-      <c r="RJ838"/>
-      <c r="RK838"/>
-      <c r="RL838"/>
-      <c r="RM838"/>
-      <c r="RN838"/>
-      <c r="RO838"/>
-      <c r="RP838"/>
-      <c r="RQ838"/>
-      <c r="RR838"/>
-      <c r="RS838"/>
-      <c r="RT838"/>
-      <c r="RU838"/>
-      <c r="RV838"/>
-      <c r="RW838"/>
-      <c r="RX838"/>
-      <c r="RY838"/>
-      <c r="RZ838"/>
-      <c r="SA838"/>
-      <c r="SB838"/>
-      <c r="SC838"/>
-      <c r="SD838"/>
-      <c r="SE838"/>
-      <c r="SF838"/>
-      <c r="SG838"/>
-      <c r="SH838"/>
-      <c r="SI838"/>
-      <c r="SJ838"/>
-      <c r="SK838"/>
-      <c r="SL838"/>
-      <c r="SM838"/>
-      <c r="SN838"/>
-      <c r="SO838"/>
-      <c r="SP838"/>
-      <c r="SQ838"/>
-      <c r="SR838"/>
-      <c r="SS838"/>
-      <c r="ST838"/>
-      <c r="SU838"/>
-      <c r="SV838"/>
-      <c r="SW838"/>
-      <c r="SX838"/>
-      <c r="SY838"/>
-      <c r="SZ838"/>
-      <c r="TA838"/>
-      <c r="TB838"/>
-      <c r="TC838"/>
-      <c r="TD838"/>
-      <c r="TE838"/>
-      <c r="TF838"/>
-      <c r="TG838"/>
-      <c r="TH838"/>
-      <c r="TI838"/>
-      <c r="TJ838"/>
-      <c r="TK838"/>
-      <c r="TL838"/>
-      <c r="TM838"/>
-      <c r="TN838"/>
-      <c r="TO838"/>
-      <c r="TP838"/>
-      <c r="TQ838"/>
-      <c r="TR838"/>
-      <c r="TS838"/>
-      <c r="TT838"/>
-      <c r="TU838"/>
-      <c r="TV838"/>
-      <c r="TW838"/>
-      <c r="TX838"/>
-      <c r="TY838"/>
-      <c r="TZ838"/>
-      <c r="UA838"/>
-      <c r="UB838"/>
-      <c r="UC838"/>
-      <c r="UD838"/>
-      <c r="UE838"/>
-      <c r="UF838"/>
-      <c r="UG838"/>
-      <c r="UH838"/>
-      <c r="UI838"/>
-      <c r="UJ838"/>
-      <c r="UK838"/>
-      <c r="UL838"/>
-      <c r="UM838"/>
-      <c r="UN838"/>
-      <c r="UO838"/>
-      <c r="UP838"/>
-      <c r="UQ838"/>
-      <c r="UR838"/>
-      <c r="US838"/>
-      <c r="UT838"/>
-      <c r="UU838"/>
-      <c r="UV838"/>
-      <c r="UW838"/>
-      <c r="UX838"/>
-      <c r="UY838"/>
-      <c r="UZ838"/>
-      <c r="VA838"/>
-      <c r="VB838"/>
-      <c r="VC838"/>
-      <c r="VD838"/>
-      <c r="VE838"/>
-      <c r="VF838"/>
-      <c r="VG838"/>
-      <c r="VH838"/>
-      <c r="VI838"/>
-      <c r="VJ838"/>
-      <c r="VK838"/>
-      <c r="VL838"/>
-      <c r="VM838"/>
-      <c r="VN838"/>
-      <c r="VO838"/>
-      <c r="VP838"/>
-      <c r="VQ838"/>
-      <c r="VR838"/>
-      <c r="VS838"/>
-      <c r="VT838"/>
-      <c r="VU838"/>
-      <c r="VV838"/>
-      <c r="VW838"/>
-      <c r="VX838"/>
-      <c r="VY838"/>
-      <c r="VZ838"/>
-      <c r="WA838"/>
-      <c r="WB838"/>
-      <c r="WC838"/>
-      <c r="WD838"/>
-      <c r="WE838"/>
-      <c r="WF838"/>
-      <c r="WG838"/>
-      <c r="WH838"/>
-      <c r="WI838"/>
-      <c r="WJ838"/>
-      <c r="WK838"/>
-      <c r="WL838"/>
-      <c r="WM838"/>
-      <c r="WN838"/>
-      <c r="WO838"/>
-      <c r="WP838"/>
-      <c r="WQ838"/>
-      <c r="WR838"/>
-      <c r="WS838"/>
-      <c r="WT838"/>
-      <c r="WU838"/>
-      <c r="WV838"/>
-      <c r="WW838"/>
-      <c r="WX838"/>
-      <c r="WY838"/>
-      <c r="WZ838"/>
-      <c r="XA838"/>
-      <c r="XB838"/>
-      <c r="XC838"/>
-      <c r="XD838"/>
-      <c r="XE838"/>
-      <c r="XF838"/>
-      <c r="XG838"/>
-      <c r="XH838"/>
-      <c r="XI838"/>
-      <c r="XJ838"/>
-      <c r="XK838"/>
-      <c r="XL838"/>
-      <c r="XM838"/>
-      <c r="XN838"/>
-      <c r="XO838"/>
-      <c r="XP838"/>
-      <c r="XQ838"/>
-      <c r="XR838"/>
-      <c r="XS838"/>
-      <c r="XT838"/>
-      <c r="XU838"/>
-      <c r="XV838"/>
-      <c r="XW838"/>
-      <c r="XX838"/>
-      <c r="XY838"/>
-      <c r="XZ838"/>
-      <c r="YA838"/>
-      <c r="YB838"/>
-      <c r="YC838"/>
-      <c r="YD838"/>
-      <c r="YE838"/>
-      <c r="YF838"/>
-      <c r="YG838"/>
-      <c r="YH838"/>
-      <c r="YI838"/>
-      <c r="YJ838"/>
-      <c r="YK838"/>
-      <c r="YL838"/>
-      <c r="YM838"/>
-      <c r="YN838"/>
-      <c r="YO838"/>
-      <c r="YP838"/>
-      <c r="YQ838"/>
-      <c r="YR838"/>
-      <c r="YS838"/>
-      <c r="YT838"/>
-      <c r="YU838"/>
-      <c r="YV838"/>
-      <c r="YW838"/>
-      <c r="YX838"/>
-      <c r="YY838"/>
-      <c r="YZ838"/>
-      <c r="ZA838"/>
-      <c r="ZB838"/>
-      <c r="ZC838"/>
-      <c r="ZD838"/>
-      <c r="ZE838"/>
-      <c r="ZF838"/>
-      <c r="ZG838"/>
-      <c r="ZH838"/>
-      <c r="ZI838"/>
-      <c r="ZJ838"/>
-      <c r="ZK838"/>
-      <c r="ZL838"/>
-      <c r="ZM838"/>
-      <c r="ZN838"/>
-      <c r="ZO838"/>
-      <c r="ZP838"/>
-      <c r="ZQ838"/>
-      <c r="ZR838"/>
-      <c r="ZS838"/>
-      <c r="ZT838"/>
-      <c r="ZU838"/>
-      <c r="ZV838"/>
-      <c r="ZW838"/>
-      <c r="ZX838"/>
-      <c r="ZY838"/>
-      <c r="ZZ838"/>
-      <c r="AAA838"/>
-      <c r="AAB838"/>
-      <c r="AAC838"/>
-      <c r="AAD838"/>
-      <c r="AAE838"/>
-      <c r="AAF838"/>
-      <c r="AAG838"/>
-      <c r="AAH838"/>
-      <c r="AAI838"/>
-      <c r="AAJ838"/>
-      <c r="AAK838"/>
-      <c r="AAL838"/>
-      <c r="AAM838"/>
-      <c r="AAN838"/>
-      <c r="AAO838"/>
-      <c r="AAP838"/>
-      <c r="AAQ838"/>
-      <c r="AAR838"/>
-      <c r="AAS838"/>
-      <c r="AAT838"/>
-      <c r="AAU838"/>
-      <c r="AAV838"/>
-      <c r="AAW838"/>
-      <c r="AAX838"/>
-      <c r="AAY838"/>
-      <c r="AAZ838"/>
-      <c r="ABA838"/>
-      <c r="ABB838"/>
-      <c r="ABC838"/>
-      <c r="ABD838"/>
-      <c r="ABE838"/>
-      <c r="ABF838"/>
-      <c r="ABG838"/>
-      <c r="ABH838"/>
-      <c r="ABI838"/>
-      <c r="ABJ838"/>
-      <c r="ABK838"/>
-      <c r="ABL838"/>
-      <c r="ABM838"/>
-      <c r="ABN838"/>
-      <c r="ABO838"/>
-      <c r="ABP838"/>
-      <c r="ABQ838"/>
-      <c r="ABR838"/>
-      <c r="ABS838"/>
-      <c r="ABT838"/>
-      <c r="ABU838"/>
-      <c r="ABV838"/>
-      <c r="ABW838"/>
-      <c r="ABX838"/>
-      <c r="ABY838"/>
-      <c r="ABZ838"/>
-      <c r="ACA838"/>
-      <c r="ACB838"/>
-      <c r="ACC838"/>
-      <c r="ACD838"/>
-      <c r="ACE838"/>
-      <c r="ACF838"/>
-      <c r="ACG838"/>
-      <c r="ACH838"/>
-      <c r="ACI838"/>
-      <c r="ACJ838"/>
-      <c r="ACK838"/>
-      <c r="ACL838"/>
-      <c r="ACM838"/>
-      <c r="ACN838"/>
-      <c r="ACO838"/>
-      <c r="ACP838"/>
-      <c r="ACQ838"/>
-      <c r="ACR838"/>
-      <c r="ACS838"/>
-      <c r="ACT838"/>
-      <c r="ACU838"/>
-      <c r="ACV838"/>
-      <c r="ACW838"/>
-      <c r="ACX838"/>
-      <c r="ACY838"/>
-      <c r="ACZ838"/>
-      <c r="ADA838"/>
-      <c r="ADB838"/>
-      <c r="ADC838"/>
-      <c r="ADD838"/>
-      <c r="ADE838"/>
-      <c r="ADF838"/>
-      <c r="ADG838"/>
-      <c r="ADH838"/>
-      <c r="ADI838"/>
-      <c r="ADJ838"/>
-      <c r="ADK838"/>
-      <c r="ADL838"/>
-      <c r="ADM838"/>
-      <c r="ADN838"/>
-      <c r="ADO838"/>
-      <c r="ADP838"/>
-      <c r="ADQ838"/>
-      <c r="ADR838"/>
-      <c r="ADS838"/>
-      <c r="ADT838"/>
-      <c r="ADU838"/>
-      <c r="ADV838"/>
-      <c r="ADW838"/>
-      <c r="ADX838"/>
-      <c r="ADY838"/>
-      <c r="ADZ838"/>
-      <c r="AEA838"/>
-      <c r="AEB838"/>
-      <c r="AEC838"/>
-      <c r="AED838"/>
-      <c r="AEE838"/>
-      <c r="AEF838"/>
-      <c r="AEG838"/>
-      <c r="AEH838"/>
-      <c r="AEI838"/>
-      <c r="AEJ838"/>
-      <c r="AEK838"/>
-      <c r="AEL838"/>
-      <c r="AEM838"/>
-      <c r="AEN838"/>
-      <c r="AEO838"/>
-      <c r="AEP838"/>
-      <c r="AEQ838"/>
-      <c r="AER838"/>
-      <c r="AES838"/>
-      <c r="AET838"/>
-      <c r="AEU838"/>
-      <c r="AEV838"/>
-      <c r="AEW838"/>
-      <c r="AEX838"/>
-      <c r="AEY838"/>
-      <c r="AEZ838"/>
-      <c r="AFA838"/>
-      <c r="AFB838"/>
-      <c r="AFC838"/>
-      <c r="AFD838"/>
-      <c r="AFE838"/>
-      <c r="AFF838"/>
-      <c r="AFG838"/>
-      <c r="AFH838"/>
-      <c r="AFI838"/>
-      <c r="AFJ838"/>
-      <c r="AFK838"/>
-      <c r="AFL838"/>
-      <c r="AFM838"/>
-      <c r="AFN838"/>
-      <c r="AFO838"/>
-      <c r="AFP838"/>
-      <c r="AFQ838"/>
-      <c r="AFR838"/>
-      <c r="AFS838"/>
-      <c r="AFT838"/>
-      <c r="AFU838"/>
-      <c r="AFV838"/>
-      <c r="AFW838"/>
-      <c r="AFX838"/>
-      <c r="AFY838"/>
-      <c r="AFZ838"/>
-      <c r="AGA838"/>
-      <c r="AGB838"/>
-      <c r="AGC838"/>
-      <c r="AGD838"/>
-      <c r="AGE838"/>
-      <c r="AGF838"/>
-      <c r="AGG838"/>
-      <c r="AGH838"/>
-      <c r="AGI838"/>
-      <c r="AGJ838"/>
-      <c r="AGK838"/>
-      <c r="AGL838"/>
-      <c r="AGM838"/>
-      <c r="AGN838"/>
-      <c r="AGO838"/>
-      <c r="AGP838"/>
-      <c r="AGQ838"/>
-      <c r="AGR838"/>
-      <c r="AGS838"/>
-      <c r="AGT838"/>
-      <c r="AGU838"/>
-      <c r="AGV838"/>
-      <c r="AGW838"/>
-      <c r="AGX838"/>
-      <c r="AGY838"/>
-      <c r="AGZ838"/>
-      <c r="AHA838"/>
-      <c r="AHB838"/>
-      <c r="AHC838"/>
-      <c r="AHD838"/>
-      <c r="AHE838"/>
-      <c r="AHF838"/>
-      <c r="AHG838"/>
-      <c r="AHH838"/>
-      <c r="AHI838"/>
-      <c r="AHJ838"/>
-      <c r="AHK838"/>
-      <c r="AHL838"/>
-      <c r="AHM838"/>
-      <c r="AHN838"/>
-      <c r="AHO838"/>
-      <c r="AHP838"/>
-      <c r="AHQ838"/>
-      <c r="AHR838"/>
-      <c r="AHS838"/>
-      <c r="AHT838"/>
-      <c r="AHU838"/>
-      <c r="AHV838"/>
-      <c r="AHW838"/>
-      <c r="AHX838"/>
-      <c r="AHY838"/>
-      <c r="AHZ838"/>
-      <c r="AIA838"/>
-      <c r="AIB838"/>
-      <c r="AIC838"/>
-      <c r="AID838"/>
-      <c r="AIE838"/>
-      <c r="AIF838"/>
-      <c r="AIG838"/>
-      <c r="AIH838"/>
-      <c r="AII838"/>
-      <c r="AIJ838"/>
-      <c r="AIK838"/>
-      <c r="AIL838"/>
-      <c r="AIM838"/>
-      <c r="AIN838"/>
-      <c r="AIO838"/>
-      <c r="AIP838"/>
-      <c r="AIQ838"/>
-      <c r="AIR838"/>
-      <c r="AIS838"/>
-      <c r="AIT838"/>
-      <c r="AIU838"/>
-      <c r="AIV838"/>
-      <c r="AIW838"/>
-      <c r="AIX838"/>
-      <c r="AIY838"/>
-      <c r="AIZ838"/>
-      <c r="AJA838"/>
-      <c r="AJB838"/>
-      <c r="AJC838"/>
-      <c r="AJD838"/>
-      <c r="AJE838"/>
-      <c r="AJF838"/>
-      <c r="AJG838"/>
-      <c r="AJH838"/>
-      <c r="AJI838"/>
-      <c r="AJJ838"/>
-      <c r="AJK838"/>
-      <c r="AJL838"/>
-      <c r="AJM838"/>
-      <c r="AJN838"/>
-      <c r="AJO838"/>
-      <c r="AJP838"/>
-      <c r="AJQ838"/>
-      <c r="AJR838"/>
-      <c r="AJS838"/>
-      <c r="AJT838"/>
-      <c r="AJU838"/>
-      <c r="AJV838"/>
-      <c r="AJW838"/>
-      <c r="AJX838"/>
-      <c r="AJY838"/>
-      <c r="AJZ838"/>
-      <c r="AKA838"/>
-      <c r="AKB838"/>
-      <c r="AKC838"/>
-      <c r="AKD838"/>
-      <c r="AKE838"/>
-      <c r="AKF838"/>
-      <c r="AKG838"/>
-      <c r="AKH838"/>
-      <c r="AKI838"/>
-      <c r="AKJ838"/>
-      <c r="AKK838"/>
-      <c r="AKL838"/>
-      <c r="AKM838"/>
-      <c r="AKN838"/>
-      <c r="AKO838"/>
-      <c r="AKP838"/>
-      <c r="AKQ838"/>
-      <c r="AKR838"/>
-      <c r="AKS838"/>
-      <c r="AKT838"/>
-      <c r="AKU838"/>
-      <c r="AKV838"/>
-      <c r="AKW838"/>
-      <c r="AKX838"/>
-      <c r="AKY838"/>
-      <c r="AKZ838"/>
-      <c r="ALA838"/>
-      <c r="ALB838"/>
-      <c r="ALC838"/>
-      <c r="ALD838"/>
-      <c r="ALE838"/>
-      <c r="ALF838"/>
-      <c r="ALG838"/>
-      <c r="ALH838"/>
-      <c r="ALI838"/>
-      <c r="ALJ838"/>
-      <c r="ALK838"/>
-      <c r="ALL838"/>
-      <c r="ALM838"/>
-      <c r="ALN838"/>
-      <c r="ALO838"/>
-      <c r="ALP838"/>
-      <c r="ALQ838"/>
-      <c r="ALR838"/>
-      <c r="ALS838"/>
-      <c r="ALT838"/>
-      <c r="ALU838"/>
-      <c r="ALV838"/>
-      <c r="ALW838"/>
-      <c r="ALX838"/>
-      <c r="ALY838"/>
-      <c r="ALZ838"/>
-      <c r="AMA838"/>
-      <c r="AMB838"/>
-      <c r="AMC838"/>
-      <c r="AMD838"/>
-      <c r="AME838"/>
-      <c r="AMF838"/>
-      <c r="AMG838"/>
-      <c r="AMH838"/>
+        <v>2964</v>
+      </c>
     </row>
     <row r="839" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A839" s="8" t="s">
-        <v>2965</v>
+        <v>2318</v>
       </c>
       <c r="B839" s="8" t="s">
-        <v>2955</v>
+        <v>206</v>
       </c>
       <c r="C839" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_ptm_enrichment:ionchromatography</v>
+        <v>att_quant_algorithm:directlfq</v>
       </c>
       <c r="D839" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E839" s="8" t="s">
-        <v>2963</v>
-      </c>
-      <c r="F839" s="8" t="s">
-        <v>2964</v>
+        <v>2319</v>
+      </c>
+      <c r="F839" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="840" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A840" s="8" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="B840" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C840" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_quant_algorithm:directlfq</v>
+        <v>att_quant_algorithm:maxlfq</v>
       </c>
       <c r="D840" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E840" s="8" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="F840" s="9" t="s">
         <v>17</v>
@@ -39848,20 +39848,20 @@
     </row>
     <row r="841" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A841" s="8" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="B841" s="8" t="s">
         <v>206</v>
       </c>
       <c r="C841" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_quant_algorithm:maxlfq</v>
+        <v>att_quant_algorithm:speccount</v>
       </c>
       <c r="D841" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E841" s="8" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="F841" s="9" t="s">
         <v>17</v>
@@ -39869,965 +39869,965 @@
     </row>
     <row r="842" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A842" s="8" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="B842" s="8" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C842" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_quant_algorithm:speccount</v>
+        <v>att_quantification:isobaric</v>
       </c>
       <c r="D842" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E842" s="8" t="s">
-        <v>2323</v>
-      </c>
-      <c r="F842" s="9" t="s">
-        <v>17</v>
+        <v>2324</v>
+      </c>
+      <c r="F842" s="8" t="s">
+        <v>2325</v>
       </c>
     </row>
     <row r="843" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A843" s="8" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="B843" s="8" t="s">
         <v>207</v>
       </c>
       <c r="C843" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_quantification:isobaric</v>
+        <v>att_quantification:istopic</v>
       </c>
       <c r="D843" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E843" s="8" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="F843" s="8" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="844" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A844" s="8" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="B844" s="8" t="s">
         <v>207</v>
       </c>
       <c r="C844" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_quantification:istopic</v>
+        <v>att_quantification:label_free</v>
       </c>
       <c r="D844" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E844" s="8" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="F844" s="8" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="845" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A845" s="8" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="B845" s="8" t="s">
         <v>207</v>
       </c>
       <c r="C845" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_quantification:label_free</v>
+        <v>att_quantification:silac</v>
       </c>
       <c r="D845" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E845" s="8" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="F845" s="8" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="846" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A846" s="8" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="B846" s="8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C846" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_quantification:silac</v>
+        <v>att_reduction:dtt</v>
       </c>
       <c r="D846" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E846" s="8" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="F846" s="8" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="847" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A847" s="8" t="s">
-        <v>2333</v>
+        <v>336</v>
       </c>
       <c r="B847" s="8" t="s">
         <v>210</v>
       </c>
       <c r="C847" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_reduction:dtt</v>
+        <v>att_reduction:none</v>
       </c>
       <c r="D847" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E847" s="8" t="s">
-        <v>2334</v>
+        <v>337</v>
       </c>
       <c r="F847" s="8" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="848" spans="1:1022" x14ac:dyDescent="0.15">
       <c r="A848" s="8" t="s">
-        <v>336</v>
+        <v>2337</v>
       </c>
       <c r="B848" s="8" t="s">
         <v>210</v>
       </c>
       <c r="C848" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_reduction:none</v>
+        <v>att_reduction:tcep</v>
       </c>
       <c r="D848" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E848" s="8" t="s">
-        <v>337</v>
+        <v>2338</v>
       </c>
       <c r="F848" s="8" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="849" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A849" s="8" t="s">
-        <v>2337</v>
+        <v>1406</v>
       </c>
       <c r="B849" s="8" t="s">
-        <v>210</v>
+        <v>2340</v>
       </c>
       <c r="C849" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_reduction:tcep</v>
+        <v>att_signalling:apoptosis</v>
       </c>
       <c r="D849" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E849" s="8" t="s">
-        <v>2338</v>
+        <v>1407</v>
       </c>
       <c r="F849" s="8" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="850" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A850" s="8" t="s">
-        <v>1406</v>
+        <v>2342</v>
       </c>
       <c r="B850" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C850" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:apoptosis</v>
+        <v>att_signalling:autocrine</v>
       </c>
       <c r="D850" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E850" s="8" t="s">
-        <v>1407</v>
+        <v>2343</v>
       </c>
       <c r="F850" s="8" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="851" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A851" s="8" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="B851" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C851" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:autocrine</v>
+        <v>att_signalling:complement</v>
       </c>
       <c r="D851" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E851" s="8" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
       <c r="F851" s="8" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="852" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A852" s="8" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="B852" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C852" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:complement</v>
+        <v>att_signalling:cytokines</v>
       </c>
       <c r="D852" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E852" s="8" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
       <c r="F852" s="8" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="853" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A853" s="8" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="B853" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C853" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:cytokines</v>
+        <v>att_signalling:inflammation</v>
       </c>
       <c r="D853" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E853" s="8" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="F853" s="8" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="854" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A854" s="8" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="B854" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C854" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:inflammation</v>
+        <v>att_signalling:insulin</v>
       </c>
       <c r="D854" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E854" s="8" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="F854" s="8" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="855" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A855" s="8" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="B855" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C855" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:insulin</v>
+        <v>att_signalling:juxtacrine</v>
       </c>
       <c r="D855" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E855" s="8" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="F855" s="8" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="856" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A856" s="8" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="B856" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C856" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:juxtacrine</v>
+        <v>att_signalling:necrosis</v>
       </c>
       <c r="D856" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E856" s="8" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="F856" s="8" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="857" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A857" s="8" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="B857" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C857" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:necrosis</v>
+        <v>att_signalling:paracrine</v>
       </c>
       <c r="D857" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E857" s="8" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="F857" s="8" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="858" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A858" s="8" t="s">
-        <v>2363</v>
+        <v>1754</v>
       </c>
       <c r="B858" s="8" t="s">
         <v>2340</v>
       </c>
       <c r="C858" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:paracrine</v>
+        <v>att_signalling:signaling</v>
       </c>
       <c r="D858" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E858" s="8" t="s">
-        <v>2364</v>
+        <v>1755</v>
       </c>
       <c r="F858" s="8" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="859" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A859" s="8" t="s">
-        <v>1754</v>
+        <v>2367</v>
       </c>
       <c r="B859" s="8" t="s">
-        <v>2340</v>
+        <v>31</v>
       </c>
       <c r="C859" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_signalling:signaling</v>
+        <v>att_software:diann</v>
       </c>
       <c r="D859" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E859" s="8" t="s">
-        <v>1755</v>
+        <v>2368</v>
       </c>
       <c r="F859" s="8" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="860" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A860" s="8" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="B860" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C860" s="8" t="str">
         <f t="shared" si="38"/>
-        <v>att_software:diann</v>
+        <v>att_software:maxquant</v>
       </c>
       <c r="D860" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E860" s="8" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="F860" s="8" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="861" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A861" s="8" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="B861" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C861" s="8" t="str">
-        <f t="shared" si="38"/>
-        <v>att_software:maxquant</v>
+        <f t="shared" ref="C861:C932" si="39">B861&amp;":"&amp;A861</f>
+        <v>att_software:metamorpheus</v>
       </c>
       <c r="D861" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E861" s="8" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="F861" s="8" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="862" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A862" s="8" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="B862" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C862" s="8" t="str">
-        <f t="shared" ref="C862:C933" si="39">B862&amp;":"&amp;A862</f>
-        <v>att_software:metamorpheus</v>
+        <f t="shared" si="39"/>
+        <v>att_software:minora</v>
       </c>
       <c r="D862" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E862" s="8" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
       <c r="F862" s="8" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="863" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A863" s="8" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="B863" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C863" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_software:minora</v>
+        <v>att_software:msfragger</v>
       </c>
       <c r="D863" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E863" s="8" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="F863" s="8" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="864" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A864" s="8" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="B864" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C864" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_software:msfragger</v>
+        <v>att_software:msgf</v>
       </c>
       <c r="D864" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E864" s="8" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="F864" s="8" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="865" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A865" s="8" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="B865" s="8" t="s">
         <v>31</v>
       </c>
       <c r="C865" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_software:msgf</v>
+        <v>att_software:spectronaut</v>
       </c>
       <c r="D865" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E865" s="8" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
       <c r="F865" s="8" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="866" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A866" s="8" t="s">
-        <v>2385</v>
+        <v>2909</v>
       </c>
       <c r="B866" s="8" t="s">
-        <v>31</v>
+        <v>2908</v>
       </c>
       <c r="C866" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_software:spectronaut</v>
+        <v>att_subcellular_compartment:wc</v>
       </c>
       <c r="D866" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E866" s="8" t="s">
-        <v>2386</v>
+        <v>2910</v>
       </c>
       <c r="F866" s="8" t="s">
-        <v>2387</v>
+        <v>2911</v>
       </c>
     </row>
     <row r="867" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A867" s="8" t="s">
-        <v>2909</v>
+        <v>2913</v>
       </c>
       <c r="B867" s="8" t="s">
         <v>2908</v>
       </c>
       <c r="C867" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_subcellular_compartment:wc</v>
+        <v>att_subcellular_compartment:membrane</v>
       </c>
       <c r="D867" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E867" s="8" t="s">
-        <v>2910</v>
+        <v>2914</v>
       </c>
       <c r="F867" s="8" t="s">
-        <v>2911</v>
+        <v>2915</v>
       </c>
     </row>
     <row r="868" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A868" s="8" t="s">
-        <v>2913</v>
+        <v>2912</v>
       </c>
       <c r="B868" s="8" t="s">
         <v>2908</v>
       </c>
       <c r="C868" s="8" t="str">
-        <f t="shared" si="39"/>
-        <v>att_subcellular_compartment:membrane</v>
+        <f t="shared" ref="C868" si="40">B868&amp;":"&amp;A868</f>
+        <v>att_subcellular_compartment:mitochondria</v>
       </c>
       <c r="D868" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E868" s="8" t="s">
-        <v>2914</v>
+        <v>2929</v>
       </c>
       <c r="F868" s="8" t="s">
-        <v>2915</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="869" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A869" s="8" t="s">
-        <v>2912</v>
+        <v>2942</v>
       </c>
       <c r="B869" s="8" t="s">
         <v>2908</v>
       </c>
       <c r="C869" s="8" t="str">
-        <f t="shared" ref="C869" si="40">B869&amp;":"&amp;A869</f>
-        <v>att_subcellular_compartment:mitochondria</v>
+        <f t="shared" ref="C869" si="41">B869&amp;":"&amp;A869</f>
+        <v>att_subcellular_compartment:mitochondriapk</v>
       </c>
       <c r="D869" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E869" s="8" t="s">
-        <v>2929</v>
+        <v>2940</v>
       </c>
       <c r="F869" s="8" t="s">
-        <v>2928</v>
+        <v>2941</v>
       </c>
     </row>
     <row r="870" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A870" s="8" t="s">
-        <v>2942</v>
+        <v>2916</v>
       </c>
       <c r="B870" s="8" t="s">
         <v>2908</v>
       </c>
       <c r="C870" s="8" t="str">
-        <f t="shared" ref="C870" si="41">B870&amp;":"&amp;A870</f>
-        <v>att_subcellular_compartment:mitochondriapk</v>
+        <f t="shared" si="39"/>
+        <v>att_subcellular_compartment:golgi</v>
       </c>
       <c r="D870" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E870" s="8" t="s">
-        <v>2940</v>
+        <v>2917</v>
       </c>
       <c r="F870" s="8" t="s">
-        <v>2941</v>
+        <v>2918</v>
       </c>
     </row>
     <row r="871" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A871" s="8" t="s">
-        <v>2916</v>
+        <v>2919</v>
       </c>
       <c r="B871" s="8" t="s">
         <v>2908</v>
       </c>
       <c r="C871" s="8" t="str">
-        <f t="shared" si="39"/>
-        <v>att_subcellular_compartment:golgi</v>
+        <f t="shared" ref="C871:C873" si="42">B871&amp;":"&amp;A871</f>
+        <v>att_subcellular_compartment:plasmamembrane</v>
       </c>
       <c r="D871" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E871" s="8" t="s">
-        <v>2917</v>
+        <v>2927</v>
       </c>
       <c r="F871" s="8" t="s">
-        <v>2918</v>
+        <v>2920</v>
       </c>
     </row>
     <row r="872" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A872" s="8" t="s">
-        <v>2919</v>
+        <v>2921</v>
       </c>
       <c r="B872" s="8" t="s">
         <v>2908</v>
       </c>
       <c r="C872" s="8" t="str">
-        <f t="shared" ref="C872:C874" si="42">B872&amp;":"&amp;A872</f>
-        <v>att_subcellular_compartment:plasmamembrane</v>
+        <f t="shared" si="42"/>
+        <v>att_subcellular_compartment:nucleus</v>
       </c>
       <c r="D872" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E872" s="8" t="s">
-        <v>2927</v>
+        <v>2922</v>
       </c>
       <c r="F872" s="8" t="s">
-        <v>2920</v>
+        <v>2923</v>
       </c>
     </row>
     <row r="873" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A873" s="8" t="s">
-        <v>2921</v>
+        <v>2924</v>
       </c>
       <c r="B873" s="8" t="s">
         <v>2908</v>
       </c>
       <c r="C873" s="8" t="str">
         <f t="shared" si="42"/>
-        <v>att_subcellular_compartment:nucleus</v>
+        <v>att_subcellular_compartment:cytosol</v>
       </c>
       <c r="D873" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E873" s="8" t="s">
-        <v>2922</v>
+        <v>2925</v>
       </c>
       <c r="F873" s="8" t="s">
-        <v>2923</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="874" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A874" s="8" t="s">
-        <v>2924</v>
+        <v>2388</v>
       </c>
       <c r="B874" s="8" t="s">
-        <v>2908</v>
+        <v>232</v>
       </c>
       <c r="C874" s="8" t="str">
-        <f t="shared" si="42"/>
-        <v>att_subcellular_compartment:cytosol</v>
-      </c>
-      <c r="D874" s="9" t="s">
-        <v>17</v>
+        <f t="shared" si="39"/>
+        <v>att_tissue:adipose</v>
+      </c>
+      <c r="D874" s="8" t="s">
+        <v>2388</v>
       </c>
       <c r="E874" s="8" t="s">
-        <v>2925</v>
+        <v>2389</v>
       </c>
       <c r="F874" s="8" t="s">
-        <v>2926</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="875" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A875" s="8" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="B875" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C875" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:adipose</v>
+        <v>att_tissue:areolar</v>
       </c>
       <c r="D875" s="8" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="E875" s="8" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
       <c r="F875" s="8" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="876" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A876" s="8" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="B876" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C876" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:areolar</v>
+        <v>att_tissue:blood</v>
       </c>
       <c r="D876" s="8" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="E876" s="8" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="F876" s="8" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="877" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A877" s="8" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="B877" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C877" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:blood</v>
+        <v>att_tissue:connective</v>
       </c>
       <c r="D877" s="8" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="E877" s="8" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="F877" s="8" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="878" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A878" s="8" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="B878" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C878" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:connective</v>
+        <v>att_tissue:dermis</v>
       </c>
       <c r="D878" s="8" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="E878" s="8" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="F878" s="8" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="879" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A879" s="8" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="B879" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C879" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:dermis</v>
+        <v>att_tissue:epidermis</v>
       </c>
       <c r="D879" s="8" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="E879" s="8" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="F879" s="8" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="880" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A880" s="8" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="B880" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C880" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:epidermis</v>
+        <v>att_tissue:epithelial</v>
       </c>
       <c r="D880" s="8" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="E880" s="8" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="F880" s="8" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="881" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A881" s="8" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
       <c r="B881" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C881" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:epithelial</v>
+        <v>att_tissue:hypodermis</v>
       </c>
       <c r="D881" s="8" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
       <c r="E881" s="8" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="F881" s="8" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="882" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A882" s="8" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="B882" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C882" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:hypodermis</v>
+        <v>att_tissue:muscle</v>
       </c>
       <c r="D882" s="8" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="E882" s="8" t="s">
-        <v>2407</v>
+        <v>2806</v>
       </c>
       <c r="F882" s="8" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="883" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A883" s="8" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="B883" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C883" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:muscle</v>
+        <v>att_tissue:nervous</v>
       </c>
       <c r="D883" s="8" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="E883" s="8" t="s">
-        <v>2806</v>
+        <v>2229</v>
       </c>
       <c r="F883" s="8" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="884" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A884" s="8" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="B884" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C884" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:nervous</v>
+        <v>att_tissue:reticular</v>
       </c>
       <c r="D884" s="8" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="E884" s="8" t="s">
-        <v>2229</v>
+        <v>2413</v>
       </c>
       <c r="F884" s="8" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="885" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A885" s="8" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="B885" s="8" t="s">
         <v>232</v>
       </c>
       <c r="C885" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:reticular</v>
+        <v>att_tissue:stromal</v>
       </c>
       <c r="D885" s="8" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="E885" s="8" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="F885" s="8" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="886" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A886" s="8" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="B886" s="8" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C886" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tissue:stromal</v>
-      </c>
-      <c r="D886" s="8" t="s">
-        <v>2415</v>
-      </c>
-      <c r="E886" s="8" t="s">
-        <v>2416</v>
-      </c>
-      <c r="F886" s="8" t="s">
-        <v>2417</v>
+        <v>att_tmt_channel:tmt10_126</v>
+      </c>
+      <c r="D886" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="E886" s="8">
+        <v>126</v>
+      </c>
+      <c r="F886" s="9" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="887" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A887" s="8" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="B887" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C887" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_126</v>
+        <v>att_tmt_channel:tmt10_127C</v>
       </c>
       <c r="D887" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E887" s="8">
-        <v>126</v>
+      <c r="E887" s="8" t="s">
+        <v>2420</v>
       </c>
       <c r="F887" s="9" t="s">
         <v>17</v>
@@ -40835,20 +40835,20 @@
     </row>
     <row r="888" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A888" s="8" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B888" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C888" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_127C</v>
+        <v>att_tmt_channel:tmt10_127N</v>
       </c>
       <c r="D888" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E888" s="8" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="F888" s="9" t="s">
         <v>17</v>
@@ -40856,20 +40856,20 @@
     </row>
     <row r="889" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A889" s="8" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="B889" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C889" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_127N</v>
+        <v>att_tmt_channel:tmt10_128C</v>
       </c>
       <c r="D889" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E889" s="8" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="F889" s="9" t="s">
         <v>17</v>
@@ -40877,20 +40877,20 @@
     </row>
     <row r="890" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A890" s="8" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B890" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C890" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_128C</v>
+        <v>att_tmt_channel:tmt10_128N</v>
       </c>
       <c r="D890" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E890" s="8" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="F890" s="9" t="s">
         <v>17</v>
@@ -40898,20 +40898,20 @@
     </row>
     <row r="891" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A891" s="8" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="B891" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C891" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_128N</v>
+        <v>att_tmt_channel:tmt10_129C</v>
       </c>
       <c r="D891" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E891" s="8" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="F891" s="9" t="s">
         <v>17</v>
@@ -40919,20 +40919,20 @@
     </row>
     <row r="892" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A892" s="8" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="B892" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C892" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_129C</v>
+        <v>att_tmt_channel:tmt10_129N</v>
       </c>
       <c r="D892" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E892" s="8" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="F892" s="9" t="s">
         <v>17</v>
@@ -40940,20 +40940,20 @@
     </row>
     <row r="893" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A893" s="8" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="B893" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C893" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_129N</v>
+        <v>att_tmt_channel:tmt10_130C</v>
       </c>
       <c r="D893" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E893" s="8" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="F893" s="9" t="s">
         <v>17</v>
@@ -40961,20 +40961,20 @@
     </row>
     <row r="894" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A894" s="8" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="B894" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C894" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_130C</v>
+        <v>att_tmt_channel:tmt10_130N</v>
       </c>
       <c r="D894" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E894" s="8" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="F894" s="9" t="s">
         <v>17</v>
@@ -40982,20 +40982,20 @@
     </row>
     <row r="895" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A895" s="8" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="B895" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C895" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_130N</v>
+        <v>att_tmt_channel:tmt10_131</v>
       </c>
       <c r="D895" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E895" s="8" t="s">
-        <v>2434</v>
+      <c r="E895" s="8">
+        <v>131</v>
       </c>
       <c r="F895" s="9" t="s">
         <v>17</v>
@@ -41003,20 +41003,20 @@
     </row>
     <row r="896" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A896" s="8" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="B896" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C896" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt10_131</v>
+        <v>att_tmt_channel:tmt11_126</v>
       </c>
       <c r="D896" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E896" s="8">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="F896" s="9" t="s">
         <v>17</v>
@@ -41024,20 +41024,20 @@
     </row>
     <row r="897" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A897" s="8" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="B897" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C897" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_126</v>
+        <v>att_tmt_channel:tmt11_127C</v>
       </c>
       <c r="D897" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E897" s="8">
-        <v>126</v>
+      <c r="E897" s="8" t="s">
+        <v>2420</v>
       </c>
       <c r="F897" s="9" t="s">
         <v>17</v>
@@ -41045,20 +41045,20 @@
     </row>
     <row r="898" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A898" s="8" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="B898" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C898" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_127C</v>
+        <v>att_tmt_channel:tmt11_127N</v>
       </c>
       <c r="D898" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E898" s="8" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="F898" s="9" t="s">
         <v>17</v>
@@ -41066,20 +41066,20 @@
     </row>
     <row r="899" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A899" s="8" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="B899" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C899" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_127N</v>
+        <v>att_tmt_channel:tmt11_128C</v>
       </c>
       <c r="D899" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E899" s="8" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="F899" s="9" t="s">
         <v>17</v>
@@ -41087,20 +41087,20 @@
     </row>
     <row r="900" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A900" s="8" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="B900" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C900" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_128C</v>
+        <v>att_tmt_channel:tmt11_128N</v>
       </c>
       <c r="D900" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E900" s="8" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="F900" s="9" t="s">
         <v>17</v>
@@ -41108,20 +41108,20 @@
     </row>
     <row r="901" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A901" s="8" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="B901" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C901" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_128N</v>
+        <v>att_tmt_channel:tmt11_129C</v>
       </c>
       <c r="D901" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E901" s="8" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="F901" s="9" t="s">
         <v>17</v>
@@ -41129,20 +41129,20 @@
     </row>
     <row r="902" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A902" s="8" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="B902" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C902" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_129C</v>
+        <v>att_tmt_channel:tmt11_129N</v>
       </c>
       <c r="D902" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E902" s="8" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="F902" s="9" t="s">
         <v>17</v>
@@ -41150,20 +41150,20 @@
     </row>
     <row r="903" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A903" s="8" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="B903" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C903" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_129N</v>
+        <v>att_tmt_channel:tmt11_130C</v>
       </c>
       <c r="D903" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E903" s="8" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="F903" s="9" t="s">
         <v>17</v>
@@ -41171,20 +41171,20 @@
     </row>
     <row r="904" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A904" s="8" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="B904" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C904" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_130C</v>
+        <v>att_tmt_channel:tmt11_130N</v>
       </c>
       <c r="D904" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E904" s="8" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="F904" s="9" t="s">
         <v>17</v>
@@ -41192,20 +41192,20 @@
     </row>
     <row r="905" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A905" s="8" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="B905" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C905" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_130N</v>
+        <v>att_tmt_channel:tmt11_131C</v>
       </c>
       <c r="D905" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E905" s="8" t="s">
-        <v>2434</v>
+        <v>2446</v>
       </c>
       <c r="F905" s="9" t="s">
         <v>17</v>
@@ -41213,20 +41213,20 @@
     </row>
     <row r="906" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A906" s="8" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="B906" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C906" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_131C</v>
+        <v>att_tmt_channel:tmt11_131N</v>
       </c>
       <c r="D906" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E906" s="8" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="F906" s="9" t="s">
         <v>17</v>
@@ -41234,20 +41234,20 @@
     </row>
     <row r="907" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A907" s="8" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="B907" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C907" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt11_131N</v>
+        <v>att_tmt_channel:tmt18_126</v>
       </c>
       <c r="D907" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E907" s="8" t="s">
-        <v>2448</v>
+      <c r="E907" s="8">
+        <v>126</v>
       </c>
       <c r="F907" s="9" t="s">
         <v>17</v>
@@ -41255,20 +41255,20 @@
     </row>
     <row r="908" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A908" s="8" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="B908" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C908" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_126</v>
+        <v>att_tmt_channel:tmt18_127C</v>
       </c>
       <c r="D908" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E908" s="8">
-        <v>126</v>
+      <c r="E908" s="8" t="s">
+        <v>2420</v>
       </c>
       <c r="F908" s="9" t="s">
         <v>17</v>
@@ -41276,20 +41276,20 @@
     </row>
     <row r="909" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A909" s="8" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="B909" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C909" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_127C</v>
+        <v>att_tmt_channel:tmt18_127N</v>
       </c>
       <c r="D909" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E909" s="8" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="F909" s="9" t="s">
         <v>17</v>
@@ -41297,20 +41297,20 @@
     </row>
     <row r="910" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A910" s="8" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="B910" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C910" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_127N</v>
+        <v>att_tmt_channel:tmt18_128C</v>
       </c>
       <c r="D910" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E910" s="8" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="F910" s="9" t="s">
         <v>17</v>
@@ -41318,20 +41318,20 @@
     </row>
     <row r="911" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A911" s="8" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="B911" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C911" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_128C</v>
+        <v>att_tmt_channel:tmt18_128N</v>
       </c>
       <c r="D911" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E911" s="8" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="F911" s="9" t="s">
         <v>17</v>
@@ -41339,20 +41339,20 @@
     </row>
     <row r="912" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A912" s="8" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="B912" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C912" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_128N</v>
+        <v>att_tmt_channel:tmt18_129C</v>
       </c>
       <c r="D912" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E912" s="8" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="F912" s="9" t="s">
         <v>17</v>
@@ -41360,20 +41360,20 @@
     </row>
     <row r="913" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A913" s="8" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="B913" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C913" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_129C</v>
+        <v>att_tmt_channel:tmt18_129N</v>
       </c>
       <c r="D913" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E913" s="8" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="F913" s="9" t="s">
         <v>17</v>
@@ -41381,20 +41381,20 @@
     </row>
     <row r="914" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A914" s="8" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="B914" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C914" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_129N</v>
+        <v>att_tmt_channel:tmt18_130C</v>
       </c>
       <c r="D914" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E914" s="8" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="F914" s="9" t="s">
         <v>17</v>
@@ -41402,20 +41402,20 @@
     </row>
     <row r="915" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A915" s="8" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="B915" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C915" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_130C</v>
+        <v>att_tmt_channel:tmt18_130N</v>
       </c>
       <c r="D915" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E915" s="8" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="F915" s="9" t="s">
         <v>17</v>
@@ -41423,20 +41423,20 @@
     </row>
     <row r="916" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A916" s="8" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="B916" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C916" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_130N</v>
+        <v>att_tmt_channel:tmt18_131C</v>
       </c>
       <c r="D916" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E916" s="8" t="s">
-        <v>2434</v>
+        <v>2446</v>
       </c>
       <c r="F916" s="9" t="s">
         <v>17</v>
@@ -41444,20 +41444,20 @@
     </row>
     <row r="917" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A917" s="8" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="B917" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C917" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_131C</v>
+        <v>att_tmt_channel:tmt18_131N</v>
       </c>
       <c r="D917" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E917" s="8" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="F917" s="9" t="s">
         <v>17</v>
@@ -41465,20 +41465,20 @@
     </row>
     <row r="918" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A918" s="8" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="B918" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C918" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_131N</v>
+        <v>att_tmt_channel:tmt18_132C</v>
       </c>
       <c r="D918" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E918" s="8" t="s">
-        <v>2448</v>
+        <v>2461</v>
       </c>
       <c r="F918" s="9" t="s">
         <v>17</v>
@@ -41486,20 +41486,20 @@
     </row>
     <row r="919" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A919" s="8" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="B919" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C919" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_132C</v>
+        <v>att_tmt_channel:tmt18_132N</v>
       </c>
       <c r="D919" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E919" s="8" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="F919" s="9" t="s">
         <v>17</v>
@@ -41507,20 +41507,20 @@
     </row>
     <row r="920" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A920" s="8" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="B920" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C920" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_132N</v>
+        <v>att_tmt_channel:tmt18_133C</v>
       </c>
       <c r="D920" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E920" s="8" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="F920" s="9" t="s">
         <v>17</v>
@@ -41528,20 +41528,20 @@
     </row>
     <row r="921" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A921" s="8" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="B921" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C921" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_133C</v>
+        <v>att_tmt_channel:tmt18_133N</v>
       </c>
       <c r="D921" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E921" s="8" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="F921" s="9" t="s">
         <v>17</v>
@@ -41549,20 +41549,20 @@
     </row>
     <row r="922" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A922" s="8" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="B922" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C922" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_133N</v>
+        <v>att_tmt_channel:tmt18_134C</v>
       </c>
       <c r="D922" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E922" s="8" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="F922" s="9" t="s">
         <v>17</v>
@@ -41570,20 +41570,20 @@
     </row>
     <row r="923" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A923" s="8" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="B923" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C923" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_134C</v>
+        <v>att_tmt_channel:tmt18_134N</v>
       </c>
       <c r="D923" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E923" s="8" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="F923" s="9" t="s">
         <v>17</v>
@@ -41591,20 +41591,20 @@
     </row>
     <row r="924" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A924" s="8" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="B924" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C924" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_134N</v>
+        <v>att_tmt_channel:tmt18_135N</v>
       </c>
       <c r="D924" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E924" s="8" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="F924" s="9" t="s">
         <v>17</v>
@@ -41612,20 +41612,20 @@
     </row>
     <row r="925" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A925" s="8" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="B925" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C925" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt18_135N</v>
+        <v>att_tmt_channel:tmt6_126</v>
       </c>
       <c r="D925" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E925" s="8" t="s">
-        <v>2473</v>
+      <c r="E925" s="8">
+        <v>126</v>
       </c>
       <c r="F925" s="9" t="s">
         <v>17</v>
@@ -41633,20 +41633,20 @@
     </row>
     <row r="926" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A926" s="8" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="B926" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C926" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt6_126</v>
+        <v>att_tmt_channel:tmt6_127</v>
       </c>
       <c r="D926" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E926" s="8">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F926" s="9" t="s">
         <v>17</v>
@@ -41654,20 +41654,20 @@
     </row>
     <row r="927" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A927" s="8" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="B927" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C927" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt6_127</v>
+        <v>att_tmt_channel:tmt6_128</v>
       </c>
       <c r="D927" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E927" s="8">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F927" s="9" t="s">
         <v>17</v>
@@ -41675,20 +41675,20 @@
     </row>
     <row r="928" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A928" s="8" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="B928" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C928" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt6_128</v>
+        <v>att_tmt_channel:tmt6_129</v>
       </c>
       <c r="D928" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E928" s="8">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F928" s="9" t="s">
         <v>17</v>
@@ -41696,20 +41696,20 @@
     </row>
     <row r="929" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A929" s="8" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="B929" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C929" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt6_129</v>
+        <v>att_tmt_channel:tmt6_130</v>
       </c>
       <c r="D929" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E929" s="8">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F929" s="9" t="s">
         <v>17</v>
@@ -41717,20 +41717,20 @@
     </row>
     <row r="930" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A930" s="8" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="B930" s="8" t="s">
         <v>234</v>
       </c>
       <c r="C930" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt6_130</v>
+        <v>att_tmt_channel:tmt6_131</v>
       </c>
       <c r="D930" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E930" s="8">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F930" s="9" t="s">
         <v>17</v>
@@ -41738,230 +41738,230 @@
     </row>
     <row r="931" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A931" s="8" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="B931" s="8" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="C931" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_tmt_channel:tmt6_131</v>
+        <v>att_user_institute:biochem</v>
       </c>
       <c r="D931" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E931" s="8">
-        <v>131</v>
-      </c>
-      <c r="F931" s="9" t="s">
-        <v>17</v>
+      <c r="E931" s="8" t="s">
+        <v>2481</v>
+      </c>
+      <c r="F931" s="8" t="s">
+        <v>2482</v>
       </c>
     </row>
     <row r="932" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A932" s="8" t="s">
-        <v>2480</v>
+        <v>2483</v>
       </c>
       <c r="B932" s="8" t="s">
         <v>242</v>
       </c>
       <c r="C932" s="8" t="str">
         <f t="shared" si="39"/>
-        <v>att_user_institute:biochem</v>
+        <v>att_user_institute:cecad</v>
       </c>
       <c r="D932" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E932" s="8" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="F932" s="8" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="933" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A933" s="8" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="B933" s="8" t="s">
         <v>242</v>
       </c>
       <c r="C933" s="8" t="str">
-        <f t="shared" si="39"/>
-        <v>att_user_institute:cecad</v>
+        <f t="shared" ref="C933:C942" si="43">B933&amp;":"&amp;A933</f>
+        <v>att_user_institute:mpiage</v>
       </c>
       <c r="D933" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E933" s="8" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
       <c r="F933" s="8" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="934" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A934" s="8" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
       <c r="B934" s="8" t="s">
         <v>242</v>
       </c>
       <c r="C934" s="8" t="str">
-        <f t="shared" ref="C934:C943" si="43">B934&amp;":"&amp;A934</f>
-        <v>att_user_institute:mpiage</v>
+        <f t="shared" si="43"/>
+        <v>att_user_institute:mpimetab</v>
       </c>
       <c r="D934" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E934" s="8" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
       <c r="F934" s="8" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="935" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A935" s="8" t="s">
-        <v>2489</v>
+        <v>3053</v>
       </c>
       <c r="B935" s="8" t="s">
         <v>242</v>
       </c>
       <c r="C935" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_institute:mpimetab</v>
+        <v>att_user_institute:unibonn</v>
       </c>
       <c r="D935" s="9" t="s">
         <v>17</v>
       </c>
       <c r="E935" s="8" t="s">
-        <v>2490</v>
+        <v>3054</v>
       </c>
       <c r="F935" s="8" t="s">
-        <v>2491</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="936" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A936" s="8" t="s">
-        <v>3053</v>
+        <v>2492</v>
       </c>
       <c r="B936" s="8" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="C936" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_institute:unibonn</v>
-      </c>
-      <c r="D936" s="9" t="s">
+        <v>att_user_research_group:mitoprotea</v>
+      </c>
+      <c r="D936" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E936" s="8" t="s">
-        <v>3054</v>
+        <v>2493</v>
       </c>
       <c r="F936" s="8" t="s">
-        <v>3054</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="937" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A937" s="8" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="B937" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C937" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_research_group:mitoprotea</v>
+        <v>att_user_research_group:molageing</v>
       </c>
       <c r="D937" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E937" s="8" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="F937" s="8" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="938" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A938" s="8" t="s">
-        <v>2495</v>
+        <v>3159</v>
       </c>
       <c r="B938" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C938" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_research_group:molageing</v>
+        <v>att_user_research_group:protfa</v>
       </c>
       <c r="D938" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E938" s="8" t="s">
-        <v>2496</v>
+        <v>3158</v>
       </c>
       <c r="F938" s="8" t="s">
-        <v>2497</v>
+        <v>3157</v>
       </c>
     </row>
     <row r="939" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A939" s="8" t="s">
-        <v>3159</v>
+        <v>2859</v>
       </c>
       <c r="B939" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C939" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_research_group:protfa</v>
+        <v>att_user_research_group:frezza</v>
       </c>
       <c r="D939" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E939" s="8" t="s">
-        <v>3158</v>
+        <v>2860</v>
       </c>
       <c r="F939" s="8" t="s">
-        <v>3157</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="940" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A940" s="8" t="s">
-        <v>2859</v>
+        <v>2862</v>
       </c>
       <c r="B940" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C940" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_research_group:frezza</v>
+        <v>att_user_research_group:krueger</v>
       </c>
       <c r="D940" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E940" s="8" t="s">
-        <v>2860</v>
+        <v>2863</v>
       </c>
       <c r="F940" s="8" t="s">
-        <v>2861</v>
+        <v>2864</v>
       </c>
     </row>
     <row r="941" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A941" s="8" t="s">
-        <v>2862</v>
+        <v>2865</v>
       </c>
       <c r="B941" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C941" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_research_group:krueger</v>
+        <v>att_user_research_group:rugarli</v>
       </c>
       <c r="D941" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E941" s="8" t="s">
-        <v>2863</v>
+        <v>2866</v>
       </c>
       <c r="F941" s="8" t="s">
         <v>2864</v>
@@ -41969,272 +41969,272 @@
     </row>
     <row r="942" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A942" s="8" t="s">
-        <v>2865</v>
+        <v>2867</v>
       </c>
       <c r="B942" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C942" s="8" t="str">
         <f t="shared" si="43"/>
-        <v>att_user_research_group:rugarli</v>
+        <v>att_user_research_group:trifunovic</v>
       </c>
       <c r="D942" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E942" s="8" t="s">
-        <v>2866</v>
+        <v>2868</v>
       </c>
       <c r="F942" s="8" t="s">
-        <v>2864</v>
+        <v>2869</v>
       </c>
     </row>
     <row r="943" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A943" s="8" t="s">
-        <v>2867</v>
+        <v>3027</v>
       </c>
       <c r="B943" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C943" s="8" t="str">
-        <f t="shared" si="43"/>
-        <v>att_user_research_group:trifunovic</v>
+        <f t="shared" ref="C943:C952" si="44">B943&amp;":"&amp;A943</f>
+        <v>att_user_research_group:bergmani</v>
       </c>
       <c r="D943" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E943" s="8" t="s">
-        <v>2868</v>
+        <v>3035</v>
       </c>
       <c r="F943" s="8" t="s">
-        <v>2869</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="944" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A944" s="8" t="s">
-        <v>3027</v>
+        <v>3028</v>
       </c>
       <c r="B944" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C944" s="8" t="str">
-        <f t="shared" ref="C944:C953" si="44">B944&amp;":"&amp;A944</f>
-        <v>att_user_research_group:bergmani</v>
+        <f t="shared" si="44"/>
+        <v>att_user_research_group:motori</v>
       </c>
       <c r="D944" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E944" s="8" t="s">
-        <v>3035</v>
+        <v>3036</v>
       </c>
       <c r="F944" s="8" t="s">
-        <v>3045</v>
+        <v>3046</v>
       </c>
     </row>
     <row r="945" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A945" s="8" t="s">
-        <v>3028</v>
+        <v>3029</v>
       </c>
       <c r="B945" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C945" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:motori</v>
+        <v>att_user_research_group:becker</v>
       </c>
       <c r="D945" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E945" s="8" t="s">
-        <v>3036</v>
+        <v>3037</v>
       </c>
       <c r="F945" s="8" t="s">
-        <v>3046</v>
+        <v>3052</v>
       </c>
     </row>
     <row r="946" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A946" s="8" t="s">
-        <v>3029</v>
+        <v>3030</v>
       </c>
       <c r="B946" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C946" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:becker</v>
+        <v>att_user_research_group:bruening</v>
       </c>
       <c r="D946" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E946" s="8" t="s">
-        <v>3037</v>
+        <v>3050</v>
       </c>
       <c r="F946" s="8" t="s">
-        <v>3052</v>
+        <v>3049</v>
       </c>
     </row>
     <row r="947" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A947" s="8" t="s">
-        <v>3030</v>
+        <v>3039</v>
       </c>
       <c r="B947" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C947" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:bruening</v>
+        <v>att_user_research_group:escobar</v>
       </c>
       <c r="D947" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E947" s="8" t="s">
-        <v>3050</v>
+        <v>3038</v>
       </c>
       <c r="F947" s="8" t="s">
-        <v>3049</v>
+        <v>3047</v>
       </c>
     </row>
     <row r="948" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A948" s="8" t="s">
-        <v>3039</v>
+        <v>2896</v>
       </c>
       <c r="B948" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C948" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:escobar</v>
+        <v>att_user_research_group:garcia</v>
       </c>
       <c r="D948" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E948" s="8" t="s">
-        <v>3038</v>
+        <v>2897</v>
       </c>
       <c r="F948" s="8" t="s">
-        <v>3047</v>
+        <v>3048</v>
       </c>
     </row>
     <row r="949" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A949" s="8" t="s">
-        <v>2896</v>
+        <v>3031</v>
       </c>
       <c r="B949" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C949" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:garcia</v>
+        <v>att_user_research_group:piano</v>
       </c>
       <c r="D949" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E949" s="8" t="s">
-        <v>2897</v>
+        <v>3040</v>
       </c>
       <c r="F949" s="8" t="s">
-        <v>3048</v>
+        <v>3055</v>
       </c>
     </row>
     <row r="950" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A950" s="8" t="s">
-        <v>3031</v>
+        <v>3032</v>
       </c>
       <c r="B950" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C950" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:piano</v>
+        <v>att_user_research_group:schwarz</v>
       </c>
       <c r="D950" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E950" s="8" t="s">
-        <v>3040</v>
+        <v>3041</v>
       </c>
       <c r="F950" s="8" t="s">
-        <v>3055</v>
+        <v>3051</v>
       </c>
     </row>
     <row r="951" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A951" s="8" t="s">
-        <v>3032</v>
+        <v>3033</v>
       </c>
       <c r="B951" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C951" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:schwarz</v>
+        <v>att_user_research_group:corrado</v>
       </c>
       <c r="D951" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E951" s="8" t="s">
-        <v>3041</v>
+        <v>3042</v>
       </c>
       <c r="F951" s="8" t="s">
-        <v>3051</v>
+        <v>3056</v>
       </c>
     </row>
     <row r="952" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A952" s="8" t="s">
-        <v>3033</v>
+        <v>3034</v>
       </c>
       <c r="B952" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C952" s="8" t="str">
         <f t="shared" si="44"/>
-        <v>att_user_research_group:corrado</v>
+        <v>att_user_research_group:eming</v>
       </c>
       <c r="D952" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E952" s="8" t="s">
-        <v>3042</v>
+        <v>3043</v>
       </c>
       <c r="F952" s="8" t="s">
-        <v>3056</v>
+        <v>3044</v>
       </c>
     </row>
     <row r="953" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A953" s="8" t="s">
-        <v>3034</v>
+        <v>2893</v>
       </c>
       <c r="B953" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C953" s="8" t="str">
-        <f t="shared" si="44"/>
-        <v>att_user_research_group:eming</v>
+        <f t="shared" ref="C953:C989" si="45">B953&amp;":"&amp;A953</f>
+        <v>att_user_research_group:hoppe</v>
       </c>
       <c r="D953" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E953" s="8" t="s">
-        <v>3043</v>
+        <v>2894</v>
       </c>
       <c r="F953" s="8" t="s">
-        <v>3044</v>
+        <v>2895</v>
       </c>
     </row>
     <row r="954" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A954" s="8" t="s">
-        <v>2893</v>
+        <v>2896</v>
       </c>
       <c r="B954" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C954" s="8" t="str">
-        <f t="shared" ref="C954:C990" si="45">B954&amp;":"&amp;A954</f>
-        <v>att_user_research_group:hoppe</v>
+        <f t="shared" si="45"/>
+        <v>att_user_research_group:garcia</v>
       </c>
       <c r="D954" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E954" s="8" t="s">
-        <v>2894</v>
+        <v>2897</v>
       </c>
       <c r="F954" s="8" t="s">
         <v>2895</v>
@@ -42242,416 +42242,416 @@
     </row>
     <row r="955" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A955" s="8" t="s">
-        <v>2896</v>
+        <v>2898</v>
       </c>
       <c r="B955" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C955" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_user_research_group:garcia</v>
+        <v>att_user_research_group:khaskar</v>
       </c>
       <c r="D955" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E955" s="8" t="s">
-        <v>2897</v>
+        <v>2899</v>
       </c>
       <c r="F955" s="8" t="s">
-        <v>2895</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="956" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A956" s="8" t="s">
-        <v>2898</v>
+        <v>3023</v>
       </c>
       <c r="B956" s="8" t="s">
         <v>246</v>
       </c>
       <c r="C956" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_user_research_group:khaskar</v>
+        <v>att_user_research_group:riemer</v>
       </c>
       <c r="D956" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E956" s="8" t="s">
-        <v>2899</v>
+        <v>3024</v>
       </c>
       <c r="F956" s="8" t="s">
-        <v>2900</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="957" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A957" s="8" t="s">
-        <v>3023</v>
-      </c>
-      <c r="B957" s="8" t="s">
-        <v>246</v>
+        <v>2811</v>
+      </c>
+      <c r="B957" s="22" t="s">
+        <v>2807</v>
       </c>
       <c r="C957" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_user_research_group:riemer</v>
+        <v>att_diet:wd</v>
       </c>
       <c r="D957" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E957" s="8" t="s">
-        <v>3024</v>
+        <v>2810</v>
       </c>
       <c r="F957" s="8" t="s">
-        <v>3025</v>
+        <v>2809</v>
       </c>
     </row>
     <row r="958" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A958" s="8" t="s">
-        <v>2811</v>
+        <v>2812</v>
       </c>
       <c r="B958" s="22" t="s">
         <v>2807</v>
       </c>
       <c r="C958" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_diet:wd</v>
+        <v>att_diet:sd</v>
       </c>
       <c r="D958" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E958" s="8" t="s">
-        <v>2810</v>
-      </c>
-      <c r="F958" s="8" t="s">
-        <v>2809</v>
+        <v>2813</v>
       </c>
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A959" s="8" t="s">
-        <v>2812</v>
+        <v>2814</v>
       </c>
       <c r="B959" s="22" t="s">
         <v>2807</v>
       </c>
       <c r="C959" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_diet:sd</v>
+        <v>att_diet:veg</v>
       </c>
       <c r="D959" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E959" s="8" t="s">
-        <v>2813</v>
+        <v>2815</v>
+      </c>
+      <c r="F959" s="8" t="s">
+        <v>2816</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A960" s="8" t="s">
-        <v>2814</v>
+        <v>2819</v>
       </c>
       <c r="B960" s="22" t="s">
         <v>2807</v>
       </c>
       <c r="C960" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_diet:veg</v>
+        <v>att_diet:hg</v>
       </c>
       <c r="D960" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E960" s="8" t="s">
-        <v>2815</v>
+        <v>2817</v>
       </c>
       <c r="F960" s="8" t="s">
-        <v>2816</v>
+        <v>2818</v>
       </c>
     </row>
     <row r="961" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A961" s="8" t="s">
-        <v>2819</v>
-      </c>
-      <c r="B961" s="22" t="s">
+        <v>2822</v>
+      </c>
+      <c r="B961" s="8" t="s">
         <v>2807</v>
       </c>
       <c r="C961" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_diet:hg</v>
+        <v>att_diet:hfd</v>
       </c>
       <c r="D961" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E961" s="8" t="s">
-        <v>2817</v>
+        <v>2820</v>
       </c>
       <c r="F961" s="8" t="s">
-        <v>2818</v>
+        <v>2821</v>
       </c>
     </row>
     <row r="962" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A962" s="8" t="s">
-        <v>2822</v>
+        <v>2970</v>
       </c>
       <c r="B962" s="8" t="s">
-        <v>2807</v>
+        <v>40</v>
       </c>
       <c r="C962" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_diet:hfd</v>
+        <v>att_cell:mdc</v>
       </c>
       <c r="D962" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E962" s="8" t="s">
-        <v>2820</v>
+        <v>2991</v>
       </c>
       <c r="F962" s="8" t="s">
-        <v>2821</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="963" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A963" s="8" t="s">
-        <v>2970</v>
+        <v>2971</v>
       </c>
       <c r="B963" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C963" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:mdc</v>
+        <v>att_cell:mtregs</v>
       </c>
       <c r="D963" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E963" s="8" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
       <c r="F963" s="8" t="s">
-        <v>2990</v>
+        <v>2988</v>
       </c>
     </row>
     <row r="964" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A964" s="8" t="s">
-        <v>2971</v>
+        <v>2972</v>
       </c>
       <c r="B964" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C964" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:mtregs</v>
+        <v>att_cell:pdc</v>
       </c>
       <c r="D964" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E964" s="8" t="s">
-        <v>2989</v>
+        <v>2992</v>
       </c>
       <c r="F964" s="8" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
     </row>
     <row r="965" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A965" s="8" t="s">
-        <v>2972</v>
+        <v>2973</v>
       </c>
       <c r="B965" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C965" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:pdc</v>
+        <v>att_cell:attregs</v>
       </c>
       <c r="D965" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E965" s="8" t="s">
-        <v>2992</v>
+        <v>2986</v>
       </c>
       <c r="F965" s="8" t="s">
-        <v>2987</v>
+        <v>2993</v>
       </c>
     </row>
     <row r="966" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A966" s="8" t="s">
-        <v>2973</v>
+        <v>2974</v>
       </c>
       <c r="B966" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C966" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:attregs</v>
+        <v>att_cell:infdc</v>
       </c>
       <c r="D966" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E966" s="8" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="F966" s="8" t="s">
-        <v>2993</v>
+        <v>2984</v>
       </c>
     </row>
     <row r="967" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A967" s="8" t="s">
-        <v>2974</v>
+        <v>2975</v>
       </c>
       <c r="B967" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C967" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:infdc</v>
+        <v>att_cell:itgres</v>
       </c>
       <c r="D967" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E967" s="8" t="s">
-        <v>2985</v>
+        <v>2983</v>
       </c>
       <c r="F967" s="8" t="s">
-        <v>2984</v>
+        <v>2982</v>
       </c>
     </row>
     <row r="968" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A968" s="8" t="s">
-        <v>2975</v>
+        <v>2976</v>
       </c>
       <c r="B968" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C968" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:itgres</v>
+        <v>att_cell:dendritic</v>
       </c>
       <c r="D968" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E968" s="8" t="s">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="F968" s="8" t="s">
-        <v>2982</v>
+        <v>2980</v>
       </c>
     </row>
     <row r="969" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A969" s="8" t="s">
-        <v>2976</v>
+        <v>2977</v>
       </c>
       <c r="B969" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C969" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:dendritic</v>
+        <v>att_cell:ememcell</v>
       </c>
       <c r="D969" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E969" s="8" t="s">
-        <v>2981</v>
+        <v>2979</v>
       </c>
       <c r="F969" s="8" t="s">
-        <v>2980</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="970" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A970" s="8" t="s">
-        <v>2977</v>
+        <v>2994</v>
       </c>
       <c r="B970" s="8" t="s">
-        <v>40</v>
+        <v>2908</v>
       </c>
       <c r="C970" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_cell:ememcell</v>
+        <v>att_subcellular_compartment:supernatant</v>
       </c>
       <c r="D970" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E970" s="8" t="s">
-        <v>2979</v>
+        <v>2995</v>
       </c>
       <c r="F970" s="8" t="s">
-        <v>2978</v>
+        <v>2996</v>
       </c>
     </row>
     <row r="971" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A971" s="8" t="s">
-        <v>2994</v>
+        <v>2998</v>
       </c>
       <c r="B971" s="8" t="s">
-        <v>2908</v>
+        <v>2997</v>
       </c>
       <c r="C971" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_subcellular_compartment:supernatant</v>
+        <v>att_heart:leftatrium</v>
       </c>
       <c r="D971" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E971" s="8" t="s">
-        <v>2995</v>
+        <v>2999</v>
       </c>
       <c r="F971" s="8" t="s">
-        <v>2996</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="972" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A972" s="8" t="s">
-        <v>2998</v>
+        <v>3001</v>
       </c>
       <c r="B972" s="8" t="s">
         <v>2997</v>
       </c>
       <c r="C972" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_heart:leftatrium</v>
+        <v>att_heart:rightatrium</v>
       </c>
       <c r="D972" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E972" s="8" t="s">
-        <v>2999</v>
+        <v>3002</v>
       </c>
       <c r="F972" s="8" t="s">
-        <v>3000</v>
+        <v>3003</v>
       </c>
     </row>
     <row r="973" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A973" s="8" t="s">
-        <v>3001</v>
+        <v>3021</v>
       </c>
       <c r="B973" s="8" t="s">
         <v>2997</v>
       </c>
       <c r="C973" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_heart:rightatrium</v>
+        <v>att_heart:leftventri</v>
       </c>
       <c r="D973" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E973" s="8" t="s">
-        <v>3002</v>
+        <v>3019</v>
       </c>
       <c r="F973" s="8" t="s">
-        <v>3003</v>
+        <v>3004</v>
       </c>
     </row>
     <row r="974" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A974" s="8" t="s">
-        <v>3021</v>
+        <v>3022</v>
       </c>
       <c r="B974" s="8" t="s">
         <v>2997</v>
       </c>
       <c r="C974" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_heart:leftventri</v>
+        <v>att_heart:rightventri</v>
       </c>
       <c r="D974" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E974" s="8" t="s">
-        <v>3019</v>
+        <v>3020</v>
       </c>
       <c r="F974" s="8" t="s">
         <v>3004</v>
@@ -42659,335 +42659,335 @@
     </row>
     <row r="975" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A975" s="8" t="s">
-        <v>3022</v>
+        <v>3095</v>
       </c>
       <c r="B975" s="8" t="s">
-        <v>2997</v>
+        <v>3093</v>
       </c>
       <c r="C975" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_heart:rightventri</v>
+        <v>att_muscle_fiber_type:type1</v>
       </c>
       <c r="D975" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E975" s="8" t="s">
-        <v>3020</v>
+        <v>3113</v>
       </c>
       <c r="F975" s="8" t="s">
-        <v>3004</v>
+        <v>3118</v>
       </c>
     </row>
     <row r="976" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A976" s="8" t="s">
-        <v>3095</v>
+        <v>3096</v>
       </c>
       <c r="B976" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C976" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:type1</v>
+        <v>att_muscle_fiber_type:type2a</v>
       </c>
       <c r="D976" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E976" s="8" t="s">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="F976" s="8" t="s">
-        <v>3118</v>
+        <v>3119</v>
       </c>
     </row>
     <row r="977" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A977" s="8" t="s">
-        <v>3096</v>
+        <v>3097</v>
       </c>
       <c r="B977" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C977" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:type2a</v>
+        <v>att_muscle_fiber_type:type2b</v>
       </c>
       <c r="D977" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E977" s="8" t="s">
-        <v>3114</v>
+        <v>3115</v>
       </c>
       <c r="F977" s="8" t="s">
-        <v>3119</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="978" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A978" s="8" t="s">
-        <v>3097</v>
+        <v>3098</v>
       </c>
       <c r="B978" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C978" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:type2b</v>
+        <v>att_muscle_fiber_type:type2x</v>
       </c>
       <c r="D978" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E978" s="8" t="s">
-        <v>3115</v>
+        <v>3116</v>
       </c>
       <c r="F978" s="8" t="s">
-        <v>3120</v>
+        <v>3121</v>
       </c>
     </row>
     <row r="979" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A979" s="8" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="B979" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C979" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:type2x</v>
+        <v>att_muscle_fiber_type:type2d</v>
       </c>
       <c r="D979" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E979" s="8" t="s">
-        <v>3116</v>
+        <v>3117</v>
       </c>
       <c r="F979" s="8" t="s">
-        <v>3121</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="980" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A980" s="8" t="s">
-        <v>3099</v>
+        <v>3101</v>
       </c>
       <c r="B980" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C980" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:type2d</v>
+        <v>att_muscle_fiber_type:mixedt12a</v>
       </c>
       <c r="D980" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E980" s="8" t="s">
-        <v>3117</v>
+        <v>3102</v>
       </c>
       <c r="F980" s="8" t="s">
-        <v>3100</v>
+        <v>3123</v>
       </c>
     </row>
     <row r="981" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A981" s="8" t="s">
-        <v>3101</v>
+        <v>3103</v>
       </c>
       <c r="B981" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C981" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:mixedt12a</v>
+        <v>att_muscle_fiber_type:mixedt12x</v>
       </c>
       <c r="D981" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E981" s="8" t="s">
-        <v>3102</v>
+        <v>3104</v>
       </c>
       <c r="F981" s="8" t="s">
-        <v>3123</v>
+        <v>3122</v>
       </c>
     </row>
     <row r="982" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A982" s="8" t="s">
-        <v>3103</v>
+        <v>3105</v>
       </c>
       <c r="B982" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C982" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:mixedt12x</v>
+        <v>att_muscle_fiber_type:mixedt1tb</v>
       </c>
       <c r="D982" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E982" s="8" t="s">
-        <v>3104</v>
+        <v>3106</v>
       </c>
       <c r="F982" s="8" t="s">
-        <v>3122</v>
+        <v>3124</v>
       </c>
     </row>
     <row r="983" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A983" s="8" t="s">
-        <v>3105</v>
+        <v>3107</v>
       </c>
       <c r="B983" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C983" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:mixedt1tb</v>
+        <v>att_muscle_fiber_type:mixed2a2b</v>
       </c>
       <c r="D983" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E983" s="8" t="s">
-        <v>3106</v>
+        <v>3108</v>
       </c>
       <c r="F983" s="8" t="s">
-        <v>3124</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A984" s="8" t="s">
-        <v>3107</v>
+        <v>3109</v>
       </c>
       <c r="B984" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C984" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:mixed2a2b</v>
+        <v>att_muscle_fiber_type:mixed2a2x</v>
       </c>
       <c r="D984" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E984" s="8" t="s">
-        <v>3108</v>
+        <v>3110</v>
       </c>
       <c r="F984" s="8" t="s">
-        <v>3125</v>
+        <v>3126</v>
       </c>
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A985" s="8" t="s">
-        <v>3109</v>
+        <v>3111</v>
       </c>
       <c r="B985" s="8" t="s">
         <v>3093</v>
       </c>
       <c r="C985" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:mixed2a2x</v>
+        <v>att_muscle_fiber_type:mixed2b2x</v>
       </c>
       <c r="D985" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E985" s="8" t="s">
-        <v>3110</v>
+        <v>3112</v>
       </c>
       <c r="F985" s="8" t="s">
-        <v>3126</v>
+        <v>3127</v>
       </c>
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A986" s="8" t="s">
-        <v>3111</v>
+        <v>3167</v>
       </c>
       <c r="B986" s="8" t="s">
-        <v>3093</v>
+        <v>3173</v>
       </c>
       <c r="C986" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_muscle_fiber_type:mixed2b2x</v>
+        <v>att_solubilization_frac:pellet</v>
       </c>
       <c r="D986" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E986" s="8" t="s">
-        <v>3112</v>
+        <v>3168</v>
       </c>
       <c r="F986" s="8" t="s">
-        <v>3127</v>
+        <v>3174</v>
       </c>
     </row>
     <row r="987" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A987" s="8" t="s">
-        <v>3167</v>
+        <v>1243</v>
       </c>
       <c r="B987" s="8" t="s">
         <v>3173</v>
       </c>
       <c r="C987" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_solubilization_frac:pellet</v>
+        <v>att_solubilization_frac:total</v>
       </c>
       <c r="D987" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E987" s="8" t="s">
-        <v>3168</v>
+        <v>1244</v>
       </c>
       <c r="F987" s="8" t="s">
-        <v>3174</v>
+        <v>3175</v>
       </c>
     </row>
     <row r="988" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A988" s="8" t="s">
-        <v>1243</v>
+        <v>2994</v>
       </c>
       <c r="B988" s="8" t="s">
         <v>3173</v>
       </c>
       <c r="C988" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_solubilization_frac:total</v>
+        <v>att_solubilization_frac:supernatant</v>
       </c>
       <c r="D988" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E988" s="8" t="s">
-        <v>1244</v>
+        <v>2995</v>
       </c>
       <c r="F988" s="8" t="s">
-        <v>3175</v>
+        <v>3176</v>
       </c>
     </row>
     <row r="989" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A989" s="8" t="s">
-        <v>2994</v>
+      <c r="A989" s="8">
+        <v>275</v>
       </c>
       <c r="B989" s="8" t="s">
-        <v>3173</v>
+        <v>37</v>
       </c>
       <c r="C989" s="8" t="str">
         <f t="shared" si="45"/>
-        <v>att_solubilization_frac:supernatant</v>
+        <v>att_cap_temp:275</v>
       </c>
       <c r="D989" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E989" s="8" t="s">
-        <v>2995</v>
+      <c r="E989" s="8">
+        <v>275</v>
       </c>
       <c r="F989" s="8" t="s">
-        <v>3176</v>
+        <v>17</v>
       </c>
     </row>
     <row r="990" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A990" s="8">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="B990" s="8" t="s">
         <v>37</v>
       </c>
       <c r="C990" s="8" t="str">
-        <f t="shared" si="45"/>
-        <v>att_cap_temp:275</v>
+        <f t="shared" ref="C990:C993" si="46">B990&amp;":"&amp;A990</f>
+        <v>att_cap_temp:320</v>
       </c>
       <c r="D990" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E990" s="8">
-        <v>275</v>
+        <v>320</v>
       </c>
       <c r="F990" s="8" t="s">
         <v>17</v>
@@ -42995,279 +42995,261 @@
     </row>
     <row r="991" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A991" s="8">
-        <v>320</v>
+        <v>-45</v>
       </c>
       <c r="B991" s="8" t="s">
-        <v>37</v>
+        <v>114</v>
       </c>
       <c r="C991" s="8" t="str">
-        <f t="shared" ref="C991:C994" si="46">B991&amp;":"&amp;A991</f>
-        <v>att_cap_temp:320</v>
+        <f t="shared" si="46"/>
+        <v>att_faims_cv:-45</v>
       </c>
       <c r="D991" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E991" s="8">
-        <v>320</v>
+        <v>-45</v>
       </c>
       <c r="F991" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="992" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A992" s="8">
-        <v>-45</v>
-      </c>
-      <c r="B992" s="8" t="s">
-        <v>114</v>
+      <c r="A992" s="8" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B992" t="s">
+        <v>3223</v>
       </c>
       <c r="C992" s="8" t="str">
         <f t="shared" si="46"/>
-        <v>att_faims_cv:-45</v>
+        <v>att_enrich_frac:input</v>
       </c>
       <c r="D992" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E992" s="8">
-        <v>-45</v>
-      </c>
-      <c r="F992" s="8" t="s">
-        <v>17</v>
+      <c r="E992" s="8" t="s">
+        <v>3225</v>
+      </c>
+      <c r="F992" t="s">
+        <v>3226</v>
       </c>
     </row>
     <row r="993" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A993" s="8" t="s">
-        <v>3224</v>
+        <v>3230</v>
       </c>
       <c r="B993" t="s">
         <v>3223</v>
       </c>
       <c r="C993" s="8" t="str">
         <f t="shared" si="46"/>
-        <v>att_enrich_frac:input</v>
+        <v>att_enrich_frac:elution</v>
       </c>
       <c r="D993" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E993" s="8" t="s">
-        <v>3225</v>
-      </c>
-      <c r="F993" t="s">
-        <v>3226</v>
+        <v>3227</v>
+      </c>
+      <c r="F993" s="8" t="s">
+        <v>3232</v>
       </c>
     </row>
     <row r="994" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A994" s="8" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="B994" t="s">
         <v>3223</v>
       </c>
       <c r="C994" s="8" t="str">
-        <f t="shared" si="46"/>
-        <v>att_enrich_frac:elution</v>
+        <f t="shared" ref="C994:C1002" si="47">B994&amp;":"&amp;A994</f>
+        <v>att_enrich_frac:wash</v>
       </c>
       <c r="D994" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E994" s="8" t="s">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="F994" s="8" t="s">
-        <v>3232</v>
-      </c>
-    </row>
-    <row r="995" spans="1:6" x14ac:dyDescent="0.15">
+        <v>3231</v>
+      </c>
+    </row>
+    <row r="995" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A995" s="8" t="s">
-        <v>3229</v>
-      </c>
-      <c r="B995" t="s">
-        <v>3223</v>
+        <v>3237</v>
+      </c>
+      <c r="B995" s="25" t="s">
+        <v>3239</v>
       </c>
       <c r="C995" s="8" t="str">
-        <f t="shared" ref="C995:C1003" si="47">B995&amp;":"&amp;A995</f>
-        <v>att_enrich_frac:wash</v>
+        <f t="shared" si="47"/>
+        <v>att_cellculture_media:fbs</v>
       </c>
       <c r="D995" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E995" s="8" t="s">
-        <v>3228</v>
-      </c>
-      <c r="F995" s="8" t="s">
-        <v>3231</v>
+        <v>3243</v>
+      </c>
+      <c r="F995" s="27" t="s">
+        <v>3241</v>
       </c>
     </row>
     <row r="996" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A996" s="8" t="s">
-        <v>3237</v>
+        <v>3238</v>
       </c>
       <c r="B996" s="25" t="s">
         <v>3239</v>
       </c>
       <c r="C996" s="8" t="str">
         <f t="shared" si="47"/>
-        <v>att_cellculture_media:fbs</v>
+        <v>att_cellculture_media:nofbs</v>
       </c>
       <c r="D996" s="8" t="s">
         <v>17</v>
       </c>
       <c r="E996" s="8" t="s">
-        <v>3243</v>
-      </c>
-      <c r="F996" s="27" t="s">
-        <v>3241</v>
-      </c>
-    </row>
-    <row r="997" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+        <v>3244</v>
+      </c>
+      <c r="F996" s="8" t="s">
+        <v>3242</v>
+      </c>
+    </row>
+    <row r="997" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A997" s="8" t="s">
-        <v>3238</v>
-      </c>
-      <c r="B997" s="25" t="s">
-        <v>3239</v>
+        <v>2186</v>
+      </c>
+      <c r="B997" s="8" t="s">
+        <v>192</v>
       </c>
       <c r="C997" s="8" t="str">
         <f t="shared" si="47"/>
-        <v>att_cellculture_media:nofbs</v>
+        <v>att_organism:UP000000589</v>
       </c>
       <c r="D997" s="8" t="s">
-        <v>17</v>
+        <v>2187</v>
       </c>
       <c r="E997" s="8" t="s">
-        <v>3244</v>
+        <v>2188</v>
       </c>
       <c r="F997" s="8" t="s">
-        <v>3242</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="998" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A998" s="8" t="s">
-        <v>2186</v>
+        <v>2190</v>
       </c>
       <c r="B998" s="8" t="s">
         <v>192</v>
       </c>
       <c r="C998" s="8" t="str">
         <f t="shared" si="47"/>
-        <v>att_organism:UP000000589</v>
+        <v>att_organism:UP000001940</v>
       </c>
       <c r="D998" s="8" t="s">
-        <v>2187</v>
+        <v>2191</v>
       </c>
       <c r="E998" s="8" t="s">
-        <v>2188</v>
+        <v>2192</v>
       </c>
       <c r="F998" s="8" t="s">
-        <v>2189</v>
+        <v>2193</v>
       </c>
     </row>
     <row r="999" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A999" s="8" t="s">
-        <v>2190</v>
+        <v>2194</v>
       </c>
       <c r="B999" s="8" t="s">
         <v>192</v>
       </c>
       <c r="C999" s="8" t="str">
         <f t="shared" si="47"/>
-        <v>att_organism:UP000001940</v>
+        <v>att_organism:UP000002311</v>
       </c>
       <c r="D999" s="8" t="s">
-        <v>2191</v>
+        <v>2195</v>
       </c>
       <c r="E999" s="8" t="s">
-        <v>2192</v>
+        <v>2196</v>
       </c>
       <c r="F999" s="8" t="s">
-        <v>2193</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="1000" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1000" s="8" t="s">
-        <v>2194</v>
+        <v>2198</v>
       </c>
       <c r="B1000" s="8" t="s">
         <v>192</v>
       </c>
       <c r="C1000" s="8" t="str">
         <f t="shared" si="47"/>
-        <v>att_organism:UP000002311</v>
+        <v>att_organism:UP000002494</v>
       </c>
       <c r="D1000" s="8" t="s">
-        <v>2195</v>
+        <v>2199</v>
       </c>
       <c r="E1000" s="8" t="s">
-        <v>2196</v>
+        <v>2200</v>
       </c>
       <c r="F1000" s="8" t="s">
-        <v>2197</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="1001" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1001" s="8" t="s">
-        <v>2198</v>
+        <v>2202</v>
       </c>
       <c r="B1001" s="8" t="s">
         <v>192</v>
       </c>
       <c r="C1001" s="8" t="str">
         <f t="shared" si="47"/>
-        <v>att_organism:UP000002494</v>
+        <v>att_organism:UP000005640</v>
       </c>
       <c r="D1001" s="8" t="s">
-        <v>2199</v>
+        <v>2203</v>
       </c>
       <c r="E1001" s="8" t="s">
-        <v>2200</v>
+        <v>2204</v>
       </c>
       <c r="F1001" s="8" t="s">
-        <v>2201</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="1002" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A1002" s="8" t="s">
-        <v>2202</v>
+        <v>2907</v>
       </c>
       <c r="B1002" s="8" t="s">
         <v>192</v>
       </c>
       <c r="C1002" s="8" t="str">
         <f t="shared" si="47"/>
-        <v>att_organism:UP000005640</v>
+        <v>att_organism:controls</v>
       </c>
       <c r="D1002" s="8" t="s">
-        <v>2203</v>
+        <v>2904</v>
       </c>
       <c r="E1002" s="8" t="s">
-        <v>2204</v>
+        <v>2905</v>
       </c>
       <c r="F1002" s="8" t="s">
-        <v>2205</v>
-      </c>
-    </row>
-    <row r="1003" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A1003" s="8" t="s">
-        <v>2907</v>
-      </c>
-      <c r="B1003" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C1003" s="8" t="str">
-        <f t="shared" si="47"/>
-        <v>att_organism:controls</v>
-      </c>
-      <c r="D1003" s="8" t="s">
-        <v>2904</v>
-      </c>
-      <c r="E1003" s="8" t="s">
-        <v>2905</v>
-      </c>
-      <c r="F1003" s="8" t="s">
         <v>2906</v>
       </c>
     </row>
+    <row r="1003" spans="1:6" ht="16" x14ac:dyDescent="0.2">
+      <c r="B1003" s="24"/>
+    </row>
     <row r="1004" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1004" s="24"/>
+      <c r="B1004" s="25"/>
     </row>
     <row r="1005" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B1005" s="25"/>
@@ -43291,13 +43273,13 @@
       <c r="B1011" s="25"/>
     </row>
     <row r="1012" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1012" s="25"/>
+      <c r="B1012" s="24"/>
     </row>
     <row r="1013" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1013" s="24"/>
     </row>
     <row r="1014" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1014" s="24"/>
+      <c r="B1014" s="25"/>
     </row>
     <row r="1015" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1015" s="25"/>
@@ -43321,13 +43303,13 @@
       <c r="B1021" s="25"/>
     </row>
     <row r="1022" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1022" s="25"/>
+      <c r="B1022" s="24"/>
     </row>
     <row r="1023" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1023" s="24"/>
     </row>
     <row r="1024" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1024" s="24"/>
+      <c r="B1024" s="25"/>
     </row>
     <row r="1025" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1025" s="25"/>
@@ -43351,13 +43333,13 @@
       <c r="B1031" s="25"/>
     </row>
     <row r="1032" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1032" s="25"/>
+      <c r="B1032" s="24"/>
     </row>
     <row r="1033" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1033" s="24"/>
     </row>
     <row r="1034" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1034" s="24"/>
+      <c r="B1034" s="25"/>
     </row>
     <row r="1035" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1035" s="25"/>
@@ -43381,13 +43363,13 @@
       <c r="B1041" s="25"/>
     </row>
     <row r="1042" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1042" s="25"/>
+      <c r="B1042" s="24"/>
     </row>
     <row r="1043" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1043" s="24"/>
     </row>
     <row r="1044" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1044" s="24"/>
+      <c r="B1044" s="25"/>
     </row>
     <row r="1045" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1045" s="25"/>
@@ -43411,13 +43393,13 @@
       <c r="B1051" s="25"/>
     </row>
     <row r="1052" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1052" s="25"/>
+      <c r="B1052" s="24"/>
     </row>
     <row r="1053" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1053" s="24"/>
     </row>
     <row r="1054" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1054" s="24"/>
+      <c r="B1054" s="25"/>
     </row>
     <row r="1055" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1055" s="25"/>
@@ -43441,13 +43423,13 @@
       <c r="B1061" s="25"/>
     </row>
     <row r="1062" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1062" s="25"/>
+      <c r="B1062" s="24"/>
     </row>
     <row r="1063" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1063" s="24"/>
     </row>
     <row r="1064" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1064" s="24"/>
+      <c r="B1064" s="25"/>
     </row>
     <row r="1065" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1065" s="25"/>
@@ -43471,13 +43453,13 @@
       <c r="B1071" s="25"/>
     </row>
     <row r="1072" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1072" s="25"/>
+      <c r="B1072" s="24"/>
     </row>
     <row r="1073" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1073" s="24"/>
     </row>
     <row r="1074" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1074" s="24"/>
+      <c r="B1074" s="25"/>
     </row>
     <row r="1075" spans="2:2" ht="16" x14ac:dyDescent="0.2">
       <c r="B1075" s="25"/>
@@ -43501,43 +43483,10 @@
       <c r="B1081" s="25"/>
     </row>
     <row r="1082" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1082" s="25"/>
-    </row>
-    <row r="1083" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1083" s="24"/>
-    </row>
-    <row r="1084" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1084" s="24"/>
-    </row>
-    <row r="1085" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1085" s="25"/>
-    </row>
-    <row r="1086" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1086" s="25"/>
-    </row>
-    <row r="1087" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1087" s="25"/>
-    </row>
-    <row r="1088" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1088" s="25"/>
-    </row>
-    <row r="1089" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1089" s="25"/>
-    </row>
-    <row r="1090" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1090" s="25"/>
-    </row>
-    <row r="1091" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1091" s="25"/>
-    </row>
-    <row r="1092" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1092" s="25"/>
-    </row>
-    <row r="1093" spans="2:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1093" s="24"/>
+      <c r="B1082" s="24"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="E253 F345:F353 F9:F196 F198:F343">
+  <conditionalFormatting sqref="F9:F196 F198:F343 E253 F345:F353">
     <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10908"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{579A62BC-53DC-8648-A376-A383129074C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D154D36-7BF3-E644-B455-492CBE963BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8300" yWindow="4580" windowWidth="29540" windowHeight="20300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11085" uniqueCount="3245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11141" uniqueCount="3272">
   <si>
     <t>tag</t>
   </si>
@@ -9672,9 +9672,6 @@
     <t>voltage</t>
   </si>
   <si>
-    <t>weight</t>
-  </si>
-  <si>
     <t>volume</t>
   </si>
   <si>
@@ -9781,6 +9778,90 @@
   </si>
   <si>
     <t>Cell culture conditions</t>
+  </si>
+  <si>
+    <t>att_mice_group_age</t>
+  </si>
+  <si>
+    <t>Age Group [years]</t>
+  </si>
+  <si>
+    <t>sol_total</t>
+  </si>
+  <si>
+    <t>sol_pellet</t>
+  </si>
+  <si>
+    <t>sol_supernatant</t>
+  </si>
+  <si>
+    <t>embryo</t>
+  </si>
+  <si>
+    <t>young</t>
+  </si>
+  <si>
+    <t>adult</t>
+  </si>
+  <si>
+    <t>old</t>
+  </si>
+  <si>
+    <t>Embryonic mouse sample</t>
+  </si>
+  <si>
+    <t>Embryo</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Adult</t>
+  </si>
+  <si>
+    <t>Old</t>
+  </si>
+  <si>
+    <t>Young mouse (&lt;3 weeks)</t>
+  </si>
+  <si>
+    <t>Old mouse ( &gt; 16 month)</t>
+  </si>
+  <si>
+    <t>Adult mouse (&gt; 3 weeks &lt; 16 month)</t>
+  </si>
+  <si>
+    <t>att_qc_material</t>
+  </si>
+  <si>
+    <t>QC Material</t>
+  </si>
+  <si>
+    <t>mass</t>
+  </si>
+  <si>
+    <t>qc_hela</t>
+  </si>
+  <si>
+    <t>HeLa Digest</t>
+  </si>
+  <si>
+    <t>Pierce human HeLa digest</t>
+  </si>
+  <si>
+    <t>qc_base</t>
+  </si>
+  <si>
+    <t>BSA Digest</t>
+  </si>
+  <si>
+    <t>BSA digest</t>
+  </si>
+  <si>
+    <t>no_reduction</t>
+  </si>
+  <si>
+    <t>no_interface</t>
   </si>
 </sst>
 </file>
@@ -10394,7 +10475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH135"/>
+  <dimension ref="A1:AMH137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -10482,7 +10563,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
       <c r="D2">
         <v>500</v>
@@ -10597,7 +10678,7 @@
         <v>24</v>
       </c>
       <c r="D4">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>19</v>
@@ -10627,7 +10708,7 @@
         <v>19</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O4" s="1" t="s">
         <v>21</v>
@@ -10821,7 +10902,7 @@
         <v>39</v>
       </c>
       <c r="D8">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -11269,7 +11350,7 @@
         <v>57</v>
       </c>
       <c r="D16">
-        <v>500</v>
+        <v>690</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>19</v>
@@ -11605,7 +11686,7 @@
         <v>68</v>
       </c>
       <c r="D22">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>19</v>
@@ -12498,7 +12579,7 @@
         <v>27</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>3210</v>
+        <v>3209</v>
       </c>
       <c r="D38">
         <v>500</v>
@@ -12711,7 +12792,7 @@
         <v>1</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.15">
@@ -12890,7 +12971,7 @@
         <v>115</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
       <c r="D45">
         <v>500</v>
@@ -13730,7 +13811,7 @@
         <v>142</v>
       </c>
       <c r="C60" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
       <c r="D60">
         <v>500</v>
@@ -13775,7 +13856,7 @@
         <v>1</v>
       </c>
       <c r="R60" s="1" t="s">
-        <v>3211</v>
+        <v>3210</v>
       </c>
     </row>
     <row r="61" spans="1:18" x14ac:dyDescent="0.15">
@@ -13786,10 +13867,10 @@
         <v>142</v>
       </c>
       <c r="C61" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
       <c r="D61">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E61" s="1" t="s">
         <v>19</v>
@@ -14461,7 +14542,7 @@
         <v>158</v>
       </c>
       <c r="D73">
-        <v>610</v>
+        <v>720</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>19</v>
@@ -14547,7 +14628,7 @@
         <v>19</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O74" s="1" t="s">
         <v>21</v>
@@ -14629,7 +14710,7 @@
         <v>162</v>
       </c>
       <c r="D76">
-        <v>500</v>
+        <v>710</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>19</v>
@@ -15959,7 +16040,7 @@
         <v>1</v>
       </c>
       <c r="R99" s="1" t="s">
-        <v>3208</v>
+        <v>3263</v>
       </c>
     </row>
     <row r="100" spans="1:18" x14ac:dyDescent="0.15">
@@ -16524,13 +16605,13 @@
     </row>
     <row r="110" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B110" t="s">
+        <v>17</v>
+      </c>
+      <c r="C110" t="s">
         <v>3220</v>
-      </c>
-      <c r="B110" t="s">
-        <v>17</v>
-      </c>
-      <c r="C110" t="s">
-        <v>3221</v>
       </c>
       <c r="D110">
         <v>500</v>
@@ -17868,13 +17949,13 @@
     </row>
     <row r="134" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="B134" t="s">
         <v>17</v>
       </c>
       <c r="C134" t="s">
-        <v>3222</v>
+        <v>3221</v>
       </c>
       <c r="D134">
         <v>500</v>
@@ -17924,13 +18005,13 @@
     </row>
     <row r="135" spans="1:18" ht="16" x14ac:dyDescent="0.2">
       <c r="A135" s="25" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="B135" t="s">
         <v>17</v>
       </c>
       <c r="C135" t="s">
-        <v>3244</v>
+        <v>3243</v>
       </c>
       <c r="D135">
         <v>500</v>
@@ -17976,6 +18057,118 @@
       </c>
       <c r="R135" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="136" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A136" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B136" t="s">
+        <v>17</v>
+      </c>
+      <c r="C136" t="s">
+        <v>3245</v>
+      </c>
+      <c r="D136">
+        <v>500</v>
+      </c>
+      <c r="E136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G136" t="s">
+        <v>42</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J136" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K136" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N136" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O136" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P136" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q136" t="b">
+        <v>0</v>
+      </c>
+      <c r="R136" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="137" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A137" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B137" t="s">
+        <v>17</v>
+      </c>
+      <c r="C137" t="s">
+        <v>3262</v>
+      </c>
+      <c r="D137">
+        <v>600</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G137" t="s">
+        <v>42</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N137" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="O137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="P137" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q137" t="b">
+        <v>1</v>
+      </c>
+      <c r="R137" s="1" t="s">
+        <v>3263</v>
       </c>
     </row>
   </sheetData>
@@ -17994,7 +18187,7 @@
       <formula>NOT(ISERROR(SEARCH("TRUE",M129)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R135 J127:P128">
+  <conditionalFormatting sqref="J127:P128 R2:R137">
     <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J2)))</formula>
     </cfRule>
@@ -24739,7 +24932,7 @@
         <v>30</v>
       </c>
       <c r="F320" s="8" t="s">
-        <v>3219</v>
+        <v>3218</v>
       </c>
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.15">
@@ -25773,7 +25966,7 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A370" s="8" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="B370" s="8" t="s">
         <v>111</v>
@@ -25783,13 +25976,13 @@
         <v>proximity</v>
       </c>
       <c r="D370" s="8" t="s">
+        <v>3214</v>
+      </c>
+      <c r="E370" s="8" t="s">
         <v>3215</v>
       </c>
-      <c r="E370" s="8" t="s">
+      <c r="F370" s="8" t="s">
         <v>3216</v>
-      </c>
-      <c r="F370" s="8" t="s">
-        <v>3217</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.15">
@@ -32810,14 +33003,14 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A657" s="8" t="s">
-        <v>336</v>
+        <v>3271</v>
       </c>
       <c r="B657" s="8" t="s">
         <v>115</v>
       </c>
       <c r="C657" s="8" t="str">
         <f t="shared" si="10"/>
-        <v>none</v>
+        <v>no_interface</v>
       </c>
       <c r="D657" s="9" t="s">
         <v>17</v>
@@ -39743,14 +39936,14 @@
     </row>
     <row r="842" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A842" s="8" t="s">
-        <v>336</v>
+        <v>3270</v>
       </c>
       <c r="B842" s="8" t="s">
         <v>210</v>
       </c>
       <c r="C842" s="8" t="str">
         <f t="shared" si="13"/>
-        <v>none</v>
+        <v>no_reduction</v>
       </c>
       <c r="D842" s="9" t="s">
         <v>17</v>
@@ -42197,7 +42390,7 @@
     </row>
     <row r="959" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A959" s="8" t="s">
-        <v>3235</v>
+        <v>3234</v>
       </c>
       <c r="B959" s="8" t="s">
         <v>69</v>
@@ -42210,10 +42403,10 @@
         <v>17</v>
       </c>
       <c r="E959" s="8" t="s">
+        <v>3232</v>
+      </c>
+      <c r="F959" s="8" t="s">
         <v>3233</v>
-      </c>
-      <c r="F959" s="8" t="s">
-        <v>3234</v>
       </c>
     </row>
     <row r="960" spans="1:6" x14ac:dyDescent="0.15">
@@ -42287,7 +42480,7 @@
         <v>40</v>
       </c>
       <c r="C963" s="8" t="str">
-        <f t="shared" ref="C963:C994" si="15">A963</f>
+        <f t="shared" ref="C963:C1000" si="15">A963</f>
         <v>attregs</v>
       </c>
       <c r="D963" s="8" t="s">
@@ -42722,14 +42915,14 @@
     </row>
     <row r="984" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A984" s="8" t="s">
-        <v>3167</v>
+        <v>3247</v>
       </c>
       <c r="B984" s="8" t="s">
         <v>3173</v>
       </c>
       <c r="C984" s="8" t="str">
         <f t="shared" si="15"/>
-        <v>pellet</v>
+        <v>sol_pellet</v>
       </c>
       <c r="D984" s="8" t="s">
         <v>17</v>
@@ -42743,14 +42936,14 @@
     </row>
     <row r="985" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A985" s="8" t="s">
-        <v>1243</v>
+        <v>3246</v>
       </c>
       <c r="B985" s="8" t="s">
         <v>3173</v>
       </c>
       <c r="C985" s="8" t="str">
         <f t="shared" si="15"/>
-        <v>total</v>
+        <v>sol_total</v>
       </c>
       <c r="D985" s="8" t="s">
         <v>17</v>
@@ -42764,14 +42957,14 @@
     </row>
     <row r="986" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A986" s="8" t="s">
-        <v>2994</v>
+        <v>3248</v>
       </c>
       <c r="B986" s="8" t="s">
         <v>3173</v>
       </c>
       <c r="C986" s="8" t="str">
         <f t="shared" si="15"/>
-        <v>supernatant</v>
+        <v>sol_supernatant</v>
       </c>
       <c r="D986" s="8" t="s">
         <v>17</v>
@@ -42848,10 +43041,10 @@
     </row>
     <row r="990" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A990" s="8" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
       <c r="B990" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C990" s="8" t="str">
         <f t="shared" si="15"/>
@@ -42861,18 +43054,18 @@
         <v>17</v>
       </c>
       <c r="E990" s="8" t="s">
+        <v>3224</v>
+      </c>
+      <c r="F990" t="s">
         <v>3225</v>
-      </c>
-      <c r="F990" t="s">
-        <v>3226</v>
       </c>
     </row>
     <row r="991" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A991" s="8" t="s">
-        <v>3230</v>
+        <v>3229</v>
       </c>
       <c r="B991" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C991" s="8" t="str">
         <f t="shared" si="15"/>
@@ -42882,18 +43075,18 @@
         <v>17</v>
       </c>
       <c r="E991" s="8" t="s">
-        <v>3227</v>
+        <v>3226</v>
       </c>
       <c r="F991" s="8" t="s">
-        <v>3232</v>
+        <v>3231</v>
       </c>
     </row>
     <row r="992" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A992" s="8" t="s">
-        <v>3229</v>
+        <v>3228</v>
       </c>
       <c r="B992" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
       <c r="C992" s="8" t="str">
         <f t="shared" si="15"/>
@@ -42903,18 +43096,18 @@
         <v>17</v>
       </c>
       <c r="E992" s="8" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="F992" s="8" t="s">
-        <v>3231</v>
+        <v>3230</v>
       </c>
     </row>
     <row r="993" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A993" s="8" t="s">
-        <v>3237</v>
+        <v>3236</v>
       </c>
       <c r="B993" s="25" t="s">
-        <v>3239</v>
+        <v>3238</v>
       </c>
       <c r="C993" s="8" t="str">
         <f t="shared" si="15"/>
@@ -42924,18 +43117,18 @@
         <v>17</v>
       </c>
       <c r="E993" s="8" t="s">
-        <v>3240</v>
+        <v>3239</v>
       </c>
       <c r="F993" s="27" t="s">
-        <v>3243</v>
+        <v>3242</v>
       </c>
     </row>
     <row r="994" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A994" s="8" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B994" s="25" t="s">
         <v>3238</v>
-      </c>
-      <c r="B994" s="25" t="s">
-        <v>3239</v>
       </c>
       <c r="C994" s="8" t="str">
         <f t="shared" si="15"/>
@@ -42945,29 +43138,137 @@
         <v>17</v>
       </c>
       <c r="E994" s="8" t="s">
+        <v>3240</v>
+      </c>
+      <c r="F994" s="8" t="s">
         <v>3241</v>
       </c>
-      <c r="F994" s="8" t="s">
-        <v>3242</v>
-      </c>
-    </row>
-    <row r="995" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B995" s="25"/>
-    </row>
-    <row r="996" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B996" s="25"/>
-    </row>
-    <row r="997" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B997" s="25"/>
-    </row>
-    <row r="998" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B998" s="25"/>
-    </row>
-    <row r="999" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B999" s="25"/>
-    </row>
-    <row r="1000" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="B1000" s="24"/>
+    </row>
+    <row r="995" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A995" s="8" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B995" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C995" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>embryo</v>
+      </c>
+      <c r="D995" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E995" s="8" t="s">
+        <v>3254</v>
+      </c>
+      <c r="F995" s="8" t="s">
+        <v>3253</v>
+      </c>
+    </row>
+    <row r="996" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A996" s="8" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B996" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C996" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>young</v>
+      </c>
+      <c r="D996" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E996" s="8" t="s">
+        <v>3255</v>
+      </c>
+      <c r="F996" s="8" t="s">
+        <v>3258</v>
+      </c>
+    </row>
+    <row r="997" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A997" s="8" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B997" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C997" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>adult</v>
+      </c>
+      <c r="D997" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E997" s="8" t="s">
+        <v>3256</v>
+      </c>
+      <c r="F997" s="8" t="s">
+        <v>3260</v>
+      </c>
+    </row>
+    <row r="998" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A998" s="8" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B998" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C998" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>old</v>
+      </c>
+      <c r="D998" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E998" s="8" t="s">
+        <v>3257</v>
+      </c>
+      <c r="F998" s="8" t="s">
+        <v>3259</v>
+      </c>
+    </row>
+    <row r="999" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A999" s="8" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B999" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C999" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>qc_hela</v>
+      </c>
+      <c r="D999" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E999" s="8" t="s">
+        <v>3265</v>
+      </c>
+      <c r="F999" s="8" t="s">
+        <v>3266</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A1000" s="8" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B1000" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C1000" s="8" t="str">
+        <f t="shared" si="15"/>
+        <v>qc_base</v>
+      </c>
+      <c r="D1000" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1000" s="8" t="s">
+        <v>3268</v>
+      </c>
+      <c r="F1000" s="8" t="s">
+        <v>3269</v>
+      </c>
     </row>
     <row r="1001" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="B1001" s="24"/>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C73029A-C218-104A-A9F4-7268D847F023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B475B5-C0CC-174C-BEBC-789FC6576D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10267" uniqueCount="2930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10304" uniqueCount="2947">
   <si>
     <t>tag</t>
   </si>
@@ -8832,6 +8832,57 @@
   </si>
   <si>
     <t>controls</t>
+  </si>
+  <si>
+    <t>att_pisa_cond</t>
+  </si>
+  <si>
+    <t>Proteome Integral Solubility Alteration Chemicals</t>
+  </si>
+  <si>
+    <t>vehicle</t>
+  </si>
+  <si>
+    <t>fumarate-1</t>
+  </si>
+  <si>
+    <t>Fumarte 1mM</t>
+  </si>
+  <si>
+    <t>fumarate-10</t>
+  </si>
+  <si>
+    <t>Fumarate 10 mM</t>
+  </si>
+  <si>
+    <t>dmf</t>
+  </si>
+  <si>
+    <t>Dimethylfumarate</t>
+  </si>
+  <si>
+    <t>fumarate-25</t>
+  </si>
+  <si>
+    <t>Fumarate 25 mM</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Control vehicle in a PISA study</t>
+  </si>
+  <si>
+    <t>Fumarate used at a concentration of 1 mM</t>
+  </si>
+  <si>
+    <t>Fumarate used at a concentration of 10 mM (similiar to FH KO accumulation in the cell)</t>
+  </si>
+  <si>
+    <t>Dimethylfumarate is a very active compound and leads to succination of cystein residues.</t>
+  </si>
+  <si>
+    <t>Fumarate used at a concentration of 25 mM.</t>
   </si>
 </sst>
 </file>
@@ -8997,9 +9048,11 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <font>
-        <color rgb="FFCC0000"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC5E0B4"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -9420,7 +9473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH115"/>
+  <dimension ref="A1:AMH116"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -15194,20 +15247,75 @@
         <v>19</v>
       </c>
     </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.15">
+      <c r="A116" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B116" t="s">
+        <v>17</v>
+      </c>
+      <c r="C116" t="s">
+        <v>2931</v>
+      </c>
+      <c r="D116">
+        <v>600</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G116" t="s">
+        <v>20</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J116" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K116" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P116" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E1:F112 K1:P112 I2:J112">
-    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J113:P114">
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J113)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M115:P115">
-    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",M115)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E116:F116 I116:P116">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TRUE">
+      <formula>NOT(ISERROR(SEARCH("TRUE",E116)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15217,7 +15325,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ913"/>
+  <dimension ref="A1:AMJ918"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -33742,7 +33850,7 @@
         <v>248</v>
       </c>
       <c r="C882" s="8" t="str">
-        <f t="shared" ref="C882:C913" si="19">B882&amp;":"&amp;A882</f>
+        <f t="shared" ref="C882:C917" si="19">B882&amp;":"&amp;A882</f>
         <v>att_user_institute:mpiage</v>
       </c>
       <c r="D882" s="9" t="s">
@@ -34403,19 +34511,119 @@
         <v>2834</v>
       </c>
     </row>
+    <row r="914" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A914" s="8" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B914" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C914" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_pisa_cond:vehicle</v>
+      </c>
+      <c r="D914" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E914" s="8" t="s">
+        <v>2941</v>
+      </c>
+      <c r="F914" s="8" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="915" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A915" s="8" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B915" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C915" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_pisa_cond:fumarate-1</v>
+      </c>
+      <c r="D915" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E915" s="8" t="s">
+        <v>2934</v>
+      </c>
+      <c r="F915" s="8" t="s">
+        <v>2943</v>
+      </c>
+    </row>
+    <row r="916" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A916" s="8" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B916" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C916" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_pisa_cond:fumarate-10</v>
+      </c>
+      <c r="D916" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E916" s="8" t="s">
+        <v>2936</v>
+      </c>
+      <c r="F916" s="8" t="s">
+        <v>2944</v>
+      </c>
+    </row>
+    <row r="917" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A917" s="8" t="s">
+        <v>2937</v>
+      </c>
+      <c r="B917" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C917" s="8" t="str">
+        <f t="shared" si="19"/>
+        <v>att_pisa_cond:dmf</v>
+      </c>
+      <c r="D917" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E917" s="8" t="s">
+        <v>2938</v>
+      </c>
+      <c r="F917" s="8" t="s">
+        <v>2945</v>
+      </c>
+    </row>
+    <row r="918" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="A918" s="8" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B918" s="8" t="s">
+        <v>2930</v>
+      </c>
+      <c r="C918" s="8" t="str">
+        <f t="shared" ref="C918" si="20">B918&amp;":"&amp;A918</f>
+        <v>att_pisa_cond:fumarate-25</v>
+      </c>
+      <c r="D918" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="E918" s="8" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F918" s="8" t="s">
+        <v>2946</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="F331:F339 E240 F9:F329">
+  <conditionalFormatting sqref="F9:F329 E240 F331:F339">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F369">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F158">
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56695,13 +56903,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O365" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <conditionalFormatting sqref="C323:C335 I320 I175:I177 C365 C2:C321">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+  <conditionalFormatting sqref="C2:C321 I175:I177 I320 C323:C335 C365">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C439">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/resources/attributes/attributes.xlsx
+++ b/resources/attributes/attributes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hnolte/Documents/GitHub/mitocube-backend/resources/attributes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76B475B5-C0CC-174C-BEBC-789FC6576D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C73029A-C218-104A-A9F4-7268D847F023}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8460" yWindow="660" windowWidth="29560" windowHeight="19560" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="attributes" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10304" uniqueCount="2947">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10267" uniqueCount="2930">
   <si>
     <t>tag</t>
   </si>
@@ -8832,57 +8832,6 @@
   </si>
   <si>
     <t>controls</t>
-  </si>
-  <si>
-    <t>att_pisa_cond</t>
-  </si>
-  <si>
-    <t>Proteome Integral Solubility Alteration Chemicals</t>
-  </si>
-  <si>
-    <t>vehicle</t>
-  </si>
-  <si>
-    <t>fumarate-1</t>
-  </si>
-  <si>
-    <t>Fumarte 1mM</t>
-  </si>
-  <si>
-    <t>fumarate-10</t>
-  </si>
-  <si>
-    <t>Fumarate 10 mM</t>
-  </si>
-  <si>
-    <t>dmf</t>
-  </si>
-  <si>
-    <t>Dimethylfumarate</t>
-  </si>
-  <si>
-    <t>fumarate-25</t>
-  </si>
-  <si>
-    <t>Fumarate 25 mM</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Control vehicle in a PISA study</t>
-  </si>
-  <si>
-    <t>Fumarate used at a concentration of 1 mM</t>
-  </si>
-  <si>
-    <t>Fumarate used at a concentration of 10 mM (similiar to FH KO accumulation in the cell)</t>
-  </si>
-  <si>
-    <t>Dimethylfumarate is a very active compound and leads to succination of cystein residues.</t>
-  </si>
-  <si>
-    <t>Fumarate used at a concentration of 25 mM.</t>
   </si>
 </sst>
 </file>
@@ -9048,11 +8997,9 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC5E0B4"/>
-        </patternFill>
-      </fill>
+      <font>
+        <color rgb="FFCC0000"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -9473,7 +9420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AMH116"/>
+  <dimension ref="A1:AMH115"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
@@ -15247,75 +15194,20 @@
         <v>19</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.15">
-      <c r="A116" t="s">
-        <v>2930</v>
-      </c>
-      <c r="B116" t="s">
-        <v>17</v>
-      </c>
-      <c r="C116" t="s">
-        <v>2931</v>
-      </c>
-      <c r="D116">
-        <v>600</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G116" t="s">
-        <v>20</v>
-      </c>
-      <c r="H116">
-        <v>0</v>
-      </c>
-      <c r="I116" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="J116" s="7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N116" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O116" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="P116" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="E1:F112 K1:P112 I2:J112">
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="7" priority="5" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",E1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J113:P114">
-    <cfRule type="containsText" dxfId="6" priority="3" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",J113)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M115:P115">
-    <cfRule type="containsText" dxfId="5" priority="2" operator="containsText" text="TRUE">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="TRUE">
       <formula>NOT(ISERROR(SEARCH("TRUE",M115)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E116:F116 I116:P116">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="TRUE">
-      <formula>NOT(ISERROR(SEARCH("TRUE",E116)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -15325,7 +15217,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AMJ918"/>
+  <dimension ref="A1:AMJ913"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="19.1640625" style="8" customWidth="1"/>
@@ -33850,7 +33742,7 @@
         <v>248</v>
       </c>
       <c r="C882" s="8" t="str">
-        <f t="shared" ref="C882:C917" si="19">B882&amp;":"&amp;A882</f>
+        <f t="shared" ref="C882:C913" si="19">B882&amp;":"&amp;A882</f>
         <v>att_user_institute:mpiage</v>
       </c>
       <c r="D882" s="9" t="s">
@@ -34511,119 +34403,19 @@
         <v>2834</v>
       </c>
     </row>
-    <row r="914" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A914" s="8" t="s">
-        <v>2932</v>
-      </c>
-      <c r="B914" s="8" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C914" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_pisa_cond:vehicle</v>
-      </c>
-      <c r="D914" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E914" s="8" t="s">
-        <v>2941</v>
-      </c>
-      <c r="F914" s="8" t="s">
-        <v>2942</v>
-      </c>
-    </row>
-    <row r="915" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A915" s="8" t="s">
-        <v>2933</v>
-      </c>
-      <c r="B915" s="8" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C915" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_pisa_cond:fumarate-1</v>
-      </c>
-      <c r="D915" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E915" s="8" t="s">
-        <v>2934</v>
-      </c>
-      <c r="F915" s="8" t="s">
-        <v>2943</v>
-      </c>
-    </row>
-    <row r="916" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A916" s="8" t="s">
-        <v>2935</v>
-      </c>
-      <c r="B916" s="8" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C916" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_pisa_cond:fumarate-10</v>
-      </c>
-      <c r="D916" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E916" s="8" t="s">
-        <v>2936</v>
-      </c>
-      <c r="F916" s="8" t="s">
-        <v>2944</v>
-      </c>
-    </row>
-    <row r="917" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A917" s="8" t="s">
-        <v>2937</v>
-      </c>
-      <c r="B917" s="8" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C917" s="8" t="str">
-        <f t="shared" si="19"/>
-        <v>att_pisa_cond:dmf</v>
-      </c>
-      <c r="D917" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E917" s="8" t="s">
-        <v>2938</v>
-      </c>
-      <c r="F917" s="8" t="s">
-        <v>2945</v>
-      </c>
-    </row>
-    <row r="918" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A918" s="8" t="s">
-        <v>2939</v>
-      </c>
-      <c r="B918" s="8" t="s">
-        <v>2930</v>
-      </c>
-      <c r="C918" s="8" t="str">
-        <f t="shared" ref="C918" si="20">B918&amp;":"&amp;A918</f>
-        <v>att_pisa_cond:fumarate-25</v>
-      </c>
-      <c r="D918" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="E918" s="8" t="s">
-        <v>2940</v>
-      </c>
-      <c r="F918" s="8" t="s">
-        <v>2946</v>
-      </c>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="F9:F329 E240 F331:F339">
+  <conditionalFormatting sqref="F331:F339 E240 F9:F329">
     <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F369">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+      <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F158">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -56903,13 +56695,13 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:O365" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <conditionalFormatting sqref="C2:C321 I175:I177 I320 C323:C335 C365">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="C323:C335 I320 I175:I177 C365 C2:C321">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C439">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>INDIRECT(ADDRESS(ROW()-1,COLUMN()))</formula>
     </cfRule>
   </conditionalFormatting>
